--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -1792,9 +1792,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Ssancar LTD 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea   Phone: +82-505-366-9977</t>
-    </r>
+    <t>Heyman LTD 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea   Phone: +82-505-366-9977</t>
   </si>
   <si>
     <r>
@@ -1852,9 +1850,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">SSANCAR CO LTD</t>
-    </r>
+    <t>HEYMAN CO LTD</t>
   </si>
   <si>
     <r>
@@ -1892,9 +1888,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">180-008-400167</t>
-    </r>
+    <t>180-012-458342</t>
   </si>
   <si>
     <r>
@@ -13303,12 +13297,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" customHeight="1" ht="11.25" s="246" customFormat="1">
-      <c r="A2" s="244" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Ssancar LTD 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea   Phone: +82-505-366-9977</t>
-          </r>
-        </is>
+      <c r="A2" s="244" t="s">
+        <v>348</v>
       </c>
       <c r="D2" s="244"/>
     </row>
@@ -13495,12 +13485,8 @@
         </is>
       </c>
       <c r="B16" s="388"/>
-      <c r="C16" s="389" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">SSANCAR CO LTD</t>
-          </r>
-        </is>
+      <c r="C16" s="389" t="s">
+        <v>360</v>
       </c>
       <c r="D16" s="388"/>
       <c r="E16" s="240" t="inlineStr">
@@ -13561,12 +13547,8 @@
         </is>
       </c>
       <c r="B18" s="388"/>
-      <c r="C18" s="389" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">180-008-400167</t>
-          </r>
-        </is>
+      <c r="C18" s="389" t="s">
+        <v>368</v>
       </c>
       <c r="D18" s="388"/>
       <c r="E18" s="240" t="inlineStr">

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
+    <workbookView activeTab="3" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="구매리스트" sheetId="1" r:id="rId4"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="380">
   <si>
     <r>
       <t xml:space="preserve">말소증</t>
@@ -553,6 +553,9 @@
     </r>
   </si>
   <si>
+    <t>대　한　민　국</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">1.제  원 </t>
     </r>
@@ -975,6 +978,9 @@
     <r>
       <t xml:space="preserve">※ Note: In the case of an electric vehicle or hydrogen fuel cell vehicle, the 'prime motor type' in column ⑦ refers to the 'drive motor type</t>
     </r>
+  </si>
+  <si>
+    <t>Republic of Korea</t>
   </si>
   <si>
     <r>
@@ -1958,7 +1964,7 @@
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="74">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -2368,15 +2374,6 @@
       <name val="Malgun Gothic"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="22"/>
-      <color rgb="FF000000"/>
-      <name val="HY견명조"/>
-    </font>
-    <font>
       <b val="0"/>
       <i val="0"/>
       <strike val="0"/>
@@ -2623,6 +2620,34 @@
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Impact"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="HY견명조"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="HY견명조"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -3494,7 +3519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="397">
+  <cellXfs count="399">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -3963,16 +3988,13 @@
     <xf xfId="0" fontId="4" numFmtId="170" fillId="11" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="4"/>
     </xf>
-    <xf xfId="0" fontId="44" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="3" numFmtId="0" fillId="11" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="45" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="44" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -3987,10 +4009,10 @@
     <xf xfId="0" fontId="41" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="45" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="47" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -3999,7 +4021,7 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="47" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="4" numFmtId="165" fillId="11" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
@@ -4008,16 +4030,16 @@
     <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="16" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="47" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="45" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="44" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="47" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4086,7 +4108,7 @@
     <xf xfId="0" fontId="35" numFmtId="0" fillId="0" borderId="34" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="48" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="47" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="38" numFmtId="0" fillId="7" borderId="17" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4098,7 +4120,7 @@
     <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="26" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="49" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="48" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="25" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4107,7 +4129,7 @@
     <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="21" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false" indent="1"/>
     </xf>
-    <xf xfId="0" fontId="50" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="49" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="17" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4155,7 +4177,7 @@
     <xf xfId="0" fontId="37" numFmtId="171" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
     </xf>
-    <xf xfId="0" fontId="51" numFmtId="0" fillId="7" borderId="17" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="50" numFmtId="0" fillId="7" borderId="17" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="35" numFmtId="0" fillId="0" borderId="16" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4176,7 +4198,7 @@
     <xf xfId="0" fontId="12" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="52" numFmtId="168" fillId="11" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="51" numFmtId="168" fillId="11" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="14" numFmtId="167" fillId="0" borderId="42" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4203,10 +4225,10 @@
     <xf xfId="0" fontId="12" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="53" numFmtId="0" fillId="0" borderId="43" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="52" numFmtId="0" fillId="0" borderId="43" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="53" numFmtId="3" fillId="0" borderId="42" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="52" numFmtId="3" fillId="0" borderId="42" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
     </xf>
     <xf xfId="0" fontId="18" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -4221,13 +4243,13 @@
     <xf xfId="0" fontId="19" numFmtId="0" fillId="0" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="54" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="53" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="55" numFmtId="0" fillId="12" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="54" numFmtId="0" fillId="12" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="56" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="55" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="18" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -4245,298 +4267,298 @@
     <xf xfId="0" fontId="39" numFmtId="172" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="56" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="16" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="24" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="4" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="5" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="9" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="49" fillId="11" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="3"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="170" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="170" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="5"/>
+    </xf>
+    <xf xfId="0" fontId="38" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="11" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="29" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="49" fillId="11" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="3" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="49" fillId="11" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="45" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+    </xf>
     <xf xfId="0" fontId="57" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="58" numFmtId="173" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="59" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="60" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="15" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="60" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+    </xf>
+    <xf xfId="0" fontId="61" numFmtId="170" fillId="7" borderId="17" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="45" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="36" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="37" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="21" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="34" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="47" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="31" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="34" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="47" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="31" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="30" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="20" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="50" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="36" numFmtId="14" fillId="11" borderId="51" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="36" numFmtId="0" fillId="0" borderId="51" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="52" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="38" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="53" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="16" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="24" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="54" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="4" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="40" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="5" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="9" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="49" fillId="11" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="3"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="170" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="170" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="5"/>
-    </xf>
-    <xf xfId="0" fontId="38" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="11" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="29" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="49" fillId="11" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="3" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="49" fillId="11" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="46" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="58" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="59" numFmtId="173" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="60" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="61" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="15" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="27" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="61" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="47" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="26" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="62" numFmtId="170" fillId="7" borderId="17" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="45" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="36" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="21" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="37" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="21" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="35" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="34" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="47" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="32" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="31" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="34" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="47" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="31" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="55" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="30" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="20" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="50" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="36" numFmtId="14" fillId="11" borderId="51" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="36" numFmtId="0" fillId="0" borderId="51" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="52" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="38" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="53" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="16" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="54" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="40" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="21" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="37" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="35" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="32" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="55" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="30" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="63" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="62" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="12" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="64" numFmtId="165" fillId="0" borderId="8" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="63" numFmtId="165" fillId="0" borderId="8" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="6" numFmtId="49" fillId="0" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false" indent="1"/>
     </xf>
-    <xf xfId="0" fontId="65" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="64" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="14" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4545,7 +4567,7 @@
     <xf xfId="0" fontId="14" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="53" numFmtId="49" fillId="11" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="52" numFmtId="49" fillId="11" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false" indent="1"/>
     </xf>
     <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4554,10 +4576,10 @@
     <xf xfId="0" fontId="14" numFmtId="0" fillId="11" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="66" numFmtId="49" fillId="0" borderId="44" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="65" numFmtId="49" fillId="0" borderId="44" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="67" numFmtId="0" fillId="11" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="66" numFmtId="0" fillId="11" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="14" numFmtId="165" fillId="0" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4614,7 +4636,7 @@
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="42" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="53" numFmtId="168" fillId="11" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="52" numFmtId="168" fillId="11" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false" indent="1"/>
     </xf>
     <xf xfId="0" fontId="11" numFmtId="167" fillId="0" borderId="15" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4635,15 +4657,15 @@
     <xf xfId="0" fontId="20" numFmtId="168" fillId="11" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="67" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="68" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="69" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="70" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="20" numFmtId="167" fillId="11" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4653,7 +4675,7 @@
     <xf xfId="0" fontId="18" numFmtId="179" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="71" numFmtId="0" fillId="4" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="70" numFmtId="0" fillId="4" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="63" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4685,6 +4707,15 @@
     </xf>
     <xf xfId="0" fontId="20" numFmtId="167" fillId="6" borderId="64" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="71" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="72" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="73" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5561,22 +5592,22 @@
   <dimension ref="A1:L65"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.375" customWidth="true" style="246"/>
-    <col min="2" max="2" width="22.25" customWidth="true" style="246"/>
-    <col min="3" max="3" width="10.5" customWidth="true" style="246"/>
-    <col min="4" max="4" width="21.125" customWidth="true" style="246"/>
-    <col min="5" max="5" width="3.125" customWidth="true" style="246"/>
-    <col min="6" max="6" width="11" customWidth="true" style="246"/>
-    <col min="7" max="7" width="20.125" customWidth="true" style="246"/>
-    <col min="8" max="8" width="9.25" customWidth="true" style="246"/>
-    <col min="9" max="9" width="21.75" customWidth="true" style="246"/>
-    <col min="10" max="10" width="20.5" customWidth="true" style="246"/>
-    <col min="11" max="11" width="10.375" customWidth="true" style="246"/>
-    <col min="12" max="12" width="11.75" customWidth="true" style="246"/>
+    <col min="1" max="1" width="10.375" customWidth="true" style="245"/>
+    <col min="2" max="2" width="22.25" customWidth="true" style="245"/>
+    <col min="3" max="3" width="10.5" customWidth="true" style="245"/>
+    <col min="4" max="4" width="21.125" customWidth="true" style="245"/>
+    <col min="5" max="5" width="3.125" customWidth="true" style="245"/>
+    <col min="6" max="6" width="11" customWidth="true" style="245"/>
+    <col min="7" max="7" width="20.125" customWidth="true" style="245"/>
+    <col min="8" max="8" width="9.25" customWidth="true" style="245"/>
+    <col min="9" max="9" width="21.75" customWidth="true" style="245"/>
+    <col min="10" max="10" width="20.5" customWidth="true" style="245"/>
+    <col min="11" max="11" width="10.375" customWidth="true" style="245"/>
+    <col min="12" max="12" width="11.75" customWidth="true" style="245"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" customHeight="1" ht="26.25" s="246" customFormat="1"/>
-    <row r="2" spans="1:12" customHeight="1" ht="25.5" s="246" customFormat="1">
+    <row r="1" spans="1:12" customHeight="1" ht="26.25" s="245" customFormat="1"/>
+    <row r="2" spans="1:12" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A2" s="105" t="inlineStr">
         <is>
           <r>
@@ -5592,7 +5623,7 @@
         </is>
       </c>
     </row>
-    <row r="3" spans="1:12" customHeight="1" ht="25.5" s="246" customFormat="1">
+    <row r="3" spans="1:12" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A3" s="103" t="inlineStr">
         <is>
           <r>
@@ -5634,7 +5665,7 @@
         <v>45875</v>
       </c>
     </row>
-    <row r="4" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="4" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A4" s="103" t="inlineStr">
         <is>
           <r>
@@ -5693,7 +5724,7 @@
         </is>
       </c>
     </row>
-    <row r="5" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="5" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A5" s="103" t="inlineStr">
         <is>
           <r>
@@ -5752,7 +5783,7 @@
         </is>
       </c>
     </row>
-    <row r="6" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="6" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A6" s="103" t="inlineStr">
         <is>
           <r>
@@ -5800,7 +5831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="7" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A7" s="103" t="inlineStr">
         <is>
           <r>
@@ -5843,7 +5874,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="8" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="8" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A8" s="103" t="inlineStr">
         <is>
           <r>
@@ -5886,7 +5917,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="9" spans="1:12" customHeight="1" ht="22.5" s="246" customFormat="1">
+    <row r="9" spans="1:12" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A9" s="105" t="inlineStr">
         <is>
           <r>
@@ -5927,7 +5958,7 @@
         </is>
       </c>
     </row>
-    <row r="10" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="10" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A10" s="103" t="inlineStr">
         <is>
           <r>
@@ -5982,7 +6013,7 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="11" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="11" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A11" s="103" t="inlineStr">
         <is>
           <r>
@@ -6037,7 +6068,7 @@
         <v>46504</v>
       </c>
     </row>
-    <row r="12" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="12" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A12" s="103" t="inlineStr">
         <is>
           <r>
@@ -6092,7 +6123,7 @@
         <v>163268</v>
       </c>
     </row>
-    <row r="13" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="13" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A13" s="105" t="inlineStr">
         <is>
           <r>
@@ -6118,13 +6149,13 @@
           </r>
         </is>
       </c>
-      <c r="H13" s="247"/>
+      <c r="H13" s="246"/>
       <c r="I13" s="113" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G13,"휘발유","GASOLINE"),"경유","DIESEL"),"LPG","LPG"),"하이브리드","HYBRID")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" customHeight="1" ht="120.75" s="246" customFormat="1">
+    <row r="14" spans="1:12" customHeight="1" ht="120.75" s="245" customFormat="1">
       <c r="A14" s="103" t="inlineStr">
         <is>
           <r>
@@ -6159,7 +6190,7 @@
       <c r="F14" s="100"/>
       <c r="G14" s="100"/>
     </row>
-    <row r="15" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
+    <row r="15" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A15" s="103" t="inlineStr">
         <is>
           <r>
@@ -6167,7 +6198,7 @@
           </r>
         </is>
       </c>
-      <c r="B15" s="248">
+      <c r="B15" s="247">
         <v>14730</v>
       </c>
       <c r="C15" s="103" t="inlineStr">
@@ -6177,25 +6208,25 @@
           </r>
         </is>
       </c>
-      <c r="D15" s="248">
+      <c r="D15" s="247">
         <v>1670</v>
       </c>
       <c r="E15" s="100"/>
       <c r="F15" s="100"/>
-      <c r="G15" s="249" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="I15" s="246" t="str">
+      <c r="G15" s="248" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="I15" s="245" t="str">
         <f t="array" ref="I15" aca="1" ca="1">_xlfn.TEXTJOIN(",",,
  _xlfn.UNIQUE(_xlfn.IFNA(INDEX({"GASOLIN","DIESEL","LPG"},
  MATCH(G15,{"휘발유","경유","LPG"},0)),""),1))</f>
       </c>
     </row>
-    <row r="16" spans="1:12" customHeight="1" ht="25.5" s="246" customFormat="1">
+    <row r="16" spans="1:12" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A16" s="100"/>
       <c r="B16" s="100"/>
       <c r="C16" s="103" t="inlineStr">
@@ -6212,7 +6243,7 @@
       <c r="E16" s="100"/>
       <c r="F16" s="100"/>
       <c r="G16" s="100"/>
-      <c r="I16" s="246" t="inlineStr">
+      <c r="I16" s="245" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -6580,22 +6611,22 @@
   <dimension ref="A1:T47"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="3.25" customWidth="true" style="246"/>
-    <col min="2" max="2" width="3.5" customWidth="true" style="246"/>
-    <col min="3" max="3" width="11.125" customWidth="true" style="246"/>
-    <col min="4" max="4" width="4.125" customWidth="true" style="246"/>
-    <col min="5" max="5" width="4.125" customWidth="true" style="246"/>
-    <col min="6" max="6" width="4.75" customWidth="true" style="246"/>
-    <col min="7" max="7" width="3.25" customWidth="true" style="246"/>
-    <col min="8" max="8" width="11.625" customWidth="true" style="246"/>
-    <col min="9" max="9" width="8.25" customWidth="true" style="246"/>
-    <col min="10" max="10" width="4.875" customWidth="true" style="246"/>
-    <col min="11" max="11" width="2.125" customWidth="true" style="246"/>
-    <col min="12" max="12" width="10.875" customWidth="true" style="246"/>
-    <col min="13" max="13" width="10.125" customWidth="true" style="246"/>
-    <col min="14" max="14" width="9.5" customWidth="true" style="246"/>
-    <col min="16" max="16" width="8.125" customWidth="true" style="246"/>
-    <col min="17" max="17" width="8.25" customWidth="true" style="246"/>
+    <col min="1" max="1" width="3.25" customWidth="true" style="245"/>
+    <col min="2" max="2" width="3.5" customWidth="true" style="245"/>
+    <col min="3" max="3" width="11.125" customWidth="true" style="245"/>
+    <col min="4" max="4" width="4.125" customWidth="true" style="245"/>
+    <col min="5" max="5" width="4.125" customWidth="true" style="245"/>
+    <col min="6" max="6" width="4.75" customWidth="true" style="245"/>
+    <col min="7" max="7" width="3.25" customWidth="true" style="245"/>
+    <col min="8" max="8" width="11.625" customWidth="true" style="245"/>
+    <col min="9" max="9" width="8.25" customWidth="true" style="245"/>
+    <col min="10" max="10" width="4.875" customWidth="true" style="245"/>
+    <col min="11" max="11" width="2.125" customWidth="true" style="245"/>
+    <col min="12" max="12" width="10.875" customWidth="true" style="245"/>
+    <col min="13" max="13" width="10.125" customWidth="true" style="245"/>
+    <col min="14" max="14" width="9.5" customWidth="true" style="245"/>
+    <col min="16" max="16" width="8.125" customWidth="true" style="245"/>
+    <col min="17" max="17" width="8.25" customWidth="true" style="245"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -6629,32 +6660,32 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:20" customHeight="1" ht="60" s="246" customFormat="1">
-      <c r="A2" s="250" t="inlineStr">
+    <row r="2" spans="1:20" customHeight="1" ht="60" s="245" customFormat="1">
+      <c r="A2" s="249" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">자  동  차  등  록  증</t>
           </r>
         </is>
       </c>
-      <c r="B2" s="251"/>
-      <c r="C2" s="251"/>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
-      <c r="M2" s="251"/>
-      <c r="N2" s="251"/>
-      <c r="O2" s="251"/>
-      <c r="P2" s="251"/>
-      <c r="Q2" s="252"/>
-    </row>
-    <row r="3" spans="1:20" customHeight="1" ht="23.25" s="246" customFormat="1">
+      <c r="B2" s="250"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="250"/>
+      <c r="E2" s="250"/>
+      <c r="F2" s="250"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="250"/>
+      <c r="J2" s="250"/>
+      <c r="K2" s="250"/>
+      <c r="L2" s="250"/>
+      <c r="M2" s="250"/>
+      <c r="N2" s="250"/>
+      <c r="O2" s="250"/>
+      <c r="P2" s="250"/>
+      <c r="Q2" s="251"/>
+    </row>
+    <row r="3" spans="1:20" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -6667,10 +6698,10 @@
         <f>구매리스트!G3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="E3" s="253"/>
-      <c r="F3" s="253"/>
-      <c r="G3" s="253"/>
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="252"/>
       <c r="H3" s="17" t="inlineStr">
         <is>
           <r>
@@ -6699,10 +6730,10 @@
         <f>구매리스트!B6</f>
         <v>0</v>
       </c>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="254"/>
-    </row>
-    <row r="4" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="P3" s="252"/>
+      <c r="Q3" s="253"/>
+    </row>
+    <row r="4" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A4" s="135" t="inlineStr">
         <is>
           <r>
@@ -6710,17 +6741,17 @@
           </r>
         </is>
       </c>
-      <c r="B4" s="255"/>
-      <c r="C4" s="255"/>
-      <c r="D4" s="255"/>
+      <c r="B4" s="254"/>
+      <c r="C4" s="254"/>
+      <c r="D4" s="254"/>
       <c r="E4" s="151" t="str">
         <f>구매리스트!B4</f>
         <v>0</v>
       </c>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
-      <c r="H4" s="255"/>
-      <c r="I4" s="256"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="255"/>
       <c r="J4" s="136" t="inlineStr">
         <is>
           <r>
@@ -6728,13 +6759,13 @@
           </r>
         </is>
       </c>
-      <c r="K4" s="255"/>
-      <c r="L4" s="256"/>
+      <c r="K4" s="254"/>
+      <c r="L4" s="255"/>
       <c r="M4" s="151" t="str">
         <f>구매리스트!G6</f>
         <v>0</v>
       </c>
-      <c r="N4" s="256"/>
+      <c r="N4" s="255"/>
       <c r="O4" s="136" t="inlineStr">
         <is>
           <r>
@@ -6749,9 +6780,9 @@
           </r>
         </is>
       </c>
-      <c r="Q4" s="256"/>
-    </row>
-    <row r="5" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="Q4" s="255"/>
+    </row>
+    <row r="5" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A5" s="136" t="inlineStr">
         <is>
           <r>
@@ -6759,17 +6790,17 @@
           </r>
         </is>
       </c>
-      <c r="B5" s="255"/>
-      <c r="C5" s="255"/>
-      <c r="D5" s="256"/>
+      <c r="B5" s="254"/>
+      <c r="C5" s="254"/>
+      <c r="D5" s="255"/>
       <c r="E5" s="151" t="str">
         <f>구매리스트!B5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="255"/>
-      <c r="G5" s="255"/>
-      <c r="H5" s="255"/>
-      <c r="I5" s="256"/>
+      <c r="F5" s="254"/>
+      <c r="G5" s="254"/>
+      <c r="H5" s="254"/>
+      <c r="I5" s="255"/>
       <c r="J5" s="136" t="inlineStr">
         <is>
           <r>
@@ -6777,21 +6808,21 @@
           </r>
         </is>
       </c>
-      <c r="K5" s="255"/>
-      <c r="L5" s="256"/>
+      <c r="K5" s="254"/>
+      <c r="L5" s="255"/>
       <c r="M5" s="134" t="str">
         <f>구매리스트!G4</f>
         <v>0</v>
       </c>
-      <c r="N5" s="255"/>
-      <c r="O5" s="255"/>
-      <c r="P5" s="257" t="str">
+      <c r="N5" s="254"/>
+      <c r="O5" s="254"/>
+      <c r="P5" s="256" t="str">
         <f>구매리스트!I5</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="256"/>
-    </row>
-    <row r="6" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="Q5" s="255"/>
+    </row>
+    <row r="6" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A6" s="136" t="inlineStr">
         <is>
           <r>
@@ -6799,17 +6830,17 @@
           </r>
         </is>
       </c>
-      <c r="B6" s="255"/>
-      <c r="C6" s="255"/>
-      <c r="D6" s="256"/>
+      <c r="B6" s="254"/>
+      <c r="C6" s="254"/>
+      <c r="D6" s="255"/>
       <c r="E6" s="151" t="str">
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="F6" s="255"/>
-      <c r="G6" s="255"/>
-      <c r="H6" s="255"/>
-      <c r="I6" s="256"/>
+      <c r="F6" s="254"/>
+      <c r="G6" s="254"/>
+      <c r="H6" s="254"/>
+      <c r="I6" s="255"/>
       <c r="J6" s="136" t="inlineStr">
         <is>
           <r>
@@ -6817,18 +6848,18 @@
           </r>
         </is>
       </c>
-      <c r="K6" s="255"/>
-      <c r="L6" s="256"/>
+      <c r="K6" s="254"/>
+      <c r="L6" s="255"/>
       <c r="M6" s="151" t="str">
         <f>구매리스트!I4</f>
         <v>0</v>
       </c>
-      <c r="N6" s="255"/>
-      <c r="O6" s="255"/>
-      <c r="P6" s="255"/>
-      <c r="Q6" s="256"/>
-    </row>
-    <row r="7" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="N6" s="254"/>
+      <c r="O6" s="254"/>
+      <c r="P6" s="254"/>
+      <c r="Q6" s="255"/>
+    </row>
+    <row r="7" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A7" s="136" t="inlineStr">
         <is>
           <r>
@@ -6836,38 +6867,38 @@
           </r>
         </is>
       </c>
-      <c r="B7" s="255"/>
-      <c r="C7" s="255"/>
-      <c r="D7" s="256"/>
-      <c r="E7" s="258" t="inlineStr">
+      <c r="B7" s="254"/>
+      <c r="C7" s="254"/>
+      <c r="D7" s="255"/>
+      <c r="E7" s="257" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">경기도 시흥시 산기대학로 163, A동 328호(정왕동)</t>
           </r>
         </is>
       </c>
-      <c r="F7" s="255"/>
-      <c r="G7" s="255"/>
-      <c r="H7" s="255"/>
-      <c r="I7" s="255"/>
-      <c r="J7" s="255"/>
-      <c r="K7" s="255"/>
-      <c r="L7" s="255"/>
-      <c r="M7" s="255"/>
-      <c r="N7" s="255"/>
-      <c r="O7" s="255"/>
-      <c r="P7" s="255"/>
-      <c r="Q7" s="256"/>
-    </row>
-    <row r="8" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
-      <c r="A8" s="259" t="inlineStr">
+      <c r="F7" s="254"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="254"/>
+      <c r="I7" s="254"/>
+      <c r="J7" s="254"/>
+      <c r="K7" s="254"/>
+      <c r="L7" s="254"/>
+      <c r="M7" s="254"/>
+      <c r="N7" s="254"/>
+      <c r="O7" s="254"/>
+      <c r="P7" s="254"/>
+      <c r="Q7" s="255"/>
+    </row>
+    <row r="8" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
+      <c r="A8" s="258" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">소유자</t>
           </r>
         </is>
       </c>
-      <c r="B8" s="256"/>
+      <c r="B8" s="255"/>
       <c r="C8" s="135" t="inlineStr">
         <is>
           <r>
@@ -6875,15 +6906,15 @@
           </r>
         </is>
       </c>
-      <c r="D8" s="255"/>
-      <c r="E8" s="260" t="s">
+      <c r="D8" s="254"/>
+      <c r="E8" s="259" t="s">
         <v>99</v>
       </c>
-      <c r="F8" s="255"/>
-      <c r="G8" s="255"/>
-      <c r="H8" s="255"/>
-      <c r="I8" s="256"/>
-      <c r="J8" s="261" t="inlineStr">
+      <c r="F8" s="254"/>
+      <c r="G8" s="254"/>
+      <c r="H8" s="254"/>
+      <c r="I8" s="255"/>
+      <c r="J8" s="260" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">      생   년   월   일
@@ -6891,28 +6922,28 @@
           </r>
         </is>
       </c>
-      <c r="K8" s="255"/>
-      <c r="L8" s="256"/>
-      <c r="M8" s="260" t="inlineStr">
+      <c r="K8" s="254"/>
+      <c r="L8" s="255"/>
+      <c r="M8" s="259" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">120111-0922270</t>
           </r>
         </is>
       </c>
-      <c r="N8" s="255"/>
-      <c r="O8" s="255"/>
-      <c r="P8" s="255"/>
-      <c r="Q8" s="256"/>
-      <c r="T8" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="9" spans="1:20" customHeight="1" ht="6.75" s="246" customFormat="1">
+      <c r="N8" s="254"/>
+      <c r="O8" s="254"/>
+      <c r="P8" s="254"/>
+      <c r="Q8" s="255"/>
+      <c r="T8" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:20" customHeight="1" ht="6.75" s="245" customFormat="1">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -6931,17 +6962,17 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:20" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A10" s="262" t="inlineStr">
+    <row r="10" spans="1:20" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A10" s="261" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">「자동차관리법」제8조에 따라 위와 같이 등록하였음을 증명합니다. </t>
           </r>
         </is>
       </c>
-      <c r="Q10" s="263"/>
-    </row>
-    <row r="11" spans="1:20" customHeight="1" ht="22.5" s="246" customFormat="1">
+      <c r="Q10" s="262"/>
+    </row>
+    <row r="11" spans="1:20" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A11" s="1"/>
       <c r="B11" s="154" t="inlineStr">
         <is>
@@ -6950,9 +6981,9 @@
           </r>
         </is>
       </c>
-      <c r="Q11" s="263"/>
-    </row>
-    <row r="12" spans="1:20" customHeight="1" ht="20.25" s="246" customFormat="1">
+      <c r="Q11" s="262"/>
+    </row>
+    <row r="12" spans="1:20" customHeight="1" ht="20.25" s="245" customFormat="1">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -6971,7 +7002,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="1:20" customHeight="1" ht="26.25" s="246" customFormat="1">
+    <row r="13" spans="1:20" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <r>
@@ -6979,7 +7010,7 @@
           </r>
         </is>
       </c>
-      <c r="B13" s="246" t="inlineStr">
+      <c r="B13" s="245" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -6990,11 +7021,11 @@
         <f>구매리스트!I3</f>
         <v>0</v>
       </c>
-      <c r="O13" s="246"/>
-      <c r="P13" s="264"/>
+      <c r="O13" s="245"/>
+      <c r="P13" s="263"/>
       <c r="Q13" s="5"/>
     </row>
-    <row r="14" spans="1:20" customHeight="1" ht="23.25" s="246" customFormat="1">
+    <row r="14" spans="1:20" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A14" s="4"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
@@ -7002,18 +7033,14 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="5"/>
     </row>
-    <row r="15" spans="1:20" customHeight="1" ht="39" s="246" customFormat="1">
+    <row r="15" spans="1:20" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
-      <c r="J15" s="156" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="Q15" s="263"/>
-    </row>
-    <row r="16" spans="1:20" customHeight="1" ht="9" s="246" customFormat="1">
+      <c r="J15" s="396" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q15" s="262"/>
+    </row>
+    <row r="16" spans="1:20" customHeight="1" ht="9" s="245" customFormat="1">
       <c r="A16" s="7"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -7032,54 +7059,54 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="9"/>
     </row>
-    <row r="17" spans="1:20" customHeight="1" ht="8.25" s="246" customFormat="1">
+    <row r="17" spans="1:20" customHeight="1" ht="8.25" s="245" customFormat="1">
       <c r="A17" s="4"/>
-      <c r="B17" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="I17" s="265"/>
-      <c r="J17" s="265"/>
-      <c r="K17" s="265"/>
-      <c r="L17" s="265"/>
-      <c r="M17" s="265"/>
-      <c r="N17" s="265"/>
+      <c r="B17" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="I17" s="264"/>
+      <c r="J17" s="264"/>
+      <c r="K17" s="264"/>
+      <c r="L17" s="264"/>
+      <c r="M17" s="264"/>
+      <c r="N17" s="264"/>
       <c r="Q17" s="5"/>
     </row>
-    <row r="18" spans="1:20" customHeight="1" ht="21.75" s="246" customFormat="1">
-      <c r="A18" s="266" t="inlineStr">
+    <row r="18" spans="1:20" customHeight="1" ht="21.75" s="245" customFormat="1">
+      <c r="A18" s="265" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1.제  원 </t>
           </r>
         </is>
       </c>
-      <c r="B18" s="255"/>
-      <c r="C18" s="255"/>
-      <c r="D18" s="255"/>
-      <c r="E18" s="255"/>
-      <c r="F18" s="255"/>
-      <c r="G18" s="255"/>
-      <c r="H18" s="255"/>
-      <c r="I18" s="255"/>
-      <c r="J18" s="256"/>
-      <c r="L18" s="267" t="inlineStr">
+      <c r="B18" s="254"/>
+      <c r="C18" s="254"/>
+      <c r="D18" s="254"/>
+      <c r="E18" s="254"/>
+      <c r="F18" s="254"/>
+      <c r="G18" s="254"/>
+      <c r="H18" s="254"/>
+      <c r="I18" s="254"/>
+      <c r="J18" s="255"/>
+      <c r="L18" s="266" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">  4. 검사유효기간</t>
           </r>
         </is>
       </c>
-      <c r="M18" s="255"/>
-      <c r="N18" s="255"/>
-      <c r="O18" s="255"/>
-      <c r="P18" s="255"/>
-      <c r="Q18" s="256"/>
-    </row>
-    <row r="19" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+      <c r="M18" s="254"/>
+      <c r="N18" s="254"/>
+      <c r="O18" s="254"/>
+      <c r="P18" s="254"/>
+      <c r="Q18" s="255"/>
+    </row>
+    <row r="19" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A19" s="60" t="inlineStr">
         <is>
           <r>
@@ -7094,39 +7121,39 @@
           </r>
         </is>
       </c>
-      <c r="C19" s="251"/>
-      <c r="D19" s="251"/>
-      <c r="E19" s="251"/>
-      <c r="F19" s="268" t="str">
+      <c r="C19" s="250"/>
+      <c r="D19" s="250"/>
+      <c r="E19" s="250"/>
+      <c r="F19" s="267" t="str">
         <f>구매리스트!G5</f>
         <v>0</v>
       </c>
-      <c r="G19" s="251"/>
-      <c r="H19" s="251"/>
-      <c r="I19" s="251"/>
-      <c r="J19" s="252"/>
-      <c r="L19" s="166" t="inlineStr">
+      <c r="G19" s="250"/>
+      <c r="H19" s="250"/>
+      <c r="I19" s="250"/>
+      <c r="J19" s="251"/>
+      <c r="L19" s="165" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">연월일</t>
           </r>
         </is>
       </c>
-      <c r="M19" s="166" t="inlineStr">
+      <c r="M19" s="165" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">연월일</t>
           </r>
         </is>
       </c>
-      <c r="N19" s="166" t="inlineStr">
+      <c r="N19" s="165" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">  검    사</t>
           </r>
         </is>
       </c>
-      <c r="O19" s="166" t="inlineStr">
+      <c r="O19" s="165" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">주  행</t>
@@ -7140,7 +7167,7 @@
           </r>
         </is>
       </c>
-      <c r="Q19" s="166" t="inlineStr">
+      <c r="Q19" s="165" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">검  사</t>
@@ -7148,7 +7175,7 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="20" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A20" s="58" t="inlineStr">
         <is>
           <r>
@@ -7163,50 +7190,50 @@
           </r>
         </is>
       </c>
-      <c r="C20" s="253"/>
-      <c r="D20" s="253"/>
-      <c r="E20" s="253"/>
-      <c r="F20" s="253"/>
-      <c r="G20" s="253"/>
-      <c r="H20" s="253"/>
-      <c r="I20" s="253"/>
-      <c r="J20" s="254"/>
-      <c r="L20" s="167" t="inlineStr">
+      <c r="C20" s="252"/>
+      <c r="D20" s="252"/>
+      <c r="E20" s="252"/>
+      <c r="F20" s="252"/>
+      <c r="G20" s="252"/>
+      <c r="H20" s="252"/>
+      <c r="I20" s="252"/>
+      <c r="J20" s="253"/>
+      <c r="L20" s="166" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">부   터</t>
           </r>
         </is>
       </c>
-      <c r="M20" s="167" t="inlineStr">
+      <c r="M20" s="166" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">까   지</t>
           </r>
         </is>
       </c>
-      <c r="N20" s="167" t="inlineStr">
+      <c r="N20" s="166" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">  시행장소</t>
           </r>
         </is>
       </c>
-      <c r="O20" s="167" t="inlineStr">
+      <c r="O20" s="166" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">거  리</t>
           </r>
         </is>
       </c>
-      <c r="P20" s="175" t="inlineStr">
+      <c r="P20" s="174" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">임자확인</t>
           </r>
         </is>
       </c>
-      <c r="Q20" s="167" t="inlineStr">
+      <c r="Q20" s="166" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">구  분</t>
@@ -7214,7 +7241,7 @@
         </is>
       </c>
     </row>
-    <row r="21" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="21" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A21" s="62" t="inlineStr">
         <is>
           <r>
@@ -7229,12 +7256,12 @@
           </r>
         </is>
       </c>
-      <c r="C21" s="256"/>
-      <c r="D21" s="157" t="str">
+      <c r="C21" s="255"/>
+      <c r="D21" s="156" t="str">
         <f>구매리스트!G7</f>
         <v>0</v>
       </c>
-      <c r="E21" s="255"/>
+      <c r="E21" s="254"/>
       <c r="F21" s="16" t="inlineStr">
         <is>
           <r>
@@ -7283,7 +7310,7 @@
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
     </row>
-    <row r="22" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="22" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A22" s="63" t="inlineStr">
         <is>
           <r>
@@ -7298,12 +7325,12 @@
           </r>
         </is>
       </c>
-      <c r="C22" s="256"/>
+      <c r="C22" s="255"/>
       <c r="D22" s="141" t="str">
         <f>구매리스트!G8</f>
         <v>0</v>
       </c>
-      <c r="E22" s="255"/>
+      <c r="E22" s="254"/>
       <c r="F22" s="16" t="inlineStr">
         <is>
           <r>
@@ -7343,7 +7370,7 @@
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
     </row>
-    <row r="23" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="23" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A23" s="63" t="inlineStr">
         <is>
           <r>
@@ -7358,12 +7385,12 @@
           </r>
         </is>
       </c>
-      <c r="C23" s="256"/>
+      <c r="C23" s="255"/>
       <c r="D23" s="141" t="str">
         <f>구매리스트!G9</f>
         <v>0</v>
       </c>
-      <c r="E23" s="255"/>
+      <c r="E23" s="254"/>
       <c r="F23" s="16" t="inlineStr">
         <is>
           <r>
@@ -7402,8 +7429,8 @@
       <c r="P23" s="14"/>
       <c r="Q23" s="14"/>
     </row>
-    <row r="24" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A24" s="269" t="inlineStr">
+    <row r="24" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A24" s="268" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">⑱</t>
@@ -7417,23 +7444,23 @@
           </r>
         </is>
       </c>
-      <c r="C24" s="252"/>
-      <c r="D24" s="270" t="str">
+      <c r="C24" s="251"/>
+      <c r="D24" s="269" t="str">
         <f>구매리스트!G10</f>
         <v>0</v>
       </c>
-      <c r="E24" s="251"/>
-      <c r="F24" s="251"/>
-      <c r="G24" s="251"/>
-      <c r="H24" s="251"/>
-      <c r="I24" s="271" t="inlineStr">
+      <c r="E24" s="250"/>
+      <c r="F24" s="250"/>
+      <c r="G24" s="250"/>
+      <c r="H24" s="250"/>
+      <c r="I24" s="270" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">cc,(Ah ,[Ah]</t>
           </r>
         </is>
       </c>
-      <c r="J24" s="252"/>
+      <c r="J24" s="251"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
       <c r="N24" s="14"/>
@@ -7441,8 +7468,8 @@
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
     </row>
-    <row r="25" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A25" s="272"/>
+    <row r="25" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A25" s="271"/>
       <c r="B25" s="144" t="inlineStr">
         <is>
           <r>
@@ -7450,9 +7477,9 @@
           </r>
         </is>
       </c>
-      <c r="C25" s="263"/>
-      <c r="D25" s="272"/>
-      <c r="J25" s="263"/>
+      <c r="C25" s="262"/>
+      <c r="D25" s="271"/>
+      <c r="J25" s="262"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
@@ -7460,17 +7487,17 @@
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
     </row>
-    <row r="26" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A26" s="273"/>
-      <c r="B26" s="253"/>
-      <c r="C26" s="254"/>
-      <c r="D26" s="273"/>
-      <c r="E26" s="253"/>
-      <c r="F26" s="253"/>
-      <c r="G26" s="253"/>
-      <c r="H26" s="253"/>
-      <c r="I26" s="253"/>
-      <c r="J26" s="254"/>
+    <row r="26" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A26" s="272"/>
+      <c r="B26" s="252"/>
+      <c r="C26" s="253"/>
+      <c r="D26" s="272"/>
+      <c r="E26" s="252"/>
+      <c r="F26" s="252"/>
+      <c r="G26" s="252"/>
+      <c r="H26" s="252"/>
+      <c r="I26" s="252"/>
+      <c r="J26" s="253"/>
       <c r="L26" s="68"/>
       <c r="M26" s="68"/>
       <c r="N26" s="68"/>
@@ -7478,7 +7505,7 @@
       <c r="P26" s="68"/>
       <c r="Q26" s="68"/>
     </row>
-    <row r="27" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="27" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A27" s="63" t="inlineStr">
         <is>
           <r>
@@ -7493,14 +7520,14 @@
           </r>
         </is>
       </c>
-      <c r="C27" s="256"/>
+      <c r="C27" s="255"/>
       <c r="D27" s="141" t="str">
         <f>구매리스트!G11</f>
         <v>0</v>
       </c>
-      <c r="E27" s="255"/>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
+      <c r="E27" s="254"/>
+      <c r="F27" s="254"/>
+      <c r="G27" s="254"/>
       <c r="H27" s="140" t="inlineStr">
         <is>
           <r>
@@ -7508,8 +7535,8 @@
           </r>
         </is>
       </c>
-      <c r="I27" s="255"/>
-      <c r="J27" s="256"/>
+      <c r="I27" s="254"/>
+      <c r="J27" s="255"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
       <c r="N27" s="14"/>
@@ -7517,7 +7544,7 @@
       <c r="P27" s="14"/>
       <c r="Q27" s="14"/>
     </row>
-    <row r="28" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="28" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A28" s="64" t="inlineStr">
         <is>
           <r>
@@ -7532,15 +7559,15 @@
           </r>
         </is>
       </c>
-      <c r="C28" s="252"/>
-      <c r="D28" s="274" t="str">
+      <c r="C28" s="251"/>
+      <c r="D28" s="273" t="str">
         <f>구매리스트!G12</f>
         <v>0</v>
       </c>
-      <c r="E28" s="251"/>
-      <c r="F28" s="251"/>
-      <c r="G28" s="251"/>
-      <c r="H28" s="251"/>
+      <c r="E28" s="250"/>
+      <c r="F28" s="250"/>
+      <c r="G28" s="250"/>
+      <c r="H28" s="250"/>
       <c r="I28" s="137" t="inlineStr">
         <is>
           <r>
@@ -7548,7 +7575,7 @@
           </r>
         </is>
       </c>
-      <c r="J28" s="252"/>
+      <c r="J28" s="251"/>
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
       <c r="N28" s="14"/>
@@ -7556,17 +7583,17 @@
       <c r="P28" s="14"/>
       <c r="Q28" s="14"/>
     </row>
-    <row r="29" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A29" s="275" t="inlineStr">
+    <row r="29" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A29" s="274" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">(구동축전지정격전압)</t>
           </r>
         </is>
       </c>
-      <c r="C29" s="263"/>
-      <c r="D29" s="272"/>
-      <c r="J29" s="263"/>
+      <c r="C29" s="262"/>
+      <c r="D29" s="271"/>
+      <c r="J29" s="262"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
       <c r="N29" s="14"/>
@@ -7574,23 +7601,23 @@
       <c r="P29" s="14"/>
       <c r="Q29" s="14"/>
     </row>
-    <row r="30" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A30" s="276" t="inlineStr">
+    <row r="30" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A30" s="275" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">[연료전지 최고출력]</t>
           </r>
         </is>
       </c>
-      <c r="B30" s="253"/>
-      <c r="C30" s="254"/>
-      <c r="D30" s="273"/>
-      <c r="E30" s="253"/>
-      <c r="F30" s="253"/>
-      <c r="G30" s="253"/>
-      <c r="H30" s="253"/>
-      <c r="I30" s="253"/>
-      <c r="J30" s="254"/>
+      <c r="B30" s="252"/>
+      <c r="C30" s="253"/>
+      <c r="D30" s="272"/>
+      <c r="E30" s="252"/>
+      <c r="F30" s="252"/>
+      <c r="G30" s="252"/>
+      <c r="H30" s="252"/>
+      <c r="I30" s="252"/>
+      <c r="J30" s="253"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
@@ -7598,7 +7625,7 @@
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
     </row>
-    <row r="31" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="31" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A31" s="65" t="inlineStr">
         <is>
           <r>
@@ -7606,33 +7633,33 @@
           </r>
         </is>
       </c>
-      <c r="B31" s="160" t="inlineStr">
+      <c r="B31" s="159" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">연료의종류 및 연료소비율</t>
           </r>
         </is>
       </c>
-      <c r="C31" s="256"/>
+      <c r="C31" s="255"/>
       <c r="D31" s="146" t="str">
         <f>구매리스트!G13</f>
         <v>0</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="254"/>
       <c r="F31" s="145" t="str">
         <f>구매리스트!H13</f>
         <v>0</v>
       </c>
-      <c r="G31" s="255"/>
-      <c r="H31" s="161" t="inlineStr">
+      <c r="G31" s="254"/>
+      <c r="H31" s="160" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">km/l,(km/kWh),[km/kg]</t>
           </r>
         </is>
       </c>
-      <c r="I31" s="255"/>
-      <c r="J31" s="256"/>
+      <c r="I31" s="254"/>
+      <c r="J31" s="255"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
@@ -7640,7 +7667,7 @@
       <c r="P31" s="14"/>
       <c r="Q31" s="14"/>
     </row>
-    <row r="32" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="32" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A32" s="66" t="inlineStr">
         <is>
           <r>
@@ -7648,23 +7675,23 @@
           </r>
         </is>
       </c>
-      <c r="B32" s="158" t="inlineStr">
+      <c r="B32" s="157" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">구동축전지 셀의제조사</t>
           </r>
         </is>
       </c>
-      <c r="C32" s="256"/>
-      <c r="D32" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="E32" s="255"/>
-      <c r="F32" s="256"/>
+      <c r="C32" s="255"/>
+      <c r="D32" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="E32" s="254"/>
+      <c r="F32" s="255"/>
       <c r="G32" s="59" t="inlineStr">
         <is>
           <r>
@@ -7679,14 +7706,14 @@
           </r>
         </is>
       </c>
-      <c r="I32" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J32" s="256"/>
+      <c r="I32" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J32" s="255"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
@@ -7694,7 +7721,7 @@
       <c r="P32" s="14"/>
       <c r="Q32" s="14"/>
     </row>
-    <row r="33" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="33" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A33" s="66" t="inlineStr">
         <is>
           <r>
@@ -7702,23 +7729,23 @@
           </r>
         </is>
       </c>
-      <c r="B33" s="159" t="inlineStr">
+      <c r="B33" s="158" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">구동축전지셀의주요원료</t>
           </r>
         </is>
       </c>
-      <c r="C33" s="256"/>
-      <c r="D33" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="E33" s="255"/>
-      <c r="F33" s="256"/>
+      <c r="C33" s="255"/>
+      <c r="D33" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="E33" s="254"/>
+      <c r="F33" s="255"/>
       <c r="G33" s="136" t="inlineStr">
         <is>
           <r>
@@ -7726,15 +7753,15 @@
           </r>
         </is>
       </c>
-      <c r="H33" s="256"/>
-      <c r="I33" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J33" s="256"/>
+      <c r="H33" s="255"/>
+      <c r="I33" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J33" s="255"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
@@ -7742,23 +7769,23 @@
       <c r="P33" s="14"/>
       <c r="Q33" s="14"/>
     </row>
-    <row r="34" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A34" s="278" t="inlineStr">
+    <row r="34" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A34" s="277" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">유의사항 : ⑱~㉑에서 기재 단위는 사용연료의 종류가 전기인 자동차의 경우는 (),수소전기자동차의 경우는[]을 말합니다.「자동차관리법 시행규칙」별표1 제2회의 특수자동차의 경우 최대적재량은 피견인자동차를 연결하기위해 허용되는 최대수직하중을 말하며 견인능력과는무관합니다,㉒~㉔는 구동축전지를 갖춘 자동차(외부 전기공급원을 통해 충전할 수 없는 구조인 자동차는제외)의경우만 해당합니다.</t>
           </r>
         </is>
       </c>
-      <c r="B34" s="251"/>
-      <c r="C34" s="251"/>
-      <c r="D34" s="251"/>
-      <c r="E34" s="251"/>
-      <c r="F34" s="251"/>
-      <c r="G34" s="251"/>
-      <c r="H34" s="251"/>
-      <c r="I34" s="251"/>
-      <c r="J34" s="252"/>
+      <c r="B34" s="250"/>
+      <c r="C34" s="250"/>
+      <c r="D34" s="250"/>
+      <c r="E34" s="250"/>
+      <c r="F34" s="250"/>
+      <c r="G34" s="250"/>
+      <c r="H34" s="250"/>
+      <c r="I34" s="250"/>
+      <c r="J34" s="251"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
@@ -7766,9 +7793,9 @@
       <c r="P34" s="14"/>
       <c r="Q34" s="14"/>
     </row>
-    <row r="35" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A35" s="272"/>
-      <c r="J35" s="263"/>
+    <row r="35" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A35" s="271"/>
+      <c r="J35" s="262"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
@@ -7776,9 +7803,9 @@
       <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
     </row>
-    <row r="36" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A36" s="272"/>
-      <c r="J36" s="263"/>
+    <row r="36" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A36" s="271"/>
+      <c r="J36" s="262"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
@@ -7786,17 +7813,17 @@
       <c r="P36" s="14"/>
       <c r="Q36" s="14"/>
     </row>
-    <row r="37" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A37" s="273"/>
-      <c r="B37" s="253"/>
-      <c r="C37" s="253"/>
-      <c r="D37" s="253"/>
-      <c r="E37" s="253"/>
-      <c r="F37" s="253"/>
-      <c r="G37" s="253"/>
-      <c r="H37" s="253"/>
-      <c r="I37" s="253"/>
-      <c r="J37" s="254"/>
+    <row r="37" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A37" s="272"/>
+      <c r="B37" s="252"/>
+      <c r="C37" s="252"/>
+      <c r="D37" s="252"/>
+      <c r="E37" s="252"/>
+      <c r="F37" s="252"/>
+      <c r="G37" s="252"/>
+      <c r="H37" s="252"/>
+      <c r="I37" s="252"/>
+      <c r="J37" s="253"/>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
@@ -7804,79 +7831,79 @@
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
     </row>
-    <row r="38" spans="1:20" customHeight="1" ht="25.5" s="246" customFormat="1">
-      <c r="A38" s="173" t="inlineStr">
+    <row r="38" spans="1:20" customHeight="1" ht="25.5" s="245" customFormat="1">
+      <c r="A38" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2.등록번호판 교부 및 봉인</t>
           </r>
         </is>
       </c>
-      <c r="B38" s="255"/>
-      <c r="C38" s="255"/>
-      <c r="D38" s="255"/>
-      <c r="E38" s="255"/>
-      <c r="F38" s="255"/>
-      <c r="G38" s="255"/>
-      <c r="H38" s="255"/>
-      <c r="I38" s="255"/>
-      <c r="J38" s="256"/>
-      <c r="L38" s="279" t="inlineStr">
+      <c r="B38" s="254"/>
+      <c r="C38" s="254"/>
+      <c r="D38" s="254"/>
+      <c r="E38" s="254"/>
+      <c r="F38" s="254"/>
+      <c r="G38" s="254"/>
+      <c r="H38" s="254"/>
+      <c r="I38" s="254"/>
+      <c r="J38" s="255"/>
+      <c r="L38" s="278" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">※ 주의사항 :      ㉚ 항 첫째란에는 신규등록일을 적습니다.</t>
           </r>
         </is>
       </c>
-      <c r="M38" s="251"/>
-      <c r="N38" s="251"/>
-      <c r="O38" s="251"/>
-      <c r="P38" s="251"/>
-      <c r="Q38" s="252"/>
-    </row>
-    <row r="39" spans="1:20" customHeight="1" ht="25.5" s="246" customFormat="1">
-      <c r="A39" s="280" t="inlineStr">
+      <c r="M38" s="250"/>
+      <c r="N38" s="250"/>
+      <c r="O38" s="250"/>
+      <c r="P38" s="250"/>
+      <c r="Q38" s="251"/>
+    </row>
+    <row r="39" spans="1:20" customHeight="1" ht="25.5" s="245" customFormat="1">
+      <c r="A39" s="279" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉕ 구분</t>
           </r>
         </is>
       </c>
-      <c r="B39" s="255"/>
-      <c r="C39" s="256"/>
-      <c r="D39" s="173" t="inlineStr">
+      <c r="B39" s="254"/>
+      <c r="C39" s="255"/>
+      <c r="D39" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> ㉖ 번호판발급일</t>
           </r>
         </is>
       </c>
-      <c r="E39" s="255"/>
-      <c r="F39" s="255"/>
-      <c r="G39" s="256"/>
-      <c r="H39" s="280" t="inlineStr">
+      <c r="E39" s="254"/>
+      <c r="F39" s="254"/>
+      <c r="G39" s="255"/>
+      <c r="H39" s="279" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉗ 발급대행자확인</t>
           </r>
         </is>
       </c>
-      <c r="I39" s="255"/>
-      <c r="J39" s="256"/>
-      <c r="L39" s="281" t="inlineStr">
+      <c r="I39" s="254"/>
+      <c r="J39" s="255"/>
+      <c r="L39" s="280" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">   비고</t>
           </r>
         </is>
       </c>
-      <c r="M39" s="251"/>
-      <c r="N39" s="251"/>
-      <c r="O39" s="251"/>
-      <c r="P39" s="251"/>
-      <c r="Q39" s="252"/>
-    </row>
-    <row r="40" spans="1:20" customHeight="1" ht="19.5" s="246" customFormat="1">
+      <c r="M39" s="250"/>
+      <c r="N39" s="250"/>
+      <c r="O39" s="250"/>
+      <c r="P39" s="250"/>
+      <c r="Q39" s="251"/>
+    </row>
+    <row r="40" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A40" s="136" t="inlineStr">
         <is>
           <r>
@@ -7884,7 +7911,7 @@
           </r>
         </is>
       </c>
-      <c r="B40" s="256"/>
+      <c r="B40" s="255"/>
       <c r="C40" s="136" t="inlineStr">
         <is>
           <r>
@@ -7892,8 +7919,8 @@
           </r>
         </is>
       </c>
-      <c r="D40" s="255"/>
-      <c r="E40" s="256"/>
+      <c r="D40" s="254"/>
+      <c r="E40" s="255"/>
       <c r="F40" s="136" t="inlineStr">
         <is>
           <r>
@@ -7901,7 +7928,7 @@
           </r>
         </is>
       </c>
-      <c r="G40" s="256"/>
+      <c r="G40" s="255"/>
       <c r="H40" s="136" t="inlineStr">
         <is>
           <r>
@@ -7909,12 +7936,12 @@
           </r>
         </is>
       </c>
-      <c r="I40" s="255"/>
-      <c r="J40" s="256"/>
+      <c r="I40" s="254"/>
+      <c r="J40" s="255"/>
       <c r="L40" s="4"/>
       <c r="Q40" s="5"/>
     </row>
-    <row r="41" spans="1:20" customHeight="1" ht="19.5" s="246" customFormat="1">
+    <row r="41" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A41" s="136" t="inlineStr">
         <is>
           <r>
@@ -7922,7 +7949,7 @@
           </r>
         </is>
       </c>
-      <c r="B41" s="256"/>
+      <c r="B41" s="255"/>
       <c r="C41" s="136" t="inlineStr">
         <is>
           <r>
@@ -7930,8 +7957,8 @@
           </r>
         </is>
       </c>
-      <c r="D41" s="255"/>
-      <c r="E41" s="256"/>
+      <c r="D41" s="254"/>
+      <c r="E41" s="255"/>
       <c r="F41" s="136" t="inlineStr">
         <is>
           <r>
@@ -7939,7 +7966,7 @@
           </r>
         </is>
       </c>
-      <c r="G41" s="256"/>
+      <c r="G41" s="255"/>
       <c r="H41" s="136" t="inlineStr">
         <is>
           <r>
@@ -7947,10 +7974,10 @@
           </r>
         </is>
       </c>
-      <c r="I41" s="255"/>
-      <c r="J41" s="256"/>
+      <c r="I41" s="254"/>
+      <c r="J41" s="255"/>
       <c r="L41" s="4"/>
-      <c r="O41" s="246" t="inlineStr">
+      <c r="O41" s="245" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -7959,8 +7986,8 @@
       </c>
       <c r="Q41" s="5"/>
     </row>
-    <row r="42" spans="1:20" customHeight="1" ht="33" s="246" customFormat="1">
-      <c r="A42" s="267" t="inlineStr">
+    <row r="42" spans="1:20" customHeight="1" ht="33" s="245" customFormat="1">
+      <c r="A42" s="266" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3. 저당권등록사실(저당권등록의 내용은 자동차등록원부(을)를
@@ -7968,45 +7995,45 @@
           </r>
         </is>
       </c>
-      <c r="B42" s="255"/>
-      <c r="C42" s="255"/>
-      <c r="D42" s="255"/>
-      <c r="E42" s="255"/>
-      <c r="F42" s="255"/>
-      <c r="G42" s="255"/>
-      <c r="H42" s="255"/>
-      <c r="I42" s="255"/>
-      <c r="J42" s="256"/>
+      <c r="B42" s="254"/>
+      <c r="C42" s="254"/>
+      <c r="D42" s="254"/>
+      <c r="E42" s="254"/>
+      <c r="F42" s="254"/>
+      <c r="G42" s="254"/>
+      <c r="H42" s="254"/>
+      <c r="I42" s="254"/>
+      <c r="J42" s="255"/>
       <c r="L42" s="4"/>
       <c r="Q42" s="5"/>
     </row>
-    <row r="43" spans="1:20" customHeight="1" ht="22.5" s="246" customFormat="1">
-      <c r="A43" s="282" t="inlineStr">
+    <row r="43" spans="1:20" customHeight="1" ht="22.5" s="245" customFormat="1">
+      <c r="A43" s="281" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉘ 구분(설정 또는 말소)</t>
           </r>
         </is>
       </c>
-      <c r="B43" s="255"/>
-      <c r="C43" s="255"/>
-      <c r="D43" s="255"/>
-      <c r="E43" s="255"/>
-      <c r="F43" s="255"/>
-      <c r="G43" s="256"/>
-      <c r="H43" s="162" t="inlineStr">
+      <c r="B43" s="254"/>
+      <c r="C43" s="254"/>
+      <c r="D43" s="254"/>
+      <c r="E43" s="254"/>
+      <c r="F43" s="254"/>
+      <c r="G43" s="255"/>
+      <c r="H43" s="161" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉙ 날         짜</t>
           </r>
         </is>
       </c>
-      <c r="I43" s="255"/>
-      <c r="J43" s="256"/>
+      <c r="I43" s="254"/>
+      <c r="J43" s="255"/>
       <c r="L43" s="4"/>
       <c r="Q43" s="5"/>
     </row>
-    <row r="44" spans="1:20" customHeight="1" ht="19.5" s="246" customFormat="1">
+    <row r="44" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A44" s="136" t="inlineStr">
         <is>
           <r>
@@ -8014,12 +8041,12 @@
           </r>
         </is>
       </c>
-      <c r="B44" s="255"/>
-      <c r="C44" s="255"/>
-      <c r="D44" s="255"/>
-      <c r="E44" s="255"/>
-      <c r="F44" s="255"/>
-      <c r="G44" s="256"/>
+      <c r="B44" s="254"/>
+      <c r="C44" s="254"/>
+      <c r="D44" s="254"/>
+      <c r="E44" s="254"/>
+      <c r="F44" s="254"/>
+      <c r="G44" s="255"/>
       <c r="H44" s="136" t="inlineStr">
         <is>
           <r>
@@ -8027,12 +8054,12 @@
           </r>
         </is>
       </c>
-      <c r="I44" s="255"/>
-      <c r="J44" s="256"/>
+      <c r="I44" s="254"/>
+      <c r="J44" s="255"/>
       <c r="L44" s="4"/>
       <c r="Q44" s="5"/>
     </row>
-    <row r="45" spans="1:20" customHeight="1" ht="19.5" s="246" customFormat="1">
+    <row r="45" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A45" s="136" t="inlineStr">
         <is>
           <r>
@@ -8040,12 +8067,12 @@
           </r>
         </is>
       </c>
-      <c r="B45" s="255"/>
-      <c r="C45" s="255"/>
-      <c r="D45" s="255"/>
-      <c r="E45" s="255"/>
-      <c r="F45" s="255"/>
-      <c r="G45" s="256"/>
+      <c r="B45" s="254"/>
+      <c r="C45" s="254"/>
+      <c r="D45" s="254"/>
+      <c r="E45" s="254"/>
+      <c r="F45" s="254"/>
+      <c r="G45" s="255"/>
       <c r="H45" s="136" t="inlineStr">
         <is>
           <r>
@@ -8053,8 +8080,8 @@
           </r>
         </is>
       </c>
-      <c r="I45" s="255"/>
-      <c r="J45" s="256"/>
+      <c r="I45" s="254"/>
+      <c r="J45" s="255"/>
       <c r="K45" s="8"/>
       <c r="L45" s="7"/>
       <c r="M45" s="8"/>
@@ -8063,16 +8090,16 @@
       <c r="P45" s="8"/>
       <c r="Q45" s="9"/>
     </row>
-    <row r="46" spans="1:20" customHeight="1" ht="6" s="246" customFormat="1"/>
-    <row r="47" spans="1:20" customHeight="1" ht="23.25" s="246" customFormat="1">
-      <c r="G47" s="163" t="inlineStr">
+    <row r="46" spans="1:20" customHeight="1" ht="6" s="245" customFormat="1"/>
+    <row r="47" spans="1:20" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="G47" s="162" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">※ 뒷면의 '유의사항'을 꼭 읽어보시기 바랍니다.</t>
           </r>
         </is>
       </c>
-      <c r="N47" s="164" t="inlineStr">
+      <c r="N47" s="163" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">210㎜ x 297㎜[백상지 또는 중질지 80g/㎡]</t>
@@ -8196,22 +8223,22 @@
   <dimension ref="A1:W47"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="3.25" customWidth="true" style="246"/>
-    <col min="2" max="2" width="4.125" customWidth="true" style="246"/>
-    <col min="3" max="3" width="11.125" customWidth="true" style="246"/>
-    <col min="4" max="4" width="4.125" customWidth="true" style="246"/>
-    <col min="5" max="5" width="4.125" customWidth="true" style="246"/>
-    <col min="6" max="6" width="4.75" customWidth="true" style="246"/>
-    <col min="7" max="7" width="3.25" customWidth="true" style="246"/>
-    <col min="8" max="8" width="11.625" customWidth="true" style="246"/>
-    <col min="9" max="9" width="8.25" customWidth="true" style="246"/>
-    <col min="10" max="10" width="4.875" customWidth="true" style="246"/>
-    <col min="11" max="11" width="2.125" customWidth="true" style="246"/>
-    <col min="12" max="12" width="10.875" customWidth="true" style="246"/>
-    <col min="13" max="13" width="12.375" customWidth="true" style="246"/>
-    <col min="14" max="14" width="9.5" customWidth="true" style="246"/>
-    <col min="16" max="16" width="10.625" customWidth="true" style="246"/>
-    <col min="17" max="17" width="9.125" customWidth="true" style="246"/>
+    <col min="1" max="1" width="3.25" customWidth="true" style="245"/>
+    <col min="2" max="2" width="4.125" customWidth="true" style="245"/>
+    <col min="3" max="3" width="11.125" customWidth="true" style="245"/>
+    <col min="4" max="4" width="4.125" customWidth="true" style="245"/>
+    <col min="5" max="5" width="4.125" customWidth="true" style="245"/>
+    <col min="6" max="6" width="4.75" customWidth="true" style="245"/>
+    <col min="7" max="7" width="3.25" customWidth="true" style="245"/>
+    <col min="8" max="8" width="11.625" customWidth="true" style="245"/>
+    <col min="9" max="9" width="8.25" customWidth="true" style="245"/>
+    <col min="10" max="10" width="4.875" customWidth="true" style="245"/>
+    <col min="11" max="11" width="2.125" customWidth="true" style="245"/>
+    <col min="12" max="12" width="10.875" customWidth="true" style="245"/>
+    <col min="13" max="13" width="12.375" customWidth="true" style="245"/>
+    <col min="14" max="14" width="9.5" customWidth="true" style="245"/>
+    <col min="16" max="16" width="10.625" customWidth="true" style="245"/>
+    <col min="17" max="17" width="9.125" customWidth="true" style="245"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -8245,32 +8272,32 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:23" customHeight="1" ht="60" s="246" customFormat="1">
-      <c r="A2" s="283" t="inlineStr">
+    <row r="2" spans="1:23" customHeight="1" ht="60" s="245" customFormat="1">
+      <c r="A2" s="282" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Certificate of Registration of Automobile</t>
           </r>
         </is>
       </c>
-      <c r="B2" s="251"/>
-      <c r="C2" s="251"/>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
-      <c r="M2" s="251"/>
-      <c r="N2" s="251"/>
-      <c r="O2" s="251"/>
-      <c r="P2" s="251"/>
-      <c r="Q2" s="252"/>
-    </row>
-    <row r="3" spans="1:23" customHeight="1" ht="23.25" s="246" customFormat="1">
+      <c r="B2" s="250"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="250"/>
+      <c r="E2" s="250"/>
+      <c r="F2" s="250"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="250"/>
+      <c r="J2" s="250"/>
+      <c r="K2" s="250"/>
+      <c r="L2" s="250"/>
+      <c r="M2" s="250"/>
+      <c r="N2" s="250"/>
+      <c r="O2" s="250"/>
+      <c r="P2" s="250"/>
+      <c r="Q2" s="251"/>
+    </row>
+    <row r="3" spans="1:23" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -8283,10 +8310,10 @@
         <f>구매리스트!G3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="E3" s="253"/>
-      <c r="F3" s="253"/>
-      <c r="G3" s="253"/>
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="252"/>
       <c r="H3" s="17" t="inlineStr">
         <is>
           <r>
@@ -8301,43 +8328,43 @@
           </r>
         </is>
       </c>
-      <c r="J3" s="165" t="inlineStr">
+      <c r="J3" s="164" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">First Registration Date : </t>
           </r>
         </is>
       </c>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="M3" s="253"/>
-      <c r="N3" s="253"/>
-      <c r="O3" s="176" t="str">
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
+      <c r="M3" s="252"/>
+      <c r="N3" s="252"/>
+      <c r="O3" s="175" t="str">
         <f>구매리스트!B6</f>
         <v>0</v>
       </c>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="254"/>
-    </row>
-    <row r="4" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
-      <c r="A4" s="173" t="inlineStr">
+      <c r="P3" s="252"/>
+      <c r="Q3" s="253"/>
+    </row>
+    <row r="4" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
+      <c r="A4" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">① Registration No.</t>
           </r>
         </is>
       </c>
-      <c r="B4" s="255"/>
-      <c r="C4" s="255"/>
-      <c r="D4" s="256"/>
+      <c r="B4" s="254"/>
+      <c r="C4" s="254"/>
+      <c r="D4" s="255"/>
       <c r="E4" s="151" t="str">
         <f>구매리스트!D4</f>
         <v>0</v>
       </c>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
-      <c r="H4" s="255"/>
-      <c r="I4" s="256"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="255"/>
       <c r="J4" s="138" t="inlineStr">
         <is>
           <r>
@@ -8345,13 +8372,13 @@
           </r>
         </is>
       </c>
-      <c r="K4" s="255"/>
-      <c r="L4" s="255"/>
-      <c r="M4" s="177" t="str">
+      <c r="K4" s="254"/>
+      <c r="L4" s="254"/>
+      <c r="M4" s="176" t="str">
         <f>구매리스트!I6</f>
         <v>0</v>
       </c>
-      <c r="N4" s="256"/>
+      <c r="N4" s="255"/>
       <c r="O4" s="136" t="inlineStr">
         <is>
           <r>
@@ -8359,146 +8386,146 @@
           </r>
         </is>
       </c>
-      <c r="P4" s="178" t="inlineStr">
+      <c r="P4" s="177" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Private car</t>
           </r>
         </is>
       </c>
-      <c r="Q4" s="256"/>
-    </row>
-    <row r="5" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
-      <c r="A5" s="173" t="inlineStr">
+      <c r="Q4" s="255"/>
+    </row>
+    <row r="5" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
+      <c r="A5" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">④ Car Name</t>
           </r>
         </is>
       </c>
-      <c r="B5" s="255"/>
-      <c r="C5" s="255"/>
-      <c r="D5" s="256"/>
+      <c r="B5" s="254"/>
+      <c r="C5" s="254"/>
+      <c r="D5" s="255"/>
       <c r="E5" s="151" t="str">
         <f>구매리스트!B5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="255"/>
-      <c r="G5" s="255"/>
-      <c r="H5" s="255"/>
-      <c r="I5" s="256"/>
-      <c r="J5" s="173" t="inlineStr">
+      <c r="F5" s="254"/>
+      <c r="G5" s="254"/>
+      <c r="H5" s="254"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">⑤ Model &amp;Year</t>
           </r>
         </is>
       </c>
-      <c r="K5" s="255"/>
-      <c r="L5" s="256"/>
+      <c r="K5" s="254"/>
+      <c r="L5" s="255"/>
       <c r="M5" s="134" t="str">
         <f>구매리스트!G4</f>
         <v>0</v>
       </c>
-      <c r="N5" s="255"/>
-      <c r="O5" s="255"/>
-      <c r="P5" s="257" t="str">
+      <c r="N5" s="254"/>
+      <c r="O5" s="254"/>
+      <c r="P5" s="256" t="str">
         <f>구매리스트!I5</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="256"/>
-      <c r="S5" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
-      <c r="A6" s="173" t="inlineStr">
+      <c r="Q5" s="255"/>
+      <c r="S5" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
+      <c r="A6" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">⑥ Vehicle ID No.</t>
           </r>
         </is>
       </c>
-      <c r="B6" s="255"/>
-      <c r="C6" s="255"/>
-      <c r="D6" s="256"/>
+      <c r="B6" s="254"/>
+      <c r="C6" s="254"/>
+      <c r="D6" s="255"/>
       <c r="E6" s="151" t="str">
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="F6" s="255"/>
-      <c r="G6" s="255"/>
-      <c r="H6" s="255"/>
-      <c r="I6" s="256"/>
-      <c r="J6" s="173" t="inlineStr">
+      <c r="F6" s="254"/>
+      <c r="G6" s="254"/>
+      <c r="H6" s="254"/>
+      <c r="I6" s="255"/>
+      <c r="J6" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">⑦ Motor Type</t>
           </r>
         </is>
       </c>
-      <c r="K6" s="255"/>
-      <c r="L6" s="256"/>
+      <c r="K6" s="254"/>
+      <c r="L6" s="255"/>
       <c r="M6" s="151" t="str">
         <f>구매리스트!I4</f>
         <v>0</v>
       </c>
-      <c r="N6" s="255"/>
-      <c r="O6" s="255"/>
-      <c r="P6" s="255"/>
-      <c r="Q6" s="256"/>
-      <c r="S6" s="284" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="7" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
-      <c r="A7" s="173" t="inlineStr">
+      <c r="N6" s="254"/>
+      <c r="O6" s="254"/>
+      <c r="P6" s="254"/>
+      <c r="Q6" s="255"/>
+      <c r="S6" s="283" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
+      <c r="A7" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">⑧ Usage Basc</t>
           </r>
         </is>
       </c>
-      <c r="B7" s="255"/>
-      <c r="C7" s="255"/>
-      <c r="D7" s="256"/>
-      <c r="E7" s="258" t="inlineStr">
+      <c r="B7" s="254"/>
+      <c r="C7" s="254"/>
+      <c r="D7" s="255"/>
+      <c r="E7" s="257" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea </t>
           </r>
         </is>
       </c>
-      <c r="F7" s="255"/>
-      <c r="G7" s="255"/>
-      <c r="H7" s="255"/>
-      <c r="I7" s="255"/>
-      <c r="J7" s="255"/>
-      <c r="K7" s="255"/>
-      <c r="L7" s="255"/>
-      <c r="M7" s="255"/>
-      <c r="N7" s="255"/>
-      <c r="O7" s="255"/>
-      <c r="P7" s="255"/>
-      <c r="Q7" s="256"/>
-    </row>
-    <row r="8" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
-      <c r="A8" s="259" t="inlineStr">
+      <c r="F7" s="254"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="254"/>
+      <c r="I7" s="254"/>
+      <c r="J7" s="254"/>
+      <c r="K7" s="254"/>
+      <c r="L7" s="254"/>
+      <c r="M7" s="254"/>
+      <c r="N7" s="254"/>
+      <c r="O7" s="254"/>
+      <c r="P7" s="254"/>
+      <c r="Q7" s="255"/>
+    </row>
+    <row r="8" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
+      <c r="A8" s="258" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Owner</t>
           </r>
         </is>
       </c>
-      <c r="B8" s="256"/>
+      <c r="B8" s="255"/>
       <c r="C8" s="135" t="inlineStr">
         <is>
           <r>
@@ -8506,43 +8533,43 @@
           </r>
         </is>
       </c>
-      <c r="D8" s="255"/>
-      <c r="E8" s="260" t="s">
-        <v>185</v>
-      </c>
-      <c r="F8" s="255"/>
-      <c r="G8" s="255"/>
-      <c r="H8" s="255"/>
-      <c r="I8" s="256"/>
-      <c r="J8" s="261" t="inlineStr">
+      <c r="D8" s="254"/>
+      <c r="E8" s="259" t="s">
+        <v>186</v>
+      </c>
+      <c r="F8" s="254"/>
+      <c r="G8" s="254"/>
+      <c r="H8" s="254"/>
+      <c r="I8" s="255"/>
+      <c r="J8" s="260" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">      ID Card No.</t>
           </r>
         </is>
       </c>
-      <c r="K8" s="255"/>
-      <c r="L8" s="256"/>
-      <c r="M8" s="260" t="inlineStr">
+      <c r="K8" s="254"/>
+      <c r="L8" s="255"/>
+      <c r="M8" s="259" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">120111-0922270</t>
           </r>
         </is>
       </c>
-      <c r="N8" s="255"/>
-      <c r="O8" s="255"/>
-      <c r="P8" s="255"/>
-      <c r="Q8" s="256"/>
-      <c r="R8" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="9" spans="1:23" customHeight="1" ht="6.75" s="246" customFormat="1">
+      <c r="N8" s="254"/>
+      <c r="O8" s="254"/>
+      <c r="P8" s="254"/>
+      <c r="Q8" s="255"/>
+      <c r="R8" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:23" customHeight="1" ht="6.75" s="245" customFormat="1">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -8561,28 +8588,28 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:23" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A10" s="285" t="inlineStr">
+    <row r="10" spans="1:23" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A10" s="284" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">「It is proved that it was registered as above in accordance with Article 8 of the Motor Vehicle Management Act.</t>
           </r>
         </is>
       </c>
-      <c r="Q10" s="263"/>
-    </row>
-    <row r="11" spans="1:23" customHeight="1" ht="22.5" s="246" customFormat="1">
+      <c r="Q10" s="262"/>
+    </row>
+    <row r="11" spans="1:23" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="168" t="inlineStr">
+      <c r="B11" s="167" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">※ Note: In the case of an electric vehicle or hydrogen fuel cell vehicle, the 'prime motor type' in column ⑦ refers to the 'drive motor type</t>
           </r>
         </is>
       </c>
-      <c r="Q11" s="263"/>
-    </row>
-    <row r="12" spans="1:23" customHeight="1" ht="20.25" s="246" customFormat="1">
+      <c r="Q11" s="262"/>
+    </row>
+    <row r="12" spans="1:23" customHeight="1" ht="20.25" s="245" customFormat="1">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -8607,7 +8634,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="1:23" customHeight="1" ht="26.25" s="246" customFormat="1">
+    <row r="13" spans="1:23" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <r>
@@ -8615,30 +8642,30 @@
           </r>
         </is>
       </c>
-      <c r="B13" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J13" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="L13" s="169" t="str">
+      <c r="B13" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J13" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="L13" s="168" t="str">
         <f>구매리스트!I3</f>
         <v>0</v>
       </c>
-      <c r="O13" s="246"/>
-      <c r="P13" s="264"/>
+      <c r="O13" s="245"/>
+      <c r="P13" s="263"/>
       <c r="Q13" s="5"/>
       <c r="S13" s="72"/>
     </row>
-    <row r="14" spans="1:23" customHeight="1" ht="23.25" s="246" customFormat="1">
+    <row r="14" spans="1:23" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A14" s="4"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
@@ -8646,25 +8673,21 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="5"/>
     </row>
-    <row r="15" spans="1:23" customHeight="1" ht="39" s="246" customFormat="1">
+    <row r="15" spans="1:23" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
-      <c r="J15" s="156" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="Q15" s="263"/>
-      <c r="W15" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="16" spans="1:23" customHeight="1" ht="9" s="246" customFormat="1">
+      <c r="J15" s="397" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q15" s="262"/>
+      <c r="W15" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:23" customHeight="1" ht="9" s="245" customFormat="1">
       <c r="A16" s="7"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -8683,54 +8706,54 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="9"/>
     </row>
-    <row r="17" spans="1:23" customHeight="1" ht="8.25" s="246" customFormat="1">
+    <row r="17" spans="1:23" customHeight="1" ht="8.25" s="245" customFormat="1">
       <c r="A17" s="4"/>
-      <c r="B17" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="I17" s="265"/>
-      <c r="J17" s="265"/>
-      <c r="K17" s="265"/>
-      <c r="L17" s="265"/>
-      <c r="M17" s="265"/>
-      <c r="N17" s="265"/>
+      <c r="B17" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="I17" s="264"/>
+      <c r="J17" s="264"/>
+      <c r="K17" s="264"/>
+      <c r="L17" s="264"/>
+      <c r="M17" s="264"/>
+      <c r="N17" s="264"/>
       <c r="Q17" s="5"/>
     </row>
-    <row r="18" spans="1:23" customHeight="1" ht="21.75" s="246" customFormat="1">
-      <c r="A18" s="266" t="inlineStr">
+    <row r="18" spans="1:23" customHeight="1" ht="21.75" s="245" customFormat="1">
+      <c r="A18" s="265" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1.Specifications</t>
           </r>
         </is>
       </c>
-      <c r="B18" s="255"/>
-      <c r="C18" s="255"/>
-      <c r="D18" s="255"/>
-      <c r="E18" s="255"/>
-      <c r="F18" s="255"/>
-      <c r="G18" s="255"/>
-      <c r="H18" s="255"/>
-      <c r="I18" s="255"/>
-      <c r="J18" s="256"/>
-      <c r="L18" s="267" t="inlineStr">
+      <c r="B18" s="254"/>
+      <c r="C18" s="254"/>
+      <c r="D18" s="254"/>
+      <c r="E18" s="254"/>
+      <c r="F18" s="254"/>
+      <c r="G18" s="254"/>
+      <c r="H18" s="254"/>
+      <c r="I18" s="254"/>
+      <c r="J18" s="255"/>
+      <c r="L18" s="266" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">  4. Validity period of inspection</t>
           </r>
         </is>
       </c>
-      <c r="M18" s="255"/>
-      <c r="N18" s="255"/>
-      <c r="O18" s="255"/>
-      <c r="P18" s="255"/>
-      <c r="Q18" s="256"/>
-    </row>
-    <row r="19" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+      <c r="M18" s="254"/>
+      <c r="N18" s="254"/>
+      <c r="O18" s="254"/>
+      <c r="P18" s="254"/>
+      <c r="Q18" s="255"/>
+    </row>
+    <row r="19" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A19" s="60" t="inlineStr">
         <is>
           <r>
@@ -8738,25 +8761,25 @@
           </r>
         </is>
       </c>
-      <c r="B19" s="170" t="inlineStr">
+      <c r="B19" s="169" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Specification Control Number</t>
           </r>
         </is>
       </c>
-      <c r="C19" s="251"/>
-      <c r="D19" s="251"/>
-      <c r="E19" s="251"/>
-      <c r="F19" s="268" t="str">
+      <c r="C19" s="250"/>
+      <c r="D19" s="250"/>
+      <c r="E19" s="250"/>
+      <c r="F19" s="267" t="str">
         <f>구매리스트!G5</f>
         <v>0</v>
       </c>
-      <c r="G19" s="251"/>
-      <c r="H19" s="251"/>
-      <c r="I19" s="251"/>
-      <c r="J19" s="252"/>
-      <c r="L19" s="286" t="inlineStr">
+      <c r="G19" s="250"/>
+      <c r="H19" s="250"/>
+      <c r="I19" s="250"/>
+      <c r="J19" s="251"/>
+      <c r="L19" s="285" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">    Date
@@ -8764,7 +8787,7 @@
           </r>
         </is>
       </c>
-      <c r="M19" s="286" t="inlineStr">
+      <c r="M19" s="285" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">    Date
@@ -8772,7 +8795,7 @@
           </r>
         </is>
       </c>
-      <c r="N19" s="287" t="inlineStr">
+      <c r="N19" s="286" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> Place of
@@ -8780,21 +8803,21 @@
           </r>
         </is>
       </c>
-      <c r="O19" s="288" t="inlineStr">
+      <c r="O19" s="287" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">mileage</t>
           </r>
         </is>
       </c>
-      <c r="P19" s="289" t="inlineStr">
+      <c r="P19" s="288" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> Inspect manager check</t>
           </r>
         </is>
       </c>
-      <c r="Q19" s="290" t="inlineStr">
+      <c r="Q19" s="289" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Prosecutor
@@ -8803,7 +8826,7 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="20" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A20" s="58" t="inlineStr">
         <is>
           <r>
@@ -8811,29 +8834,29 @@
           </r>
         </is>
       </c>
-      <c r="B20" s="174" t="inlineStr">
+      <c r="B20" s="173" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">(Type approval number)</t>
           </r>
         </is>
       </c>
-      <c r="C20" s="253"/>
-      <c r="D20" s="253"/>
-      <c r="E20" s="253"/>
-      <c r="F20" s="253"/>
-      <c r="G20" s="253"/>
-      <c r="H20" s="253"/>
-      <c r="I20" s="253"/>
-      <c r="J20" s="254"/>
-      <c r="L20" s="291"/>
-      <c r="M20" s="291"/>
-      <c r="N20" s="291"/>
-      <c r="O20" s="291"/>
-      <c r="P20" s="291"/>
-      <c r="Q20" s="291"/>
-    </row>
-    <row r="21" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+      <c r="C20" s="252"/>
+      <c r="D20" s="252"/>
+      <c r="E20" s="252"/>
+      <c r="F20" s="252"/>
+      <c r="G20" s="252"/>
+      <c r="H20" s="252"/>
+      <c r="I20" s="252"/>
+      <c r="J20" s="253"/>
+      <c r="L20" s="290"/>
+      <c r="M20" s="290"/>
+      <c r="N20" s="290"/>
+      <c r="O20" s="290"/>
+      <c r="P20" s="290"/>
+      <c r="Q20" s="290"/>
+    </row>
+    <row r="21" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A21" s="62" t="inlineStr">
         <is>
           <r>
@@ -8848,12 +8871,12 @@
           </r>
         </is>
       </c>
-      <c r="C21" s="256"/>
-      <c r="D21" s="157" t="str">
+      <c r="C21" s="255"/>
+      <c r="D21" s="156" t="str">
         <f>구매리스트!G7</f>
         <v>0</v>
       </c>
-      <c r="E21" s="255"/>
+      <c r="E21" s="254"/>
       <c r="F21" s="16" t="inlineStr">
         <is>
           <r>
@@ -8901,15 +8924,15 @@
       </c>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
-      <c r="R21" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="22" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+      <c r="R21" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A22" s="63" t="inlineStr">
         <is>
           <r>
@@ -8924,12 +8947,12 @@
           </r>
         </is>
       </c>
-      <c r="C22" s="256"/>
+      <c r="C22" s="255"/>
       <c r="D22" s="141" t="str">
         <f>구매리스트!G8</f>
         <v>0</v>
       </c>
-      <c r="E22" s="255"/>
+      <c r="E22" s="254"/>
       <c r="F22" s="16" t="inlineStr">
         <is>
           <r>
@@ -8968,15 +8991,15 @@
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
-      <c r="S22" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="23" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+      <c r="S22" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A23" s="63" t="inlineStr">
         <is>
           <r>
@@ -8984,19 +9007,19 @@
           </r>
         </is>
       </c>
-      <c r="B23" s="158" t="inlineStr">
+      <c r="B23" s="157" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Passenger Capacity</t>
           </r>
         </is>
       </c>
-      <c r="C23" s="256"/>
+      <c r="C23" s="255"/>
       <c r="D23" s="141" t="str">
         <f>구매리스트!G9</f>
         <v>0</v>
       </c>
-      <c r="E23" s="255"/>
+      <c r="E23" s="254"/>
       <c r="F23" s="73" t="inlineStr">
         <is>
           <r>
@@ -9035,55 +9058,55 @@
       <c r="P23" s="14"/>
       <c r="Q23" s="14"/>
     </row>
-    <row r="24" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A24" s="269" t="inlineStr">
+    <row r="24" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A24" s="268" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">⑱</t>
           </r>
         </is>
       </c>
-      <c r="B24" s="171" t="inlineStr">
+      <c r="B24" s="170" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Displacement or</t>
           </r>
         </is>
       </c>
-      <c r="C24" s="252"/>
-      <c r="D24" s="270" t="str">
+      <c r="C24" s="251"/>
+      <c r="D24" s="269" t="str">
         <f>구매리스트!G10</f>
         <v>0</v>
       </c>
-      <c r="E24" s="251"/>
-      <c r="F24" s="251"/>
-      <c r="G24" s="251"/>
-      <c r="H24" s="251"/>
-      <c r="I24" s="271" t="inlineStr">
+      <c r="E24" s="250"/>
+      <c r="F24" s="250"/>
+      <c r="G24" s="250"/>
+      <c r="H24" s="250"/>
+      <c r="I24" s="270" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">cc,(Ah ,[Ah]</t>
           </r>
         </is>
       </c>
-      <c r="J24" s="252"/>
+      <c r="J24" s="251"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
-      <c r="S24" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="25" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A25" s="272"/>
-      <c r="B25" s="292" t="inlineStr">
+      <c r="S24" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A25" s="271"/>
+      <c r="B25" s="291" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Drive battery 
@@ -9091,9 +9114,9 @@
           </r>
         </is>
       </c>
-      <c r="C25" s="263"/>
-      <c r="D25" s="272"/>
-      <c r="J25" s="263"/>
+      <c r="C25" s="262"/>
+      <c r="D25" s="271"/>
+      <c r="J25" s="262"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
@@ -9101,32 +9124,32 @@
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
     </row>
-    <row r="26" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A26" s="273"/>
-      <c r="B26" s="253"/>
-      <c r="C26" s="254"/>
-      <c r="D26" s="273"/>
-      <c r="E26" s="253"/>
-      <c r="F26" s="253"/>
-      <c r="G26" s="253"/>
-      <c r="H26" s="253"/>
-      <c r="I26" s="253"/>
-      <c r="J26" s="254"/>
+    <row r="26" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A26" s="272"/>
+      <c r="B26" s="252"/>
+      <c r="C26" s="253"/>
+      <c r="D26" s="272"/>
+      <c r="E26" s="252"/>
+      <c r="F26" s="252"/>
+      <c r="G26" s="252"/>
+      <c r="H26" s="252"/>
+      <c r="I26" s="252"/>
+      <c r="J26" s="253"/>
       <c r="L26" s="68"/>
       <c r="M26" s="68"/>
       <c r="N26" s="68"/>
       <c r="O26" s="68"/>
       <c r="P26" s="68"/>
       <c r="Q26" s="68"/>
-      <c r="S26" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="27" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+      <c r="S26" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A27" s="63" t="inlineStr">
         <is>
           <r>
@@ -9141,14 +9164,14 @@
           </r>
         </is>
       </c>
-      <c r="C27" s="256"/>
+      <c r="C27" s="255"/>
       <c r="D27" s="141" t="str">
         <f>구매리스트!G11</f>
         <v>0</v>
       </c>
-      <c r="E27" s="255"/>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
+      <c r="E27" s="254"/>
+      <c r="F27" s="254"/>
+      <c r="G27" s="254"/>
       <c r="H27" s="140" t="inlineStr">
         <is>
           <r>
@@ -9156,8 +9179,8 @@
           </r>
         </is>
       </c>
-      <c r="I27" s="255"/>
-      <c r="J27" s="256"/>
+      <c r="I27" s="254"/>
+      <c r="J27" s="255"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
       <c r="N27" s="14"/>
@@ -9165,7 +9188,7 @@
       <c r="P27" s="14"/>
       <c r="Q27" s="14"/>
     </row>
-    <row r="28" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="28" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A28" s="64" t="inlineStr">
         <is>
           <r>
@@ -9173,22 +9196,22 @@
           </r>
         </is>
       </c>
-      <c r="B28" s="172" t="inlineStr">
+      <c r="B28" s="171" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Number of Cylinders</t>
           </r>
         </is>
       </c>
-      <c r="C28" s="252"/>
-      <c r="D28" s="274" t="str">
+      <c r="C28" s="251"/>
+      <c r="D28" s="273" t="str">
         <f>구매리스트!G12</f>
         <v>0</v>
       </c>
-      <c r="E28" s="251"/>
-      <c r="F28" s="251"/>
-      <c r="G28" s="251"/>
-      <c r="H28" s="251"/>
+      <c r="E28" s="250"/>
+      <c r="F28" s="250"/>
+      <c r="G28" s="250"/>
+      <c r="H28" s="250"/>
       <c r="I28" s="139" t="inlineStr">
         <is>
           <r>
@@ -9197,7 +9220,7 @@
           </r>
         </is>
       </c>
-      <c r="J28" s="252"/>
+      <c r="J28" s="251"/>
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
       <c r="N28" s="14"/>
@@ -9205,17 +9228,17 @@
       <c r="P28" s="14"/>
       <c r="Q28" s="14"/>
     </row>
-    <row r="29" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A29" s="293" t="inlineStr">
+    <row r="29" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A29" s="292" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">(Drive Storage Voltage)</t>
           </r>
         </is>
       </c>
-      <c r="C29" s="263"/>
-      <c r="D29" s="272"/>
-      <c r="J29" s="263"/>
+      <c r="C29" s="262"/>
+      <c r="D29" s="271"/>
+      <c r="J29" s="262"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
       <c r="N29" s="14"/>
@@ -9223,23 +9246,23 @@
       <c r="P29" s="14"/>
       <c r="Q29" s="14"/>
     </row>
-    <row r="30" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A30" s="294" t="inlineStr">
+    <row r="30" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A30" s="293" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">[Maximum Fuel Cell Output]</t>
           </r>
         </is>
       </c>
-      <c r="B30" s="253"/>
-      <c r="C30" s="254"/>
-      <c r="D30" s="273"/>
-      <c r="E30" s="253"/>
-      <c r="F30" s="253"/>
-      <c r="G30" s="253"/>
-      <c r="H30" s="253"/>
-      <c r="I30" s="253"/>
-      <c r="J30" s="254"/>
+      <c r="B30" s="252"/>
+      <c r="C30" s="253"/>
+      <c r="D30" s="272"/>
+      <c r="E30" s="252"/>
+      <c r="F30" s="252"/>
+      <c r="G30" s="252"/>
+      <c r="H30" s="252"/>
+      <c r="I30" s="252"/>
+      <c r="J30" s="253"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
@@ -9247,7 +9270,7 @@
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
     </row>
-    <row r="31" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="31" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A31" s="65" t="inlineStr">
         <is>
           <r>
@@ -9255,7 +9278,7 @@
           </r>
         </is>
       </c>
-      <c r="B31" s="295" t="inlineStr">
+      <c r="B31" s="294" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Type of fuel and fuel 
@@ -9263,26 +9286,26 @@
           </r>
         </is>
       </c>
-      <c r="C31" s="256"/>
+      <c r="C31" s="255"/>
       <c r="D31" s="146" t="str">
         <f>구매리스트!I13</f>
         <v>0</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="254"/>
       <c r="F31" s="145" t="str">
         <f>구매리스트!H13</f>
         <v>0</v>
       </c>
-      <c r="G31" s="255"/>
-      <c r="H31" s="161" t="inlineStr">
+      <c r="G31" s="254"/>
+      <c r="H31" s="160" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">km/l,(km/kWh),[km/kg]</t>
           </r>
         </is>
       </c>
-      <c r="I31" s="255"/>
-      <c r="J31" s="256"/>
+      <c r="I31" s="254"/>
+      <c r="J31" s="255"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
@@ -9290,7 +9313,7 @@
       <c r="P31" s="14"/>
       <c r="Q31" s="14"/>
     </row>
-    <row r="32" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="32" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A32" s="66" t="inlineStr">
         <is>
           <r>
@@ -9298,7 +9321,7 @@
           </r>
         </is>
       </c>
-      <c r="B32" s="295" t="inlineStr">
+      <c r="B32" s="294" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Manufacturer of 
@@ -9306,16 +9329,16 @@
           </r>
         </is>
       </c>
-      <c r="C32" s="256"/>
-      <c r="D32" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="E32" s="255"/>
-      <c r="F32" s="256"/>
+      <c r="C32" s="255"/>
+      <c r="D32" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="E32" s="254"/>
+      <c r="F32" s="255"/>
       <c r="G32" s="59" t="inlineStr">
         <is>
           <r>
@@ -9330,14 +9353,14 @@
           </r>
         </is>
       </c>
-      <c r="I32" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J32" s="256"/>
+      <c r="I32" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J32" s="255"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
@@ -9345,7 +9368,7 @@
       <c r="P32" s="14"/>
       <c r="Q32" s="14"/>
     </row>
-    <row r="33" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
+    <row r="33" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A33" s="66" t="inlineStr">
         <is>
           <r>
@@ -9353,7 +9376,7 @@
           </r>
         </is>
       </c>
-      <c r="B33" s="296" t="inlineStr">
+      <c r="B33" s="295" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Main raw materials of 
@@ -9361,16 +9384,16 @@
           </r>
         </is>
       </c>
-      <c r="C33" s="256"/>
-      <c r="D33" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="E33" s="255"/>
-      <c r="F33" s="256"/>
+      <c r="C33" s="255"/>
+      <c r="D33" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="E33" s="254"/>
+      <c r="F33" s="255"/>
       <c r="G33" s="136" t="inlineStr">
         <is>
           <r>
@@ -9378,15 +9401,15 @@
           </r>
         </is>
       </c>
-      <c r="H33" s="256"/>
-      <c r="I33" s="277" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J33" s="256"/>
+      <c r="H33" s="255"/>
+      <c r="I33" s="276" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J33" s="255"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
@@ -9394,23 +9417,23 @@
       <c r="P33" s="14"/>
       <c r="Q33" s="14"/>
     </row>
-    <row r="34" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A34" s="278" t="inlineStr">
+    <row r="34" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A34" s="277" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Note: In (18)~(21), the unit used refers to () in the case of an electric vehicle and [] in the case of a hydrogen fuel electric vehicle. In the case of special vehicles in Schedule 1 2 of the Enforcement Regulations of the Motor Vehicle Management Act, the maximum load refers to the maximum vertical load allowed to connect the towed vehicle and is not related to the towing capacity, (22)~(24) applies only to vehicles equipped with drive storage batteries (excluding vehicles with structures that cannot be charged through an external electricity source).</t>
           </r>
         </is>
       </c>
-      <c r="B34" s="251"/>
-      <c r="C34" s="251"/>
-      <c r="D34" s="251"/>
-      <c r="E34" s="251"/>
-      <c r="F34" s="251"/>
-      <c r="G34" s="251"/>
-      <c r="H34" s="251"/>
-      <c r="I34" s="251"/>
-      <c r="J34" s="252"/>
+      <c r="B34" s="250"/>
+      <c r="C34" s="250"/>
+      <c r="D34" s="250"/>
+      <c r="E34" s="250"/>
+      <c r="F34" s="250"/>
+      <c r="G34" s="250"/>
+      <c r="H34" s="250"/>
+      <c r="I34" s="250"/>
+      <c r="J34" s="251"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
@@ -9418,9 +9441,9 @@
       <c r="P34" s="14"/>
       <c r="Q34" s="14"/>
     </row>
-    <row r="35" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A35" s="272"/>
-      <c r="J35" s="263"/>
+    <row r="35" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A35" s="271"/>
+      <c r="J35" s="262"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
@@ -9428,9 +9451,9 @@
       <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
     </row>
-    <row r="36" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A36" s="272"/>
-      <c r="J36" s="263"/>
+    <row r="36" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A36" s="271"/>
+      <c r="J36" s="262"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
@@ -9438,17 +9461,17 @@
       <c r="P36" s="14"/>
       <c r="Q36" s="14"/>
     </row>
-    <row r="37" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
-      <c r="A37" s="273"/>
-      <c r="B37" s="253"/>
-      <c r="C37" s="253"/>
-      <c r="D37" s="253"/>
-      <c r="E37" s="253"/>
-      <c r="F37" s="253"/>
-      <c r="G37" s="253"/>
-      <c r="H37" s="253"/>
-      <c r="I37" s="253"/>
-      <c r="J37" s="254"/>
+    <row r="37" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
+      <c r="A37" s="272"/>
+      <c r="B37" s="252"/>
+      <c r="C37" s="252"/>
+      <c r="D37" s="252"/>
+      <c r="E37" s="252"/>
+      <c r="F37" s="252"/>
+      <c r="G37" s="252"/>
+      <c r="H37" s="252"/>
+      <c r="I37" s="252"/>
+      <c r="J37" s="253"/>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
@@ -9456,47 +9479,47 @@
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
     </row>
-    <row r="38" spans="1:23" customHeight="1" ht="25.5" s="246" customFormat="1">
-      <c r="A38" s="173" t="inlineStr">
+    <row r="38" spans="1:23" customHeight="1" ht="25.5" s="245" customFormat="1">
+      <c r="A38" s="172" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2.Registration plate issued and sealed</t>
           </r>
         </is>
       </c>
-      <c r="B38" s="255"/>
-      <c r="C38" s="255"/>
-      <c r="D38" s="255"/>
-      <c r="E38" s="255"/>
-      <c r="F38" s="255"/>
-      <c r="G38" s="255"/>
-      <c r="H38" s="255"/>
-      <c r="I38" s="255"/>
-      <c r="J38" s="256"/>
-      <c r="L38" s="297" t="inlineStr">
+      <c r="B38" s="254"/>
+      <c r="C38" s="254"/>
+      <c r="D38" s="254"/>
+      <c r="E38" s="254"/>
+      <c r="F38" s="254"/>
+      <c r="G38" s="254"/>
+      <c r="H38" s="254"/>
+      <c r="I38" s="254"/>
+      <c r="J38" s="255"/>
+      <c r="L38" s="296" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">※ Note: In the first column of paragraph ㉚, write the date of new registration.</t>
           </r>
         </is>
       </c>
-      <c r="M38" s="251"/>
-      <c r="N38" s="251"/>
-      <c r="O38" s="251"/>
-      <c r="P38" s="251"/>
-      <c r="Q38" s="252"/>
-    </row>
-    <row r="39" spans="1:23" customHeight="1" ht="25.5" s="246" customFormat="1">
-      <c r="A39" s="280" t="inlineStr">
+      <c r="M38" s="250"/>
+      <c r="N38" s="250"/>
+      <c r="O38" s="250"/>
+      <c r="P38" s="250"/>
+      <c r="Q38" s="251"/>
+    </row>
+    <row r="39" spans="1:23" customHeight="1" ht="25.5" s="245" customFormat="1">
+      <c r="A39" s="279" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉕ Classification</t>
           </r>
         </is>
       </c>
-      <c r="B39" s="255"/>
-      <c r="C39" s="256"/>
-      <c r="D39" s="298" t="inlineStr">
+      <c r="B39" s="254"/>
+      <c r="C39" s="255"/>
+      <c r="D39" s="297" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> ㉖ License plate 
@@ -9504,32 +9527,32 @@
           </r>
         </is>
       </c>
-      <c r="E39" s="255"/>
-      <c r="F39" s="255"/>
-      <c r="G39" s="256"/>
-      <c r="H39" s="299" t="inlineStr">
+      <c r="E39" s="254"/>
+      <c r="F39" s="254"/>
+      <c r="G39" s="255"/>
+      <c r="H39" s="298" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉗ Confirmation of issuing agent</t>
           </r>
         </is>
       </c>
-      <c r="I39" s="255"/>
-      <c r="J39" s="256"/>
-      <c r="L39" s="300" t="inlineStr">
+      <c r="I39" s="254"/>
+      <c r="J39" s="255"/>
+      <c r="L39" s="299" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> REMARKS</t>
           </r>
         </is>
       </c>
-      <c r="M39" s="251"/>
-      <c r="N39" s="251"/>
-      <c r="O39" s="251"/>
-      <c r="P39" s="251"/>
-      <c r="Q39" s="252"/>
-    </row>
-    <row r="40" spans="1:23" customHeight="1" ht="19.5" s="246" customFormat="1">
+      <c r="M39" s="250"/>
+      <c r="N39" s="250"/>
+      <c r="O39" s="250"/>
+      <c r="P39" s="250"/>
+      <c r="Q39" s="251"/>
+    </row>
+    <row r="40" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A40" s="136" t="inlineStr">
         <is>
           <r>
@@ -9537,7 +9560,7 @@
           </r>
         </is>
       </c>
-      <c r="B40" s="256"/>
+      <c r="B40" s="255"/>
       <c r="C40" s="136" t="inlineStr">
         <is>
           <r>
@@ -9545,8 +9568,8 @@
           </r>
         </is>
       </c>
-      <c r="D40" s="255"/>
-      <c r="E40" s="256"/>
+      <c r="D40" s="254"/>
+      <c r="E40" s="255"/>
       <c r="F40" s="136" t="inlineStr">
         <is>
           <r>
@@ -9554,7 +9577,7 @@
           </r>
         </is>
       </c>
-      <c r="G40" s="256"/>
+      <c r="G40" s="255"/>
       <c r="H40" s="136" t="inlineStr">
         <is>
           <r>
@@ -9562,12 +9585,12 @@
           </r>
         </is>
       </c>
-      <c r="I40" s="255"/>
-      <c r="J40" s="256"/>
+      <c r="I40" s="254"/>
+      <c r="J40" s="255"/>
       <c r="L40" s="4"/>
       <c r="Q40" s="5"/>
     </row>
-    <row r="41" spans="1:23" customHeight="1" ht="19.5" s="246" customFormat="1">
+    <row r="41" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A41" s="136" t="inlineStr">
         <is>
           <r>
@@ -9575,7 +9598,7 @@
           </r>
         </is>
       </c>
-      <c r="B41" s="256"/>
+      <c r="B41" s="255"/>
       <c r="C41" s="136" t="inlineStr">
         <is>
           <r>
@@ -9583,8 +9606,8 @@
           </r>
         </is>
       </c>
-      <c r="D41" s="255"/>
-      <c r="E41" s="256"/>
+      <c r="D41" s="254"/>
+      <c r="E41" s="255"/>
       <c r="F41" s="136" t="inlineStr">
         <is>
           <r>
@@ -9592,7 +9615,7 @@
           </r>
         </is>
       </c>
-      <c r="G41" s="256"/>
+      <c r="G41" s="255"/>
       <c r="H41" s="136" t="inlineStr">
         <is>
           <r>
@@ -9600,10 +9623,10 @@
           </r>
         </is>
       </c>
-      <c r="I41" s="255"/>
-      <c r="J41" s="256"/>
+      <c r="I41" s="254"/>
+      <c r="J41" s="255"/>
       <c r="L41" s="4"/>
-      <c r="O41" s="246" t="inlineStr">
+      <c r="O41" s="245" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -9612,53 +9635,53 @@
       </c>
       <c r="Q41" s="5"/>
     </row>
-    <row r="42" spans="1:23" customHeight="1" ht="33" s="246" customFormat="1">
-      <c r="A42" s="298" t="inlineStr">
+    <row r="42" spans="1:23" customHeight="1" ht="33" s="245" customFormat="1">
+      <c r="A42" s="297" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3. Fact of mortgage registration (The contents of the mortgage registration are in the motor vehicle registration ledgerPlease perusal and confirm)</t>
           </r>
         </is>
       </c>
-      <c r="B42" s="255"/>
-      <c r="C42" s="255"/>
-      <c r="D42" s="255"/>
-      <c r="E42" s="255"/>
-      <c r="F42" s="255"/>
-      <c r="G42" s="255"/>
-      <c r="H42" s="255"/>
-      <c r="I42" s="255"/>
-      <c r="J42" s="256"/>
+      <c r="B42" s="254"/>
+      <c r="C42" s="254"/>
+      <c r="D42" s="254"/>
+      <c r="E42" s="254"/>
+      <c r="F42" s="254"/>
+      <c r="G42" s="254"/>
+      <c r="H42" s="254"/>
+      <c r="I42" s="254"/>
+      <c r="J42" s="255"/>
       <c r="L42" s="4"/>
       <c r="Q42" s="5"/>
     </row>
-    <row r="43" spans="1:23" customHeight="1" ht="22.5" s="246" customFormat="1">
-      <c r="A43" s="301" t="inlineStr">
+    <row r="43" spans="1:23" customHeight="1" ht="22.5" s="245" customFormat="1">
+      <c r="A43" s="300" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉘ Classification (setting or erasure)</t>
           </r>
         </is>
       </c>
-      <c r="B43" s="255"/>
-      <c r="C43" s="255"/>
-      <c r="D43" s="255"/>
-      <c r="E43" s="255"/>
-      <c r="F43" s="255"/>
-      <c r="G43" s="256"/>
-      <c r="H43" s="162" t="inlineStr">
+      <c r="B43" s="254"/>
+      <c r="C43" s="254"/>
+      <c r="D43" s="254"/>
+      <c r="E43" s="254"/>
+      <c r="F43" s="254"/>
+      <c r="G43" s="255"/>
+      <c r="H43" s="161" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">㉙ Date</t>
           </r>
         </is>
       </c>
-      <c r="I43" s="255"/>
-      <c r="J43" s="256"/>
+      <c r="I43" s="254"/>
+      <c r="J43" s="255"/>
       <c r="L43" s="4"/>
       <c r="Q43" s="5"/>
     </row>
-    <row r="44" spans="1:23" customHeight="1" ht="19.5" s="246" customFormat="1">
+    <row r="44" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A44" s="136" t="inlineStr">
         <is>
           <r>
@@ -9666,12 +9689,12 @@
           </r>
         </is>
       </c>
-      <c r="B44" s="255"/>
-      <c r="C44" s="255"/>
-      <c r="D44" s="255"/>
-      <c r="E44" s="255"/>
-      <c r="F44" s="255"/>
-      <c r="G44" s="256"/>
+      <c r="B44" s="254"/>
+      <c r="C44" s="254"/>
+      <c r="D44" s="254"/>
+      <c r="E44" s="254"/>
+      <c r="F44" s="254"/>
+      <c r="G44" s="255"/>
       <c r="H44" s="136" t="inlineStr">
         <is>
           <r>
@@ -9679,12 +9702,12 @@
           </r>
         </is>
       </c>
-      <c r="I44" s="255"/>
-      <c r="J44" s="256"/>
+      <c r="I44" s="254"/>
+      <c r="J44" s="255"/>
       <c r="L44" s="4"/>
       <c r="Q44" s="5"/>
     </row>
-    <row r="45" spans="1:23" customHeight="1" ht="19.5" s="246" customFormat="1">
+    <row r="45" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A45" s="136" t="inlineStr">
         <is>
           <r>
@@ -9692,12 +9715,12 @@
           </r>
         </is>
       </c>
-      <c r="B45" s="255"/>
-      <c r="C45" s="255"/>
-      <c r="D45" s="255"/>
-      <c r="E45" s="255"/>
-      <c r="F45" s="255"/>
-      <c r="G45" s="256"/>
+      <c r="B45" s="254"/>
+      <c r="C45" s="254"/>
+      <c r="D45" s="254"/>
+      <c r="E45" s="254"/>
+      <c r="F45" s="254"/>
+      <c r="G45" s="255"/>
       <c r="H45" s="136" t="inlineStr">
         <is>
           <r>
@@ -9705,8 +9728,8 @@
           </r>
         </is>
       </c>
-      <c r="I45" s="255"/>
-      <c r="J45" s="256"/>
+      <c r="I45" s="254"/>
+      <c r="J45" s="255"/>
       <c r="K45" s="8"/>
       <c r="L45" s="7"/>
       <c r="M45" s="8"/>
@@ -9715,16 +9738,16 @@
       <c r="P45" s="8"/>
       <c r="Q45" s="9"/>
     </row>
-    <row r="46" spans="1:23" customHeight="1" ht="6" s="246" customFormat="1"/>
-    <row r="47" spans="1:23" customHeight="1" ht="23.25" s="246" customFormat="1">
-      <c r="G47" s="163" t="inlineStr">
+    <row r="46" spans="1:23" customHeight="1" ht="6" s="245" customFormat="1"/>
+    <row r="47" spans="1:23" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="G47" s="162" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">※ Please read the 'Notes' on the back.</t>
           </r>
         </is>
       </c>
-      <c r="N47" s="164" t="inlineStr">
+      <c r="N47" s="163" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">210mm x 297mm [white or heavy paper 80g/㎡]</t>
@@ -9854,25 +9877,25 @@
   <dimension ref="A1:O56"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="6.25" customWidth="true" style="246"/>
-    <col min="2" max="2" width="14" customWidth="true" style="246"/>
-    <col min="3" max="3" width="6.25" customWidth="true" style="246"/>
-    <col min="4" max="4" width="16.875" customWidth="true" style="246"/>
-    <col min="5" max="5" width="6.375" customWidth="true" style="246"/>
-    <col min="6" max="6" width="8.125" customWidth="true" style="246"/>
-    <col min="7" max="7" width="17.625" customWidth="true" style="246"/>
-    <col min="8" max="8" width="5.875" customWidth="true" style="246"/>
-    <col min="9" max="9" width="2.125" customWidth="true" style="246"/>
-    <col min="10" max="10" width="23.625" customWidth="true" style="246"/>
-    <col min="11" max="11" width="19" customWidth="true" style="246"/>
-    <col min="12" max="12" width="3.5" customWidth="true" style="246"/>
-    <col min="13" max="13" width="2.875" customWidth="true" style="246"/>
-    <col min="14" max="14" width="8.375" customWidth="true" style="246"/>
-    <col min="15" max="15" width="5.25" customWidth="true" style="246"/>
+    <col min="1" max="1" width="6.25" customWidth="true" style="245"/>
+    <col min="2" max="2" width="14" customWidth="true" style="245"/>
+    <col min="3" max="3" width="6.25" customWidth="true" style="245"/>
+    <col min="4" max="4" width="16.875" customWidth="true" style="245"/>
+    <col min="5" max="5" width="6.375" customWidth="true" style="245"/>
+    <col min="6" max="6" width="8.125" customWidth="true" style="245"/>
+    <col min="7" max="7" width="17.625" customWidth="true" style="245"/>
+    <col min="8" max="8" width="5.875" customWidth="true" style="245"/>
+    <col min="9" max="9" width="2.125" customWidth="true" style="245"/>
+    <col min="10" max="10" width="23.625" customWidth="true" style="245"/>
+    <col min="11" max="11" width="19" customWidth="true" style="245"/>
+    <col min="12" max="12" width="3.5" customWidth="true" style="245"/>
+    <col min="13" max="13" width="2.875" customWidth="true" style="245"/>
+    <col min="14" max="14" width="8.375" customWidth="true" style="245"/>
+    <col min="15" max="15" width="5.25" customWidth="true" style="245"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" customHeight="1" ht="17.25" s="246" customFormat="1">
-      <c r="A1" s="201" t="inlineStr">
+    <row r="1" spans="1:15" customHeight="1" ht="17.25" s="245" customFormat="1">
+      <c r="A1" s="200" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">■ 자동차등록규칙 [별지 제 20호 서식] &lt;개정 2025. 1. 10.&gt;</t>
@@ -9880,8 +9903,8 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:15" customHeight="1" ht="17.25" s="246" customFormat="1">
-      <c r="A2" s="201" t="inlineStr">
+    <row r="2" spans="1:15" customHeight="1" ht="17.25" s="245" customFormat="1">
+      <c r="A2" s="200" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">■ 자동차등록규칙 [별지 제 20호 서식] &lt;개정 2025. 1. 10.&gt;</t>
@@ -9889,8 +9912,8 @@
         </is>
       </c>
     </row>
-    <row r="3" spans="1:15" customHeight="1" ht="17.25" s="246" customFormat="1">
-      <c r="A3" s="201" t="inlineStr">
+    <row r="3" spans="1:15" customHeight="1" ht="17.25" s="245" customFormat="1">
+      <c r="A3" s="200" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">     Motor vehicle Registration Rules [Annex Form 20]</t>
@@ -9898,8 +9921,8 @@
         </is>
       </c>
     </row>
-    <row r="4" spans="1:15" customHeight="1" ht="38.25" s="246" customFormat="1">
-      <c r="A4" s="197" t="inlineStr">
+    <row r="4" spans="1:15" customHeight="1" ht="38.25" s="245" customFormat="1">
+      <c r="A4" s="196" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">자동차말소등록사실증명서</t>
@@ -9907,8 +9930,8 @@
         </is>
       </c>
     </row>
-    <row r="5" spans="1:15" customHeight="1" ht="27.75" s="246" customFormat="1">
-      <c r="A5" s="204" t="inlineStr">
+    <row r="5" spans="1:15" customHeight="1" ht="27.75" s="245" customFormat="1">
+      <c r="A5" s="203" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Certificate of De-registration of Motor Vehicle</t>
@@ -9916,7 +9939,7 @@
         </is>
       </c>
     </row>
-    <row r="6" spans="1:15" customHeight="1" ht="24.95" s="246" customFormat="1">
+    <row r="6" spans="1:15" customHeight="1" ht="24.95" s="245" customFormat="1">
       <c r="A6" s="92" t="inlineStr">
         <is>
           <r>
@@ -9924,43 +9947,43 @@
           </r>
         </is>
       </c>
-      <c r="B6" s="205" t="str">
+      <c r="B6" s="204" t="str">
         <f>구매리스트!D3</f>
         <v>0</v>
       </c>
-      <c r="C6" s="255"/>
-      <c r="D6" s="255"/>
-      <c r="E6" s="255"/>
-      <c r="F6" s="206" t="inlineStr">
+      <c r="C6" s="254"/>
+      <c r="D6" s="254"/>
+      <c r="E6" s="254"/>
+      <c r="F6" s="205" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">호 (No.        )</t>
           </r>
         </is>
       </c>
-      <c r="G6" s="255"/>
+      <c r="G6" s="254"/>
       <c r="H6" s="93"/>
       <c r="I6" s="93"/>
       <c r="J6" s="93"/>
-      <c r="K6" s="198" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="L6" s="255"/>
-      <c r="M6" s="302" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="N6" s="255"/>
-      <c r="O6" s="255"/>
-    </row>
-    <row r="7" spans="1:15" customHeight="1" ht="11.25" s="246" customFormat="1">
+      <c r="K6" s="197" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="L6" s="254"/>
+      <c r="M6" s="301" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="N6" s="254"/>
+      <c r="O6" s="254"/>
+    </row>
+    <row r="7" spans="1:15" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A7" s="74"/>
       <c r="B7" s="74"/>
       <c r="C7" s="74"/>
@@ -9977,8 +10000,8 @@
       <c r="N7" s="74"/>
       <c r="O7" s="74"/>
     </row>
-    <row r="8" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="A8" s="303" t="inlineStr">
+    <row r="8" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A8" s="302" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">자동차의
@@ -9988,39 +10011,39 @@
           </r>
         </is>
       </c>
-      <c r="B8" s="304"/>
-      <c r="C8" s="207" t="inlineStr">
+      <c r="B8" s="303"/>
+      <c r="C8" s="206" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">자동차등록번호</t>
           </r>
         </is>
       </c>
-      <c r="D8" s="304"/>
-      <c r="E8" s="199" t="str">
+      <c r="D8" s="303"/>
+      <c r="E8" s="198" t="str">
         <f>구매리스트!B4</f>
         <v>0</v>
       </c>
-      <c r="F8" s="251"/>
-      <c r="G8" s="304"/>
-      <c r="H8" s="207" t="inlineStr">
+      <c r="F8" s="250"/>
+      <c r="G8" s="303"/>
+      <c r="H8" s="206" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">차종 및 주행거리</t>
           </r>
         </is>
       </c>
-      <c r="I8" s="251"/>
-      <c r="J8" s="304"/>
-      <c r="K8" s="208" t="inlineStr">
+      <c r="I8" s="250"/>
+      <c r="J8" s="303"/>
+      <c r="K8" s="207" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">승용</t>
           </r>
         </is>
       </c>
-      <c r="L8" s="251"/>
-      <c r="M8" s="251"/>
+      <c r="L8" s="250"/>
+      <c r="M8" s="250"/>
       <c r="N8" s="80" t="inlineStr">
         <is>
           <r>
@@ -10030,162 +10053,162 @@
       </c>
       <c r="O8" s="81"/>
     </row>
-    <row r="9" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B9" s="305"/>
-      <c r="C9" s="181" t="inlineStr">
+    <row r="9" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B9" s="304"/>
+      <c r="C9" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Registration No.</t>
           </r>
         </is>
       </c>
-      <c r="D9" s="305"/>
-      <c r="E9" s="306"/>
-      <c r="G9" s="305"/>
-      <c r="H9" s="181" t="inlineStr">
+      <c r="D9" s="304"/>
+      <c r="E9" s="305"/>
+      <c r="G9" s="304"/>
+      <c r="H9" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Vehicle Type and Mileage</t>
           </r>
         </is>
       </c>
-      <c r="J9" s="305"/>
-      <c r="K9" s="203" t="str">
+      <c r="J9" s="304"/>
+      <c r="K9" s="202" t="str">
         <f>구매리스트!D7</f>
         <v>0</v>
       </c>
       <c r="N9" s="82"/>
       <c r="O9" s="83"/>
     </row>
-    <row r="10" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B10" s="305"/>
-      <c r="C10" s="202" t="inlineStr">
+    <row r="10" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B10" s="304"/>
+      <c r="C10" s="201" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">차명</t>
           </r>
         </is>
       </c>
-      <c r="D10" s="307"/>
-      <c r="E10" s="308" t="str">
+      <c r="D10" s="306"/>
+      <c r="E10" s="307" t="str">
         <f>구매리스트!B5</f>
         <v>0</v>
       </c>
-      <c r="F10" s="309"/>
-      <c r="G10" s="307"/>
-      <c r="H10" s="202" t="inlineStr">
+      <c r="F10" s="308"/>
+      <c r="G10" s="306"/>
+      <c r="H10" s="201" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">차대번호</t>
           </r>
         </is>
       </c>
-      <c r="I10" s="309"/>
-      <c r="J10" s="307"/>
-      <c r="K10" s="310" t="str">
+      <c r="I10" s="308"/>
+      <c r="J10" s="306"/>
+      <c r="K10" s="309" t="str">
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="L10" s="309"/>
-      <c r="M10" s="309"/>
-      <c r="N10" s="309"/>
-      <c r="O10" s="309"/>
-    </row>
-    <row r="11" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B11" s="305"/>
-      <c r="C11" s="200" t="inlineStr">
+      <c r="L10" s="308"/>
+      <c r="M10" s="308"/>
+      <c r="N10" s="308"/>
+      <c r="O10" s="308"/>
+    </row>
+    <row r="11" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B11" s="304"/>
+      <c r="C11" s="199" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Model</t>
           </r>
         </is>
       </c>
-      <c r="D11" s="311"/>
-      <c r="E11" s="312"/>
-      <c r="F11" s="313"/>
-      <c r="G11" s="311"/>
-      <c r="H11" s="200" t="inlineStr">
+      <c r="D11" s="310"/>
+      <c r="E11" s="311"/>
+      <c r="F11" s="312"/>
+      <c r="G11" s="310"/>
+      <c r="H11" s="199" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Chassis No.</t>
           </r>
         </is>
       </c>
-      <c r="I11" s="313"/>
-      <c r="J11" s="311"/>
-      <c r="K11" s="312"/>
-      <c r="L11" s="313"/>
-      <c r="M11" s="313"/>
-      <c r="N11" s="313"/>
-      <c r="O11" s="313"/>
-    </row>
-    <row r="12" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B12" s="305"/>
-      <c r="C12" s="181" t="inlineStr">
+      <c r="I11" s="312"/>
+      <c r="J11" s="310"/>
+      <c r="K11" s="311"/>
+      <c r="L11" s="312"/>
+      <c r="M11" s="312"/>
+      <c r="N11" s="312"/>
+      <c r="O11" s="312"/>
+    </row>
+    <row r="12" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B12" s="304"/>
+      <c r="C12" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">원동기형식</t>
           </r>
         </is>
       </c>
-      <c r="D12" s="305"/>
-      <c r="E12" s="185" t="str">
+      <c r="D12" s="304"/>
+      <c r="E12" s="184" t="str">
         <f>구매리스트!I4</f>
         <v>0</v>
       </c>
-      <c r="G12" s="305"/>
-      <c r="H12" s="181" t="inlineStr">
+      <c r="G12" s="304"/>
+      <c r="H12" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">모델연도</t>
           </r>
         </is>
       </c>
-      <c r="J12" s="305"/>
-      <c r="K12" s="184" t="str">
+      <c r="J12" s="304"/>
+      <c r="K12" s="183" t="str">
         <f>구매리스트!D6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B13" s="305"/>
-      <c r="C13" s="181" t="inlineStr">
+    <row r="13" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B13" s="304"/>
+      <c r="C13" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Type of Engine</t>
           </r>
         </is>
       </c>
-      <c r="D13" s="305"/>
-      <c r="E13" s="306"/>
-      <c r="G13" s="305"/>
-      <c r="H13" s="181" t="inlineStr">
+      <c r="D13" s="304"/>
+      <c r="E13" s="305"/>
+      <c r="G13" s="304"/>
+      <c r="H13" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Model Year</t>
           </r>
         </is>
       </c>
-      <c r="J13" s="305"/>
-      <c r="K13" s="306"/>
-    </row>
-    <row r="14" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B14" s="305"/>
-      <c r="C14" s="179" t="inlineStr">
+      <c r="J13" s="304"/>
+      <c r="K13" s="305"/>
+    </row>
+    <row r="14" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B14" s="304"/>
+      <c r="C14" s="178" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">제원관리번호</t>
           </r>
         </is>
       </c>
-      <c r="D14" s="314"/>
-      <c r="E14" s="315" t="str">
+      <c r="D14" s="313"/>
+      <c r="E14" s="314" t="str">
         <f>구매리스트!G5</f>
         <v>0</v>
       </c>
-      <c r="F14" s="316"/>
-      <c r="G14" s="314"/>
-      <c r="H14" s="317" t="inlineStr">
+      <c r="F14" s="315"/>
+      <c r="G14" s="313"/>
+      <c r="H14" s="316" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">용도
@@ -10193,141 +10216,141 @@
           </r>
         </is>
       </c>
-      <c r="I14" s="316"/>
-      <c r="J14" s="314"/>
-      <c r="K14" s="318" t="inlineStr">
+      <c r="I14" s="315"/>
+      <c r="J14" s="313"/>
+      <c r="K14" s="317" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">자가용</t>
           </r>
         </is>
       </c>
-      <c r="L14" s="316"/>
-      <c r="M14" s="316"/>
-      <c r="N14" s="316"/>
-      <c r="O14" s="316"/>
-    </row>
-    <row r="15" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="B15" s="305"/>
-      <c r="C15" s="181" t="inlineStr">
+      <c r="L14" s="315"/>
+      <c r="M14" s="315"/>
+      <c r="N14" s="315"/>
+      <c r="O14" s="315"/>
+    </row>
+    <row r="15" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="B15" s="304"/>
+      <c r="C15" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Specification</t>
           </r>
         </is>
       </c>
-      <c r="D15" s="305"/>
-      <c r="E15" s="306"/>
-      <c r="G15" s="305"/>
-      <c r="H15" s="306"/>
-      <c r="J15" s="305"/>
-      <c r="K15" s="306"/>
-    </row>
-    <row r="16" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="B16" s="305"/>
-      <c r="C16" s="180" t="inlineStr">
+      <c r="D15" s="304"/>
+      <c r="E15" s="305"/>
+      <c r="G15" s="304"/>
+      <c r="H15" s="305"/>
+      <c r="J15" s="304"/>
+      <c r="K15" s="305"/>
+    </row>
+    <row r="16" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="B16" s="304"/>
+      <c r="C16" s="179" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Management no.</t>
           </r>
         </is>
       </c>
-      <c r="D16" s="319"/>
-      <c r="E16" s="320"/>
-      <c r="F16" s="321"/>
-      <c r="G16" s="319"/>
-      <c r="H16" s="320"/>
-      <c r="I16" s="321"/>
-      <c r="J16" s="319"/>
-      <c r="K16" s="320"/>
-      <c r="L16" s="321"/>
-      <c r="M16" s="321"/>
-      <c r="N16" s="321"/>
-      <c r="O16" s="321"/>
-    </row>
-    <row r="17" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
-      <c r="B17" s="305"/>
-      <c r="C17" s="181" t="inlineStr">
+      <c r="D16" s="318"/>
+      <c r="E16" s="319"/>
+      <c r="F16" s="320"/>
+      <c r="G16" s="318"/>
+      <c r="H16" s="319"/>
+      <c r="I16" s="320"/>
+      <c r="J16" s="318"/>
+      <c r="K16" s="319"/>
+      <c r="L16" s="320"/>
+      <c r="M16" s="320"/>
+      <c r="N16" s="320"/>
+      <c r="O16" s="320"/>
+    </row>
+    <row r="17" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="B17" s="304"/>
+      <c r="C17" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">최초등록일</t>
           </r>
         </is>
       </c>
-      <c r="D17" s="305"/>
-      <c r="E17" s="188" t="str">
+      <c r="D17" s="304"/>
+      <c r="E17" s="187" t="str">
         <f>구매리스트!B6</f>
         <v>0</v>
       </c>
-      <c r="G17" s="305"/>
-      <c r="H17" s="181" t="inlineStr">
+      <c r="G17" s="304"/>
+      <c r="H17" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">사업용사용기간</t>
           </r>
         </is>
       </c>
-      <c r="J17" s="305"/>
-      <c r="K17" s="210" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="18" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="B18" s="305"/>
-      <c r="C18" s="181" t="inlineStr">
+      <c r="J17" s="304"/>
+      <c r="K17" s="209" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="B18" s="304"/>
+      <c r="C18" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Dete of initial</t>
           </r>
         </is>
       </c>
-      <c r="D18" s="305"/>
-      <c r="E18" s="306"/>
-      <c r="G18" s="305"/>
-      <c r="H18" s="181" t="inlineStr">
+      <c r="D18" s="304"/>
+      <c r="E18" s="305"/>
+      <c r="G18" s="304"/>
+      <c r="H18" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Period of</t>
           </r>
         </is>
       </c>
-      <c r="J18" s="305"/>
-      <c r="K18" s="306"/>
-    </row>
-    <row r="19" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A19" s="253"/>
-      <c r="B19" s="322"/>
-      <c r="C19" s="183" t="inlineStr">
+      <c r="J18" s="304"/>
+      <c r="K18" s="305"/>
+    </row>
+    <row r="19" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A19" s="252"/>
+      <c r="B19" s="321"/>
+      <c r="C19" s="182" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Registraton</t>
           </r>
         </is>
       </c>
-      <c r="D19" s="322"/>
-      <c r="E19" s="323"/>
-      <c r="F19" s="253"/>
-      <c r="G19" s="322"/>
-      <c r="H19" s="183" t="inlineStr">
+      <c r="D19" s="321"/>
+      <c r="E19" s="322"/>
+      <c r="F19" s="252"/>
+      <c r="G19" s="321"/>
+      <c r="H19" s="182" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Business Usage</t>
           </r>
         </is>
       </c>
-      <c r="I19" s="253"/>
-      <c r="J19" s="322"/>
-      <c r="K19" s="323"/>
-      <c r="L19" s="253"/>
-      <c r="M19" s="253"/>
-      <c r="N19" s="253"/>
-      <c r="O19" s="253"/>
-    </row>
-    <row r="20" spans="1:15" customHeight="1" ht="11.25" s="246" customFormat="1">
+      <c r="I19" s="252"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="322"/>
+      <c r="L19" s="252"/>
+      <c r="M19" s="252"/>
+      <c r="N19" s="252"/>
+      <c r="O19" s="252"/>
+    </row>
+    <row r="20" spans="1:15" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A20" s="84"/>
       <c r="B20" s="84"/>
       <c r="C20" s="84"/>
@@ -10344,70 +10367,70 @@
       <c r="N20" s="84"/>
       <c r="O20" s="84"/>
     </row>
-    <row r="21" spans="1:15" customHeight="1" ht="33.75" s="246" customFormat="1">
-      <c r="A21" s="209" t="inlineStr">
+    <row r="21" spans="1:15" customHeight="1" ht="33.75" s="245" customFormat="1">
+      <c r="A21" s="208" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">소유자</t>
           </r>
         </is>
       </c>
-      <c r="B21" s="304"/>
-      <c r="C21" s="207" t="inlineStr">
+      <c r="B21" s="303"/>
+      <c r="C21" s="206" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">성명 (명칭)</t>
           </r>
         </is>
       </c>
-      <c r="D21" s="304"/>
-      <c r="E21" s="324" t="s">
-        <v>256</v>
-      </c>
-      <c r="F21" s="251"/>
-      <c r="G21" s="304"/>
-      <c r="H21" s="186" t="inlineStr">
+      <c r="D21" s="303"/>
+      <c r="E21" s="323" t="s">
+        <v>258</v>
+      </c>
+      <c r="F21" s="250"/>
+      <c r="G21" s="303"/>
+      <c r="H21" s="185" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">생년월일(법인등록번호)</t>
           </r>
         </is>
       </c>
-      <c r="I21" s="251"/>
-      <c r="J21" s="304"/>
-      <c r="K21" s="324" t="inlineStr">
+      <c r="I21" s="250"/>
+      <c r="J21" s="303"/>
+      <c r="K21" s="323" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">120111-0922270</t>
           </r>
         </is>
       </c>
-      <c r="L21" s="251"/>
-      <c r="M21" s="251"/>
-      <c r="N21" s="251"/>
-      <c r="O21" s="304"/>
-    </row>
-    <row r="22" spans="1:15" customHeight="1" ht="33.75" s="246" customFormat="1">
-      <c r="A22" s="212" t="inlineStr">
+      <c r="L21" s="250"/>
+      <c r="M21" s="250"/>
+      <c r="N21" s="250"/>
+      <c r="O21" s="303"/>
+    </row>
+    <row r="22" spans="1:15" customHeight="1" ht="33.75" s="245" customFormat="1">
+      <c r="A22" s="211" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Owner</t>
           </r>
         </is>
       </c>
-      <c r="B22" s="322"/>
-      <c r="C22" s="183" t="inlineStr">
+      <c r="B22" s="321"/>
+      <c r="C22" s="182" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Name</t>
           </r>
         </is>
       </c>
-      <c r="D22" s="322"/>
-      <c r="E22" s="323"/>
-      <c r="F22" s="253"/>
-      <c r="G22" s="322"/>
-      <c r="H22" s="187" t="inlineStr">
+      <c r="D22" s="321"/>
+      <c r="E22" s="322"/>
+      <c r="F22" s="252"/>
+      <c r="G22" s="321"/>
+      <c r="H22" s="186" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Date of birth
@@ -10415,15 +10438,15 @@
           </r>
         </is>
       </c>
-      <c r="I22" s="253"/>
-      <c r="J22" s="322"/>
-      <c r="K22" s="323"/>
-      <c r="L22" s="253"/>
-      <c r="M22" s="253"/>
-      <c r="N22" s="253"/>
-      <c r="O22" s="322"/>
-    </row>
-    <row r="23" spans="1:15" customHeight="1" ht="11.25" s="246" customFormat="1">
+      <c r="I22" s="252"/>
+      <c r="J22" s="321"/>
+      <c r="K22" s="322"/>
+      <c r="L22" s="252"/>
+      <c r="M22" s="252"/>
+      <c r="N22" s="252"/>
+      <c r="O22" s="321"/>
+    </row>
+    <row r="23" spans="1:15" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A23" s="84"/>
       <c r="B23" s="84"/>
       <c r="C23" s="84"/>
@@ -10440,98 +10463,98 @@
       <c r="N23" s="84"/>
       <c r="O23" s="84"/>
     </row>
-    <row r="24" spans="1:15" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A24" s="213" t="inlineStr">
+    <row r="24" spans="1:15" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A24" s="212" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록일</t>
           </r>
         </is>
       </c>
-      <c r="B24" s="251"/>
-      <c r="C24" s="251"/>
-      <c r="D24" s="304"/>
-      <c r="E24" s="325" t="str">
+      <c r="B24" s="250"/>
+      <c r="C24" s="250"/>
+      <c r="D24" s="303"/>
+      <c r="E24" s="324" t="str">
         <f>구매리스트!B7</f>
         <v>0</v>
       </c>
-      <c r="F24" s="251"/>
-      <c r="G24" s="304"/>
-      <c r="H24" s="207" t="inlineStr">
+      <c r="F24" s="250"/>
+      <c r="G24" s="303"/>
+      <c r="H24" s="206" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">증명서 용도</t>
           </r>
         </is>
       </c>
-      <c r="I24" s="251"/>
-      <c r="J24" s="304"/>
-      <c r="K24" s="326" t="inlineStr">
+      <c r="I24" s="250"/>
+      <c r="J24" s="303"/>
+      <c r="K24" s="325" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">증명용</t>
           </r>
         </is>
       </c>
-      <c r="L24" s="251"/>
-      <c r="M24" s="251"/>
-      <c r="N24" s="251"/>
-      <c r="O24" s="304"/>
-    </row>
-    <row r="25" spans="1:15" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A25" s="215" t="inlineStr">
+      <c r="L24" s="250"/>
+      <c r="M24" s="250"/>
+      <c r="N24" s="250"/>
+      <c r="O24" s="303"/>
+    </row>
+    <row r="25" spans="1:15" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A25" s="214" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Date of De-reglstration</t>
           </r>
         </is>
       </c>
-      <c r="B25" s="327"/>
-      <c r="C25" s="327"/>
-      <c r="D25" s="328"/>
-      <c r="E25" s="329"/>
-      <c r="F25" s="327"/>
-      <c r="G25" s="328"/>
-      <c r="H25" s="216" t="inlineStr">
+      <c r="B25" s="326"/>
+      <c r="C25" s="326"/>
+      <c r="D25" s="327"/>
+      <c r="E25" s="328"/>
+      <c r="F25" s="326"/>
+      <c r="G25" s="327"/>
+      <c r="H25" s="215" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Use of Certificate</t>
           </r>
         </is>
       </c>
-      <c r="I25" s="327"/>
-      <c r="J25" s="328"/>
-      <c r="K25" s="329"/>
-      <c r="L25" s="327"/>
-      <c r="M25" s="327"/>
-      <c r="N25" s="327"/>
-      <c r="O25" s="328"/>
-    </row>
-    <row r="26" spans="1:15" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A26" s="214" t="inlineStr">
+      <c r="I25" s="326"/>
+      <c r="J25" s="327"/>
+      <c r="K25" s="328"/>
+      <c r="L25" s="326"/>
+      <c r="M25" s="326"/>
+      <c r="N25" s="326"/>
+      <c r="O25" s="327"/>
+    </row>
+    <row r="26" spans="1:15" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A26" s="213" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록구분</t>
           </r>
         </is>
       </c>
-      <c r="D26" s="305"/>
-      <c r="E26" s="217" t="inlineStr">
+      <c r="D26" s="304"/>
+      <c r="E26" s="216" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">수출예정(수출말소)</t>
           </r>
         </is>
       </c>
-      <c r="G26" s="305"/>
-      <c r="H26" s="181" t="inlineStr">
+      <c r="G26" s="304"/>
+      <c r="H26" s="180" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">권리관계여부</t>
           </r>
         </is>
       </c>
-      <c r="J26" s="305"/>
+      <c r="J26" s="304"/>
       <c r="K26" s="94" t="inlineStr">
         <is>
           <r>
@@ -10558,29 +10581,29 @@
         </is>
       </c>
     </row>
-    <row r="27" spans="1:15" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A27" s="211" t="inlineStr">
+    <row r="27" spans="1:15" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A27" s="210" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Reason for De-registration</t>
           </r>
         </is>
       </c>
-      <c r="B27" s="253"/>
-      <c r="C27" s="253"/>
-      <c r="D27" s="322"/>
-      <c r="E27" s="323"/>
-      <c r="F27" s="253"/>
-      <c r="G27" s="322"/>
-      <c r="H27" s="183" t="inlineStr">
+      <c r="B27" s="252"/>
+      <c r="C27" s="252"/>
+      <c r="D27" s="321"/>
+      <c r="E27" s="322"/>
+      <c r="F27" s="252"/>
+      <c r="G27" s="321"/>
+      <c r="H27" s="182" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Relation of Rights</t>
           </r>
         </is>
       </c>
-      <c r="I27" s="253"/>
-      <c r="J27" s="322"/>
+      <c r="I27" s="252"/>
+      <c r="J27" s="321"/>
       <c r="K27" s="98" t="inlineStr">
         <is>
           <r>
@@ -10607,7 +10630,7 @@
         </is>
       </c>
     </row>
-    <row r="28" spans="1:15" customHeight="1" ht="11.25" s="246" customFormat="1">
+    <row r="28" spans="1:15" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A28" s="77"/>
       <c r="B28" s="77"/>
       <c r="C28" s="77"/>
@@ -10624,8 +10647,8 @@
       <c r="N28" s="77"/>
       <c r="O28" s="77"/>
     </row>
-    <row r="29" spans="1:15" customHeight="1" ht="32.25" s="246" customFormat="1">
-      <c r="A29" s="218" t="inlineStr">
+    <row r="29" spans="1:15" customHeight="1" ht="32.25" s="245" customFormat="1">
+      <c r="A29" s="217" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">「자동차관리법」제13조 및 「자동차등록규칙」제40조에 따라 말소등록 되었음을 증명합니다.</t>
@@ -10633,8 +10656,8 @@
         </is>
       </c>
     </row>
-    <row r="30" spans="1:15" customHeight="1" ht="32.25" s="246" customFormat="1">
-      <c r="A30" s="218" t="inlineStr">
+    <row r="30" spans="1:15" customHeight="1" ht="32.25" s="245" customFormat="1">
+      <c r="A30" s="217" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">  This is to certify that the above vehicle was de-registered in accordance with Article 13 of the Motor</t>
@@ -10642,8 +10665,8 @@
         </is>
       </c>
     </row>
-    <row r="31" spans="1:15" customHeight="1" ht="32.25" s="246" customFormat="1">
-      <c r="A31" s="218" t="inlineStr">
+    <row r="31" spans="1:15" customHeight="1" ht="32.25" s="245" customFormat="1">
+      <c r="A31" s="217" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Vehicle Management Act and Article 40 of the Motor Vehicle Registration Rules.</t>
@@ -10651,7 +10674,7 @@
         </is>
       </c>
     </row>
-    <row r="32" spans="1:15" customHeight="1" ht="9.75" s="246" customFormat="1">
+    <row r="32" spans="1:15" customHeight="1" ht="9.75" s="245" customFormat="1">
       <c r="A32" s="77"/>
       <c r="B32" s="77"/>
       <c r="C32" s="77"/>
@@ -10668,7 +10691,7 @@
       <c r="N32" s="77"/>
       <c r="O32" s="77"/>
     </row>
-    <row r="33" spans="1:15" customHeight="1" ht="35.25" s="246" customFormat="1">
+    <row r="33" spans="1:15" customHeight="1" ht="35.25" s="245" customFormat="1">
       <c r="A33" s="77" t="inlineStr">
         <is>
           <r>
@@ -10687,27 +10710,29 @@
       <c r="D33" s="77"/>
       <c r="E33" s="77"/>
       <c r="F33" s="77"/>
-      <c r="G33" s="191" t="inlineStr">
+      <c r="G33" s="190" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">발행 연월일 Date of Issue :</t>
           </r>
         </is>
       </c>
-      <c r="K33" s="219" t="str">
+      <c r="K33" s="218" t="str">
         <f>E24</f>
         <v>0</v>
       </c>
       <c r="O33" s="77"/>
     </row>
-    <row r="34" spans="1:15" customHeight="1" ht="85.5" s="246" customFormat="1">
+    <row r="34" spans="1:15" customHeight="1" ht="85.5" s="245" customFormat="1">
       <c r="A34" s="77"/>
       <c r="B34" s="77"/>
       <c r="C34" s="77"/>
       <c r="D34" s="77"/>
       <c r="E34" s="77"/>
       <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
+      <c r="G34" s="398" t="s">
+        <v>104</v>
+      </c>
       <c r="H34" s="77"/>
       <c r="I34" s="77"/>
       <c r="J34" s="77"/>
@@ -10717,8 +10742,8 @@
       <c r="N34" s="78"/>
       <c r="O34" s="77"/>
     </row>
-    <row r="35" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A35" s="191" t="inlineStr">
+    <row r="35" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A35" s="190" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Speial Metropolitan City Mayor ' Metropolitan City Mayor'</t>
@@ -10728,8 +10753,8 @@
       <c r="N35" s="77"/>
       <c r="O35" s="77"/>
     </row>
-    <row r="36" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A36" s="191" t="inlineStr">
+    <row r="36" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A36" s="190" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Special Self-Governing City Mayor ' Do Governor ' Special Self-Governign Province Governor</t>
@@ -10739,8 +10764,8 @@
       <c r="N36" s="78"/>
       <c r="O36" s="77"/>
     </row>
-    <row r="37" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A37" s="191" t="inlineStr">
+    <row r="37" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A37" s="190" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">(The Head of a Si / Gun / Gu</t>
@@ -10750,54 +10775,54 @@
       <c r="N37" s="86"/>
       <c r="O37" s="87"/>
     </row>
-    <row r="38" spans="1:15" customHeight="1" ht="24.95" s="246" customFormat="1">
-      <c r="A38" s="220" t="inlineStr">
+    <row r="38" spans="1:15" customHeight="1" ht="24.95" s="245" customFormat="1">
+      <c r="A38" s="219" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">유의사항</t>
           </r>
         </is>
       </c>
-      <c r="B38" s="330"/>
-      <c r="C38" s="330"/>
-      <c r="D38" s="330"/>
-      <c r="E38" s="330"/>
-      <c r="F38" s="330"/>
-      <c r="G38" s="330"/>
-      <c r="H38" s="330"/>
-      <c r="I38" s="330"/>
-      <c r="J38" s="330"/>
-      <c r="K38" s="330"/>
-      <c r="L38" s="330"/>
-      <c r="M38" s="330"/>
-      <c r="N38" s="330"/>
-      <c r="O38" s="330"/>
-    </row>
-    <row r="39" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A39" s="221" t="inlineStr">
+      <c r="B38" s="329"/>
+      <c r="C38" s="329"/>
+      <c r="D38" s="329"/>
+      <c r="E38" s="329"/>
+      <c r="F38" s="329"/>
+      <c r="G38" s="329"/>
+      <c r="H38" s="329"/>
+      <c r="I38" s="329"/>
+      <c r="J38" s="329"/>
+      <c r="K38" s="329"/>
+      <c r="L38" s="329"/>
+      <c r="M38" s="329"/>
+      <c r="N38" s="329"/>
+      <c r="O38" s="329"/>
+    </row>
+    <row r="39" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A39" s="220" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1. 말소등록된 자동차를 다시 등록하여 사용하려는 경우에는 「자동차등록령」 제20조 및 아래 표의 구분에 따른 기간에 신규등록을 신청해야 하며,그 </t>
           </r>
         </is>
       </c>
-      <c r="B39" s="331"/>
-      <c r="C39" s="331"/>
-      <c r="D39" s="331"/>
-      <c r="E39" s="331"/>
-      <c r="F39" s="331"/>
-      <c r="G39" s="331"/>
-      <c r="H39" s="331"/>
-      <c r="I39" s="331"/>
-      <c r="J39" s="331"/>
-      <c r="K39" s="331"/>
-      <c r="L39" s="331"/>
-      <c r="M39" s="331"/>
-      <c r="N39" s="331"/>
-      <c r="O39" s="331"/>
-    </row>
-    <row r="40" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A40" s="192" t="inlineStr">
+      <c r="B39" s="330"/>
+      <c r="C39" s="330"/>
+      <c r="D39" s="330"/>
+      <c r="E39" s="330"/>
+      <c r="F39" s="330"/>
+      <c r="G39" s="330"/>
+      <c r="H39" s="330"/>
+      <c r="I39" s="330"/>
+      <c r="J39" s="330"/>
+      <c r="K39" s="330"/>
+      <c r="L39" s="330"/>
+      <c r="M39" s="330"/>
+      <c r="N39" s="330"/>
+      <c r="O39" s="330"/>
+    </row>
+    <row r="40" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A40" s="191" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">    신청기간을 경과한 때에는 「자동차관리법」제84조제4항제7호에 따라 100만원 이하의 과태료를 납부해야 합니다. </t>
@@ -10805,8 +10830,8 @@
         </is>
       </c>
     </row>
-    <row r="41" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A41" s="192" t="inlineStr">
+    <row r="41" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A41" s="191" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2. 말소등록 당시에 압류 및 저당권 등이 등록된 자동차는 「자동차관리법」제13조제10항 후단에 따라 해당 관리관계가 소멸되었음을 「자동차등록규칙」</t>
@@ -10814,8 +10839,8 @@
         </is>
       </c>
     </row>
-    <row r="42" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A42" s="192" t="inlineStr">
+    <row r="42" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A42" s="191" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">    제27조제3항에 따라 증명한 경우에만 신규등록을 신청할 수 있습니다. </t>
@@ -10823,36 +10848,36 @@
         </is>
       </c>
     </row>
-    <row r="43" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A43" s="222" t="inlineStr">
+    <row r="43" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A43" s="221" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록 사유</t>
           </r>
         </is>
       </c>
-      <c r="B43" s="332"/>
-      <c r="C43" s="332"/>
-      <c r="D43" s="332"/>
-      <c r="E43" s="332"/>
-      <c r="F43" s="332"/>
-      <c r="G43" s="332"/>
-      <c r="H43" s="332"/>
-      <c r="I43" s="332"/>
-      <c r="J43" s="333"/>
-      <c r="K43" s="223" t="inlineStr">
+      <c r="B43" s="331"/>
+      <c r="C43" s="331"/>
+      <c r="D43" s="331"/>
+      <c r="E43" s="331"/>
+      <c r="F43" s="331"/>
+      <c r="G43" s="331"/>
+      <c r="H43" s="331"/>
+      <c r="I43" s="331"/>
+      <c r="J43" s="332"/>
+      <c r="K43" s="222" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">신규등록 신청 기간</t>
           </r>
         </is>
       </c>
-      <c r="L43" s="332"/>
-      <c r="M43" s="332"/>
-      <c r="N43" s="332"/>
-      <c r="O43" s="333"/>
-    </row>
-    <row r="44" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
+      <c r="L43" s="331"/>
+      <c r="M43" s="331"/>
+      <c r="N43" s="331"/>
+      <c r="O43" s="332"/>
+    </row>
+    <row r="44" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A44" s="76" t="inlineStr">
         <is>
           <r>
@@ -10869,19 +10894,19 @@
       <c r="H44" s="76"/>
       <c r="I44" s="76"/>
       <c r="J44" s="76"/>
-      <c r="K44" s="182" t="inlineStr">
+      <c r="K44" s="181" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록일부터 3개월 이내</t>
           </r>
         </is>
       </c>
-      <c r="L44" s="309"/>
-      <c r="M44" s="309"/>
-      <c r="N44" s="309"/>
-      <c r="O44" s="334"/>
-    </row>
-    <row r="45" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
+      <c r="L44" s="308"/>
+      <c r="M44" s="308"/>
+      <c r="N44" s="308"/>
+      <c r="O44" s="333"/>
+    </row>
+    <row r="45" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A45" s="76" t="inlineStr">
         <is>
           <r>
@@ -10898,163 +10923,163 @@
       <c r="H45" s="76"/>
       <c r="I45" s="76"/>
       <c r="J45" s="76"/>
-      <c r="K45" s="335"/>
-      <c r="O45" s="336"/>
-    </row>
-    <row r="46" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A46" s="224" t="inlineStr">
+      <c r="K45" s="334"/>
+      <c r="O45" s="335"/>
+    </row>
+    <row r="46" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A46" s="223" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2. 자동차를 교육,연구의 목적으로 사용하는 등 「자동차등록령」제31조제5항에 해당하는 사유로 말소등록된 경우</t>
           </r>
         </is>
       </c>
-      <c r="K46" s="335"/>
-      <c r="O46" s="336"/>
-    </row>
-    <row r="47" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A47" s="192" t="inlineStr">
+      <c r="K46" s="334"/>
+      <c r="O46" s="335"/>
+    </row>
+    <row r="47" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A47" s="191" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3. 자동차의 차대[차대가 없는 자동차의 경우에는 차체(車體)를 말합니다. 이하 이 호에서 같습니다]가 등록원부상의</t>
           </r>
         </is>
       </c>
-      <c r="K47" s="335"/>
-      <c r="O47" s="336"/>
-    </row>
-    <row r="48" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A48" s="192" t="inlineStr">
+      <c r="K47" s="334"/>
+      <c r="O47" s="335"/>
+    </row>
+    <row r="48" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A48" s="191" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">    차대와 달라 직권으로 말소등록된 경우</t>
           </r>
         </is>
       </c>
-      <c r="K48" s="335"/>
-      <c r="O48" s="336"/>
-    </row>
-    <row r="49" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A49" s="192" t="inlineStr">
+      <c r="K48" s="334"/>
+      <c r="O48" s="335"/>
+    </row>
+    <row r="49" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A49" s="191" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">4. 속임수나 그밖의 부정한 방법으로 등록되어 직권으로 말소등록된경우</t>
           </r>
         </is>
       </c>
-      <c r="B49" s="246"/>
-      <c r="K49" s="335"/>
-      <c r="O49" s="336"/>
-    </row>
-    <row r="50" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A50" s="196" t="inlineStr">
+      <c r="B49" s="245"/>
+      <c r="K49" s="334"/>
+      <c r="O49" s="335"/>
+    </row>
+    <row r="50" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A50" s="195" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">5. 자동차를 제작.조립 또는 수입하는 자(이들로부터 자동차의 판매위탁을 받은 자를 포함합니다)에게 반품(「자동차</t>
           </r>
         </is>
       </c>
-      <c r="B50" s="309"/>
-      <c r="C50" s="309"/>
-      <c r="D50" s="309"/>
-      <c r="E50" s="309"/>
-      <c r="F50" s="309"/>
-      <c r="G50" s="309"/>
-      <c r="H50" s="309"/>
-      <c r="I50" s="309"/>
-      <c r="J50" s="309"/>
-      <c r="K50" s="337" t="inlineStr">
+      <c r="B50" s="308"/>
+      <c r="C50" s="308"/>
+      <c r="D50" s="308"/>
+      <c r="E50" s="308"/>
+      <c r="F50" s="308"/>
+      <c r="G50" s="308"/>
+      <c r="H50" s="308"/>
+      <c r="I50" s="308"/>
+      <c r="J50" s="308"/>
+      <c r="K50" s="336" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록일부터 6개월 이내</t>
           </r>
         </is>
       </c>
-      <c r="L50" s="309"/>
-      <c r="M50" s="309"/>
-      <c r="N50" s="309"/>
-      <c r="O50" s="334"/>
-    </row>
-    <row r="51" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A51" s="193" t="inlineStr">
+      <c r="L50" s="308"/>
+      <c r="M50" s="308"/>
+      <c r="N50" s="308"/>
+      <c r="O50" s="333"/>
+    </row>
+    <row r="51" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A51" s="192" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">     관리법」제47조의2의 교환 또는 환불 요구에 따라 반품된 경우를 포함합니다)하여 말소등록된 경우</t>
           </r>
         </is>
       </c>
-      <c r="B51" s="313"/>
-      <c r="C51" s="313"/>
-      <c r="D51" s="313"/>
-      <c r="E51" s="313"/>
-      <c r="F51" s="313"/>
-      <c r="G51" s="313"/>
-      <c r="H51" s="313"/>
-      <c r="I51" s="313"/>
-      <c r="J51" s="313"/>
-      <c r="K51" s="338"/>
-      <c r="L51" s="313"/>
-      <c r="M51" s="313"/>
-      <c r="N51" s="313"/>
-      <c r="O51" s="339"/>
-    </row>
-    <row r="52" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A52" s="194" t="inlineStr">
+      <c r="B51" s="312"/>
+      <c r="C51" s="312"/>
+      <c r="D51" s="312"/>
+      <c r="E51" s="312"/>
+      <c r="F51" s="312"/>
+      <c r="G51" s="312"/>
+      <c r="H51" s="312"/>
+      <c r="I51" s="312"/>
+      <c r="J51" s="312"/>
+      <c r="K51" s="337"/>
+      <c r="L51" s="312"/>
+      <c r="M51" s="312"/>
+      <c r="N51" s="312"/>
+      <c r="O51" s="338"/>
+    </row>
+    <row r="52" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A52" s="193" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">6. 수출로 말소등록된 경우</t>
           </r>
         </is>
       </c>
-      <c r="B52" s="340"/>
-      <c r="C52" s="340"/>
-      <c r="D52" s="340"/>
-      <c r="E52" s="340"/>
-      <c r="F52" s="340"/>
-      <c r="G52" s="340"/>
-      <c r="H52" s="340"/>
-      <c r="I52" s="340"/>
-      <c r="J52" s="340"/>
-      <c r="K52" s="195" t="inlineStr">
+      <c r="B52" s="339"/>
+      <c r="C52" s="339"/>
+      <c r="D52" s="339"/>
+      <c r="E52" s="339"/>
+      <c r="F52" s="339"/>
+      <c r="G52" s="339"/>
+      <c r="H52" s="339"/>
+      <c r="I52" s="339"/>
+      <c r="J52" s="339"/>
+      <c r="K52" s="194" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록일부터 1년 이내</t>
           </r>
         </is>
       </c>
-      <c r="L52" s="340"/>
-      <c r="M52" s="340"/>
-      <c r="N52" s="340"/>
-      <c r="O52" s="341"/>
-    </row>
-    <row r="53" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
-      <c r="A53" s="190" t="inlineStr">
+      <c r="L52" s="339"/>
+      <c r="M52" s="339"/>
+      <c r="N52" s="339"/>
+      <c r="O52" s="340"/>
+    </row>
+    <row r="53" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
+      <c r="A53" s="189" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">7. 도난,횡령 또는 편취 당하여 말소등록된 경우</t>
           </r>
         </is>
       </c>
-      <c r="B53" s="253"/>
-      <c r="C53" s="253"/>
-      <c r="D53" s="253"/>
-      <c r="E53" s="253"/>
-      <c r="F53" s="253"/>
-      <c r="G53" s="253"/>
-      <c r="H53" s="253"/>
-      <c r="I53" s="253"/>
-      <c r="J53" s="342"/>
-      <c r="K53" s="189" t="inlineStr">
+      <c r="B53" s="252"/>
+      <c r="C53" s="252"/>
+      <c r="D53" s="252"/>
+      <c r="E53" s="252"/>
+      <c r="F53" s="252"/>
+      <c r="G53" s="252"/>
+      <c r="H53" s="252"/>
+      <c r="I53" s="252"/>
+      <c r="J53" s="341"/>
+      <c r="K53" s="188" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">해당 자동차를 회수한 날부터 3개월 이내</t>
           </r>
         </is>
       </c>
-      <c r="L53" s="253"/>
-      <c r="M53" s="253"/>
-      <c r="N53" s="253"/>
-      <c r="O53" s="253"/>
+      <c r="L53" s="252"/>
+      <c r="M53" s="252"/>
+      <c r="N53" s="252"/>
+      <c r="O53" s="252"/>
     </row>
     <row r="54" spans="1:15" customHeight="1" ht="20.25" s="89" customFormat="1">
       <c r="A54" s="88" t="inlineStr">
@@ -11089,7 +11114,7 @@
       </c>
     </row>
     <row r="56" spans="1:15">
-      <c r="A56" s="246"/>
+      <c r="A56" s="245"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -11182,6 +11207,7 @@
     <mergeCell ref="K50:O51"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="H25:J25"/>
+    <mergeCell ref="G34:K34"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.31496062992126" right="0.23622047244094" top="0.45" bottom="0.51181102362205" header="0.31496062992126" footer="0.31496062992126"/>
@@ -11209,68 +11235,68 @@
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="4.25" customWidth="true" style="246"/>
-    <col min="2" max="2" width="21.625" customWidth="true" style="246"/>
-    <col min="3" max="3" width="7.5" customWidth="true" style="246"/>
-    <col min="4" max="4" width="23.625" customWidth="true" style="246"/>
-    <col min="5" max="5" width="7.75" customWidth="true" style="246"/>
-    <col min="6" max="6" width="2.125" customWidth="true" style="246"/>
-    <col min="7" max="7" width="12.25" customWidth="true" style="246"/>
-    <col min="8" max="8" width="13.75" customWidth="true" style="246"/>
-    <col min="9" max="9" width="13.25" customWidth="true" style="246"/>
+    <col min="1" max="1" width="4.25" customWidth="true" style="245"/>
+    <col min="2" max="2" width="21.625" customWidth="true" style="245"/>
+    <col min="3" max="3" width="7.5" customWidth="true" style="245"/>
+    <col min="4" max="4" width="23.625" customWidth="true" style="245"/>
+    <col min="5" max="5" width="7.75" customWidth="true" style="245"/>
+    <col min="6" max="6" width="2.125" customWidth="true" style="245"/>
+    <col min="7" max="7" width="12.25" customWidth="true" style="245"/>
+    <col min="8" max="8" width="13.75" customWidth="true" style="245"/>
+    <col min="9" max="9" width="13.25" customWidth="true" style="245"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customHeight="1" ht="47.25" s="246" customFormat="1">
-      <c r="A1" s="343" t="inlineStr">
+    <row r="1" spans="1:10" customHeight="1" ht="47.25" s="245" customFormat="1">
+      <c r="A1" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">COMMERCIAL INVOICE</t>
           </r>
         </is>
       </c>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="255"/>
-      <c r="F1" s="255"/>
-      <c r="G1" s="255"/>
-      <c r="H1" s="255"/>
-      <c r="I1" s="256"/>
-    </row>
-    <row r="2" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A2" s="344" t="inlineStr">
+      <c r="B1" s="254"/>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
+      <c r="E1" s="254"/>
+      <c r="F1" s="254"/>
+      <c r="G1" s="254"/>
+      <c r="H1" s="254"/>
+      <c r="I1" s="255"/>
+    </row>
+    <row r="2" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A2" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1) Shipper / Exporter</t>
           </r>
         </is>
       </c>
-      <c r="B2" s="251"/>
-      <c r="C2" s="251"/>
-      <c r="D2" s="252"/>
-      <c r="E2" s="225" t="inlineStr">
+      <c r="B2" s="250"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="251"/>
+      <c r="E2" s="224" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Reference No.      DFSU6646075</t>
           </r>
         </is>
       </c>
-      <c r="F2" s="251"/>
+      <c r="F2" s="250"/>
       <c r="G2" s="128" t="str">
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
-      <c r="H2" s="345" t="inlineStr">
+      <c r="H2" s="344" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">ORIGINAL</t>
           </r>
         </is>
       </c>
-      <c r="I2" s="252"/>
-    </row>
-    <row r="3" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A3" s="346" t="inlineStr">
+      <c r="I2" s="251"/>
+    </row>
+    <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A3" s="345" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SSANCAR LTD.,
@@ -11281,8 +11307,8 @@
           </r>
         </is>
       </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="229" t="inlineStr">
+      <c r="D3" s="262"/>
+      <c r="E3" s="228" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Reference code.   DFSU6646075</t>
@@ -11293,122 +11319,122 @@
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
-      <c r="H3" s="273"/>
-      <c r="I3" s="254"/>
-    </row>
-    <row r="4" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A4" s="272"/>
-      <c r="D4" s="263"/>
-      <c r="E4" s="347" t="inlineStr">
+      <c r="H3" s="272"/>
+      <c r="I3" s="253"/>
+    </row>
+    <row r="4" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A4" s="271"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">CERTIFICATE OF ORIGIN</t>
           </r>
         </is>
       </c>
-      <c r="I4" s="263"/>
-    </row>
-    <row r="5" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A5" s="272"/>
-      <c r="D5" s="263"/>
-      <c r="E5" s="272"/>
-      <c r="I5" s="263"/>
-    </row>
-    <row r="6" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A6" s="272"/>
-      <c r="D6" s="263"/>
-      <c r="E6" s="348" t="inlineStr">
+      <c r="I4" s="262"/>
+    </row>
+    <row r="5" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A5" s="271"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="271"/>
+      <c r="I5" s="262"/>
+    </row>
+    <row r="6" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A6" s="271"/>
+      <c r="D6" s="262"/>
+      <c r="E6" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Issued by</t>
           </r>
         </is>
       </c>
-      <c r="I6" s="263"/>
-    </row>
-    <row r="7" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A7" s="273"/>
-      <c r="B7" s="253"/>
-      <c r="C7" s="253"/>
-      <c r="D7" s="254"/>
-      <c r="E7" s="348" t="inlineStr">
+      <c r="I6" s="262"/>
+    </row>
+    <row r="7" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A7" s="272"/>
+      <c r="B7" s="252"/>
+      <c r="C7" s="252"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">THE KOREA CHAMBER OF COMMERCE &amp; INDUSTRY</t>
           </r>
         </is>
       </c>
-      <c r="I7" s="263"/>
-    </row>
-    <row r="8" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A8" s="344" t="inlineStr">
+      <c r="I7" s="262"/>
+    </row>
+    <row r="8" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A8" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2) For account &amp; risk of Messers.</t>
           </r>
         </is>
       </c>
-      <c r="B8" s="251"/>
-      <c r="C8" s="251"/>
-      <c r="D8" s="252"/>
-      <c r="E8" s="349" t="inlineStr">
+      <c r="B8" s="250"/>
+      <c r="C8" s="250"/>
+      <c r="D8" s="251"/>
+      <c r="E8" s="348" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Seoul, Republic of korea</t>
           </r>
         </is>
       </c>
-      <c r="F8" s="253"/>
-      <c r="G8" s="253"/>
-      <c r="H8" s="253"/>
-      <c r="I8" s="254"/>
-    </row>
-    <row r="9" spans="1:10" customHeight="1" ht="65.25" s="246" customFormat="1">
-      <c r="A9" s="350" t="str">
+      <c r="F8" s="252"/>
+      <c r="G8" s="252"/>
+      <c r="H8" s="252"/>
+      <c r="I8" s="253"/>
+    </row>
+    <row r="9" spans="1:10" customHeight="1" ht="65.25" s="245" customFormat="1">
+      <c r="A9" s="349" t="str">
         <f>구매리스트!B14</f>
         <v>0</v>
       </c>
-      <c r="D9" s="263"/>
-      <c r="E9" s="235" t="inlineStr">
+      <c r="D9" s="262"/>
+      <c r="E9" s="234" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> *Remark</t>
           </r>
         </is>
       </c>
-      <c r="F9" s="251"/>
-      <c r="G9" s="251"/>
-      <c r="H9" s="251"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="10" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A10" s="272"/>
-      <c r="D10" s="263"/>
-      <c r="E10" s="226" t="inlineStr">
+      <c r="F9" s="250"/>
+      <c r="G9" s="250"/>
+      <c r="H9" s="250"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A10" s="271"/>
+      <c r="D10" s="262"/>
+      <c r="E10" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">8) No. &amp; date of invoice</t>
           </r>
         </is>
       </c>
-      <c r="F10" s="251"/>
-      <c r="G10" s="251"/>
-      <c r="H10" s="251"/>
-      <c r="I10" s="252"/>
-    </row>
-    <row r="11" spans="1:10" customHeight="1" ht="35.25" s="246" customFormat="1">
-      <c r="A11" s="273"/>
-      <c r="B11" s="253"/>
-      <c r="C11" s="253"/>
-      <c r="D11" s="254"/>
-      <c r="E11" s="227" t="str">
+      <c r="F10" s="250"/>
+      <c r="G10" s="250"/>
+      <c r="H10" s="250"/>
+      <c r="I10" s="251"/>
+    </row>
+    <row r="11" spans="1:10" customHeight="1" ht="35.25" s="245" customFormat="1">
+      <c r="A11" s="272"/>
+      <c r="B11" s="252"/>
+      <c r="C11" s="252"/>
+      <c r="D11" s="253"/>
+      <c r="E11" s="226" t="str">
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
@@ -11417,151 +11443,151 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A12" s="344" t="inlineStr">
+    <row r="12" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A12" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3) Notify party</t>
           </r>
         </is>
       </c>
-      <c r="B12" s="251"/>
-      <c r="C12" s="251"/>
-      <c r="D12" s="252"/>
-      <c r="E12" s="344" t="inlineStr">
+      <c r="B12" s="250"/>
+      <c r="C12" s="250"/>
+      <c r="D12" s="251"/>
+      <c r="E12" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">9) No. &amp; date of L/C</t>
           </r>
         </is>
       </c>
-      <c r="F12" s="251"/>
-      <c r="G12" s="251"/>
-      <c r="H12" s="251"/>
-      <c r="I12" s="252"/>
-    </row>
-    <row r="13" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A13" s="351" t="inlineStr">
+      <c r="F12" s="250"/>
+      <c r="G12" s="250"/>
+      <c r="H12" s="250"/>
+      <c r="I12" s="251"/>
+    </row>
+    <row r="13" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A13" s="350" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SAME AS ABOVE</t>
           </r>
         </is>
       </c>
-      <c r="D13" s="263"/>
-      <c r="E13" s="230" t="inlineStr">
+      <c r="D13" s="262"/>
+      <c r="E13" s="229" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">TTR BASE</t>
           </r>
         </is>
       </c>
-      <c r="I13" s="263"/>
-    </row>
-    <row r="14" spans="1:10" customHeight="1" ht="9.75" s="246" customFormat="1">
-      <c r="A14" s="273"/>
-      <c r="B14" s="253"/>
-      <c r="C14" s="253"/>
-      <c r="D14" s="254"/>
-      <c r="E14" s="253"/>
-      <c r="F14" s="253"/>
-      <c r="G14" s="253"/>
-      <c r="H14" s="253"/>
-      <c r="I14" s="254"/>
-    </row>
-    <row r="15" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
-      <c r="A15" s="344" t="inlineStr">
+      <c r="I13" s="262"/>
+    </row>
+    <row r="14" spans="1:10" customHeight="1" ht="9.75" s="245" customFormat="1">
+      <c r="A14" s="272"/>
+      <c r="B14" s="252"/>
+      <c r="C14" s="252"/>
+      <c r="D14" s="253"/>
+      <c r="E14" s="252"/>
+      <c r="F14" s="252"/>
+      <c r="G14" s="252"/>
+      <c r="H14" s="252"/>
+      <c r="I14" s="253"/>
+    </row>
+    <row r="15" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
+      <c r="A15" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">4) Port of loading</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="252"/>
-      <c r="C15" s="226" t="inlineStr">
+      <c r="B15" s="251"/>
+      <c r="C15" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">5) Final Destination</t>
           </r>
         </is>
       </c>
-      <c r="D15" s="252"/>
-      <c r="E15" s="226" t="inlineStr">
+      <c r="D15" s="251"/>
+      <c r="E15" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">10) L/C issuing bank</t>
           </r>
         </is>
       </c>
-      <c r="F15" s="251"/>
-      <c r="G15" s="251"/>
-      <c r="H15" s="251"/>
-      <c r="I15" s="252"/>
-    </row>
-    <row r="16" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A16" s="232" t="str">
+      <c r="F15" s="250"/>
+      <c r="G15" s="250"/>
+      <c r="H15" s="250"/>
+      <c r="I15" s="251"/>
+    </row>
+    <row r="16" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A16" s="231" t="str">
         <f>구매리스트!B10</f>
         <v>0</v>
       </c>
-      <c r="B16" s="253"/>
-      <c r="C16" s="352" t="str">
+      <c r="B16" s="252"/>
+      <c r="C16" s="351" t="str">
         <f>구매리스트!D10</f>
         <v>0</v>
       </c>
-      <c r="D16" s="254"/>
-      <c r="E16" s="353" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="I16" s="263"/>
-    </row>
-    <row r="17" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
-      <c r="A17" s="344" t="inlineStr">
+      <c r="D16" s="253"/>
+      <c r="E16" s="352" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="I16" s="262"/>
+    </row>
+    <row r="17" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
+      <c r="A17" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">6) Vessel name</t>
           </r>
         </is>
       </c>
-      <c r="B17" s="252"/>
-      <c r="C17" s="226" t="inlineStr">
+      <c r="B17" s="251"/>
+      <c r="C17" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">7) Sailing on or about</t>
           </r>
         </is>
       </c>
-      <c r="D17" s="252"/>
-      <c r="E17" s="354" t="str">
+      <c r="D17" s="251"/>
+      <c r="E17" s="353" t="str">
         <f>구매리스트!D12</f>
         <v>0</v>
       </c>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="252"/>
-    </row>
-    <row r="18" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A18" s="352" t="str">
+      <c r="F17" s="250"/>
+      <c r="G17" s="250"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="251"/>
+    </row>
+    <row r="18" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A18" s="351" t="str">
         <f>구매리스트!B11</f>
         <v>0</v>
       </c>
-      <c r="B18" s="254"/>
-      <c r="C18" s="355" t="str">
+      <c r="B18" s="253"/>
+      <c r="C18" s="354" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
-      <c r="D18" s="254"/>
-      <c r="E18" s="273"/>
-      <c r="F18" s="253"/>
-      <c r="G18" s="253"/>
-      <c r="H18" s="253"/>
-      <c r="I18" s="254"/>
-    </row>
-    <row r="19" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
+      <c r="D18" s="253"/>
+      <c r="E18" s="272"/>
+      <c r="F18" s="252"/>
+      <c r="G18" s="252"/>
+      <c r="H18" s="252"/>
+      <c r="I18" s="253"/>
+    </row>
+    <row r="19" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A19" s="22" t="inlineStr">
         <is>
           <r>
@@ -11578,14 +11604,14 @@
         </is>
       </c>
       <c r="D19" s="26"/>
-      <c r="E19" s="356" t="inlineStr">
+      <c r="E19" s="355" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">13) Quantity</t>
           </r>
         </is>
       </c>
-      <c r="F19" s="256"/>
+      <c r="F19" s="255"/>
       <c r="G19" s="22" t="inlineStr">
         <is>
           <r>
@@ -11608,7 +11634,7 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:10" customHeight="1" ht="10.5" s="246" customFormat="1">
+    <row r="20" spans="1:10" customHeight="1" ht="10.5" s="245" customFormat="1">
       <c r="A20" s="30"/>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
@@ -11619,7 +11645,7 @@
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
     </row>
-    <row r="21" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
+    <row r="21" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A21" s="36" t="inlineStr">
         <is>
           <r>
@@ -11648,29 +11674,29 @@
           </r>
         </is>
       </c>
-      <c r="E21" s="357" t="inlineStr">
+      <c r="E21" s="356" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Q'TY</t>
           </r>
         </is>
       </c>
-      <c r="F21" s="256"/>
-      <c r="G21" s="358" t="inlineStr">
+      <c r="F21" s="255"/>
+      <c r="G21" s="357" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Unit Price</t>
           </r>
         </is>
       </c>
-      <c r="H21" s="359" t="inlineStr">
+      <c r="H21" s="358" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">AMOUNT</t>
           </r>
         </is>
       </c>
-      <c r="I21" s="360" t="inlineStr">
+      <c r="I21" s="359" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Shipping</t>
@@ -11679,8 +11705,8 @@
       </c>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A22" s="361">
+    <row r="22" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A22" s="360">
         <v>1</v>
       </c>
       <c r="B22" s="123" t="str">
@@ -11695,10 +11721,10 @@
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="E22" s="362">
+      <c r="E22" s="361">
         <v>1</v>
       </c>
-      <c r="F22" s="256"/>
+      <c r="F22" s="255"/>
       <c r="G22" s="126" t="str">
         <f>구매리스트!B15</f>
         <v>0</v>
@@ -11716,23 +11742,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A23" s="364"/>
-      <c r="B23" s="365"/>
-      <c r="C23" s="255"/>
-      <c r="D23" s="255"/>
-      <c r="E23" s="255"/>
-      <c r="F23" s="255"/>
-      <c r="G23" s="255"/>
-      <c r="H23" s="255"/>
-      <c r="I23" s="256"/>
-      <c r="J23" s="363"/>
-    </row>
-    <row r="24" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A24" s="364">
+    <row r="23" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A23" s="363"/>
+      <c r="B23" s="364"/>
+      <c r="C23" s="254"/>
+      <c r="D23" s="254"/>
+      <c r="E23" s="254"/>
+      <c r="F23" s="254"/>
+      <c r="G23" s="254"/>
+      <c r="H23" s="254"/>
+      <c r="I23" s="255"/>
+      <c r="J23" s="362"/>
+    </row>
+    <row r="24" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A24" s="363">
         <v>2</v>
       </c>
-      <c r="B24" s="366" t="inlineStr">
+      <c r="B24" s="365" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11753,9 +11779,9 @@
           </r>
         </is>
       </c>
-      <c r="E24" s="367"/>
-      <c r="F24" s="256"/>
-      <c r="G24" s="368" t="inlineStr">
+      <c r="E24" s="366"/>
+      <c r="F24" s="255"/>
+      <c r="G24" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11769,40 +11795,40 @@
           </r>
         </is>
       </c>
-      <c r="I24" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J24" s="363">
+      <c r="I24" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J24" s="362">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A25" s="364"/>
-      <c r="B25" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C25" s="255"/>
-      <c r="D25" s="255"/>
-      <c r="E25" s="255"/>
-      <c r="F25" s="255"/>
-      <c r="G25" s="255"/>
-      <c r="H25" s="255"/>
-      <c r="I25" s="256"/>
-      <c r="J25" s="363"/>
-    </row>
-    <row r="26" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A26" s="364">
+    <row r="25" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A25" s="363"/>
+      <c r="B25" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C25" s="254"/>
+      <c r="D25" s="254"/>
+      <c r="E25" s="254"/>
+      <c r="F25" s="254"/>
+      <c r="G25" s="254"/>
+      <c r="H25" s="254"/>
+      <c r="I25" s="255"/>
+      <c r="J25" s="362"/>
+    </row>
+    <row r="26" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A26" s="363">
         <v>3</v>
       </c>
-      <c r="B26" s="366" t="inlineStr">
+      <c r="B26" s="365" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11823,9 +11849,9 @@
           </r>
         </is>
       </c>
-      <c r="E26" s="367"/>
-      <c r="F26" s="256"/>
-      <c r="G26" s="368" t="inlineStr">
+      <c r="E26" s="366"/>
+      <c r="F26" s="255"/>
+      <c r="G26" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11839,40 +11865,40 @@
           </r>
         </is>
       </c>
-      <c r="I26" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J26" s="363">
+      <c r="I26" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="362">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A27" s="364"/>
-      <c r="B27" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C27" s="255"/>
-      <c r="D27" s="255"/>
-      <c r="E27" s="255"/>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
-      <c r="H27" s="255"/>
-      <c r="I27" s="256"/>
-      <c r="J27" s="363"/>
-    </row>
-    <row r="28" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A28" s="364">
+    <row r="27" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A27" s="363"/>
+      <c r="B27" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C27" s="254"/>
+      <c r="D27" s="254"/>
+      <c r="E27" s="254"/>
+      <c r="F27" s="254"/>
+      <c r="G27" s="254"/>
+      <c r="H27" s="254"/>
+      <c r="I27" s="255"/>
+      <c r="J27" s="362"/>
+    </row>
+    <row r="28" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A28" s="363">
         <v>4</v>
       </c>
-      <c r="B28" s="370" t="inlineStr">
+      <c r="B28" s="369" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11893,9 +11919,9 @@
           </r>
         </is>
       </c>
-      <c r="E28" s="367"/>
-      <c r="F28" s="256"/>
-      <c r="G28" s="368" t="inlineStr">
+      <c r="E28" s="366"/>
+      <c r="F28" s="255"/>
+      <c r="G28" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11909,46 +11935,46 @@
           </r>
         </is>
       </c>
-      <c r="I28" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J28" s="363">
+      <c r="I28" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="362">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A29" s="364" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B29" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C29" s="255"/>
-      <c r="D29" s="255"/>
-      <c r="E29" s="255"/>
-      <c r="F29" s="255"/>
-      <c r="G29" s="255"/>
-      <c r="H29" s="255"/>
-      <c r="I29" s="256"/>
+    <row r="29" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A29" s="363" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C29" s="254"/>
+      <c r="D29" s="254"/>
+      <c r="E29" s="254"/>
+      <c r="F29" s="254"/>
+      <c r="G29" s="254"/>
+      <c r="H29" s="254"/>
+      <c r="I29" s="255"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A30" s="364">
+    <row r="30" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A30" s="363">
         <v>5</v>
       </c>
-      <c r="B30" s="370" t="inlineStr">
+      <c r="B30" s="369" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11969,9 +11995,9 @@
           </r>
         </is>
       </c>
-      <c r="E30" s="367"/>
-      <c r="F30" s="256"/>
-      <c r="G30" s="368" t="inlineStr">
+      <c r="E30" s="366"/>
+      <c r="F30" s="255"/>
+      <c r="G30" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11985,7 +12011,7 @@
           </r>
         </is>
       </c>
-      <c r="I30" s="369" t="inlineStr">
+      <c r="I30" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11994,76 +12020,76 @@
       </c>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A31" s="364" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B31" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C31" s="255"/>
-      <c r="D31" s="255"/>
-      <c r="E31" s="255"/>
-      <c r="F31" s="255"/>
-      <c r="G31" s="255"/>
-      <c r="H31" s="255"/>
-      <c r="I31" s="256"/>
+    <row r="31" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A31" s="363" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B31" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C31" s="254"/>
+      <c r="D31" s="254"/>
+      <c r="E31" s="254"/>
+      <c r="F31" s="254"/>
+      <c r="G31" s="254"/>
+      <c r="H31" s="254"/>
+      <c r="I31" s="255"/>
       <c r="J31" s="18"/>
     </row>
-    <row r="32" spans="1:10" customHeight="1" ht="39.75" s="246" customFormat="1">
+    <row r="32" spans="1:10" customHeight="1" ht="39.75" s="245" customFormat="1">
       <c r="A32" s="27"/>
-      <c r="B32" s="233" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C32" s="371"/>
-      <c r="D32" s="234" t="inlineStr">
+      <c r="B32" s="232" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C32" s="370"/>
+      <c r="D32" s="233" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> GRAND TOTAL :</t>
           </r>
         </is>
       </c>
-      <c r="E32" s="371"/>
-      <c r="F32" s="234"/>
-      <c r="G32" s="234"/>
-      <c r="H32" s="228" t="str">
+      <c r="E32" s="370"/>
+      <c r="F32" s="233"/>
+      <c r="G32" s="233"/>
+      <c r="H32" s="227" t="str">
         <f>SUM(H22:I22,H24:I24,H26:I26,H28:I28,H30:I30)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="372"/>
+      <c r="I32" s="371"/>
       <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="28"/>
-      <c r="B33" s="231"/>
-      <c r="C33" s="231"/>
-      <c r="D33" s="231" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="E33" s="231" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="G33" s="246"/>
+      <c r="B33" s="230"/>
+      <c r="C33" s="230"/>
+      <c r="D33" s="230" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="E33" s="230" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="G33" s="245"/>
       <c r="I33" s="29"/>
       <c r="J33" s="18"/>
     </row>
@@ -12078,7 +12104,7 @@
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
-      <c r="E34" s="231" t="inlineStr">
+      <c r="E34" s="230" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Signed By    </t>
@@ -12235,72 +12261,72 @@
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="4.25" customWidth="true" style="246"/>
-    <col min="2" max="2" width="21.625" customWidth="true" style="246"/>
-    <col min="3" max="3" width="7.5" customWidth="true" style="246"/>
-    <col min="4" max="4" width="23.625" customWidth="true" style="246"/>
-    <col min="5" max="5" width="7.75" customWidth="true" style="246"/>
-    <col min="6" max="6" width="2.125" customWidth="true" style="246"/>
-    <col min="7" max="7" width="12.25" customWidth="true" style="246"/>
-    <col min="8" max="8" width="13.75" customWidth="true" style="246"/>
-    <col min="9" max="9" width="14" customWidth="true" style="246"/>
+    <col min="1" max="1" width="4.25" customWidth="true" style="245"/>
+    <col min="2" max="2" width="21.625" customWidth="true" style="245"/>
+    <col min="3" max="3" width="7.5" customWidth="true" style="245"/>
+    <col min="4" max="4" width="23.625" customWidth="true" style="245"/>
+    <col min="5" max="5" width="7.75" customWidth="true" style="245"/>
+    <col min="6" max="6" width="2.125" customWidth="true" style="245"/>
+    <col min="7" max="7" width="12.25" customWidth="true" style="245"/>
+    <col min="8" max="8" width="13.75" customWidth="true" style="245"/>
+    <col min="9" max="9" width="14" customWidth="true" style="245"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customHeight="1" ht="47.25" s="246" customFormat="1">
-      <c r="A1" s="343" t="inlineStr">
+    <row r="1" spans="1:10" customHeight="1" ht="47.25" s="245" customFormat="1">
+      <c r="A1" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">COMMERCIAL PACKING LIST</t>
           </r>
         </is>
       </c>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="255"/>
-      <c r="F1" s="255"/>
-      <c r="G1" s="255"/>
-      <c r="H1" s="255"/>
-      <c r="I1" s="256"/>
-    </row>
-    <row r="2" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A2" s="344" t="inlineStr">
+      <c r="B1" s="254"/>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
+      <c r="E1" s="254"/>
+      <c r="F1" s="254"/>
+      <c r="G1" s="254"/>
+      <c r="H1" s="254"/>
+      <c r="I1" s="255"/>
+    </row>
+    <row r="2" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A2" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1) Shipper / Exporter</t>
           </r>
         </is>
       </c>
-      <c r="B2" s="251"/>
-      <c r="C2" s="251"/>
-      <c r="D2" s="252"/>
-      <c r="E2" s="225" t="inlineStr">
+      <c r="B2" s="250"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="251"/>
+      <c r="E2" s="224" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Reference No.      DFSU6646075</t>
           </r>
         </is>
       </c>
-      <c r="F2" s="251"/>
+      <c r="F2" s="250"/>
       <c r="G2" s="128" t="str">
         <f>차량인보이스!G2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="345" t="inlineStr">
+      <c r="H2" s="344" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">ORIGINAL</t>
           </r>
         </is>
       </c>
-      <c r="I2" s="252"/>
-    </row>
-    <row r="3" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A3" s="346" t="s">
-        <v>344</v>
-      </c>
-      <c r="D3" s="263"/>
-      <c r="E3" s="229" t="inlineStr">
+      <c r="I2" s="251"/>
+    </row>
+    <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A3" s="345" t="s">
+        <v>346</v>
+      </c>
+      <c r="D3" s="262"/>
+      <c r="E3" s="228" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Reference code.   DFSU6646075</t>
@@ -12311,122 +12337,122 @@
         <f>차량인보이스!G3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="273"/>
-      <c r="I3" s="254"/>
-    </row>
-    <row r="4" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A4" s="272"/>
-      <c r="D4" s="263"/>
-      <c r="E4" s="347" t="inlineStr">
+      <c r="H3" s="272"/>
+      <c r="I3" s="253"/>
+    </row>
+    <row r="4" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A4" s="271"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">CERTIFICATE OF ORIGIN</t>
           </r>
         </is>
       </c>
-      <c r="I4" s="263"/>
-    </row>
-    <row r="5" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A5" s="272"/>
-      <c r="D5" s="263"/>
-      <c r="E5" s="272"/>
-      <c r="I5" s="263"/>
-    </row>
-    <row r="6" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A6" s="272"/>
-      <c r="D6" s="263"/>
-      <c r="E6" s="348" t="inlineStr">
+      <c r="I4" s="262"/>
+    </row>
+    <row r="5" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A5" s="271"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="271"/>
+      <c r="I5" s="262"/>
+    </row>
+    <row r="6" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A6" s="271"/>
+      <c r="D6" s="262"/>
+      <c r="E6" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Issued by</t>
           </r>
         </is>
       </c>
-      <c r="I6" s="263"/>
-    </row>
-    <row r="7" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A7" s="273"/>
-      <c r="B7" s="253"/>
-      <c r="C7" s="253"/>
-      <c r="D7" s="254"/>
-      <c r="E7" s="348" t="inlineStr">
+      <c r="I6" s="262"/>
+    </row>
+    <row r="7" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A7" s="272"/>
+      <c r="B7" s="252"/>
+      <c r="C7" s="252"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">THE KOREA CHAMBER OF COMMERCE &amp; INDUSTRY</t>
           </r>
         </is>
       </c>
-      <c r="I7" s="263"/>
-    </row>
-    <row r="8" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A8" s="344" t="inlineStr">
+      <c r="I7" s="262"/>
+    </row>
+    <row r="8" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A8" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2) For account &amp; risk of Messers.</t>
           </r>
         </is>
       </c>
-      <c r="B8" s="251"/>
-      <c r="C8" s="251"/>
-      <c r="D8" s="252"/>
-      <c r="E8" s="349" t="inlineStr">
+      <c r="B8" s="250"/>
+      <c r="C8" s="250"/>
+      <c r="D8" s="251"/>
+      <c r="E8" s="348" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Seoul, Republic of korea</t>
           </r>
         </is>
       </c>
-      <c r="F8" s="253"/>
-      <c r="G8" s="253"/>
-      <c r="H8" s="253"/>
-      <c r="I8" s="254"/>
-    </row>
-    <row r="9" spans="1:10" customHeight="1" ht="65.25" s="246" customFormat="1">
-      <c r="A9" s="373" t="str">
+      <c r="F8" s="252"/>
+      <c r="G8" s="252"/>
+      <c r="H8" s="252"/>
+      <c r="I8" s="253"/>
+    </row>
+    <row r="9" spans="1:10" customHeight="1" ht="65.25" s="245" customFormat="1">
+      <c r="A9" s="372" t="str">
         <f>차량인보이스!A9</f>
         <v>0</v>
       </c>
-      <c r="D9" s="263"/>
-      <c r="E9" s="235" t="inlineStr">
+      <c r="D9" s="262"/>
+      <c r="E9" s="234" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> *Remark</t>
           </r>
         </is>
       </c>
-      <c r="F9" s="251"/>
-      <c r="G9" s="251"/>
-      <c r="H9" s="251"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="246" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="10" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A10" s="272"/>
-      <c r="D10" s="263"/>
-      <c r="E10" s="226" t="inlineStr">
+      <c r="F9" s="250"/>
+      <c r="G9" s="250"/>
+      <c r="H9" s="250"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="245" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A10" s="271"/>
+      <c r="D10" s="262"/>
+      <c r="E10" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">8) No. &amp; date of invoice</t>
           </r>
         </is>
       </c>
-      <c r="F10" s="251"/>
-      <c r="G10" s="251"/>
-      <c r="H10" s="251"/>
-      <c r="I10" s="252"/>
-    </row>
-    <row r="11" spans="1:10" customHeight="1" ht="35.25" s="246" customFormat="1">
-      <c r="A11" s="273"/>
-      <c r="B11" s="253"/>
-      <c r="C11" s="253"/>
-      <c r="D11" s="254"/>
-      <c r="E11" s="227" t="str">
+      <c r="F10" s="250"/>
+      <c r="G10" s="250"/>
+      <c r="H10" s="250"/>
+      <c r="I10" s="251"/>
+    </row>
+    <row r="11" spans="1:10" customHeight="1" ht="35.25" s="245" customFormat="1">
+      <c r="A11" s="272"/>
+      <c r="B11" s="252"/>
+      <c r="C11" s="252"/>
+      <c r="D11" s="253"/>
+      <c r="E11" s="226" t="str">
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
@@ -12435,151 +12461,151 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A12" s="344" t="inlineStr">
+    <row r="12" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A12" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3) Notify party</t>
           </r>
         </is>
       </c>
-      <c r="B12" s="251"/>
-      <c r="C12" s="251"/>
-      <c r="D12" s="252"/>
-      <c r="E12" s="344" t="inlineStr">
+      <c r="B12" s="250"/>
+      <c r="C12" s="250"/>
+      <c r="D12" s="251"/>
+      <c r="E12" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">9) No. &amp; date of L/C</t>
           </r>
         </is>
       </c>
-      <c r="F12" s="251"/>
-      <c r="G12" s="251"/>
-      <c r="H12" s="251"/>
-      <c r="I12" s="252"/>
-    </row>
-    <row r="13" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A13" s="351" t="inlineStr">
+      <c r="F12" s="250"/>
+      <c r="G12" s="250"/>
+      <c r="H12" s="250"/>
+      <c r="I12" s="251"/>
+    </row>
+    <row r="13" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A13" s="350" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SAME AS ABOVE</t>
           </r>
         </is>
       </c>
-      <c r="D13" s="263"/>
-      <c r="E13" s="230" t="inlineStr">
+      <c r="D13" s="262"/>
+      <c r="E13" s="229" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">TTR BASE</t>
           </r>
         </is>
       </c>
-      <c r="I13" s="263"/>
-    </row>
-    <row r="14" spans="1:10" customHeight="1" ht="9.75" s="246" customFormat="1">
-      <c r="A14" s="273"/>
-      <c r="B14" s="253"/>
-      <c r="C14" s="253"/>
-      <c r="D14" s="254"/>
-      <c r="E14" s="253"/>
-      <c r="F14" s="253"/>
-      <c r="G14" s="253"/>
-      <c r="H14" s="253"/>
-      <c r="I14" s="254"/>
-    </row>
-    <row r="15" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
-      <c r="A15" s="344" t="inlineStr">
+      <c r="I13" s="262"/>
+    </row>
+    <row r="14" spans="1:10" customHeight="1" ht="9.75" s="245" customFormat="1">
+      <c r="A14" s="272"/>
+      <c r="B14" s="252"/>
+      <c r="C14" s="252"/>
+      <c r="D14" s="253"/>
+      <c r="E14" s="252"/>
+      <c r="F14" s="252"/>
+      <c r="G14" s="252"/>
+      <c r="H14" s="252"/>
+      <c r="I14" s="253"/>
+    </row>
+    <row r="15" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
+      <c r="A15" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">4) Port of loading</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="252"/>
-      <c r="C15" s="226" t="inlineStr">
+      <c r="B15" s="251"/>
+      <c r="C15" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">5) Final Destination</t>
           </r>
         </is>
       </c>
-      <c r="D15" s="252"/>
-      <c r="E15" s="226" t="inlineStr">
+      <c r="D15" s="251"/>
+      <c r="E15" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">10) L/C issuing bank</t>
           </r>
         </is>
       </c>
-      <c r="F15" s="251"/>
-      <c r="G15" s="251"/>
-      <c r="H15" s="251"/>
-      <c r="I15" s="252"/>
-    </row>
-    <row r="16" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A16" s="232" t="str">
+      <c r="F15" s="250"/>
+      <c r="G15" s="250"/>
+      <c r="H15" s="250"/>
+      <c r="I15" s="251"/>
+    </row>
+    <row r="16" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A16" s="231" t="str">
         <f>구매리스트!B10</f>
         <v>0</v>
       </c>
-      <c r="B16" s="253"/>
-      <c r="C16" s="352" t="str">
+      <c r="B16" s="252"/>
+      <c r="C16" s="351" t="str">
         <f>구매리스트!D10</f>
         <v>0</v>
       </c>
-      <c r="D16" s="254"/>
-      <c r="E16" s="353" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="I16" s="263"/>
-    </row>
-    <row r="17" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
-      <c r="A17" s="344" t="inlineStr">
+      <c r="D16" s="253"/>
+      <c r="E16" s="352" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="I16" s="262"/>
+    </row>
+    <row r="17" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
+      <c r="A17" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">6) Vessel name</t>
           </r>
         </is>
       </c>
-      <c r="B17" s="252"/>
-      <c r="C17" s="226" t="inlineStr">
+      <c r="B17" s="251"/>
+      <c r="C17" s="225" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">7) Sailing on or about</t>
           </r>
         </is>
       </c>
-      <c r="D17" s="252"/>
-      <c r="E17" s="354" t="str">
+      <c r="D17" s="251"/>
+      <c r="E17" s="353" t="str">
         <f>차량인보이스!E17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="251"/>
-      <c r="G17" s="251"/>
-      <c r="H17" s="251"/>
-      <c r="I17" s="252"/>
-    </row>
-    <row r="18" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A18" s="352" t="str">
+      <c r="F17" s="250"/>
+      <c r="G17" s="250"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="251"/>
+    </row>
+    <row r="18" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
+      <c r="A18" s="351" t="str">
         <f>구매리스트!B11</f>
         <v>0</v>
       </c>
-      <c r="B18" s="254"/>
-      <c r="C18" s="355" t="str">
+      <c r="B18" s="253"/>
+      <c r="C18" s="354" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
-      <c r="D18" s="254"/>
-      <c r="E18" s="273"/>
-      <c r="F18" s="253"/>
-      <c r="G18" s="253"/>
-      <c r="H18" s="253"/>
-      <c r="I18" s="254"/>
-    </row>
-    <row r="19" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
+      <c r="D18" s="253"/>
+      <c r="E18" s="272"/>
+      <c r="F18" s="252"/>
+      <c r="G18" s="252"/>
+      <c r="H18" s="252"/>
+      <c r="I18" s="253"/>
+    </row>
+    <row r="19" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A19" s="22" t="inlineStr">
         <is>
           <r>
@@ -12596,14 +12622,14 @@
         </is>
       </c>
       <c r="D19" s="26"/>
-      <c r="E19" s="356" t="inlineStr">
+      <c r="E19" s="355" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">13) Quantity</t>
           </r>
         </is>
       </c>
-      <c r="F19" s="256"/>
+      <c r="F19" s="255"/>
       <c r="G19" s="22" t="inlineStr">
         <is>
           <r>
@@ -12626,7 +12652,7 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:10" customHeight="1" ht="10.5" s="246" customFormat="1">
+    <row r="20" spans="1:10" customHeight="1" ht="10.5" s="245" customFormat="1">
       <c r="A20" s="30"/>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
@@ -12637,7 +12663,7 @@
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
     </row>
-    <row r="21" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
+    <row r="21" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A21" s="36" t="inlineStr">
         <is>
           <r>
@@ -12666,22 +12692,22 @@
           </r>
         </is>
       </c>
-      <c r="E21" s="357" t="inlineStr">
+      <c r="E21" s="356" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Q'TY</t>
           </r>
         </is>
       </c>
-      <c r="F21" s="256"/>
-      <c r="G21" s="358" t="inlineStr">
+      <c r="F21" s="255"/>
+      <c r="G21" s="357" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Unit Price</t>
           </r>
         </is>
       </c>
-      <c r="H21" s="359" t="inlineStr">
+      <c r="H21" s="358" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">AMOUNT</t>
@@ -12698,8 +12724,8 @@
       </c>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A22" s="361">
+    <row r="22" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A22" s="360">
         <v>1</v>
       </c>
       <c r="B22" s="123" t="str">
@@ -12714,19 +12740,19 @@
         <f>차량인보이스!D22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="362" t="str">
+      <c r="E22" s="361" t="str">
         <f>차량인보이스!E22</f>
         <v>0</v>
       </c>
-      <c r="F22" s="256"/>
-      <c r="G22" s="374" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="H22" s="374" t="inlineStr">
+      <c r="F22" s="255"/>
+      <c r="G22" s="373" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="H22" s="373" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12737,31 +12763,31 @@
         <f>구매리스트!I8</f>
         <v>0</v>
       </c>
-      <c r="J22" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="23" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A23" s="364"/>
-      <c r="B23" s="365"/>
-      <c r="C23" s="255"/>
-      <c r="D23" s="255"/>
-      <c r="E23" s="255"/>
-      <c r="F23" s="255"/>
-      <c r="G23" s="255"/>
-      <c r="H23" s="255"/>
-      <c r="I23" s="256"/>
-      <c r="J23" s="363"/>
-    </row>
-    <row r="24" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A24" s="364">
+      <c r="J22" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A23" s="363"/>
+      <c r="B23" s="364"/>
+      <c r="C23" s="254"/>
+      <c r="D23" s="254"/>
+      <c r="E23" s="254"/>
+      <c r="F23" s="254"/>
+      <c r="G23" s="254"/>
+      <c r="H23" s="254"/>
+      <c r="I23" s="255"/>
+      <c r="J23" s="362"/>
+    </row>
+    <row r="24" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A24" s="363">
         <v>2</v>
       </c>
-      <c r="B24" s="366" t="inlineStr">
+      <c r="B24" s="365" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12782,9 +12808,9 @@
           </r>
         </is>
       </c>
-      <c r="E24" s="367"/>
-      <c r="F24" s="256"/>
-      <c r="G24" s="368" t="inlineStr">
+      <c r="E24" s="366"/>
+      <c r="F24" s="255"/>
+      <c r="G24" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12798,44 +12824,44 @@
           </r>
         </is>
       </c>
-      <c r="I24" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J24" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="25" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A25" s="364"/>
-      <c r="B25" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C25" s="255"/>
-      <c r="D25" s="255"/>
-      <c r="E25" s="255"/>
-      <c r="F25" s="255"/>
-      <c r="G25" s="255"/>
-      <c r="H25" s="255"/>
-      <c r="I25" s="256"/>
-      <c r="J25" s="363"/>
-    </row>
-    <row r="26" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A26" s="364">
+      <c r="I24" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J24" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A25" s="363"/>
+      <c r="B25" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C25" s="254"/>
+      <c r="D25" s="254"/>
+      <c r="E25" s="254"/>
+      <c r="F25" s="254"/>
+      <c r="G25" s="254"/>
+      <c r="H25" s="254"/>
+      <c r="I25" s="255"/>
+      <c r="J25" s="362"/>
+    </row>
+    <row r="26" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A26" s="363">
         <v>3</v>
       </c>
-      <c r="B26" s="366" t="inlineStr">
+      <c r="B26" s="365" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12856,9 +12882,9 @@
           </r>
         </is>
       </c>
-      <c r="E26" s="367"/>
-      <c r="F26" s="256"/>
-      <c r="G26" s="368" t="inlineStr">
+      <c r="E26" s="366"/>
+      <c r="F26" s="255"/>
+      <c r="G26" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12872,44 +12898,44 @@
           </r>
         </is>
       </c>
-      <c r="I26" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J26" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="27" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A27" s="364"/>
-      <c r="B27" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C27" s="255"/>
-      <c r="D27" s="255"/>
-      <c r="E27" s="255"/>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
-      <c r="H27" s="255"/>
-      <c r="I27" s="256"/>
-      <c r="J27" s="363"/>
-    </row>
-    <row r="28" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A28" s="364">
+      <c r="I26" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A27" s="363"/>
+      <c r="B27" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C27" s="254"/>
+      <c r="D27" s="254"/>
+      <c r="E27" s="254"/>
+      <c r="F27" s="254"/>
+      <c r="G27" s="254"/>
+      <c r="H27" s="254"/>
+      <c r="I27" s="255"/>
+      <c r="J27" s="362"/>
+    </row>
+    <row r="28" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A28" s="363">
         <v>4</v>
       </c>
-      <c r="B28" s="370" t="inlineStr">
+      <c r="B28" s="369" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12930,9 +12956,9 @@
           </r>
         </is>
       </c>
-      <c r="E28" s="367"/>
-      <c r="F28" s="256"/>
-      <c r="G28" s="368" t="inlineStr">
+      <c r="E28" s="366"/>
+      <c r="F28" s="255"/>
+      <c r="G28" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12946,50 +12972,50 @@
           </r>
         </is>
       </c>
-      <c r="I28" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J28" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="29" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A29" s="364" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B29" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C29" s="255"/>
-      <c r="D29" s="255"/>
-      <c r="E29" s="255"/>
-      <c r="F29" s="255"/>
-      <c r="G29" s="255"/>
-      <c r="H29" s="255"/>
-      <c r="I29" s="256"/>
+      <c r="I28" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A29" s="363" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C29" s="254"/>
+      <c r="D29" s="254"/>
+      <c r="E29" s="254"/>
+      <c r="F29" s="254"/>
+      <c r="G29" s="254"/>
+      <c r="H29" s="254"/>
+      <c r="I29" s="255"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A30" s="364">
+    <row r="30" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
+      <c r="A30" s="363">
         <v>5</v>
       </c>
-      <c r="B30" s="370" t="inlineStr">
+      <c r="B30" s="369" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13010,9 +13036,9 @@
           </r>
         </is>
       </c>
-      <c r="E30" s="367"/>
-      <c r="F30" s="256"/>
-      <c r="G30" s="368" t="inlineStr">
+      <c r="E30" s="366"/>
+      <c r="F30" s="255"/>
+      <c r="G30" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13026,7 +13052,7 @@
           </r>
         </is>
       </c>
-      <c r="I30" s="369" t="inlineStr">
+      <c r="I30" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13035,76 +13061,76 @@
       </c>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A31" s="364" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B31" s="365" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C31" s="255"/>
-      <c r="D31" s="255"/>
-      <c r="E31" s="255"/>
-      <c r="F31" s="255"/>
-      <c r="G31" s="255"/>
-      <c r="H31" s="255"/>
-      <c r="I31" s="256"/>
+    <row r="31" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
+      <c r="A31" s="363" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B31" s="364" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C31" s="254"/>
+      <c r="D31" s="254"/>
+      <c r="E31" s="254"/>
+      <c r="F31" s="254"/>
+      <c r="G31" s="254"/>
+      <c r="H31" s="254"/>
+      <c r="I31" s="255"/>
       <c r="J31" s="18"/>
     </row>
-    <row r="32" spans="1:10" customHeight="1" ht="39.75" s="246" customFormat="1">
+    <row r="32" spans="1:10" customHeight="1" ht="39.75" s="245" customFormat="1">
       <c r="A32" s="27"/>
-      <c r="B32" s="233" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="C32" s="371"/>
-      <c r="D32" s="236" t="inlineStr">
+      <c r="B32" s="232" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="C32" s="370"/>
+      <c r="D32" s="235" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> GRAND TOTAL :</t>
           </r>
         </is>
       </c>
-      <c r="E32" s="371"/>
-      <c r="F32" s="236"/>
-      <c r="G32" s="236"/>
-      <c r="H32" s="237" t="str">
+      <c r="E32" s="370"/>
+      <c r="F32" s="235"/>
+      <c r="G32" s="235"/>
+      <c r="H32" s="236" t="str">
         <f>SUM(I22,I24,I26,I28,I30)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="372"/>
+      <c r="I32" s="371"/>
       <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="28"/>
-      <c r="B33" s="231"/>
-      <c r="C33" s="231"/>
-      <c r="D33" s="231" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="E33" s="231" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="G33" s="246"/>
+      <c r="B33" s="230"/>
+      <c r="C33" s="230"/>
+      <c r="D33" s="230" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="E33" s="230" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="G33" s="245"/>
       <c r="I33" s="29"/>
       <c r="J33" s="18"/>
     </row>
@@ -13119,7 +13145,7 @@
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
-      <c r="E34" s="231" t="inlineStr">
+      <c r="E34" s="230" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Signed By    </t>
@@ -13275,20 +13301,20 @@
   <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="7.625" customWidth="true" style="246"/>
-    <col min="2" max="2" width="14.875" customWidth="true" style="246"/>
-    <col min="3" max="3" width="26.375" customWidth="true" style="246"/>
-    <col min="4" max="4" width="10.5" customWidth="true" style="246"/>
-    <col min="5" max="5" width="18.875" customWidth="true" style="246"/>
-    <col min="6" max="6" width="18" customWidth="true" style="246"/>
-    <col min="7" max="7" width="15.25" customWidth="true" style="246"/>
+    <col min="1" max="1" width="7.625" customWidth="true" style="245"/>
+    <col min="2" max="2" width="14.875" customWidth="true" style="245"/>
+    <col min="3" max="3" width="26.375" customWidth="true" style="245"/>
+    <col min="4" max="4" width="10.5" customWidth="true" style="245"/>
+    <col min="5" max="5" width="18.875" customWidth="true" style="245"/>
+    <col min="6" max="6" width="18" customWidth="true" style="245"/>
+    <col min="7" max="7" width="15.25" customWidth="true" style="245"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" customHeight="1" ht="84" s="246" customFormat="1">
-      <c r="A1" s="243"/>
+    <row r="1" spans="1:7" customHeight="1" ht="84" s="245" customFormat="1">
+      <c r="A1" s="242"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
-      <c r="E1" s="242" t="inlineStr">
+      <c r="E1" s="241" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">PROFORM INVOICE</t>
@@ -13296,14 +13322,14 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:7" customHeight="1" ht="11.25" s="246" customFormat="1">
-      <c r="A2" s="244" t="s">
-        <v>348</v>
-      </c>
-      <c r="D2" s="244"/>
-    </row>
-    <row r="3" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="D3" s="244"/>
+    <row r="2" spans="1:7" customHeight="1" ht="11.25" s="245" customFormat="1">
+      <c r="A2" s="243" t="s">
+        <v>350</v>
+      </c>
+      <c r="D2" s="243"/>
+    </row>
+    <row r="3" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="D3" s="243"/>
       <c r="E3" s="44" t="inlineStr">
         <is>
           <r>
@@ -13311,13 +13337,13 @@
           </r>
         </is>
       </c>
-      <c r="F3" s="375" t="str">
+      <c r="F3" s="374" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
-      <c r="G3" s="376"/>
-    </row>
-    <row r="4" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
+      <c r="G3" s="375"/>
+    </row>
+    <row r="4" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A4" s="47"/>
       <c r="B4" s="47"/>
       <c r="C4" s="47"/>
@@ -13329,15 +13355,15 @@
           </r>
         </is>
       </c>
-      <c r="F4" s="377" t="str">
+      <c r="F4" s="376" t="str">
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
-      <c r="G4" s="378"/>
-    </row>
-    <row r="5" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A5" s="239"/>
-      <c r="B5" s="239"/>
+      <c r="G4" s="377"/>
+    </row>
+    <row r="5" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A5" s="238"/>
+      <c r="B5" s="238"/>
       <c r="E5" s="44" t="inlineStr">
         <is>
           <r>
@@ -13345,15 +13371,15 @@
           </r>
         </is>
       </c>
-      <c r="F5" s="379" t="str">
+      <c r="F5" s="378" t="str">
         <f>구매리스트!D14</f>
         <v>0</v>
       </c>
-      <c r="G5" s="378"/>
-    </row>
-    <row r="6" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A6" s="239"/>
-      <c r="B6" s="239"/>
+      <c r="G5" s="377"/>
+    </row>
+    <row r="6" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A6" s="238"/>
+      <c r="B6" s="238"/>
       <c r="E6" s="44" t="inlineStr">
         <is>
           <r>
@@ -13361,11 +13387,11 @@
           </r>
         </is>
       </c>
-      <c r="F6" s="380"/>
-      <c r="G6" s="378"/>
-    </row>
-    <row r="7" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A7" s="239"/>
+      <c r="F6" s="379"/>
+      <c r="G6" s="377"/>
+    </row>
+    <row r="7" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A7" s="238"/>
       <c r="E7" s="44" t="inlineStr">
         <is>
           <r>
@@ -13373,11 +13399,11 @@
           </r>
         </is>
       </c>
-      <c r="F7" s="381"/>
-      <c r="G7" s="378"/>
-    </row>
-    <row r="8" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A8" s="239"/>
+      <c r="F7" s="380"/>
+      <c r="G7" s="377"/>
+    </row>
+    <row r="8" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A8" s="238"/>
       <c r="E8" s="44" t="inlineStr">
         <is>
           <r>
@@ -13385,12 +13411,12 @@
           </r>
         </is>
       </c>
-      <c r="F8" s="382"/>
-      <c r="G8" s="378"/>
-    </row>
-    <row r="9" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
-      <c r="A9" s="239"/>
-      <c r="B9" s="239"/>
+      <c r="F8" s="381"/>
+      <c r="G8" s="377"/>
+    </row>
+    <row r="9" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
       <c r="E9" s="44" t="inlineStr">
         <is>
           <r>
@@ -13398,18 +13424,18 @@
           </r>
         </is>
       </c>
-      <c r="F9" s="380"/>
-      <c r="G9" s="378"/>
-    </row>
-    <row r="10" spans="1:7" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A10" s="239"/>
+      <c r="F9" s="379"/>
+      <c r="G9" s="377"/>
+    </row>
+    <row r="10" spans="1:7" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A10" s="238"/>
       <c r="E10" s="44"/>
       <c r="F10" s="46"/>
       <c r="G10" s="45"/>
     </row>
-    <row r="11" spans="1:7" customHeight="1" ht="23.25" s="246" customFormat="1">
-      <c r="A11" s="238"/>
-      <c r="B11" s="238"/>
+    <row r="11" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="A11" s="237"/>
+      <c r="B11" s="237"/>
       <c r="E11" s="44" t="inlineStr">
         <is>
           <r>
@@ -13417,14 +13443,14 @@
           </r>
         </is>
       </c>
-      <c r="F11" s="383" t="str">
+      <c r="F11" s="382" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
-      <c r="G11" s="378"/>
-    </row>
-    <row r="12" spans="1:7" customHeight="1" ht="23.25" s="246" customFormat="1">
-      <c r="A12" s="238"/>
+      <c r="G11" s="377"/>
+    </row>
+    <row r="12" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="A12" s="237"/>
       <c r="E12" s="44" t="inlineStr">
         <is>
           <r>
@@ -13432,14 +13458,14 @@
           </r>
         </is>
       </c>
-      <c r="F12" s="383" t="str">
+      <c r="F12" s="382" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
-      <c r="G12" s="378"/>
-    </row>
-    <row r="13" spans="1:7" customHeight="1" ht="23.25" s="246" customFormat="1">
-      <c r="A13" s="245"/>
+      <c r="G12" s="377"/>
+    </row>
+    <row r="13" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="A13" s="244"/>
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="44" t="inlineStr">
@@ -13449,130 +13475,130 @@
           </r>
         </is>
       </c>
-      <c r="F13" s="384" t="str">
+      <c r="F13" s="383" t="str">
         <f>SUM(F11-F12)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="378"/>
-    </row>
-    <row r="14" spans="1:7" customHeight="1" ht="17.25" s="246" customFormat="1">
-      <c r="A14" s="245"/>
+      <c r="G13" s="377"/>
+    </row>
+    <row r="14" spans="1:7" customHeight="1" ht="17.25" s="245" customFormat="1">
+      <c r="A14" s="244"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
-      <c r="E14" s="385"/>
-    </row>
-    <row r="15" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
-      <c r="A15" s="386" t="inlineStr">
+      <c r="E14" s="384"/>
+    </row>
+    <row r="15" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
+      <c r="A15" s="385" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">BANK ACCOUNT INFORMATION</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="387"/>
-      <c r="C15" s="387"/>
-      <c r="D15" s="387"/>
-      <c r="E15" s="387"/>
-      <c r="F15" s="387"/>
-      <c r="G15" s="388"/>
-    </row>
-    <row r="16" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
-      <c r="A16" s="240" t="inlineStr">
+      <c r="B15" s="386"/>
+      <c r="C15" s="386"/>
+      <c r="D15" s="386"/>
+      <c r="E15" s="386"/>
+      <c r="F15" s="386"/>
+      <c r="G15" s="387"/>
+    </row>
+    <row r="16" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
+      <c r="A16" s="239" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Beneficiary</t>
           </r>
         </is>
       </c>
-      <c r="B16" s="388"/>
-      <c r="C16" s="389" t="s">
-        <v>360</v>
-      </c>
-      <c r="D16" s="388"/>
-      <c r="E16" s="240" t="inlineStr">
+      <c r="B16" s="387"/>
+      <c r="C16" s="388" t="s">
+        <v>362</v>
+      </c>
+      <c r="D16" s="387"/>
+      <c r="E16" s="239" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Bank Name</t>
           </r>
         </is>
       </c>
-      <c r="F16" s="390" t="inlineStr">
+      <c r="F16" s="389" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SHINHAN BANK</t>
           </r>
         </is>
       </c>
-      <c r="G16" s="388"/>
-    </row>
-    <row r="17" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
-      <c r="A17" s="240" t="inlineStr">
+      <c r="G16" s="387"/>
+    </row>
+    <row r="17" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
+      <c r="A17" s="239" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Swift Cose</t>
           </r>
         </is>
       </c>
-      <c r="B17" s="388"/>
-      <c r="C17" s="389" t="inlineStr">
+      <c r="B17" s="387"/>
+      <c r="C17" s="388" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SHBKKRSE</t>
           </r>
         </is>
       </c>
-      <c r="D17" s="388"/>
-      <c r="E17" s="240" t="inlineStr">
+      <c r="D17" s="387"/>
+      <c r="E17" s="239" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Bank Adress</t>
           </r>
         </is>
       </c>
-      <c r="F17" s="241" t="inlineStr">
+      <c r="F17" s="240" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">20,Sejong-Daero9-Gil,Jung-Gu Seoul South Korea</t>
           </r>
         </is>
       </c>
-      <c r="G17" s="388"/>
-    </row>
-    <row r="18" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
-      <c r="A18" s="240" t="inlineStr">
+      <c r="G17" s="387"/>
+    </row>
+    <row r="18" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
+      <c r="A18" s="239" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Bank Account Number</t>
           </r>
         </is>
       </c>
-      <c r="B18" s="388"/>
-      <c r="C18" s="389" t="s">
-        <v>368</v>
-      </c>
-      <c r="D18" s="388"/>
-      <c r="E18" s="240" t="inlineStr">
+      <c r="B18" s="387"/>
+      <c r="C18" s="388" t="s">
+        <v>370</v>
+      </c>
+      <c r="D18" s="387"/>
+      <c r="E18" s="239" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Beneficiary Adress</t>
           </r>
         </is>
       </c>
-      <c r="F18" s="391" t="inlineStr">
+      <c r="F18" s="390" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">163 Sangidaehak-ro, Siheung-si, Gyeonggi-do,   SOUTH KOREA</t>
           </r>
         </is>
       </c>
-      <c r="G18" s="388"/>
+      <c r="G18" s="387"/>
     </row>
     <row r="19" spans="1:7">
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="385"/>
-    </row>
-    <row r="20" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="E19" s="384"/>
+    </row>
+    <row r="20" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A20" s="42" t="inlineStr">
         <is>
           <r>
@@ -13615,9 +13641,9 @@
           </r>
         </is>
       </c>
-      <c r="G20" s="388"/>
-    </row>
-    <row r="21" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="G20" s="387"/>
+    </row>
+    <row r="21" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A21" s="133" t="str">
         <f>구매리스트!B3</f>
         <v>0</v>
@@ -13635,67 +13661,67 @@
         <v>0</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="392" t="str">
+      <c r="F21" s="391" t="str">
         <f>차량인보이스!H22</f>
         <v>0</v>
       </c>
-      <c r="G21" s="388"/>
-    </row>
-    <row r="22" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="G21" s="387"/>
+    </row>
+    <row r="22" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A22" s="41"/>
       <c r="B22" s="41"/>
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
-      <c r="F22" s="393"/>
-      <c r="G22" s="388"/>
-    </row>
-    <row r="23" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="F22" s="392"/>
+      <c r="G22" s="387"/>
+    </row>
+    <row r="23" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A23" s="41"/>
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
       <c r="D23" s="41"/>
       <c r="E23" s="41"/>
-      <c r="F23" s="393"/>
-      <c r="G23" s="388"/>
-    </row>
-    <row r="24" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="F23" s="392"/>
+      <c r="G23" s="387"/>
+    </row>
+    <row r="24" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A24" s="41"/>
       <c r="B24" s="41"/>
       <c r="C24" s="41"/>
       <c r="D24" s="41"/>
       <c r="E24" s="41"/>
-      <c r="F24" s="393"/>
-      <c r="G24" s="388"/>
-    </row>
-    <row r="25" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="F24" s="392"/>
+      <c r="G24" s="387"/>
+    </row>
+    <row r="25" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A25" s="41"/>
       <c r="B25" s="41"/>
       <c r="C25" s="41"/>
       <c r="D25" s="41"/>
       <c r="E25" s="41"/>
-      <c r="F25" s="393"/>
-      <c r="G25" s="388"/>
-    </row>
-    <row r="26" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="F25" s="392"/>
+      <c r="G25" s="387"/>
+    </row>
+    <row r="26" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A26" s="41"/>
       <c r="B26" s="41"/>
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
       <c r="E26" s="41"/>
-      <c r="F26" s="393"/>
-      <c r="G26" s="388"/>
-    </row>
-    <row r="27" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
+      <c r="F26" s="392"/>
+      <c r="G26" s="387"/>
+    </row>
+    <row r="27" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A27" s="41"/>
       <c r="B27" s="41"/>
       <c r="C27" s="41"/>
       <c r="D27" s="41"/>
       <c r="E27" s="41"/>
-      <c r="F27" s="393"/>
-      <c r="G27" s="388"/>
-    </row>
-    <row r="28" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="F27" s="392"/>
+      <c r="G27" s="387"/>
+    </row>
+    <row r="28" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A28" s="38"/>
       <c r="B28" s="38"/>
       <c r="C28" s="38"/>
@@ -13707,13 +13733,13 @@
           </r>
         </is>
       </c>
-      <c r="F28" s="394" t="str">
+      <c r="F28" s="393" t="str">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="388"/>
-    </row>
-    <row r="29" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="G28" s="387"/>
+    </row>
+    <row r="29" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A29" s="38"/>
       <c r="B29" s="38"/>
       <c r="C29" s="39"/>
@@ -13725,22 +13751,22 @@
           </r>
         </is>
       </c>
-      <c r="F29" s="394" t="str">
+      <c r="F29" s="393" t="str">
         <f>차량인보이스!I22</f>
         <v>0</v>
       </c>
-      <c r="G29" s="388"/>
-    </row>
-    <row r="30" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="G29" s="387"/>
+    </row>
+    <row r="30" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A30" s="38"/>
       <c r="B30" s="38"/>
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
       <c r="E30" s="50"/>
-      <c r="F30" s="395"/>
-      <c r="G30" s="396"/>
-    </row>
-    <row r="31" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
+      <c r="F30" s="394"/>
+      <c r="G30" s="395"/>
+    </row>
+    <row r="31" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A31" s="38"/>
       <c r="B31" s="38"/>
       <c r="C31" s="38"/>
@@ -13752,11 +13778,11 @@
           </r>
         </is>
       </c>
-      <c r="F31" s="394" t="str">
+      <c r="F31" s="393" t="str">
         <f>SUM(F28:G29)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="388"/>
+      <c r="G31" s="387"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="38"/>

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -10063,8 +10063,12 @@
         </is>
       </c>
       <c r="D9" s="304"/>
-      <c r="E9" s="305"/>
-      <c r="G9" s="304"/>
+      <c r="E9" s="184" t="str">
+        <f>구매리스트!D4</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="184"/>
+      <c r="G9" s="184"/>
       <c r="H9" s="180" t="inlineStr">
         <is>
           <r>
@@ -11130,7 +11134,6 @@
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="E8:G9"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="K33:N33"/>
     <mergeCell ref="A49:J49"/>
@@ -11208,6 +11211,8 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="G34:K34"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.31496062992126" right="0.23622047244094" top="0.45" bottom="0.51181102362205" header="0.31496062992126" footer="0.31496062992126"/>

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="381">
   <si>
     <r>
       <t xml:space="preserve">말소증</t>
@@ -171,6 +171,11 @@
   <si>
     <r>
       <t xml:space="preserve">너비</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">용도/Usage</t>
     </r>
   </si>
   <si>
@@ -485,11 +490,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">자가용</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">④ 차               명</t>
     </r>
   </si>
@@ -529,7 +529,7 @@
     </r>
   </si>
   <si>
-    <t>주식회사 헤이맨 (상품용)</t>
+    <t>주식회사 헤이맨</t>
   </si>
   <si>
     <r>
@@ -539,7 +539,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">120111-0922270</t>
+      <t xml:space="preserve">110111-7526176</t>
     </r>
   </si>
   <si>
@@ -914,11 +914,6 @@
   <si>
     <r>
       <t xml:space="preserve">③Usage</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Private car</t>
     </r>
   </si>
   <si>
@@ -1293,6 +1288,11 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">자가용</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Specification</t>
     </r>
   </si>
@@ -1343,6 +1343,9 @@
     <r>
       <t xml:space="preserve">Name</t>
     </r>
+  </si>
+  <si>
+    <t>HEYMAN LTD,.</t>
   </si>
   <si>
     <r>
@@ -3519,7 +3522,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="399">
+  <cellXfs count="400">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4716,6 +4719,9 @@
     </xf>
     <xf xfId="0" fontId="73" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="28" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5878,7 +5884,7 @@
       <c r="A8" s="103" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve"> </t>
+            <t xml:space="preserve">용도/Usage</t>
           </r>
         </is>
       </c>
@@ -6773,12 +6779,9 @@
           </r>
         </is>
       </c>
-      <c r="P4" s="152" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">자가용</t>
-          </r>
-        </is>
+      <c r="P4" s="152" t="str">
+        <f>구매리스트!B8</f>
+        <v>0</v>
       </c>
       <c r="Q4" s="255"/>
     </row>
@@ -6927,7 +6930,7 @@
       <c r="M8" s="259" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">120111-0922270</t>
+            <t xml:space="preserve">110111-7526176</t>
           </r>
         </is>
       </c>
@@ -8386,12 +8389,9 @@
           </r>
         </is>
       </c>
-      <c r="P4" s="177" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Private car</t>
-          </r>
-        </is>
+      <c r="P4" s="177" t="str">
+        <f>구매리스트!B8</f>
+        <v>0</v>
       </c>
       <c r="Q4" s="255"/>
     </row>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="D8" s="254"/>
       <c r="E8" s="259" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F8" s="254"/>
       <c r="G8" s="254"/>
@@ -8553,7 +8553,7 @@
       <c r="M8" s="259" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">120111-0922270</t>
+            <t xml:space="preserve">110111-7526176</t>
           </r>
         </is>
       </c>
@@ -8676,7 +8676,7 @@
     <row r="15" spans="1:23" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
       <c r="J15" s="397" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q15" s="262"/>
       <c r="W15" s="245" t="inlineStr">
@@ -10405,7 +10405,7 @@
       <c r="K21" s="323" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">120111-0922270</t>
+            <t xml:space="preserve">110111-7526176</t>
           </r>
         </is>
       </c>
@@ -10431,9 +10431,11 @@
         </is>
       </c>
       <c r="D22" s="321"/>
-      <c r="E22" s="322"/>
-      <c r="F22" s="252"/>
-      <c r="G22" s="321"/>
+      <c r="E22" s="399" t="s">
+        <v>261</v>
+      </c>
+      <c r="F22" s="399"/>
+      <c r="G22" s="399"/>
       <c r="H22" s="186" t="inlineStr">
         <is>
           <r>
@@ -11155,7 +11157,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="E12:G13"/>
     <mergeCell ref="M6:O6"/>
-    <mergeCell ref="E21:G22"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A42:O42"/>
@@ -11213,6 +11214,8 @@
     <mergeCell ref="G34:K34"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.31496062992126" right="0.23622047244094" top="0.45" bottom="0.51181102362205" header="0.31496062992126" footer="0.31496062992126"/>
@@ -12328,7 +12331,7 @@
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A3" s="345" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D3" s="262"/>
       <c r="E3" s="228" t="inlineStr">
@@ -13329,7 +13332,7 @@
     </row>
     <row r="2" spans="1:7" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A2" s="243" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D2" s="243"/>
     </row>
@@ -13517,7 +13520,7 @@
       </c>
       <c r="B16" s="387"/>
       <c r="C16" s="388" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D16" s="387"/>
       <c r="E16" s="239" t="inlineStr">
@@ -13579,7 +13582,7 @@
       </c>
       <c r="B18" s="387"/>
       <c r="C18" s="388" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D18" s="387"/>
       <c r="E18" s="239" t="inlineStr">

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="P4" s="177" t="str">
-        <f>구매리스트!B8</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(구매리스트!B8,"자가용","Private"),"영업용","Business"),"관용","Official")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="255"/>

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="3" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
+    <workbookView activeTab="2" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="구매리스트" sheetId="1" r:id="rId4"/>
@@ -214,6 +214,9 @@
     </r>
   </si>
   <si>
+    <t>최대적재량</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Port</t>
     </r>
@@ -514,9 +517,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">경기도 시흥시 산기대학로 163, A동 328호(정왕동)</t>
-    </r>
+    <t>서울특별시 영등포구 선유동1로 50, 513호(당산동3가, THE PARK 365)</t>
   </si>
   <si>
     <r>
@@ -942,9 +943,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea </t>
-    </r>
+    <t>#513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea</t>
   </si>
   <si>
     <r>
@@ -1288,11 +1287,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">자가용</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Specification</t>
     </r>
   </si>
@@ -1596,10 +1590,10 @@
   <si>
     <r>
       <t xml:space="preserve">SSANCAR LTD.,
-163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Kore
+#513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea
 TEL:82-505-366-9977 
 FAX:82-505-366-9977
-EMAIL : man99777@naver.com</t>
+EMAIL : heyman99888@gmail.com</t>
     </r>
   </si>
   <si>
@@ -1779,10 +1773,10 @@
   </si>
   <si>
     <t>HEYMAN LTD.,
-163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea
+#513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea
 TEL:82-505-366-9977 
 FAX:82-505-366-9977
-EMAIL : man99777@naver.com</t>
+EMAIL : heyman99888@gmail.com</t>
   </si>
   <si>
     <r>
@@ -1801,7 +1795,7 @@
     </r>
   </si>
   <si>
-    <t>Heyman LTD 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea   Phone: +82-505-366-9977</t>
+    <t>Heyman LTD #513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea   Phone: +82-505-366-9977</t>
   </si>
   <si>
     <r>
@@ -1906,7 +1900,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">163 Sangidaehak-ro, Siheung-si, Gyeonggi-do,   SOUTH KOREA</t>
+      <t xml:space="preserve">#513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul,   SOUTH KOREA</t>
     </r>
   </si>
   <si>
@@ -3522,7 +3516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="400">
+  <cellXfs count="402">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4474,9 +4468,6 @@
     <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="47" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4722,6 +4713,15 @@
     </xf>
     <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="28" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="29" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="56" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5949,12 +5949,8 @@
           </r>
         </is>
       </c>
-      <c r="H9" s="103" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
+      <c r="H9" s="103" t="s">
+        <v>37</v>
       </c>
       <c r="I9" s="101" t="inlineStr">
         <is>
@@ -6873,12 +6869,8 @@
       <c r="B7" s="254"/>
       <c r="C7" s="254"/>
       <c r="D7" s="255"/>
-      <c r="E7" s="257" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">경기도 시흥시 산기대학로 163, A동 328호(정왕동)</t>
-          </r>
-        </is>
+      <c r="E7" s="257" t="s">
+        <v>97</v>
       </c>
       <c r="F7" s="254"/>
       <c r="G7" s="254"/>
@@ -6911,7 +6903,7 @@
       </c>
       <c r="D8" s="254"/>
       <c r="E8" s="259" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F8" s="254"/>
       <c r="G8" s="254"/>
@@ -7038,8 +7030,8 @@
     </row>
     <row r="15" spans="1:20" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
-      <c r="J15" s="396" t="s">
-        <v>104</v>
+      <c r="J15" s="395" t="s">
+        <v>105</v>
       </c>
       <c r="Q15" s="262"/>
     </row>
@@ -7415,7 +7407,8 @@
           </r>
         </is>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="11" t="str">
+        <f>구매리스트!I9</f>
         <v>0</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
@@ -8497,12 +8490,8 @@
       <c r="B7" s="254"/>
       <c r="C7" s="254"/>
       <c r="D7" s="255"/>
-      <c r="E7" s="257" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea </t>
-          </r>
-        </is>
+      <c r="E7" s="257" t="s">
+        <v>183</v>
       </c>
       <c r="F7" s="254"/>
       <c r="G7" s="254"/>
@@ -8535,7 +8524,7 @@
       </c>
       <c r="D8" s="254"/>
       <c r="E8" s="259" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F8" s="254"/>
       <c r="G8" s="254"/>
@@ -8675,8 +8664,8 @@
     </row>
     <row r="15" spans="1:23" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
-      <c r="J15" s="397" t="s">
-        <v>189</v>
+      <c r="J15" s="396" t="s">
+        <v>190</v>
       </c>
       <c r="Q15" s="262"/>
       <c r="W15" s="245" t="inlineStr">
@@ -9041,7 +9030,8 @@
           </r>
         </is>
       </c>
-      <c r="I23" s="120">
+      <c r="I23" s="401" t="str">
+        <f>구매리스트!I9</f>
         <v>0</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
@@ -10222,12 +10212,9 @@
       </c>
       <c r="I14" s="315"/>
       <c r="J14" s="313"/>
-      <c r="K14" s="317" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">자가용</t>
-          </r>
-        </is>
+      <c r="K14" s="309" t="str">
+        <f>구매리스트!B8</f>
+        <v>0</v>
       </c>
       <c r="L14" s="315"/>
       <c r="M14" s="315"/>
@@ -10259,18 +10246,18 @@
           </r>
         </is>
       </c>
-      <c r="D16" s="318"/>
-      <c r="E16" s="319"/>
-      <c r="F16" s="320"/>
-      <c r="G16" s="318"/>
-      <c r="H16" s="319"/>
-      <c r="I16" s="320"/>
-      <c r="J16" s="318"/>
-      <c r="K16" s="319"/>
-      <c r="L16" s="320"/>
-      <c r="M16" s="320"/>
-      <c r="N16" s="320"/>
-      <c r="O16" s="320"/>
+      <c r="D16" s="317"/>
+      <c r="E16" s="318"/>
+      <c r="F16" s="319"/>
+      <c r="G16" s="317"/>
+      <c r="H16" s="318"/>
+      <c r="I16" s="319"/>
+      <c r="J16" s="317"/>
+      <c r="K16" s="318"/>
+      <c r="L16" s="319"/>
+      <c r="M16" s="319"/>
+      <c r="N16" s="319"/>
+      <c r="O16" s="319"/>
     </row>
     <row r="17" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
       <c r="B17" s="304"/>
@@ -10327,7 +10314,7 @@
     </row>
     <row r="19" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A19" s="252"/>
-      <c r="B19" s="321"/>
+      <c r="B19" s="320"/>
       <c r="C19" s="182" t="inlineStr">
         <is>
           <r>
@@ -10335,10 +10322,10 @@
           </r>
         </is>
       </c>
-      <c r="D19" s="321"/>
-      <c r="E19" s="322"/>
+      <c r="D19" s="320"/>
+      <c r="E19" s="321"/>
       <c r="F19" s="252"/>
-      <c r="G19" s="321"/>
+      <c r="G19" s="320"/>
       <c r="H19" s="182" t="inlineStr">
         <is>
           <r>
@@ -10347,8 +10334,8 @@
         </is>
       </c>
       <c r="I19" s="252"/>
-      <c r="J19" s="321"/>
-      <c r="K19" s="322"/>
+      <c r="J19" s="320"/>
+      <c r="K19" s="321"/>
       <c r="L19" s="252"/>
       <c r="M19" s="252"/>
       <c r="N19" s="252"/>
@@ -10388,7 +10375,7 @@
         </is>
       </c>
       <c r="D21" s="303"/>
-      <c r="E21" s="323" t="s">
+      <c r="E21" s="399" t="s">
         <v>258</v>
       </c>
       <c r="F21" s="250"/>
@@ -10402,7 +10389,7 @@
       </c>
       <c r="I21" s="250"/>
       <c r="J21" s="303"/>
-      <c r="K21" s="323" t="inlineStr">
+      <c r="K21" s="322" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">110111-7526176</t>
@@ -10422,7 +10409,7 @@
           </r>
         </is>
       </c>
-      <c r="B22" s="321"/>
+      <c r="B22" s="320"/>
       <c r="C22" s="182" t="inlineStr">
         <is>
           <r>
@@ -10430,12 +10417,12 @@
           </r>
         </is>
       </c>
-      <c r="D22" s="321"/>
-      <c r="E22" s="399" t="s">
+      <c r="D22" s="320"/>
+      <c r="E22" s="398" t="s">
         <v>261</v>
       </c>
-      <c r="F22" s="399"/>
-      <c r="G22" s="399"/>
+      <c r="F22" s="398"/>
+      <c r="G22" s="398"/>
       <c r="H22" s="186" t="inlineStr">
         <is>
           <r>
@@ -10445,12 +10432,12 @@
         </is>
       </c>
       <c r="I22" s="252"/>
-      <c r="J22" s="321"/>
-      <c r="K22" s="322"/>
+      <c r="J22" s="320"/>
+      <c r="K22" s="321"/>
       <c r="L22" s="252"/>
       <c r="M22" s="252"/>
       <c r="N22" s="252"/>
-      <c r="O22" s="321"/>
+      <c r="O22" s="320"/>
     </row>
     <row r="23" spans="1:15" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A23" s="84"/>
@@ -10480,7 +10467,7 @@
       <c r="B24" s="250"/>
       <c r="C24" s="250"/>
       <c r="D24" s="303"/>
-      <c r="E24" s="324" t="str">
+      <c r="E24" s="323" t="str">
         <f>구매리스트!B7</f>
         <v>0</v>
       </c>
@@ -10495,7 +10482,7 @@
       </c>
       <c r="I24" s="250"/>
       <c r="J24" s="303"/>
-      <c r="K24" s="325" t="inlineStr">
+      <c r="K24" s="324" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">증명용</t>
@@ -10515,12 +10502,12 @@
           </r>
         </is>
       </c>
-      <c r="B25" s="326"/>
-      <c r="C25" s="326"/>
-      <c r="D25" s="327"/>
-      <c r="E25" s="328"/>
-      <c r="F25" s="326"/>
-      <c r="G25" s="327"/>
+      <c r="B25" s="325"/>
+      <c r="C25" s="325"/>
+      <c r="D25" s="326"/>
+      <c r="E25" s="327"/>
+      <c r="F25" s="325"/>
+      <c r="G25" s="326"/>
       <c r="H25" s="215" t="inlineStr">
         <is>
           <r>
@@ -10528,13 +10515,13 @@
           </r>
         </is>
       </c>
-      <c r="I25" s="326"/>
-      <c r="J25" s="327"/>
-      <c r="K25" s="328"/>
-      <c r="L25" s="326"/>
-      <c r="M25" s="326"/>
-      <c r="N25" s="326"/>
-      <c r="O25" s="327"/>
+      <c r="I25" s="325"/>
+      <c r="J25" s="326"/>
+      <c r="K25" s="327"/>
+      <c r="L25" s="325"/>
+      <c r="M25" s="325"/>
+      <c r="N25" s="325"/>
+      <c r="O25" s="326"/>
     </row>
     <row r="26" spans="1:15" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A26" s="213" t="inlineStr">
@@ -10597,10 +10584,10 @@
       </c>
       <c r="B27" s="252"/>
       <c r="C27" s="252"/>
-      <c r="D27" s="321"/>
-      <c r="E27" s="322"/>
+      <c r="D27" s="320"/>
+      <c r="E27" s="321"/>
       <c r="F27" s="252"/>
-      <c r="G27" s="321"/>
+      <c r="G27" s="320"/>
       <c r="H27" s="182" t="inlineStr">
         <is>
           <r>
@@ -10609,7 +10596,7 @@
         </is>
       </c>
       <c r="I27" s="252"/>
-      <c r="J27" s="321"/>
+      <c r="J27" s="320"/>
       <c r="K27" s="98" t="inlineStr">
         <is>
           <r>
@@ -10736,8 +10723,8 @@
       <c r="D34" s="77"/>
       <c r="E34" s="77"/>
       <c r="F34" s="77"/>
-      <c r="G34" s="398" t="s">
-        <v>104</v>
+      <c r="G34" s="397" t="s">
+        <v>105</v>
       </c>
       <c r="H34" s="77"/>
       <c r="I34" s="77"/>
@@ -10789,20 +10776,20 @@
           </r>
         </is>
       </c>
-      <c r="B38" s="329"/>
-      <c r="C38" s="329"/>
-      <c r="D38" s="329"/>
-      <c r="E38" s="329"/>
-      <c r="F38" s="329"/>
-      <c r="G38" s="329"/>
-      <c r="H38" s="329"/>
-      <c r="I38" s="329"/>
-      <c r="J38" s="329"/>
-      <c r="K38" s="329"/>
-      <c r="L38" s="329"/>
-      <c r="M38" s="329"/>
-      <c r="N38" s="329"/>
-      <c r="O38" s="329"/>
+      <c r="B38" s="328"/>
+      <c r="C38" s="328"/>
+      <c r="D38" s="328"/>
+      <c r="E38" s="328"/>
+      <c r="F38" s="328"/>
+      <c r="G38" s="328"/>
+      <c r="H38" s="328"/>
+      <c r="I38" s="328"/>
+      <c r="J38" s="328"/>
+      <c r="K38" s="328"/>
+      <c r="L38" s="328"/>
+      <c r="M38" s="328"/>
+      <c r="N38" s="328"/>
+      <c r="O38" s="328"/>
     </row>
     <row r="39" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A39" s="220" t="inlineStr">
@@ -10812,20 +10799,20 @@
           </r>
         </is>
       </c>
-      <c r="B39" s="330"/>
-      <c r="C39" s="330"/>
-      <c r="D39" s="330"/>
-      <c r="E39" s="330"/>
-      <c r="F39" s="330"/>
-      <c r="G39" s="330"/>
-      <c r="H39" s="330"/>
-      <c r="I39" s="330"/>
-      <c r="J39" s="330"/>
-      <c r="K39" s="330"/>
-      <c r="L39" s="330"/>
-      <c r="M39" s="330"/>
-      <c r="N39" s="330"/>
-      <c r="O39" s="330"/>
+      <c r="B39" s="329"/>
+      <c r="C39" s="329"/>
+      <c r="D39" s="329"/>
+      <c r="E39" s="329"/>
+      <c r="F39" s="329"/>
+      <c r="G39" s="329"/>
+      <c r="H39" s="329"/>
+      <c r="I39" s="329"/>
+      <c r="J39" s="329"/>
+      <c r="K39" s="329"/>
+      <c r="L39" s="329"/>
+      <c r="M39" s="329"/>
+      <c r="N39" s="329"/>
+      <c r="O39" s="329"/>
     </row>
     <row r="40" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A40" s="191" t="inlineStr">
@@ -10862,15 +10849,15 @@
           </r>
         </is>
       </c>
-      <c r="B43" s="331"/>
-      <c r="C43" s="331"/>
-      <c r="D43" s="331"/>
-      <c r="E43" s="331"/>
-      <c r="F43" s="331"/>
-      <c r="G43" s="331"/>
-      <c r="H43" s="331"/>
-      <c r="I43" s="331"/>
-      <c r="J43" s="332"/>
+      <c r="B43" s="330"/>
+      <c r="C43" s="330"/>
+      <c r="D43" s="330"/>
+      <c r="E43" s="330"/>
+      <c r="F43" s="330"/>
+      <c r="G43" s="330"/>
+      <c r="H43" s="330"/>
+      <c r="I43" s="330"/>
+      <c r="J43" s="331"/>
       <c r="K43" s="222" t="inlineStr">
         <is>
           <r>
@@ -10878,10 +10865,10 @@
           </r>
         </is>
       </c>
-      <c r="L43" s="331"/>
-      <c r="M43" s="331"/>
-      <c r="N43" s="331"/>
-      <c r="O43" s="332"/>
+      <c r="L43" s="330"/>
+      <c r="M43" s="330"/>
+      <c r="N43" s="330"/>
+      <c r="O43" s="331"/>
     </row>
     <row r="44" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A44" s="76" t="inlineStr">
@@ -10910,7 +10897,7 @@
       <c r="L44" s="308"/>
       <c r="M44" s="308"/>
       <c r="N44" s="308"/>
-      <c r="O44" s="333"/>
+      <c r="O44" s="332"/>
     </row>
     <row r="45" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A45" s="76" t="inlineStr">
@@ -10929,8 +10916,8 @@
       <c r="H45" s="76"/>
       <c r="I45" s="76"/>
       <c r="J45" s="76"/>
-      <c r="K45" s="334"/>
-      <c r="O45" s="335"/>
+      <c r="K45" s="333"/>
+      <c r="O45" s="334"/>
     </row>
     <row r="46" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A46" s="223" t="inlineStr">
@@ -10940,8 +10927,8 @@
           </r>
         </is>
       </c>
-      <c r="K46" s="334"/>
-      <c r="O46" s="335"/>
+      <c r="K46" s="333"/>
+      <c r="O46" s="334"/>
     </row>
     <row r="47" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A47" s="191" t="inlineStr">
@@ -10951,8 +10938,8 @@
           </r>
         </is>
       </c>
-      <c r="K47" s="334"/>
-      <c r="O47" s="335"/>
+      <c r="K47" s="333"/>
+      <c r="O47" s="334"/>
     </row>
     <row r="48" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A48" s="191" t="inlineStr">
@@ -10962,8 +10949,8 @@
           </r>
         </is>
       </c>
-      <c r="K48" s="334"/>
-      <c r="O48" s="335"/>
+      <c r="K48" s="333"/>
+      <c r="O48" s="334"/>
     </row>
     <row r="49" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A49" s="191" t="inlineStr">
@@ -10974,8 +10961,8 @@
         </is>
       </c>
       <c r="B49" s="245"/>
-      <c r="K49" s="334"/>
-      <c r="O49" s="335"/>
+      <c r="K49" s="333"/>
+      <c r="O49" s="334"/>
     </row>
     <row r="50" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A50" s="195" t="inlineStr">
@@ -10994,7 +10981,7 @@
       <c r="H50" s="308"/>
       <c r="I50" s="308"/>
       <c r="J50" s="308"/>
-      <c r="K50" s="336" t="inlineStr">
+      <c r="K50" s="335" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록일부터 6개월 이내</t>
@@ -11004,7 +10991,7 @@
       <c r="L50" s="308"/>
       <c r="M50" s="308"/>
       <c r="N50" s="308"/>
-      <c r="O50" s="333"/>
+      <c r="O50" s="332"/>
     </row>
     <row r="51" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A51" s="192" t="inlineStr">
@@ -11023,11 +11010,11 @@
       <c r="H51" s="312"/>
       <c r="I51" s="312"/>
       <c r="J51" s="312"/>
-      <c r="K51" s="337"/>
+      <c r="K51" s="336"/>
       <c r="L51" s="312"/>
       <c r="M51" s="312"/>
       <c r="N51" s="312"/>
-      <c r="O51" s="338"/>
+      <c r="O51" s="337"/>
     </row>
     <row r="52" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A52" s="193" t="inlineStr">
@@ -11037,15 +11024,15 @@
           </r>
         </is>
       </c>
-      <c r="B52" s="339"/>
-      <c r="C52" s="339"/>
-      <c r="D52" s="339"/>
-      <c r="E52" s="339"/>
-      <c r="F52" s="339"/>
-      <c r="G52" s="339"/>
-      <c r="H52" s="339"/>
-      <c r="I52" s="339"/>
-      <c r="J52" s="339"/>
+      <c r="B52" s="338"/>
+      <c r="C52" s="338"/>
+      <c r="D52" s="338"/>
+      <c r="E52" s="338"/>
+      <c r="F52" s="338"/>
+      <c r="G52" s="338"/>
+      <c r="H52" s="338"/>
+      <c r="I52" s="338"/>
+      <c r="J52" s="338"/>
       <c r="K52" s="194" t="inlineStr">
         <is>
           <r>
@@ -11053,10 +11040,10 @@
           </r>
         </is>
       </c>
-      <c r="L52" s="339"/>
-      <c r="M52" s="339"/>
-      <c r="N52" s="339"/>
-      <c r="O52" s="340"/>
+      <c r="L52" s="338"/>
+      <c r="M52" s="338"/>
+      <c r="N52" s="338"/>
+      <c r="O52" s="339"/>
     </row>
     <row r="53" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A53" s="189" t="inlineStr">
@@ -11074,7 +11061,7 @@
       <c r="G53" s="252"/>
       <c r="H53" s="252"/>
       <c r="I53" s="252"/>
-      <c r="J53" s="341"/>
+      <c r="J53" s="340"/>
       <c r="K53" s="188" t="inlineStr">
         <is>
           <r>
@@ -11255,7 +11242,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="47.25" s="245" customFormat="1">
-      <c r="A1" s="342" t="inlineStr">
+      <c r="A1" s="341" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">COMMERCIAL INVOICE</t>
@@ -11272,7 +11259,7 @@
       <c r="I1" s="255"/>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A2" s="343" t="inlineStr">
+      <c r="A2" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1) Shipper / Exporter</t>
@@ -11294,7 +11281,7 @@
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
-      <c r="H2" s="344" t="inlineStr">
+      <c r="H2" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">ORIGINAL</t>
@@ -11304,14 +11291,14 @@
       <c r="I2" s="251"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A3" s="345" t="inlineStr">
+      <c r="A3" s="344" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SSANCAR LTD.,
-163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Kore
+#513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea
 TEL:82-505-366-9977 
 FAX:82-505-366-9977
-EMAIL : man99777@naver.com</t>
+EMAIL : heyman99888@gmail.com</t>
           </r>
         </is>
       </c>
@@ -11333,7 +11320,7 @@
     <row r="4" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A4" s="271"/>
       <c r="D4" s="262"/>
-      <c r="E4" s="346" t="inlineStr">
+      <c r="E4" s="345" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">CERTIFICATE OF ORIGIN</t>
@@ -11351,7 +11338,7 @@
     <row r="6" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A6" s="271"/>
       <c r="D6" s="262"/>
-      <c r="E6" s="347" t="inlineStr">
+      <c r="E6" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Issued by</t>
@@ -11365,7 +11352,7 @@
       <c r="B7" s="252"/>
       <c r="C7" s="252"/>
       <c r="D7" s="253"/>
-      <c r="E7" s="347" t="inlineStr">
+      <c r="E7" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">THE KOREA CHAMBER OF COMMERCE &amp; INDUSTRY</t>
@@ -11375,7 +11362,7 @@
       <c r="I7" s="262"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A8" s="343" t="inlineStr">
+      <c r="A8" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2) For account &amp; risk of Messers.</t>
@@ -11385,7 +11372,7 @@
       <c r="B8" s="250"/>
       <c r="C8" s="250"/>
       <c r="D8" s="251"/>
-      <c r="E8" s="348" t="inlineStr">
+      <c r="E8" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Seoul, Republic of korea</t>
@@ -11398,7 +11385,7 @@
       <c r="I8" s="253"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="245" customFormat="1">
-      <c r="A9" s="349" t="str">
+      <c r="A9" s="348" t="str">
         <f>구매리스트!B14</f>
         <v>0</v>
       </c>
@@ -11452,7 +11439,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A12" s="343" t="inlineStr">
+      <c r="A12" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3) Notify party</t>
@@ -11462,7 +11449,7 @@
       <c r="B12" s="250"/>
       <c r="C12" s="250"/>
       <c r="D12" s="251"/>
-      <c r="E12" s="343" t="inlineStr">
+      <c r="E12" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">9) No. &amp; date of L/C</t>
@@ -11475,7 +11462,7 @@
       <c r="I12" s="251"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A13" s="350" t="inlineStr">
+      <c r="A13" s="349" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SAME AS ABOVE</t>
@@ -11504,7 +11491,7 @@
       <c r="I14" s="253"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
-      <c r="A15" s="343" t="inlineStr">
+      <c r="A15" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">4) Port of loading</t>
@@ -11538,12 +11525,12 @@
         <v>0</v>
       </c>
       <c r="B16" s="252"/>
-      <c r="C16" s="351" t="str">
+      <c r="C16" s="350" t="str">
         <f>구매리스트!D10</f>
         <v>0</v>
       </c>
       <c r="D16" s="253"/>
-      <c r="E16" s="352" t="inlineStr">
+      <c r="E16" s="351" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11553,7 +11540,7 @@
       <c r="I16" s="262"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
-      <c r="A17" s="343" t="inlineStr">
+      <c r="A17" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">6) Vessel name</t>
@@ -11569,7 +11556,7 @@
         </is>
       </c>
       <c r="D17" s="251"/>
-      <c r="E17" s="353" t="str">
+      <c r="E17" s="352" t="str">
         <f>구매리스트!D12</f>
         <v>0</v>
       </c>
@@ -11579,12 +11566,12 @@
       <c r="I17" s="251"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
-      <c r="A18" s="351" t="str">
+      <c r="A18" s="350" t="str">
         <f>구매리스트!B11</f>
         <v>0</v>
       </c>
       <c r="B18" s="253"/>
-      <c r="C18" s="354" t="str">
+      <c r="C18" s="353" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
@@ -11612,7 +11599,7 @@
         </is>
       </c>
       <c r="D19" s="26"/>
-      <c r="E19" s="355" t="inlineStr">
+      <c r="E19" s="354" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">13) Quantity</t>
@@ -11682,7 +11669,7 @@
           </r>
         </is>
       </c>
-      <c r="E21" s="356" t="inlineStr">
+      <c r="E21" s="355" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Q'TY</t>
@@ -11690,21 +11677,21 @@
         </is>
       </c>
       <c r="F21" s="255"/>
-      <c r="G21" s="357" t="inlineStr">
+      <c r="G21" s="356" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Unit Price</t>
           </r>
         </is>
       </c>
-      <c r="H21" s="358" t="inlineStr">
+      <c r="H21" s="357" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">AMOUNT</t>
           </r>
         </is>
       </c>
-      <c r="I21" s="359" t="inlineStr">
+      <c r="I21" s="358" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Shipping</t>
@@ -11714,7 +11701,7 @@
       <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A22" s="360">
+      <c r="A22" s="359">
         <v>1</v>
       </c>
       <c r="B22" s="123" t="str">
@@ -11729,7 +11716,7 @@
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="E22" s="361">
+      <c r="E22" s="400">
         <v>1</v>
       </c>
       <c r="F22" s="255"/>
@@ -11751,8 +11738,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A23" s="363"/>
-      <c r="B23" s="364"/>
+      <c r="A23" s="362"/>
+      <c r="B23" s="363"/>
       <c r="C23" s="254"/>
       <c r="D23" s="254"/>
       <c r="E23" s="254"/>
@@ -11760,13 +11747,13 @@
       <c r="G23" s="254"/>
       <c r="H23" s="254"/>
       <c r="I23" s="255"/>
-      <c r="J23" s="362"/>
+      <c r="J23" s="361"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A24" s="363">
+      <c r="A24" s="362">
         <v>2</v>
       </c>
-      <c r="B24" s="365" t="inlineStr">
+      <c r="B24" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11787,9 +11774,9 @@
           </r>
         </is>
       </c>
-      <c r="E24" s="366"/>
+      <c r="E24" s="365"/>
       <c r="F24" s="255"/>
-      <c r="G24" s="367" t="inlineStr">
+      <c r="G24" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11803,20 +11790,20 @@
           </r>
         </is>
       </c>
-      <c r="I24" s="368" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J24" s="362">
+      <c r="I24" s="367" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J24" s="361">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A25" s="363"/>
-      <c r="B25" s="364" t="inlineStr">
+      <c r="A25" s="362"/>
+      <c r="B25" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11830,13 +11817,13 @@
       <c r="G25" s="254"/>
       <c r="H25" s="254"/>
       <c r="I25" s="255"/>
-      <c r="J25" s="362"/>
+      <c r="J25" s="361"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A26" s="363">
+      <c r="A26" s="362">
         <v>3</v>
       </c>
-      <c r="B26" s="365" t="inlineStr">
+      <c r="B26" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11857,9 +11844,9 @@
           </r>
         </is>
       </c>
-      <c r="E26" s="366"/>
+      <c r="E26" s="365"/>
       <c r="F26" s="255"/>
-      <c r="G26" s="367" t="inlineStr">
+      <c r="G26" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11873,20 +11860,20 @@
           </r>
         </is>
       </c>
-      <c r="I26" s="368" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J26" s="362">
+      <c r="I26" s="367" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="361">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A27" s="363"/>
-      <c r="B27" s="364" t="inlineStr">
+      <c r="A27" s="362"/>
+      <c r="B27" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11900,13 +11887,13 @@
       <c r="G27" s="254"/>
       <c r="H27" s="254"/>
       <c r="I27" s="255"/>
-      <c r="J27" s="362"/>
+      <c r="J27" s="361"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A28" s="363">
+      <c r="A28" s="362">
         <v>4</v>
       </c>
-      <c r="B28" s="369" t="inlineStr">
+      <c r="B28" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11927,9 +11914,9 @@
           </r>
         </is>
       </c>
-      <c r="E28" s="366"/>
+      <c r="E28" s="365"/>
       <c r="F28" s="255"/>
-      <c r="G28" s="367" t="inlineStr">
+      <c r="G28" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11943,26 +11930,26 @@
           </r>
         </is>
       </c>
-      <c r="I28" s="368" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J28" s="362">
+      <c r="I28" s="367" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="361">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A29" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B29" s="364" t="inlineStr">
+      <c r="A29" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11979,10 +11966,10 @@
       <c r="J29" s="18"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A30" s="363">
+      <c r="A30" s="362">
         <v>5</v>
       </c>
-      <c r="B30" s="369" t="inlineStr">
+      <c r="B30" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12003,9 +11990,9 @@
           </r>
         </is>
       </c>
-      <c r="E30" s="366"/>
+      <c r="E30" s="365"/>
       <c r="F30" s="255"/>
-      <c r="G30" s="367" t="inlineStr">
+      <c r="G30" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12019,7 +12006,7 @@
           </r>
         </is>
       </c>
-      <c r="I30" s="368" t="inlineStr">
+      <c r="I30" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12029,14 +12016,14 @@
       <c r="J30" s="18"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A31" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B31" s="364" t="inlineStr">
+      <c r="A31" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B31" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12061,7 +12048,7 @@
           </r>
         </is>
       </c>
-      <c r="C32" s="370"/>
+      <c r="C32" s="369"/>
       <c r="D32" s="233" t="inlineStr">
         <is>
           <r>
@@ -12069,14 +12056,14 @@
           </r>
         </is>
       </c>
-      <c r="E32" s="370"/>
+      <c r="E32" s="369"/>
       <c r="F32" s="233"/>
       <c r="G32" s="233"/>
       <c r="H32" s="227" t="str">
         <f>SUM(H22:I22,H24:I24,H26:I26,H28:I28,H30:I30)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="371"/>
+      <c r="I32" s="370"/>
       <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10">
@@ -12281,7 +12268,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="47.25" s="245" customFormat="1">
-      <c r="A1" s="342" t="inlineStr">
+      <c r="A1" s="341" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">COMMERCIAL PACKING LIST</t>
@@ -12298,7 +12285,7 @@
       <c r="I1" s="255"/>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A2" s="343" t="inlineStr">
+      <c r="A2" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1) Shipper / Exporter</t>
@@ -12320,7 +12307,7 @@
         <f>차량인보이스!G2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="344" t="inlineStr">
+      <c r="H2" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">ORIGINAL</t>
@@ -12330,7 +12317,7 @@
       <c r="I2" s="251"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A3" s="345" t="s">
+      <c r="A3" s="344" t="s">
         <v>347</v>
       </c>
       <c r="D3" s="262"/>
@@ -12351,7 +12338,7 @@
     <row r="4" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A4" s="271"/>
       <c r="D4" s="262"/>
-      <c r="E4" s="346" t="inlineStr">
+      <c r="E4" s="345" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">CERTIFICATE OF ORIGIN</t>
@@ -12369,7 +12356,7 @@
     <row r="6" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A6" s="271"/>
       <c r="D6" s="262"/>
-      <c r="E6" s="347" t="inlineStr">
+      <c r="E6" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Issued by</t>
@@ -12383,7 +12370,7 @@
       <c r="B7" s="252"/>
       <c r="C7" s="252"/>
       <c r="D7" s="253"/>
-      <c r="E7" s="347" t="inlineStr">
+      <c r="E7" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">THE KOREA CHAMBER OF COMMERCE &amp; INDUSTRY</t>
@@ -12393,7 +12380,7 @@
       <c r="I7" s="262"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A8" s="343" t="inlineStr">
+      <c r="A8" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2) For account &amp; risk of Messers.</t>
@@ -12403,7 +12390,7 @@
       <c r="B8" s="250"/>
       <c r="C8" s="250"/>
       <c r="D8" s="251"/>
-      <c r="E8" s="348" t="inlineStr">
+      <c r="E8" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Seoul, Republic of korea</t>
@@ -12416,7 +12403,7 @@
       <c r="I8" s="253"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="245" customFormat="1">
-      <c r="A9" s="372" t="str">
+      <c r="A9" s="371" t="str">
         <f>차량인보이스!A9</f>
         <v>0</v>
       </c>
@@ -12470,7 +12457,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A12" s="343" t="inlineStr">
+      <c r="A12" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3) Notify party</t>
@@ -12480,7 +12467,7 @@
       <c r="B12" s="250"/>
       <c r="C12" s="250"/>
       <c r="D12" s="251"/>
-      <c r="E12" s="343" t="inlineStr">
+      <c r="E12" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">9) No. &amp; date of L/C</t>
@@ -12493,7 +12480,7 @@
       <c r="I12" s="251"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
-      <c r="A13" s="350" t="inlineStr">
+      <c r="A13" s="349" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SAME AS ABOVE</t>
@@ -12522,7 +12509,7 @@
       <c r="I14" s="253"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
-      <c r="A15" s="343" t="inlineStr">
+      <c r="A15" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">4) Port of loading</t>
@@ -12556,12 +12543,12 @@
         <v>0</v>
       </c>
       <c r="B16" s="252"/>
-      <c r="C16" s="351" t="str">
+      <c r="C16" s="350" t="str">
         <f>구매리스트!D10</f>
         <v>0</v>
       </c>
       <c r="D16" s="253"/>
-      <c r="E16" s="352" t="inlineStr">
+      <c r="E16" s="351" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12571,7 +12558,7 @@
       <c r="I16" s="262"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
-      <c r="A17" s="343" t="inlineStr">
+      <c r="A17" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">6) Vessel name</t>
@@ -12587,7 +12574,7 @@
         </is>
       </c>
       <c r="D17" s="251"/>
-      <c r="E17" s="353" t="str">
+      <c r="E17" s="352" t="str">
         <f>차량인보이스!E17</f>
         <v>0</v>
       </c>
@@ -12597,12 +12584,12 @@
       <c r="I17" s="251"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
-      <c r="A18" s="351" t="str">
+      <c r="A18" s="350" t="str">
         <f>구매리스트!B11</f>
         <v>0</v>
       </c>
       <c r="B18" s="253"/>
-      <c r="C18" s="354" t="str">
+      <c r="C18" s="353" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
@@ -12630,7 +12617,7 @@
         </is>
       </c>
       <c r="D19" s="26"/>
-      <c r="E19" s="355" t="inlineStr">
+      <c r="E19" s="354" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">13) Quantity</t>
@@ -12700,7 +12687,7 @@
           </r>
         </is>
       </c>
-      <c r="E21" s="356" t="inlineStr">
+      <c r="E21" s="355" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Q'TY</t>
@@ -12708,14 +12695,14 @@
         </is>
       </c>
       <c r="F21" s="255"/>
-      <c r="G21" s="357" t="inlineStr">
+      <c r="G21" s="356" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Unit Price</t>
           </r>
         </is>
       </c>
-      <c r="H21" s="358" t="inlineStr">
+      <c r="H21" s="357" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">AMOUNT</t>
@@ -12733,7 +12720,7 @@
       <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A22" s="360">
+      <c r="A22" s="359">
         <v>1</v>
       </c>
       <c r="B22" s="123" t="str">
@@ -12748,19 +12735,19 @@
         <f>차량인보이스!D22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="361" t="str">
+      <c r="E22" s="360" t="str">
         <f>차량인보이스!E22</f>
         <v>0</v>
       </c>
       <c r="F22" s="255"/>
-      <c r="G22" s="373" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="H22" s="373" t="inlineStr">
+      <c r="G22" s="372" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="H22" s="372" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12771,7 +12758,7 @@
         <f>구매리스트!I8</f>
         <v>0</v>
       </c>
-      <c r="J22" s="362" t="inlineStr">
+      <c r="J22" s="361" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12780,8 +12767,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A23" s="363"/>
-      <c r="B23" s="364"/>
+      <c r="A23" s="362"/>
+      <c r="B23" s="363"/>
       <c r="C23" s="254"/>
       <c r="D23" s="254"/>
       <c r="E23" s="254"/>
@@ -12789,13 +12776,13 @@
       <c r="G23" s="254"/>
       <c r="H23" s="254"/>
       <c r="I23" s="255"/>
-      <c r="J23" s="362"/>
+      <c r="J23" s="361"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A24" s="363">
+      <c r="A24" s="362">
         <v>2</v>
       </c>
-      <c r="B24" s="365" t="inlineStr">
+      <c r="B24" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12816,9 +12803,9 @@
           </r>
         </is>
       </c>
-      <c r="E24" s="366"/>
+      <c r="E24" s="365"/>
       <c r="F24" s="255"/>
-      <c r="G24" s="367" t="inlineStr">
+      <c r="G24" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12832,14 +12819,14 @@
           </r>
         </is>
       </c>
-      <c r="I24" s="368" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J24" s="362" t="inlineStr">
+      <c r="I24" s="367" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J24" s="361" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12848,8 +12835,8 @@
       </c>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A25" s="363"/>
-      <c r="B25" s="364" t="inlineStr">
+      <c r="A25" s="362"/>
+      <c r="B25" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12863,13 +12850,13 @@
       <c r="G25" s="254"/>
       <c r="H25" s="254"/>
       <c r="I25" s="255"/>
-      <c r="J25" s="362"/>
+      <c r="J25" s="361"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A26" s="363">
+      <c r="A26" s="362">
         <v>3</v>
       </c>
-      <c r="B26" s="365" t="inlineStr">
+      <c r="B26" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12890,9 +12877,9 @@
           </r>
         </is>
       </c>
-      <c r="E26" s="366"/>
+      <c r="E26" s="365"/>
       <c r="F26" s="255"/>
-      <c r="G26" s="367" t="inlineStr">
+      <c r="G26" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12906,14 +12893,14 @@
           </r>
         </is>
       </c>
-      <c r="I26" s="368" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J26" s="362" t="inlineStr">
+      <c r="I26" s="367" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="361" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12922,8 +12909,8 @@
       </c>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A27" s="363"/>
-      <c r="B27" s="364" t="inlineStr">
+      <c r="A27" s="362"/>
+      <c r="B27" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12937,13 +12924,13 @@
       <c r="G27" s="254"/>
       <c r="H27" s="254"/>
       <c r="I27" s="255"/>
-      <c r="J27" s="362"/>
+      <c r="J27" s="361"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A28" s="363">
+      <c r="A28" s="362">
         <v>4</v>
       </c>
-      <c r="B28" s="369" t="inlineStr">
+      <c r="B28" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12964,9 +12951,9 @@
           </r>
         </is>
       </c>
-      <c r="E28" s="366"/>
+      <c r="E28" s="365"/>
       <c r="F28" s="255"/>
-      <c r="G28" s="367" t="inlineStr">
+      <c r="G28" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12980,14 +12967,14 @@
           </r>
         </is>
       </c>
-      <c r="I28" s="368" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J28" s="362" t="inlineStr">
+      <c r="I28" s="367" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="361" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12996,14 +12983,14 @@
       </c>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A29" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B29" s="364" t="inlineStr">
+      <c r="A29" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13020,10 +13007,10 @@
       <c r="J29" s="18"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
-      <c r="A30" s="363">
+      <c r="A30" s="362">
         <v>5</v>
       </c>
-      <c r="B30" s="369" t="inlineStr">
+      <c r="B30" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13044,9 +13031,9 @@
           </r>
         </is>
       </c>
-      <c r="E30" s="366"/>
+      <c r="E30" s="365"/>
       <c r="F30" s="255"/>
-      <c r="G30" s="367" t="inlineStr">
+      <c r="G30" s="366" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13060,7 +13047,7 @@
           </r>
         </is>
       </c>
-      <c r="I30" s="368" t="inlineStr">
+      <c r="I30" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13070,14 +13057,14 @@
       <c r="J30" s="18"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="36" s="245" customFormat="1">
-      <c r="A31" s="363" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B31" s="364" t="inlineStr">
+      <c r="A31" s="362" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B31" s="363" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13102,7 +13089,7 @@
           </r>
         </is>
       </c>
-      <c r="C32" s="370"/>
+      <c r="C32" s="369"/>
       <c r="D32" s="235" t="inlineStr">
         <is>
           <r>
@@ -13110,14 +13097,14 @@
           </r>
         </is>
       </c>
-      <c r="E32" s="370"/>
+      <c r="E32" s="369"/>
       <c r="F32" s="235"/>
       <c r="G32" s="235"/>
       <c r="H32" s="236" t="str">
         <f>SUM(I22,I24,I26,I28,I30)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="371"/>
+      <c r="I32" s="370"/>
       <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10">
@@ -13345,11 +13332,11 @@
           </r>
         </is>
       </c>
-      <c r="F3" s="374" t="str">
+      <c r="F3" s="373" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
-      <c r="G3" s="375"/>
+      <c r="G3" s="374"/>
     </row>
     <row r="4" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A4" s="47"/>
@@ -13363,11 +13350,11 @@
           </r>
         </is>
       </c>
-      <c r="F4" s="376" t="str">
+      <c r="F4" s="375" t="str">
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
-      <c r="G4" s="377"/>
+      <c r="G4" s="376"/>
     </row>
     <row r="5" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A5" s="238"/>
@@ -13379,11 +13366,11 @@
           </r>
         </is>
       </c>
-      <c r="F5" s="378" t="str">
+      <c r="F5" s="377" t="str">
         <f>구매리스트!D14</f>
         <v>0</v>
       </c>
-      <c r="G5" s="377"/>
+      <c r="G5" s="376"/>
     </row>
     <row r="6" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A6" s="238"/>
@@ -13395,8 +13382,8 @@
           </r>
         </is>
       </c>
-      <c r="F6" s="379"/>
-      <c r="G6" s="377"/>
+      <c r="F6" s="378"/>
+      <c r="G6" s="376"/>
     </row>
     <row r="7" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A7" s="238"/>
@@ -13407,8 +13394,8 @@
           </r>
         </is>
       </c>
-      <c r="F7" s="380"/>
-      <c r="G7" s="377"/>
+      <c r="F7" s="379"/>
+      <c r="G7" s="376"/>
     </row>
     <row r="8" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A8" s="238"/>
@@ -13419,8 +13406,8 @@
           </r>
         </is>
       </c>
-      <c r="F8" s="381"/>
-      <c r="G8" s="377"/>
+      <c r="F8" s="380"/>
+      <c r="G8" s="376"/>
     </row>
     <row r="9" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A9" s="238"/>
@@ -13432,8 +13419,8 @@
           </r>
         </is>
       </c>
-      <c r="F9" s="379"/>
-      <c r="G9" s="377"/>
+      <c r="F9" s="378"/>
+      <c r="G9" s="376"/>
     </row>
     <row r="10" spans="1:7" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A10" s="238"/>
@@ -13451,11 +13438,11 @@
           </r>
         </is>
       </c>
-      <c r="F11" s="382" t="str">
+      <c r="F11" s="381" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
-      <c r="G11" s="377"/>
+      <c r="G11" s="376"/>
     </row>
     <row r="12" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A12" s="237"/>
@@ -13466,11 +13453,11 @@
           </r>
         </is>
       </c>
-      <c r="F12" s="382" t="str">
+      <c r="F12" s="381" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
-      <c r="G12" s="377"/>
+      <c r="G12" s="376"/>
     </row>
     <row r="13" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A13" s="244"/>
@@ -13483,32 +13470,32 @@
           </r>
         </is>
       </c>
-      <c r="F13" s="383" t="str">
+      <c r="F13" s="382" t="str">
         <f>SUM(F11-F12)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="377"/>
+      <c r="G13" s="376"/>
     </row>
     <row r="14" spans="1:7" customHeight="1" ht="17.25" s="245" customFormat="1">
       <c r="A14" s="244"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
-      <c r="E14" s="384"/>
+      <c r="E14" s="383"/>
     </row>
     <row r="15" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
-      <c r="A15" s="385" t="inlineStr">
+      <c r="A15" s="384" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">BANK ACCOUNT INFORMATION</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="386"/>
-      <c r="C15" s="386"/>
-      <c r="D15" s="386"/>
-      <c r="E15" s="386"/>
-      <c r="F15" s="386"/>
-      <c r="G15" s="387"/>
+      <c r="B15" s="385"/>
+      <c r="C15" s="385"/>
+      <c r="D15" s="385"/>
+      <c r="E15" s="385"/>
+      <c r="F15" s="385"/>
+      <c r="G15" s="386"/>
     </row>
     <row r="16" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A16" s="239" t="inlineStr">
@@ -13518,11 +13505,11 @@
           </r>
         </is>
       </c>
-      <c r="B16" s="387"/>
-      <c r="C16" s="388" t="s">
+      <c r="B16" s="386"/>
+      <c r="C16" s="387" t="s">
         <v>363</v>
       </c>
-      <c r="D16" s="387"/>
+      <c r="D16" s="386"/>
       <c r="E16" s="239" t="inlineStr">
         <is>
           <r>
@@ -13530,14 +13517,14 @@
           </r>
         </is>
       </c>
-      <c r="F16" s="389" t="inlineStr">
+      <c r="F16" s="388" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SHINHAN BANK</t>
           </r>
         </is>
       </c>
-      <c r="G16" s="387"/>
+      <c r="G16" s="386"/>
     </row>
     <row r="17" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A17" s="239" t="inlineStr">
@@ -13547,15 +13534,15 @@
           </r>
         </is>
       </c>
-      <c r="B17" s="387"/>
-      <c r="C17" s="388" t="inlineStr">
+      <c r="B17" s="386"/>
+      <c r="C17" s="387" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SHBKKRSE</t>
           </r>
         </is>
       </c>
-      <c r="D17" s="387"/>
+      <c r="D17" s="386"/>
       <c r="E17" s="239" t="inlineStr">
         <is>
           <r>
@@ -13570,7 +13557,7 @@
           </r>
         </is>
       </c>
-      <c r="G17" s="387"/>
+      <c r="G17" s="386"/>
     </row>
     <row r="18" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A18" s="239" t="inlineStr">
@@ -13580,11 +13567,11 @@
           </r>
         </is>
       </c>
-      <c r="B18" s="387"/>
-      <c r="C18" s="388" t="s">
+      <c r="B18" s="386"/>
+      <c r="C18" s="387" t="s">
         <v>371</v>
       </c>
-      <c r="D18" s="387"/>
+      <c r="D18" s="386"/>
       <c r="E18" s="239" t="inlineStr">
         <is>
           <r>
@@ -13592,19 +13579,19 @@
           </r>
         </is>
       </c>
-      <c r="F18" s="390" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">163 Sangidaehak-ro, Siheung-si, Gyeonggi-do,   SOUTH KOREA</t>
-          </r>
-        </is>
-      </c>
-      <c r="G18" s="387"/>
+      <c r="F18" s="389" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">#513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul,   SOUTH KOREA</t>
+          </r>
+        </is>
+      </c>
+      <c r="G18" s="386"/>
     </row>
     <row r="19" spans="1:7">
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="384"/>
+      <c r="E19" s="383"/>
     </row>
     <row r="20" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A20" s="42" t="inlineStr">
@@ -13649,7 +13636,7 @@
           </r>
         </is>
       </c>
-      <c r="G20" s="387"/>
+      <c r="G20" s="386"/>
     </row>
     <row r="21" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A21" s="133" t="str">
@@ -13669,11 +13656,11 @@
         <v>0</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="391" t="str">
+      <c r="F21" s="390" t="str">
         <f>차량인보이스!H22</f>
         <v>0</v>
       </c>
-      <c r="G21" s="387"/>
+      <c r="G21" s="386"/>
     </row>
     <row r="22" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A22" s="41"/>
@@ -13681,8 +13668,8 @@
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
-      <c r="F22" s="392"/>
-      <c r="G22" s="387"/>
+      <c r="F22" s="391"/>
+      <c r="G22" s="386"/>
     </row>
     <row r="23" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A23" s="41"/>
@@ -13690,8 +13677,8 @@
       <c r="C23" s="41"/>
       <c r="D23" s="41"/>
       <c r="E23" s="41"/>
-      <c r="F23" s="392"/>
-      <c r="G23" s="387"/>
+      <c r="F23" s="391"/>
+      <c r="G23" s="386"/>
     </row>
     <row r="24" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A24" s="41"/>
@@ -13699,8 +13686,8 @@
       <c r="C24" s="41"/>
       <c r="D24" s="41"/>
       <c r="E24" s="41"/>
-      <c r="F24" s="392"/>
-      <c r="G24" s="387"/>
+      <c r="F24" s="391"/>
+      <c r="G24" s="386"/>
     </row>
     <row r="25" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A25" s="41"/>
@@ -13708,8 +13695,8 @@
       <c r="C25" s="41"/>
       <c r="D25" s="41"/>
       <c r="E25" s="41"/>
-      <c r="F25" s="392"/>
-      <c r="G25" s="387"/>
+      <c r="F25" s="391"/>
+      <c r="G25" s="386"/>
     </row>
     <row r="26" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A26" s="41"/>
@@ -13717,8 +13704,8 @@
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
       <c r="E26" s="41"/>
-      <c r="F26" s="392"/>
-      <c r="G26" s="387"/>
+      <c r="F26" s="391"/>
+      <c r="G26" s="386"/>
     </row>
     <row r="27" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A27" s="41"/>
@@ -13726,8 +13713,8 @@
       <c r="C27" s="41"/>
       <c r="D27" s="41"/>
       <c r="E27" s="41"/>
-      <c r="F27" s="392"/>
-      <c r="G27" s="387"/>
+      <c r="F27" s="391"/>
+      <c r="G27" s="386"/>
     </row>
     <row r="28" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A28" s="38"/>
@@ -13741,11 +13728,11 @@
           </r>
         </is>
       </c>
-      <c r="F28" s="393" t="str">
+      <c r="F28" s="392" t="str">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="387"/>
+      <c r="G28" s="386"/>
     </row>
     <row r="29" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A29" s="38"/>
@@ -13759,11 +13746,11 @@
           </r>
         </is>
       </c>
-      <c r="F29" s="393" t="str">
+      <c r="F29" s="392" t="str">
         <f>차량인보이스!I22</f>
         <v>0</v>
       </c>
-      <c r="G29" s="387"/>
+      <c r="G29" s="386"/>
     </row>
     <row r="30" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A30" s="38"/>
@@ -13771,8 +13758,8 @@
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
       <c r="E30" s="50"/>
-      <c r="F30" s="394"/>
-      <c r="G30" s="395"/>
+      <c r="F30" s="393"/>
+      <c r="G30" s="394"/>
     </row>
     <row r="31" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A31" s="38"/>
@@ -13786,11 +13773,11 @@
           </r>
         </is>
       </c>
-      <c r="F31" s="393" t="str">
+      <c r="F31" s="392" t="str">
         <f>SUM(F28:G29)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="387"/>
+      <c r="G31" s="386"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="38"/>

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -3516,7 +3516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="402">
+  <cellXfs count="401">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4719,9 +4719,6 @@
     </xf>
     <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="56" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9030,7 +9027,7 @@
           </r>
         </is>
       </c>
-      <c r="I23" s="401" t="str">
+      <c r="I23" s="11" t="str">
         <f>구매리스트!I9</f>
         <v>0</v>
       </c>
@@ -11434,7 +11431,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="53" t="str">
-        <f>구매리스트!D11</f>
+        <f>TODAY()</f>
         <v>0</v>
       </c>
     </row>
@@ -12452,7 +12449,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="53" t="str">
-        <f>구매리스트!D11</f>
+        <f>TODAY()</f>
         <v>0</v>
       </c>
     </row>

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="2" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
+    <workbookView activeTab="6" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="구매리스트" sheetId="1" r:id="rId4"/>
@@ -1961,7 +1961,7 @@
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="74">
+  <fonts count="71">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -2581,33 +2581,6 @@
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
     </font>
     <font>
       <b val="0"/>
@@ -4651,15 +4624,6 @@
     <xf xfId="0" fontId="20" numFmtId="168" fillId="11" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="67" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="68" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="69" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="20" numFmtId="167" fillId="11" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4669,7 +4633,7 @@
     <xf xfId="0" fontId="18" numFmtId="179" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="70" numFmtId="0" fillId="4" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="67" numFmtId="0" fillId="4" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="63" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4702,13 +4666,13 @@
     <xf xfId="0" fontId="20" numFmtId="167" fillId="6" borderId="64" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="71" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="68" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="72" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="69" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="73" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="70" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="28" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4719,6 +4683,15 @@
     </xf>
     <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="56" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="20" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="24" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="19" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7027,7 +7000,7 @@
     </row>
     <row r="15" spans="1:20" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
-      <c r="J15" s="395" t="s">
+      <c r="J15" s="392" t="s">
         <v>105</v>
       </c>
       <c r="Q15" s="262"/>
@@ -8661,7 +8634,7 @@
     </row>
     <row r="15" spans="1:23" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
-      <c r="J15" s="396" t="s">
+      <c r="J15" s="393" t="s">
         <v>190</v>
       </c>
       <c r="Q15" s="262"/>
@@ -10372,7 +10345,7 @@
         </is>
       </c>
       <c r="D21" s="303"/>
-      <c r="E21" s="399" t="s">
+      <c r="E21" s="396" t="s">
         <v>258</v>
       </c>
       <c r="F21" s="250"/>
@@ -10415,11 +10388,11 @@
         </is>
       </c>
       <c r="D22" s="320"/>
-      <c r="E22" s="398" t="s">
+      <c r="E22" s="395" t="s">
         <v>261</v>
       </c>
-      <c r="F22" s="398"/>
-      <c r="G22" s="398"/>
+      <c r="F22" s="395"/>
+      <c r="G22" s="395"/>
       <c r="H22" s="186" t="inlineStr">
         <is>
           <r>
@@ -10720,7 +10693,7 @@
       <c r="D34" s="77"/>
       <c r="E34" s="77"/>
       <c r="F34" s="77"/>
-      <c r="G34" s="397" t="s">
+      <c r="G34" s="394" t="s">
         <v>105</v>
       </c>
       <c r="H34" s="77"/>
@@ -11713,7 +11686,7 @@
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="E22" s="400">
+      <c r="E22" s="397">
         <v>1</v>
       </c>
       <c r="F22" s="255"/>
@@ -13379,7 +13352,7 @@
           </r>
         </is>
       </c>
-      <c r="F6" s="378"/>
+      <c r="F6" s="398"/>
       <c r="G6" s="376"/>
     </row>
     <row r="7" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
@@ -13391,7 +13364,7 @@
           </r>
         </is>
       </c>
-      <c r="F7" s="379"/>
+      <c r="F7" s="399"/>
       <c r="G7" s="376"/>
     </row>
     <row r="8" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
@@ -13403,7 +13376,7 @@
           </r>
         </is>
       </c>
-      <c r="F8" s="380"/>
+      <c r="F8" s="400"/>
       <c r="G8" s="376"/>
     </row>
     <row r="9" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
@@ -13416,7 +13389,7 @@
           </r>
         </is>
       </c>
-      <c r="F9" s="378"/>
+      <c r="F9" s="398"/>
       <c r="G9" s="376"/>
     </row>
     <row r="10" spans="1:7" customHeight="1" ht="18" s="245" customFormat="1">
@@ -13435,7 +13408,7 @@
           </r>
         </is>
       </c>
-      <c r="F11" s="381" t="str">
+      <c r="F11" s="378" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
@@ -13450,7 +13423,7 @@
           </r>
         </is>
       </c>
-      <c r="F12" s="381" t="str">
+      <c r="F12" s="378" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
@@ -13467,7 +13440,7 @@
           </r>
         </is>
       </c>
-      <c r="F13" s="382" t="str">
+      <c r="F13" s="379" t="str">
         <f>SUM(F11-F12)</f>
         <v>0</v>
       </c>
@@ -13477,22 +13450,22 @@
       <c r="A14" s="244"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
-      <c r="E14" s="383"/>
+      <c r="E14" s="380"/>
     </row>
     <row r="15" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
-      <c r="A15" s="384" t="inlineStr">
+      <c r="A15" s="381" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">BANK ACCOUNT INFORMATION</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="385"/>
-      <c r="C15" s="385"/>
-      <c r="D15" s="385"/>
-      <c r="E15" s="385"/>
-      <c r="F15" s="385"/>
-      <c r="G15" s="386"/>
+      <c r="B15" s="382"/>
+      <c r="C15" s="382"/>
+      <c r="D15" s="382"/>
+      <c r="E15" s="382"/>
+      <c r="F15" s="382"/>
+      <c r="G15" s="383"/>
     </row>
     <row r="16" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A16" s="239" t="inlineStr">
@@ -13502,11 +13475,11 @@
           </r>
         </is>
       </c>
-      <c r="B16" s="386"/>
-      <c r="C16" s="387" t="s">
+      <c r="B16" s="383"/>
+      <c r="C16" s="384" t="s">
         <v>363</v>
       </c>
-      <c r="D16" s="386"/>
+      <c r="D16" s="383"/>
       <c r="E16" s="239" t="inlineStr">
         <is>
           <r>
@@ -13514,14 +13487,14 @@
           </r>
         </is>
       </c>
-      <c r="F16" s="388" t="inlineStr">
+      <c r="F16" s="385" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SHINHAN BANK</t>
           </r>
         </is>
       </c>
-      <c r="G16" s="386"/>
+      <c r="G16" s="383"/>
     </row>
     <row r="17" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A17" s="239" t="inlineStr">
@@ -13531,15 +13504,15 @@
           </r>
         </is>
       </c>
-      <c r="B17" s="386"/>
-      <c r="C17" s="387" t="inlineStr">
+      <c r="B17" s="383"/>
+      <c r="C17" s="384" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SHBKKRSE</t>
           </r>
         </is>
       </c>
-      <c r="D17" s="386"/>
+      <c r="D17" s="383"/>
       <c r="E17" s="239" t="inlineStr">
         <is>
           <r>
@@ -13554,7 +13527,7 @@
           </r>
         </is>
       </c>
-      <c r="G17" s="386"/>
+      <c r="G17" s="383"/>
     </row>
     <row r="18" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A18" s="239" t="inlineStr">
@@ -13564,11 +13537,11 @@
           </r>
         </is>
       </c>
-      <c r="B18" s="386"/>
-      <c r="C18" s="387" t="s">
+      <c r="B18" s="383"/>
+      <c r="C18" s="384" t="s">
         <v>371</v>
       </c>
-      <c r="D18" s="386"/>
+      <c r="D18" s="383"/>
       <c r="E18" s="239" t="inlineStr">
         <is>
           <r>
@@ -13576,19 +13549,19 @@
           </r>
         </is>
       </c>
-      <c r="F18" s="389" t="inlineStr">
+      <c r="F18" s="386" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">#513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul,   SOUTH KOREA</t>
           </r>
         </is>
       </c>
-      <c r="G18" s="386"/>
+      <c r="G18" s="383"/>
     </row>
     <row r="19" spans="1:7">
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="383"/>
+      <c r="E19" s="380"/>
     </row>
     <row r="20" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A20" s="42" t="inlineStr">
@@ -13633,7 +13606,7 @@
           </r>
         </is>
       </c>
-      <c r="G20" s="386"/>
+      <c r="G20" s="383"/>
     </row>
     <row r="21" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A21" s="133" t="str">
@@ -13653,11 +13626,11 @@
         <v>0</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="390" t="str">
+      <c r="F21" s="387" t="str">
         <f>차량인보이스!H22</f>
         <v>0</v>
       </c>
-      <c r="G21" s="386"/>
+      <c r="G21" s="383"/>
     </row>
     <row r="22" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A22" s="41"/>
@@ -13665,8 +13638,8 @@
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
-      <c r="F22" s="391"/>
-      <c r="G22" s="386"/>
+      <c r="F22" s="388"/>
+      <c r="G22" s="383"/>
     </row>
     <row r="23" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A23" s="41"/>
@@ -13674,8 +13647,8 @@
       <c r="C23" s="41"/>
       <c r="D23" s="41"/>
       <c r="E23" s="41"/>
-      <c r="F23" s="391"/>
-      <c r="G23" s="386"/>
+      <c r="F23" s="388"/>
+      <c r="G23" s="383"/>
     </row>
     <row r="24" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A24" s="41"/>
@@ -13683,8 +13656,8 @@
       <c r="C24" s="41"/>
       <c r="D24" s="41"/>
       <c r="E24" s="41"/>
-      <c r="F24" s="391"/>
-      <c r="G24" s="386"/>
+      <c r="F24" s="388"/>
+      <c r="G24" s="383"/>
     </row>
     <row r="25" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A25" s="41"/>
@@ -13692,8 +13665,8 @@
       <c r="C25" s="41"/>
       <c r="D25" s="41"/>
       <c r="E25" s="41"/>
-      <c r="F25" s="391"/>
-      <c r="G25" s="386"/>
+      <c r="F25" s="388"/>
+      <c r="G25" s="383"/>
     </row>
     <row r="26" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A26" s="41"/>
@@ -13701,8 +13674,8 @@
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
       <c r="E26" s="41"/>
-      <c r="F26" s="391"/>
-      <c r="G26" s="386"/>
+      <c r="F26" s="388"/>
+      <c r="G26" s="383"/>
     </row>
     <row r="27" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A27" s="41"/>
@@ -13710,8 +13683,8 @@
       <c r="C27" s="41"/>
       <c r="D27" s="41"/>
       <c r="E27" s="41"/>
-      <c r="F27" s="391"/>
-      <c r="G27" s="386"/>
+      <c r="F27" s="388"/>
+      <c r="G27" s="383"/>
     </row>
     <row r="28" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A28" s="38"/>
@@ -13725,11 +13698,11 @@
           </r>
         </is>
       </c>
-      <c r="F28" s="392" t="str">
+      <c r="F28" s="389" t="str">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="386"/>
+      <c r="G28" s="383"/>
     </row>
     <row r="29" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A29" s="38"/>
@@ -13743,11 +13716,11 @@
           </r>
         </is>
       </c>
-      <c r="F29" s="392" t="str">
+      <c r="F29" s="389" t="str">
         <f>차량인보이스!I22</f>
         <v>0</v>
       </c>
-      <c r="G29" s="386"/>
+      <c r="G29" s="383"/>
     </row>
     <row r="30" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A30" s="38"/>
@@ -13755,8 +13728,8 @@
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
       <c r="E30" s="50"/>
-      <c r="F30" s="393"/>
-      <c r="G30" s="394"/>
+      <c r="F30" s="390"/>
+      <c r="G30" s="391"/>
     </row>
     <row r="31" spans="1:7" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A31" s="38"/>
@@ -13770,11 +13743,11 @@
           </r>
         </is>
       </c>
-      <c r="F31" s="392" t="str">
+      <c r="F31" s="389" t="str">
         <f>SUM(F28:G29)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="386"/>
+      <c r="G31" s="383"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="38"/>

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -4741,22 +4741,17 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="1057275" cy="1028700"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 32" descr=""/>
+        <xdr:cNvPr id="2" name="govt_seal" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -4768,16 +4763,14 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:ext cx="1057275" cy="1028700"/>
-        </a:xfrm>
+        <a:xfrm rot="0"/>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4822,43 +4815,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>457200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 4" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:ext cx="1057275" cy="1028700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
       <xdr:row>11</xdr:row>
@@ -4872,13 +4828,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 12" descr=""/>
+        <xdr:cNvPr id="2" name="그림 12" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4894,6 +4850,36 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1057275" cy="1028700"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="govt_seal" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="0"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4938,43 +4924,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>447675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 4" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:ext cx="1247775" cy="1228725"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>48</xdr:row>
@@ -4988,13 +4937,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 7" descr=""/>
+        <xdr:cNvPr id="2" name="그림 7" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5010,6 +4959,36 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>447675</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1247775" cy="1228725"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="govt_seal" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="0"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -1591,7 +1591,7 @@
     <r>
       <t xml:space="preserve">SSANCAR LTD.,
 #513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea
-TEL:82-505-366-9977 
+TEL:82-10-9009-9977 
 FAX:82-505-366-9977
 EMAIL : heyman99888@gmail.com</t>
     </r>
@@ -1774,7 +1774,7 @@
   <si>
     <t>HEYMAN LTD.,
 #513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea
-TEL:82-505-366-9977 
+TEL:82-10-9009-9977 
 FAX:82-505-366-9977
 EMAIL : heyman99888@gmail.com</t>
   </si>
@@ -4704,6 +4704,36 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1057275" cy="1028700"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="govt_seal" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="0"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -4719,13 +4749,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="그림 30" descr=""/>
+        <xdr:cNvPr id="2" name="그림 30" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4741,23 +4771,28 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
+      <xdr:colOff>638175</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1057275" cy="1028700"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="govt_seal" descr=""/>
+        <xdr:cNvPr id="1" name="govt_seal" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4771,11 +4806,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -4791,13 +4821,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="그림 3" descr=""/>
+        <xdr:cNvPr id="2" name="그림 3" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4828,13 +4858,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 12" descr=""/>
+        <xdr:cNvPr id="3" name="그림 12" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4850,23 +4880,28 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>447675</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1057275" cy="1028700"/>
+    <xdr:ext cx="1247775" cy="1228725"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="govt_seal" descr=""/>
+        <xdr:cNvPr id="1" name="govt_seal" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4880,11 +4915,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -4900,13 +4930,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="그림 2" descr=""/>
+        <xdr:cNvPr id="2" name="그림 2" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4937,13 +4967,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 7" descr=""/>
+        <xdr:cNvPr id="3" name="그림 7" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4959,36 +4989,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>447675</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1247775" cy="1228725"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="govt_seal" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="0"/>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -11245,7 +11245,7 @@
           <r>
             <t xml:space="preserve">SSANCAR LTD.,
 #513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea
-TEL:82-505-366-9977 
+TEL:82-10-9009-9977 
 FAX:82-505-366-9977
 EMAIL : heyman99888@gmail.com</t>
           </r>

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -1791,7 +1791,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">PROFORM INVOICE</t>
+      <t xml:space="preserve">PROFORMA INVOICE</t>
     </r>
   </si>
   <si>
@@ -1814,7 +1814,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Adress</t>
+      <t xml:space="preserve">Address</t>
     </r>
   </si>
   <si>
@@ -1867,7 +1867,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Swift Cose</t>
+      <t xml:space="preserve">Swift Code</t>
     </r>
   </si>
   <si>
@@ -1877,7 +1877,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Bank Adress</t>
+      <t xml:space="preserve">Bank Address</t>
     </r>
   </si>
   <si>
@@ -1895,7 +1895,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Beneficiary Adress</t>
+      <t xml:space="preserve">Beneficiary Address</t>
     </r>
   </si>
   <si>
@@ -5561,7 +5561,20 @@
     <col min="12" max="12" width="11.75" customWidth="true" style="245"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" customHeight="1" ht="26.25" s="245" customFormat="1"/>
+    <row r="1" spans="1:12" customHeight="1" ht="26.25" s="245" customFormat="1">
+      <c r="A1" s="245"/>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="245"/>
+      <c r="F1" s="245"/>
+      <c r="G1" s="245"/>
+      <c r="H1" s="245"/>
+      <c r="I1" s="245"/>
+      <c r="J1" s="245"/>
+      <c r="K1" s="245"/>
+      <c r="L1" s="245"/>
+    </row>
     <row r="2" spans="1:12" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A2" s="105" t="inlineStr">
         <is>
@@ -5570,6 +5583,10 @@
           </r>
         </is>
       </c>
+      <c r="B2" s="245"/>
+      <c r="C2" s="245"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
       <c r="F2" s="105" t="inlineStr">
         <is>
           <r>
@@ -5577,6 +5594,12 @@
           </r>
         </is>
       </c>
+      <c r="G2" s="245"/>
+      <c r="H2" s="245"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:12" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A3" s="103" t="inlineStr">
@@ -5601,6 +5624,7 @@
         </is>
       </c>
       <c r="D3" s="113"/>
+      <c r="E3" s="245"/>
       <c r="F3" s="106" t="inlineStr">
         <is>
           <r>
@@ -5619,6 +5643,9 @@
       <c r="I3" s="115">
         <v>45875</v>
       </c>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
     </row>
     <row r="4" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A4" s="103" t="inlineStr">
@@ -5678,6 +5705,9 @@
           </r>
         </is>
       </c>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
     </row>
     <row r="5" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A5" s="103" t="inlineStr">
@@ -5737,6 +5767,9 @@
           </r>
         </is>
       </c>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
     </row>
     <row r="6" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A6" s="103" t="inlineStr">
@@ -5785,6 +5818,9 @@
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G6,"승용 소형","Small Passenger"),"승용 중형","Medium Passenger"),"승용 대형","HEAVY Passenger"),"중형 승합","Medium Ven"),"대형 승합","Large Ven"),"중형 화물","Medium Cargo")</f>
         <v>0</v>
       </c>
+      <c r="J6" s="245"/>
+      <c r="K6" s="245"/>
+      <c r="L6" s="245"/>
     </row>
     <row r="7" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A7" s="103" t="inlineStr">
@@ -5828,6 +5864,9 @@
       <c r="I7" s="113">
         <v>1860</v>
       </c>
+      <c r="J7" s="245"/>
+      <c r="K7" s="245"/>
+      <c r="L7" s="245"/>
     </row>
     <row r="8" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A8" s="103" t="inlineStr">
@@ -5871,6 +5910,9 @@
       <c r="I8" s="113">
         <v>2095</v>
       </c>
+      <c r="J8" s="245"/>
+      <c r="K8" s="245"/>
+      <c r="L8" s="245"/>
     </row>
     <row r="9" spans="1:12" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A9" s="105" t="inlineStr">
@@ -5908,6 +5950,9 @@
           </r>
         </is>
       </c>
+      <c r="J9" s="245"/>
+      <c r="K9" s="245"/>
+      <c r="L9" s="245"/>
     </row>
     <row r="10" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A10" s="103" t="inlineStr">
@@ -5963,6 +6008,9 @@
       <c r="I10" s="115">
         <v>45775</v>
       </c>
+      <c r="J10" s="245"/>
+      <c r="K10" s="245"/>
+      <c r="L10" s="245"/>
     </row>
     <row r="11" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A11" s="103" t="inlineStr">
@@ -6018,6 +6066,9 @@
       <c r="I11" s="115">
         <v>46504</v>
       </c>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
     </row>
     <row r="12" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A12" s="103" t="inlineStr">
@@ -6073,6 +6124,9 @@
       <c r="I12" s="113">
         <v>163268</v>
       </c>
+      <c r="J12" s="245"/>
+      <c r="K12" s="245"/>
+      <c r="L12" s="245"/>
     </row>
     <row r="13" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A13" s="105" t="inlineStr">
@@ -6105,6 +6159,9 @@
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G13,"휘발유","GASOLINE"),"경유","DIESEL"),"LPG","LPG"),"하이브리드","HYBRID")</f>
         <v>0</v>
       </c>
+      <c r="J13" s="245"/>
+      <c r="K13" s="245"/>
+      <c r="L13" s="245"/>
     </row>
     <row r="14" spans="1:12" customHeight="1" ht="120.75" s="245" customFormat="1">
       <c r="A14" s="103" t="inlineStr">
@@ -6140,6 +6197,11 @@
       <c r="E14" s="100"/>
       <c r="F14" s="100"/>
       <c r="G14" s="100"/>
+      <c r="H14" s="245"/>
+      <c r="I14" s="245"/>
+      <c r="J14" s="245"/>
+      <c r="K14" s="245"/>
+      <c r="L14" s="245"/>
     </row>
     <row r="15" spans="1:12" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A15" s="103" t="inlineStr">
@@ -6171,11 +6233,15 @@
           </r>
         </is>
       </c>
+      <c r="H15" s="245"/>
       <c r="I15" s="245" t="str">
         <f t="array" ref="I15" aca="1" ca="1">_xlfn.TEXTJOIN(",",,
  _xlfn.UNIQUE(_xlfn.IFNA(INDEX({"GASOLIN","DIESEL","LPG"},
  MATCH(G15,{"휘발유","경유","LPG"},0)),""),1))</f>
       </c>
+      <c r="J15" s="245"/>
+      <c r="K15" s="245"/>
+      <c r="L15" s="245"/>
     </row>
     <row r="16" spans="1:12" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A16" s="100"/>
@@ -6194,6 +6260,7 @@
       <c r="E16" s="100"/>
       <c r="F16" s="100"/>
       <c r="G16" s="100"/>
+      <c r="H16" s="245"/>
       <c r="I16" s="245" t="inlineStr">
         <is>
           <r>
@@ -6201,6 +6268,9 @@
           </r>
         </is>
       </c>
+      <c r="J16" s="245"/>
+      <c r="K16" s="245"/>
+      <c r="L16" s="245"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="100"/>
@@ -6210,6 +6280,11 @@
       <c r="E17" s="100"/>
       <c r="F17" s="100"/>
       <c r="G17" s="100"/>
+      <c r="H17" s="245"/>
+      <c r="I17" s="245"/>
+      <c r="J17" s="245"/>
+      <c r="K17" s="245"/>
+      <c r="L17" s="245"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="100"/>
@@ -6225,6 +6300,11 @@
           </r>
         </is>
       </c>
+      <c r="H18" s="245"/>
+      <c r="I18" s="245"/>
+      <c r="J18" s="245"/>
+      <c r="K18" s="245"/>
+      <c r="L18" s="245"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="100"/>
@@ -6234,6 +6314,11 @@
       <c r="E19" s="100"/>
       <c r="F19" s="100"/>
       <c r="G19" s="100"/>
+      <c r="H19" s="245"/>
+      <c r="I19" s="245"/>
+      <c r="J19" s="245"/>
+      <c r="K19" s="245"/>
+      <c r="L19" s="245"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="100"/>
@@ -6243,6 +6328,11 @@
       <c r="E20" s="100"/>
       <c r="F20" s="100"/>
       <c r="G20" s="100"/>
+      <c r="H20" s="245"/>
+      <c r="I20" s="245"/>
+      <c r="J20" s="245"/>
+      <c r="K20" s="245"/>
+      <c r="L20" s="245"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="100"/>
@@ -6252,8 +6342,28 @@
       <c r="E21" s="100"/>
       <c r="F21" s="100"/>
       <c r="G21" s="100"/>
+      <c r="H21" s="245"/>
+      <c r="I21" s="245"/>
+      <c r="J21" s="245"/>
+      <c r="K21" s="245"/>
+      <c r="L21" s="245"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="245"/>
+      <c r="B22" s="245"/>
+      <c r="C22" s="245"/>
+      <c r="D22" s="245"/>
+      <c r="E22" s="245"/>
+      <c r="F22" s="245"/>
+      <c r="G22" s="245"/>
+      <c r="H22" s="245"/>
+      <c r="I22" s="245"/>
+      <c r="J22" s="245"/>
+      <c r="K22" s="245"/>
+      <c r="L22" s="245"/>
     </row>
     <row r="23" spans="1:12">
+      <c r="A23" s="245"/>
       <c r="B23" s="108" t="inlineStr">
         <is>
           <r>
@@ -6261,6 +6371,7 @@
           </r>
         </is>
       </c>
+      <c r="C23" s="245"/>
       <c r="D23" s="108" t="inlineStr">
         <is>
           <r>
@@ -6268,8 +6379,17 @@
           </r>
         </is>
       </c>
+      <c r="E23" s="245"/>
+      <c r="F23" s="245"/>
+      <c r="G23" s="245"/>
+      <c r="H23" s="245"/>
+      <c r="I23" s="245"/>
+      <c r="J23" s="245"/>
+      <c r="K23" s="245"/>
+      <c r="L23" s="245"/>
     </row>
     <row r="24" spans="1:12">
+      <c r="A24" s="245"/>
       <c r="B24" s="108" t="inlineStr">
         <is>
           <r>
@@ -6277,6 +6397,7 @@
           </r>
         </is>
       </c>
+      <c r="C24" s="245"/>
       <c r="D24" s="108" t="inlineStr">
         <is>
           <r>
@@ -6284,9 +6405,17 @@
           </r>
         </is>
       </c>
+      <c r="E24" s="245"/>
       <c r="F24" s="108"/>
+      <c r="G24" s="245"/>
+      <c r="H24" s="245"/>
+      <c r="I24" s="245"/>
+      <c r="J24" s="245"/>
+      <c r="K24" s="245"/>
+      <c r="L24" s="245"/>
     </row>
     <row r="25" spans="1:12">
+      <c r="A25" s="245"/>
       <c r="B25" s="108" t="inlineStr">
         <is>
           <r>
@@ -6294,6 +6423,7 @@
           </r>
         </is>
       </c>
+      <c r="C25" s="245"/>
       <c r="D25" s="108" t="inlineStr">
         <is>
           <r>
@@ -6301,9 +6431,17 @@
           </r>
         </is>
       </c>
+      <c r="E25" s="245"/>
       <c r="F25" s="108"/>
+      <c r="G25" s="245"/>
+      <c r="H25" s="245"/>
+      <c r="I25" s="245"/>
+      <c r="J25" s="245"/>
+      <c r="K25" s="245"/>
+      <c r="L25" s="245"/>
     </row>
     <row r="26" spans="1:12">
+      <c r="A26" s="245"/>
       <c r="B26" s="108" t="inlineStr">
         <is>
           <r>
@@ -6311,6 +6449,7 @@
           </r>
         </is>
       </c>
+      <c r="C26" s="245"/>
       <c r="D26" s="108" t="inlineStr">
         <is>
           <r>
@@ -6318,9 +6457,19 @@
           </r>
         </is>
       </c>
+      <c r="E26" s="245"/>
       <c r="F26" s="108"/>
+      <c r="G26" s="245"/>
+      <c r="H26" s="245"/>
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
+      <c r="K26" s="245"/>
+      <c r="L26" s="245"/>
     </row>
     <row r="27" spans="1:12">
+      <c r="A27" s="245"/>
+      <c r="B27" s="245"/>
+      <c r="C27" s="245"/>
       <c r="D27" s="108" t="inlineStr">
         <is>
           <r>
@@ -6328,9 +6477,19 @@
           </r>
         </is>
       </c>
+      <c r="E27" s="245"/>
       <c r="F27" s="108"/>
+      <c r="G27" s="245"/>
+      <c r="H27" s="245"/>
+      <c r="I27" s="245"/>
+      <c r="J27" s="245"/>
+      <c r="K27" s="245"/>
+      <c r="L27" s="245"/>
     </row>
     <row r="28" spans="1:12">
+      <c r="A28" s="245"/>
+      <c r="B28" s="245"/>
+      <c r="C28" s="245"/>
       <c r="D28" s="108" t="inlineStr">
         <is>
           <r>
@@ -6338,9 +6497,19 @@
           </r>
         </is>
       </c>
+      <c r="E28" s="245"/>
       <c r="F28" s="108"/>
+      <c r="G28" s="245"/>
+      <c r="H28" s="245"/>
+      <c r="I28" s="245"/>
+      <c r="J28" s="245"/>
+      <c r="K28" s="245"/>
+      <c r="L28" s="245"/>
     </row>
     <row r="29" spans="1:12">
+      <c r="A29" s="245"/>
+      <c r="B29" s="245"/>
+      <c r="C29" s="245"/>
       <c r="D29" s="109" t="inlineStr">
         <is>
           <r>
@@ -6348,9 +6517,19 @@
           </r>
         </is>
       </c>
+      <c r="E29" s="245"/>
       <c r="F29" s="108"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
+      <c r="J29" s="245"/>
+      <c r="K29" s="245"/>
+      <c r="L29" s="245"/>
     </row>
     <row r="30" spans="1:12">
+      <c r="A30" s="245"/>
+      <c r="B30" s="245"/>
+      <c r="C30" s="245"/>
       <c r="D30" s="108" t="inlineStr">
         <is>
           <r>
@@ -6358,8 +6537,19 @@
           </r>
         </is>
       </c>
+      <c r="E30" s="245"/>
+      <c r="F30" s="245"/>
+      <c r="G30" s="245"/>
+      <c r="H30" s="245"/>
+      <c r="I30" s="245"/>
+      <c r="J30" s="245"/>
+      <c r="K30" s="245"/>
+      <c r="L30" s="245"/>
     </row>
     <row r="31" spans="1:12">
+      <c r="A31" s="245"/>
+      <c r="B31" s="245"/>
+      <c r="C31" s="245"/>
       <c r="D31" s="108" t="inlineStr">
         <is>
           <r>
@@ -6367,8 +6557,19 @@
           </r>
         </is>
       </c>
+      <c r="E31" s="245"/>
+      <c r="F31" s="245"/>
+      <c r="G31" s="245"/>
+      <c r="H31" s="245"/>
+      <c r="I31" s="245"/>
+      <c r="J31" s="245"/>
+      <c r="K31" s="245"/>
+      <c r="L31" s="245"/>
     </row>
     <row r="32" spans="1:12">
+      <c r="A32" s="245"/>
+      <c r="B32" s="245"/>
+      <c r="C32" s="245"/>
       <c r="D32" s="108" t="inlineStr">
         <is>
           <r>
@@ -6376,8 +6577,19 @@
           </r>
         </is>
       </c>
+      <c r="E32" s="245"/>
+      <c r="F32" s="245"/>
+      <c r="G32" s="245"/>
+      <c r="H32" s="245"/>
+      <c r="I32" s="245"/>
+      <c r="J32" s="245"/>
+      <c r="K32" s="245"/>
+      <c r="L32" s="245"/>
     </row>
     <row r="33" spans="1:12">
+      <c r="A33" s="245"/>
+      <c r="B33" s="245"/>
+      <c r="C33" s="245"/>
       <c r="D33" s="108" t="inlineStr">
         <is>
           <r>
@@ -6385,8 +6597,19 @@
           </r>
         </is>
       </c>
+      <c r="E33" s="245"/>
+      <c r="F33" s="245"/>
+      <c r="G33" s="245"/>
+      <c r="H33" s="245"/>
+      <c r="I33" s="245"/>
+      <c r="J33" s="245"/>
+      <c r="K33" s="245"/>
+      <c r="L33" s="245"/>
     </row>
     <row r="34" spans="1:12">
+      <c r="A34" s="245"/>
+      <c r="B34" s="245"/>
+      <c r="C34" s="245"/>
       <c r="D34" s="108" t="inlineStr">
         <is>
           <r>
@@ -6394,8 +6617,19 @@
           </r>
         </is>
       </c>
+      <c r="E34" s="245"/>
+      <c r="F34" s="245"/>
+      <c r="G34" s="245"/>
+      <c r="H34" s="245"/>
+      <c r="I34" s="245"/>
+      <c r="J34" s="245"/>
+      <c r="K34" s="245"/>
+      <c r="L34" s="245"/>
     </row>
     <row r="35" spans="1:12">
+      <c r="A35" s="245"/>
+      <c r="B35" s="245"/>
+      <c r="C35" s="245"/>
       <c r="D35" s="108" t="inlineStr">
         <is>
           <r>
@@ -6403,8 +6637,19 @@
           </r>
         </is>
       </c>
+      <c r="E35" s="245"/>
+      <c r="F35" s="245"/>
+      <c r="G35" s="245"/>
+      <c r="H35" s="245"/>
+      <c r="I35" s="245"/>
+      <c r="J35" s="245"/>
+      <c r="K35" s="245"/>
+      <c r="L35" s="245"/>
     </row>
     <row r="36" spans="1:12">
+      <c r="A36" s="245"/>
+      <c r="B36" s="245"/>
+      <c r="C36" s="245"/>
       <c r="D36" s="108" t="inlineStr">
         <is>
           <r>
@@ -6412,8 +6657,19 @@
           </r>
         </is>
       </c>
+      <c r="E36" s="245"/>
+      <c r="F36" s="245"/>
+      <c r="G36" s="245"/>
+      <c r="H36" s="245"/>
+      <c r="I36" s="245"/>
+      <c r="J36" s="245"/>
+      <c r="K36" s="245"/>
+      <c r="L36" s="245"/>
     </row>
     <row r="37" spans="1:12">
+      <c r="A37" s="245"/>
+      <c r="B37" s="245"/>
+      <c r="C37" s="245"/>
       <c r="D37" s="108" t="inlineStr">
         <is>
           <r>
@@ -6421,8 +6677,19 @@
           </r>
         </is>
       </c>
+      <c r="E37" s="245"/>
+      <c r="F37" s="245"/>
+      <c r="G37" s="245"/>
+      <c r="H37" s="245"/>
+      <c r="I37" s="245"/>
+      <c r="J37" s="245"/>
+      <c r="K37" s="245"/>
+      <c r="L37" s="245"/>
     </row>
     <row r="38" spans="1:12">
+      <c r="A38" s="245"/>
+      <c r="B38" s="245"/>
+      <c r="C38" s="245"/>
       <c r="D38" s="108" t="inlineStr">
         <is>
           <r>
@@ -6430,8 +6697,19 @@
           </r>
         </is>
       </c>
+      <c r="E38" s="245"/>
+      <c r="F38" s="245"/>
+      <c r="G38" s="245"/>
+      <c r="H38" s="245"/>
+      <c r="I38" s="245"/>
+      <c r="J38" s="245"/>
+      <c r="K38" s="245"/>
+      <c r="L38" s="245"/>
     </row>
     <row r="39" spans="1:12">
+      <c r="A39" s="245"/>
+      <c r="B39" s="245"/>
+      <c r="C39" s="245"/>
       <c r="D39" s="108" t="inlineStr">
         <is>
           <r>
@@ -6439,86 +6717,380 @@
           </r>
         </is>
       </c>
+      <c r="E39" s="245"/>
+      <c r="F39" s="245"/>
+      <c r="G39" s="245"/>
+      <c r="H39" s="245"/>
+      <c r="I39" s="245"/>
+      <c r="J39" s="245"/>
+      <c r="K39" s="245"/>
+      <c r="L39" s="245"/>
     </row>
     <row r="40" spans="1:12">
+      <c r="A40" s="245"/>
+      <c r="B40" s="245"/>
+      <c r="C40" s="245"/>
       <c r="D40" s="108">
         <v>123456</v>
       </c>
+      <c r="E40" s="245"/>
+      <c r="F40" s="245"/>
+      <c r="G40" s="245"/>
+      <c r="H40" s="245"/>
+      <c r="I40" s="245"/>
+      <c r="J40" s="245"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="245"/>
     </row>
     <row r="41" spans="1:12">
+      <c r="A41" s="245"/>
+      <c r="B41" s="245"/>
+      <c r="C41" s="245"/>
       <c r="D41" s="108"/>
+      <c r="E41" s="245"/>
+      <c r="F41" s="245"/>
+      <c r="G41" s="245"/>
+      <c r="H41" s="245"/>
+      <c r="I41" s="245"/>
+      <c r="J41" s="245"/>
+      <c r="K41" s="245"/>
+      <c r="L41" s="245"/>
     </row>
     <row r="42" spans="1:12">
+      <c r="A42" s="245"/>
+      <c r="B42" s="245"/>
+      <c r="C42" s="245"/>
       <c r="D42" s="108"/>
+      <c r="E42" s="245"/>
+      <c r="F42" s="245"/>
+      <c r="G42" s="245"/>
+      <c r="H42" s="245"/>
+      <c r="I42" s="245"/>
+      <c r="J42" s="245"/>
+      <c r="K42" s="245"/>
+      <c r="L42" s="245"/>
     </row>
     <row r="43" spans="1:12">
+      <c r="A43" s="245"/>
+      <c r="B43" s="245"/>
+      <c r="C43" s="245"/>
       <c r="D43" s="108"/>
+      <c r="E43" s="245"/>
+      <c r="F43" s="245"/>
+      <c r="G43" s="245"/>
+      <c r="H43" s="245"/>
+      <c r="I43" s="245"/>
+      <c r="J43" s="245"/>
+      <c r="K43" s="245"/>
+      <c r="L43" s="245"/>
     </row>
     <row r="44" spans="1:12">
+      <c r="A44" s="245"/>
+      <c r="B44" s="245"/>
+      <c r="C44" s="245"/>
       <c r="D44" s="108"/>
+      <c r="E44" s="245"/>
+      <c r="F44" s="245"/>
+      <c r="G44" s="245"/>
+      <c r="H44" s="245"/>
+      <c r="I44" s="245"/>
+      <c r="J44" s="245"/>
+      <c r="K44" s="245"/>
+      <c r="L44" s="245"/>
     </row>
     <row r="45" spans="1:12">
+      <c r="A45" s="245"/>
+      <c r="B45" s="245"/>
+      <c r="C45" s="245"/>
       <c r="D45" s="108"/>
+      <c r="E45" s="245"/>
+      <c r="F45" s="245"/>
+      <c r="G45" s="245"/>
+      <c r="H45" s="245"/>
+      <c r="I45" s="245"/>
+      <c r="J45" s="245"/>
+      <c r="K45" s="245"/>
+      <c r="L45" s="245"/>
     </row>
     <row r="46" spans="1:12">
+      <c r="A46" s="245"/>
+      <c r="B46" s="245"/>
+      <c r="C46" s="245"/>
       <c r="D46" s="108"/>
+      <c r="E46" s="245"/>
+      <c r="F46" s="245"/>
+      <c r="G46" s="245"/>
+      <c r="H46" s="245"/>
+      <c r="I46" s="245"/>
+      <c r="J46" s="245"/>
+      <c r="K46" s="245"/>
+      <c r="L46" s="245"/>
     </row>
     <row r="47" spans="1:12">
+      <c r="A47" s="245"/>
+      <c r="B47" s="245"/>
+      <c r="C47" s="245"/>
       <c r="D47" s="108"/>
+      <c r="E47" s="245"/>
+      <c r="F47" s="245"/>
+      <c r="G47" s="245"/>
+      <c r="H47" s="245"/>
+      <c r="I47" s="245"/>
+      <c r="J47" s="245"/>
+      <c r="K47" s="245"/>
+      <c r="L47" s="245"/>
     </row>
     <row r="48" spans="1:12">
+      <c r="A48" s="245"/>
+      <c r="B48" s="245"/>
+      <c r="C48" s="245"/>
       <c r="D48" s="108"/>
+      <c r="E48" s="245"/>
+      <c r="F48" s="245"/>
+      <c r="G48" s="245"/>
+      <c r="H48" s="245"/>
+      <c r="I48" s="245"/>
+      <c r="J48" s="245"/>
+      <c r="K48" s="245"/>
+      <c r="L48" s="245"/>
     </row>
     <row r="49" spans="1:12">
+      <c r="A49" s="245"/>
+      <c r="B49" s="245"/>
+      <c r="C49" s="245"/>
       <c r="D49" s="108"/>
+      <c r="E49" s="245"/>
+      <c r="F49" s="245"/>
+      <c r="G49" s="245"/>
+      <c r="H49" s="245"/>
+      <c r="I49" s="245"/>
+      <c r="J49" s="245"/>
+      <c r="K49" s="245"/>
+      <c r="L49" s="245"/>
     </row>
     <row r="50" spans="1:12">
+      <c r="A50" s="245"/>
+      <c r="B50" s="245"/>
+      <c r="C50" s="245"/>
       <c r="D50" s="108"/>
+      <c r="E50" s="245"/>
+      <c r="F50" s="245"/>
+      <c r="G50" s="245"/>
+      <c r="H50" s="245"/>
+      <c r="I50" s="245"/>
+      <c r="J50" s="245"/>
+      <c r="K50" s="245"/>
+      <c r="L50" s="245"/>
     </row>
     <row r="51" spans="1:12">
+      <c r="A51" s="245"/>
+      <c r="B51" s="245"/>
+      <c r="C51" s="245"/>
       <c r="D51" s="108"/>
+      <c r="E51" s="245"/>
+      <c r="F51" s="245"/>
+      <c r="G51" s="245"/>
+      <c r="H51" s="245"/>
+      <c r="I51" s="245"/>
+      <c r="J51" s="245"/>
+      <c r="K51" s="245"/>
+      <c r="L51" s="245"/>
     </row>
     <row r="52" spans="1:12">
+      <c r="A52" s="245"/>
+      <c r="B52" s="245"/>
+      <c r="C52" s="245"/>
       <c r="D52" s="108"/>
+      <c r="E52" s="245"/>
+      <c r="F52" s="245"/>
+      <c r="G52" s="245"/>
+      <c r="H52" s="245"/>
+      <c r="I52" s="245"/>
+      <c r="J52" s="245"/>
+      <c r="K52" s="245"/>
+      <c r="L52" s="245"/>
     </row>
     <row r="53" spans="1:12">
+      <c r="A53" s="245"/>
+      <c r="B53" s="245"/>
+      <c r="C53" s="245"/>
       <c r="D53" s="108"/>
+      <c r="E53" s="245"/>
+      <c r="F53" s="245"/>
+      <c r="G53" s="245"/>
+      <c r="H53" s="245"/>
+      <c r="I53" s="245"/>
+      <c r="J53" s="245"/>
+      <c r="K53" s="245"/>
+      <c r="L53" s="245"/>
     </row>
     <row r="54" spans="1:12">
+      <c r="A54" s="245"/>
+      <c r="B54" s="245"/>
+      <c r="C54" s="245"/>
       <c r="D54" s="108"/>
+      <c r="E54" s="245"/>
+      <c r="F54" s="245"/>
+      <c r="G54" s="245"/>
+      <c r="H54" s="245"/>
+      <c r="I54" s="245"/>
+      <c r="J54" s="245"/>
+      <c r="K54" s="245"/>
+      <c r="L54" s="245"/>
     </row>
     <row r="55" spans="1:12">
+      <c r="A55" s="245"/>
+      <c r="B55" s="245"/>
+      <c r="C55" s="245"/>
       <c r="D55" s="108"/>
+      <c r="E55" s="245"/>
+      <c r="F55" s="245"/>
+      <c r="G55" s="245"/>
+      <c r="H55" s="245"/>
+      <c r="I55" s="245"/>
+      <c r="J55" s="245"/>
+      <c r="K55" s="245"/>
+      <c r="L55" s="245"/>
     </row>
     <row r="56" spans="1:12">
+      <c r="A56" s="245"/>
+      <c r="B56" s="245"/>
+      <c r="C56" s="245"/>
       <c r="D56" s="108"/>
+      <c r="E56" s="245"/>
+      <c r="F56" s="245"/>
+      <c r="G56" s="245"/>
+      <c r="H56" s="245"/>
+      <c r="I56" s="245"/>
+      <c r="J56" s="245"/>
+      <c r="K56" s="245"/>
+      <c r="L56" s="245"/>
     </row>
     <row r="57" spans="1:12">
+      <c r="A57" s="245"/>
+      <c r="B57" s="245"/>
+      <c r="C57" s="245"/>
       <c r="D57" s="108"/>
+      <c r="E57" s="245"/>
+      <c r="F57" s="245"/>
+      <c r="G57" s="245"/>
+      <c r="H57" s="245"/>
+      <c r="I57" s="245"/>
+      <c r="J57" s="245"/>
+      <c r="K57" s="245"/>
+      <c r="L57" s="245"/>
     </row>
     <row r="58" spans="1:12">
+      <c r="A58" s="245"/>
+      <c r="B58" s="245"/>
+      <c r="C58" s="245"/>
       <c r="D58" s="108"/>
+      <c r="E58" s="245"/>
+      <c r="F58" s="245"/>
+      <c r="G58" s="245"/>
+      <c r="H58" s="245"/>
+      <c r="I58" s="245"/>
+      <c r="J58" s="245"/>
+      <c r="K58" s="245"/>
+      <c r="L58" s="245"/>
     </row>
     <row r="59" spans="1:12">
+      <c r="A59" s="245"/>
+      <c r="B59" s="245"/>
+      <c r="C59" s="245"/>
       <c r="D59" s="108"/>
+      <c r="E59" s="245"/>
+      <c r="F59" s="245"/>
+      <c r="G59" s="245"/>
+      <c r="H59" s="245"/>
+      <c r="I59" s="245"/>
+      <c r="J59" s="245"/>
+      <c r="K59" s="245"/>
+      <c r="L59" s="245"/>
     </row>
     <row r="60" spans="1:12">
+      <c r="A60" s="245"/>
+      <c r="B60" s="245"/>
+      <c r="C60" s="245"/>
       <c r="D60" s="108"/>
+      <c r="E60" s="245"/>
+      <c r="F60" s="245"/>
+      <c r="G60" s="245"/>
+      <c r="H60" s="245"/>
+      <c r="I60" s="245"/>
+      <c r="J60" s="245"/>
+      <c r="K60" s="245"/>
+      <c r="L60" s="245"/>
     </row>
     <row r="61" spans="1:12">
+      <c r="A61" s="245"/>
+      <c r="B61" s="245"/>
+      <c r="C61" s="245"/>
       <c r="D61" s="108"/>
+      <c r="E61" s="245"/>
+      <c r="F61" s="245"/>
+      <c r="G61" s="245"/>
+      <c r="H61" s="245"/>
+      <c r="I61" s="245"/>
+      <c r="J61" s="245"/>
+      <c r="K61" s="245"/>
+      <c r="L61" s="245"/>
     </row>
     <row r="62" spans="1:12">
+      <c r="A62" s="245"/>
+      <c r="B62" s="245"/>
+      <c r="C62" s="245"/>
       <c r="D62" s="108"/>
+      <c r="E62" s="245"/>
+      <c r="F62" s="245"/>
+      <c r="G62" s="245"/>
+      <c r="H62" s="245"/>
+      <c r="I62" s="245"/>
+      <c r="J62" s="245"/>
+      <c r="K62" s="245"/>
+      <c r="L62" s="245"/>
     </row>
     <row r="63" spans="1:12">
+      <c r="A63" s="245"/>
+      <c r="B63" s="245"/>
+      <c r="C63" s="245"/>
       <c r="D63" s="108"/>
+      <c r="E63" s="245"/>
+      <c r="F63" s="245"/>
+      <c r="G63" s="245"/>
+      <c r="H63" s="245"/>
+      <c r="I63" s="245"/>
+      <c r="J63" s="245"/>
+      <c r="K63" s="245"/>
+      <c r="L63" s="245"/>
     </row>
     <row r="64" spans="1:12">
+      <c r="A64" s="245"/>
+      <c r="B64" s="245"/>
+      <c r="C64" s="245"/>
       <c r="D64" s="108"/>
+      <c r="E64" s="245"/>
+      <c r="F64" s="245"/>
+      <c r="G64" s="245"/>
+      <c r="H64" s="245"/>
+      <c r="I64" s="245"/>
+      <c r="J64" s="245"/>
+      <c r="K64" s="245"/>
+      <c r="L64" s="245"/>
     </row>
     <row r="65" spans="1:12">
+      <c r="A65" s="245"/>
+      <c r="B65" s="245"/>
+      <c r="C65" s="245"/>
       <c r="D65" s="108"/>
+      <c r="E65" s="245"/>
+      <c r="F65" s="245"/>
+      <c r="G65" s="245"/>
+      <c r="H65" s="245"/>
+      <c r="I65" s="245"/>
+      <c r="J65" s="245"/>
+      <c r="K65" s="245"/>
+      <c r="L65" s="245"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -6610,6 +7182,9 @@
           </r>
         </is>
       </c>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
     </row>
     <row r="2" spans="1:20" customHeight="1" ht="60" s="245" customFormat="1">
       <c r="A2" s="249" t="inlineStr">
@@ -6635,6 +7210,9 @@
       <c r="O2" s="250"/>
       <c r="P2" s="250"/>
       <c r="Q2" s="251"/>
+      <c r="R2" s="245"/>
+      <c r="S2" s="245"/>
+      <c r="T2" s="245"/>
     </row>
     <row r="3" spans="1:20" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A3" s="1"/>
@@ -6677,12 +7255,16 @@
           </r>
         </is>
       </c>
+      <c r="N3" s="245"/>
       <c r="O3" s="150" t="str">
         <f>구매리스트!B6</f>
         <v>0</v>
       </c>
       <c r="P3" s="252"/>
       <c r="Q3" s="253"/>
+      <c r="R3" s="245"/>
+      <c r="S3" s="245"/>
+      <c r="T3" s="245"/>
     </row>
     <row r="4" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A4" s="135" t="inlineStr">
@@ -6729,6 +7311,9 @@
         <v>0</v>
       </c>
       <c r="Q4" s="255"/>
+      <c r="R4" s="245"/>
+      <c r="S4" s="245"/>
+      <c r="T4" s="245"/>
     </row>
     <row r="5" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A5" s="136" t="inlineStr">
@@ -6769,6 +7354,9 @@
         <v>0</v>
       </c>
       <c r="Q5" s="255"/>
+      <c r="R5" s="245"/>
+      <c r="S5" s="245"/>
+      <c r="T5" s="245"/>
     </row>
     <row r="6" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A6" s="136" t="inlineStr">
@@ -6806,6 +7394,9 @@
       <c r="O6" s="254"/>
       <c r="P6" s="254"/>
       <c r="Q6" s="255"/>
+      <c r="R6" s="245"/>
+      <c r="S6" s="245"/>
+      <c r="T6" s="245"/>
     </row>
     <row r="7" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A7" s="136" t="inlineStr">
@@ -6833,6 +7424,9 @@
       <c r="O7" s="254"/>
       <c r="P7" s="254"/>
       <c r="Q7" s="255"/>
+      <c r="R7" s="245"/>
+      <c r="S7" s="245"/>
+      <c r="T7" s="245"/>
     </row>
     <row r="8" spans="1:20" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A8" s="258" t="inlineStr">
@@ -6879,6 +7473,8 @@
       <c r="O8" s="254"/>
       <c r="P8" s="254"/>
       <c r="Q8" s="255"/>
+      <c r="R8" s="245"/>
+      <c r="S8" s="245"/>
       <c r="T8" s="245" t="inlineStr">
         <is>
           <r>
@@ -6905,6 +7501,9 @@
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="3"/>
+      <c r="R9" s="245"/>
+      <c r="S9" s="245"/>
+      <c r="T9" s="245"/>
     </row>
     <row r="10" spans="1:20" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A10" s="261" t="inlineStr">
@@ -6914,7 +7513,25 @@
           </r>
         </is>
       </c>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="245"/>
+      <c r="G10" s="245"/>
+      <c r="H10" s="245"/>
+      <c r="I10" s="245"/>
+      <c r="J10" s="245"/>
+      <c r="K10" s="245"/>
+      <c r="L10" s="245"/>
+      <c r="M10" s="245"/>
+      <c r="N10" s="245"/>
+      <c r="O10" s="245"/>
+      <c r="P10" s="245"/>
       <c r="Q10" s="262"/>
+      <c r="R10" s="245"/>
+      <c r="S10" s="245"/>
+      <c r="T10" s="245"/>
     </row>
     <row r="11" spans="1:20" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A11" s="1"/>
@@ -6925,7 +7542,24 @@
           </r>
         </is>
       </c>
+      <c r="C11" s="245"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
+      <c r="I11" s="245"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
+      <c r="M11" s="245"/>
+      <c r="N11" s="245"/>
+      <c r="O11" s="245"/>
+      <c r="P11" s="245"/>
       <c r="Q11" s="262"/>
+      <c r="R11" s="245"/>
+      <c r="S11" s="245"/>
+      <c r="T11" s="245"/>
     </row>
     <row r="12" spans="1:20" customHeight="1" ht="20.25" s="245" customFormat="1">
       <c r="A12" s="1"/>
@@ -6945,6 +7579,9 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="3"/>
+      <c r="R12" s="245"/>
+      <c r="S12" s="245"/>
+      <c r="T12" s="245"/>
     </row>
     <row r="13" spans="1:20" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A13" s="4" t="inlineStr">
@@ -6961,28 +7598,73 @@
           </r>
         </is>
       </c>
+      <c r="C13" s="245"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
+      <c r="I13" s="245"/>
+      <c r="J13" s="245"/>
+      <c r="K13" s="245"/>
       <c r="L13" s="155" t="str">
         <f>구매리스트!I3</f>
         <v>0</v>
       </c>
+      <c r="M13" s="245"/>
+      <c r="N13" s="245"/>
       <c r="O13" s="245"/>
       <c r="P13" s="263"/>
       <c r="Q13" s="5"/>
+      <c r="R13" s="245"/>
+      <c r="S13" s="245"/>
+      <c r="T13" s="245"/>
     </row>
     <row r="14" spans="1:20" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A14" s="4"/>
+      <c r="B14" s="245"/>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="245"/>
+      <c r="G14" s="245"/>
+      <c r="H14" s="245"/>
+      <c r="I14" s="245"/>
+      <c r="J14" s="245"/>
+      <c r="K14" s="245"/>
+      <c r="L14" s="245"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="5"/>
+      <c r="R14" s="245"/>
+      <c r="S14" s="245"/>
+      <c r="T14" s="245"/>
     </row>
     <row r="15" spans="1:20" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
+      <c r="B15" s="245"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="245"/>
+      <c r="H15" s="245"/>
+      <c r="I15" s="245"/>
       <c r="J15" s="392" t="s">
         <v>105</v>
       </c>
+      <c r="K15" s="245"/>
+      <c r="L15" s="245"/>
+      <c r="M15" s="245"/>
+      <c r="N15" s="245"/>
+      <c r="O15" s="245"/>
+      <c r="P15" s="245"/>
       <c r="Q15" s="262"/>
+      <c r="R15" s="245"/>
+      <c r="S15" s="245"/>
+      <c r="T15" s="245"/>
     </row>
     <row r="16" spans="1:20" customHeight="1" ht="9" s="245" customFormat="1">
       <c r="A16" s="7"/>
@@ -7002,6 +7684,9 @@
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="9"/>
+      <c r="R16" s="245"/>
+      <c r="S16" s="245"/>
+      <c r="T16" s="245"/>
     </row>
     <row r="17" spans="1:20" customHeight="1" ht="8.25" s="245" customFormat="1">
       <c r="A17" s="4"/>
@@ -7012,13 +7697,24 @@
           </r>
         </is>
       </c>
+      <c r="C17" s="245"/>
+      <c r="D17" s="245"/>
+      <c r="E17" s="245"/>
+      <c r="F17" s="245"/>
+      <c r="G17" s="245"/>
+      <c r="H17" s="245"/>
       <c r="I17" s="264"/>
       <c r="J17" s="264"/>
       <c r="K17" s="264"/>
       <c r="L17" s="264"/>
       <c r="M17" s="264"/>
       <c r="N17" s="264"/>
+      <c r="O17" s="245"/>
+      <c r="P17" s="245"/>
       <c r="Q17" s="5"/>
+      <c r="R17" s="245"/>
+      <c r="S17" s="245"/>
+      <c r="T17" s="245"/>
     </row>
     <row r="18" spans="1:20" customHeight="1" ht="21.75" s="245" customFormat="1">
       <c r="A18" s="265" t="inlineStr">
@@ -7037,6 +7733,7 @@
       <c r="H18" s="254"/>
       <c r="I18" s="254"/>
       <c r="J18" s="255"/>
+      <c r="K18" s="245"/>
       <c r="L18" s="266" t="inlineStr">
         <is>
           <r>
@@ -7049,6 +7746,9 @@
       <c r="O18" s="254"/>
       <c r="P18" s="254"/>
       <c r="Q18" s="255"/>
+      <c r="R18" s="245"/>
+      <c r="S18" s="245"/>
+      <c r="T18" s="245"/>
     </row>
     <row r="19" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A19" s="60" t="inlineStr">
@@ -7076,6 +7776,7 @@
       <c r="H19" s="250"/>
       <c r="I19" s="250"/>
       <c r="J19" s="251"/>
+      <c r="K19" s="245"/>
       <c r="L19" s="165" t="inlineStr">
         <is>
           <r>
@@ -7118,6 +7819,9 @@
           </r>
         </is>
       </c>
+      <c r="R19" s="245"/>
+      <c r="S19" s="245"/>
+      <c r="T19" s="245"/>
     </row>
     <row r="20" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A20" s="58" t="inlineStr">
@@ -7142,6 +7846,7 @@
       <c r="H20" s="252"/>
       <c r="I20" s="252"/>
       <c r="J20" s="253"/>
+      <c r="K20" s="245"/>
       <c r="L20" s="166" t="inlineStr">
         <is>
           <r>
@@ -7184,6 +7889,9 @@
           </r>
         </is>
       </c>
+      <c r="R20" s="245"/>
+      <c r="S20" s="245"/>
+      <c r="T20" s="245"/>
     </row>
     <row r="21" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A21" s="62" t="inlineStr">
@@ -7238,6 +7946,7 @@
           </r>
         </is>
       </c>
+      <c r="K21" s="245"/>
       <c r="L21" s="121" t="str">
         <f>구매리스트!I10</f>
         <v>0</v>
@@ -7253,6 +7962,9 @@
       </c>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
+      <c r="R21" s="245"/>
+      <c r="S21" s="245"/>
+      <c r="T21" s="245"/>
     </row>
     <row r="22" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A22" s="63" t="inlineStr">
@@ -7307,12 +8019,16 @@
           </r>
         </is>
       </c>
+      <c r="K22" s="245"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
       <c r="N22" s="14"/>
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
+      <c r="R22" s="245"/>
+      <c r="S22" s="245"/>
+      <c r="T22" s="245"/>
     </row>
     <row r="23" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A23" s="63" t="inlineStr">
@@ -7367,12 +8083,16 @@
           </r>
         </is>
       </c>
+      <c r="K23" s="245"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
       <c r="N23" s="14"/>
       <c r="O23" s="14"/>
       <c r="P23" s="14"/>
       <c r="Q23" s="14"/>
+      <c r="R23" s="245"/>
+      <c r="S23" s="245"/>
+      <c r="T23" s="245"/>
     </row>
     <row r="24" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A24" s="268" t="inlineStr">
@@ -7406,12 +8126,16 @@
         </is>
       </c>
       <c r="J24" s="251"/>
+      <c r="K24" s="245"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
+      <c r="R24" s="245"/>
+      <c r="S24" s="245"/>
+      <c r="T24" s="245"/>
     </row>
     <row r="25" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A25" s="271"/>
@@ -7424,13 +8148,22 @@
       </c>
       <c r="C25" s="262"/>
       <c r="D25" s="271"/>
+      <c r="E25" s="245"/>
+      <c r="F25" s="245"/>
+      <c r="G25" s="245"/>
+      <c r="H25" s="245"/>
+      <c r="I25" s="245"/>
       <c r="J25" s="262"/>
+      <c r="K25" s="245"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
+      <c r="R25" s="245"/>
+      <c r="S25" s="245"/>
+      <c r="T25" s="245"/>
     </row>
     <row r="26" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A26" s="272"/>
@@ -7443,12 +8176,16 @@
       <c r="H26" s="252"/>
       <c r="I26" s="252"/>
       <c r="J26" s="253"/>
+      <c r="K26" s="245"/>
       <c r="L26" s="68"/>
       <c r="M26" s="68"/>
       <c r="N26" s="68"/>
       <c r="O26" s="68"/>
       <c r="P26" s="68"/>
       <c r="Q26" s="68"/>
+      <c r="R26" s="245"/>
+      <c r="S26" s="245"/>
+      <c r="T26" s="245"/>
     </row>
     <row r="27" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A27" s="63" t="inlineStr">
@@ -7482,12 +8219,16 @@
       </c>
       <c r="I27" s="254"/>
       <c r="J27" s="255"/>
+      <c r="K27" s="245"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
       <c r="N27" s="14"/>
       <c r="O27" s="14"/>
       <c r="P27" s="14"/>
       <c r="Q27" s="14"/>
+      <c r="R27" s="245"/>
+      <c r="S27" s="245"/>
+      <c r="T27" s="245"/>
     </row>
     <row r="28" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A28" s="64" t="inlineStr">
@@ -7521,12 +8262,16 @@
         </is>
       </c>
       <c r="J28" s="251"/>
+      <c r="K28" s="245"/>
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
       <c r="N28" s="14"/>
       <c r="O28" s="14"/>
       <c r="P28" s="14"/>
       <c r="Q28" s="14"/>
+      <c r="R28" s="245"/>
+      <c r="S28" s="245"/>
+      <c r="T28" s="245"/>
     </row>
     <row r="29" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A29" s="274" t="inlineStr">
@@ -7536,15 +8281,25 @@
           </r>
         </is>
       </c>
+      <c r="B29" s="245"/>
       <c r="C29" s="262"/>
       <c r="D29" s="271"/>
+      <c r="E29" s="245"/>
+      <c r="F29" s="245"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
       <c r="J29" s="262"/>
+      <c r="K29" s="245"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
       <c r="N29" s="14"/>
       <c r="O29" s="14"/>
       <c r="P29" s="14"/>
       <c r="Q29" s="14"/>
+      <c r="R29" s="245"/>
+      <c r="S29" s="245"/>
+      <c r="T29" s="245"/>
     </row>
     <row r="30" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A30" s="275" t="inlineStr">
@@ -7563,12 +8318,16 @@
       <c r="H30" s="252"/>
       <c r="I30" s="252"/>
       <c r="J30" s="253"/>
+      <c r="K30" s="245"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
+      <c r="R30" s="245"/>
+      <c r="S30" s="245"/>
+      <c r="T30" s="245"/>
     </row>
     <row r="31" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A31" s="65" t="inlineStr">
@@ -7605,12 +8364,16 @@
       </c>
       <c r="I31" s="254"/>
       <c r="J31" s="255"/>
+      <c r="K31" s="245"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
       <c r="O31" s="14"/>
       <c r="P31" s="14"/>
       <c r="Q31" s="14"/>
+      <c r="R31" s="245"/>
+      <c r="S31" s="245"/>
+      <c r="T31" s="245"/>
     </row>
     <row r="32" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A32" s="66" t="inlineStr">
@@ -7659,12 +8422,16 @@
         </is>
       </c>
       <c r="J32" s="255"/>
+      <c r="K32" s="245"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
       <c r="O32" s="14"/>
       <c r="P32" s="14"/>
       <c r="Q32" s="14"/>
+      <c r="R32" s="245"/>
+      <c r="S32" s="245"/>
+      <c r="T32" s="245"/>
     </row>
     <row r="33" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A33" s="66" t="inlineStr">
@@ -7707,12 +8474,16 @@
         </is>
       </c>
       <c r="J33" s="255"/>
+      <c r="K33" s="245"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
       <c r="O33" s="14"/>
       <c r="P33" s="14"/>
       <c r="Q33" s="14"/>
+      <c r="R33" s="245"/>
+      <c r="S33" s="245"/>
+      <c r="T33" s="245"/>
     </row>
     <row r="34" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A34" s="277" t="inlineStr">
@@ -7731,32 +8502,60 @@
       <c r="H34" s="250"/>
       <c r="I34" s="250"/>
       <c r="J34" s="251"/>
+      <c r="K34" s="245"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
       <c r="O34" s="14"/>
       <c r="P34" s="14"/>
       <c r="Q34" s="14"/>
+      <c r="R34" s="245"/>
+      <c r="S34" s="245"/>
+      <c r="T34" s="245"/>
     </row>
     <row r="35" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A35" s="271"/>
+      <c r="B35" s="245"/>
+      <c r="C35" s="245"/>
+      <c r="D35" s="245"/>
+      <c r="E35" s="245"/>
+      <c r="F35" s="245"/>
+      <c r="G35" s="245"/>
+      <c r="H35" s="245"/>
+      <c r="I35" s="245"/>
       <c r="J35" s="262"/>
+      <c r="K35" s="245"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
       <c r="O35" s="14"/>
       <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
+      <c r="R35" s="245"/>
+      <c r="S35" s="245"/>
+      <c r="T35" s="245"/>
     </row>
     <row r="36" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A36" s="271"/>
+      <c r="B36" s="245"/>
+      <c r="C36" s="245"/>
+      <c r="D36" s="245"/>
+      <c r="E36" s="245"/>
+      <c r="F36" s="245"/>
+      <c r="G36" s="245"/>
+      <c r="H36" s="245"/>
+      <c r="I36" s="245"/>
       <c r="J36" s="262"/>
+      <c r="K36" s="245"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
       <c r="O36" s="14"/>
       <c r="P36" s="14"/>
       <c r="Q36" s="14"/>
+      <c r="R36" s="245"/>
+      <c r="S36" s="245"/>
+      <c r="T36" s="245"/>
     </row>
     <row r="37" spans="1:20" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A37" s="272"/>
@@ -7769,12 +8568,16 @@
       <c r="H37" s="252"/>
       <c r="I37" s="252"/>
       <c r="J37" s="253"/>
+      <c r="K37" s="245"/>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
       <c r="O37" s="15"/>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
+      <c r="R37" s="245"/>
+      <c r="S37" s="245"/>
+      <c r="T37" s="245"/>
     </row>
     <row r="38" spans="1:20" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A38" s="172" t="inlineStr">
@@ -7793,6 +8596,7 @@
       <c r="H38" s="254"/>
       <c r="I38" s="254"/>
       <c r="J38" s="255"/>
+      <c r="K38" s="245"/>
       <c r="L38" s="278" t="inlineStr">
         <is>
           <r>
@@ -7805,6 +8609,9 @@
       <c r="O38" s="250"/>
       <c r="P38" s="250"/>
       <c r="Q38" s="251"/>
+      <c r="R38" s="245"/>
+      <c r="S38" s="245"/>
+      <c r="T38" s="245"/>
     </row>
     <row r="39" spans="1:20" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A39" s="279" t="inlineStr">
@@ -7835,6 +8642,7 @@
       </c>
       <c r="I39" s="254"/>
       <c r="J39" s="255"/>
+      <c r="K39" s="245"/>
       <c r="L39" s="280" t="inlineStr">
         <is>
           <r>
@@ -7847,6 +8655,9 @@
       <c r="O39" s="250"/>
       <c r="P39" s="250"/>
       <c r="Q39" s="251"/>
+      <c r="R39" s="245"/>
+      <c r="S39" s="245"/>
+      <c r="T39" s="245"/>
     </row>
     <row r="40" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A40" s="136" t="inlineStr">
@@ -7883,8 +8694,16 @@
       </c>
       <c r="I40" s="254"/>
       <c r="J40" s="255"/>
+      <c r="K40" s="245"/>
       <c r="L40" s="4"/>
+      <c r="M40" s="245"/>
+      <c r="N40" s="245"/>
+      <c r="O40" s="245"/>
+      <c r="P40" s="245"/>
       <c r="Q40" s="5"/>
+      <c r="R40" s="245"/>
+      <c r="S40" s="245"/>
+      <c r="T40" s="245"/>
     </row>
     <row r="41" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A41" s="136" t="inlineStr">
@@ -7921,7 +8740,10 @@
       </c>
       <c r="I41" s="254"/>
       <c r="J41" s="255"/>
+      <c r="K41" s="245"/>
       <c r="L41" s="4"/>
+      <c r="M41" s="245"/>
+      <c r="N41" s="245"/>
       <c r="O41" s="245" t="inlineStr">
         <is>
           <r>
@@ -7929,7 +8751,11 @@
           </r>
         </is>
       </c>
+      <c r="P41" s="245"/>
       <c r="Q41" s="5"/>
+      <c r="R41" s="245"/>
+      <c r="S41" s="245"/>
+      <c r="T41" s="245"/>
     </row>
     <row r="42" spans="1:20" customHeight="1" ht="33" s="245" customFormat="1">
       <c r="A42" s="266" t="inlineStr">
@@ -7949,8 +8775,16 @@
       <c r="H42" s="254"/>
       <c r="I42" s="254"/>
       <c r="J42" s="255"/>
+      <c r="K42" s="245"/>
       <c r="L42" s="4"/>
+      <c r="M42" s="245"/>
+      <c r="N42" s="245"/>
+      <c r="O42" s="245"/>
+      <c r="P42" s="245"/>
       <c r="Q42" s="5"/>
+      <c r="R42" s="245"/>
+      <c r="S42" s="245"/>
+      <c r="T42" s="245"/>
     </row>
     <row r="43" spans="1:20" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A43" s="281" t="inlineStr">
@@ -7975,8 +8809,16 @@
       </c>
       <c r="I43" s="254"/>
       <c r="J43" s="255"/>
+      <c r="K43" s="245"/>
       <c r="L43" s="4"/>
+      <c r="M43" s="245"/>
+      <c r="N43" s="245"/>
+      <c r="O43" s="245"/>
+      <c r="P43" s="245"/>
       <c r="Q43" s="5"/>
+      <c r="R43" s="245"/>
+      <c r="S43" s="245"/>
+      <c r="T43" s="245"/>
     </row>
     <row r="44" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A44" s="136" t="inlineStr">
@@ -8001,8 +8843,16 @@
       </c>
       <c r="I44" s="254"/>
       <c r="J44" s="255"/>
+      <c r="K44" s="245"/>
       <c r="L44" s="4"/>
+      <c r="M44" s="245"/>
+      <c r="N44" s="245"/>
+      <c r="O44" s="245"/>
+      <c r="P44" s="245"/>
       <c r="Q44" s="5"/>
+      <c r="R44" s="245"/>
+      <c r="S44" s="245"/>
+      <c r="T44" s="245"/>
     </row>
     <row r="45" spans="1:20" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A45" s="136" t="inlineStr">
@@ -8034,9 +8884,39 @@
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="9"/>
-    </row>
-    <row r="46" spans="1:20" customHeight="1" ht="6" s="245" customFormat="1"/>
+      <c r="R45" s="245"/>
+      <c r="S45" s="245"/>
+      <c r="T45" s="245"/>
+    </row>
+    <row r="46" spans="1:20" customHeight="1" ht="6" s="245" customFormat="1">
+      <c r="A46" s="245"/>
+      <c r="B46" s="245"/>
+      <c r="C46" s="245"/>
+      <c r="D46" s="245"/>
+      <c r="E46" s="245"/>
+      <c r="F46" s="245"/>
+      <c r="G46" s="245"/>
+      <c r="H46" s="245"/>
+      <c r="I46" s="245"/>
+      <c r="J46" s="245"/>
+      <c r="K46" s="245"/>
+      <c r="L46" s="245"/>
+      <c r="M46" s="245"/>
+      <c r="N46" s="245"/>
+      <c r="O46" s="245"/>
+      <c r="P46" s="245"/>
+      <c r="Q46" s="245"/>
+      <c r="R46" s="245"/>
+      <c r="S46" s="245"/>
+      <c r="T46" s="245"/>
+    </row>
     <row r="47" spans="1:20" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="A47" s="245"/>
+      <c r="B47" s="245"/>
+      <c r="C47" s="245"/>
+      <c r="D47" s="245"/>
+      <c r="E47" s="245"/>
+      <c r="F47" s="245"/>
       <c r="G47" s="162" t="inlineStr">
         <is>
           <r>
@@ -8044,6 +8924,12 @@
           </r>
         </is>
       </c>
+      <c r="H47" s="245"/>
+      <c r="I47" s="245"/>
+      <c r="J47" s="245"/>
+      <c r="K47" s="245"/>
+      <c r="L47" s="245"/>
+      <c r="M47" s="245"/>
       <c r="N47" s="163" t="inlineStr">
         <is>
           <r>
@@ -8051,6 +8937,12 @@
           </r>
         </is>
       </c>
+      <c r="O47" s="245"/>
+      <c r="P47" s="245"/>
+      <c r="Q47" s="245"/>
+      <c r="R47" s="245"/>
+      <c r="S47" s="245"/>
+      <c r="T47" s="245"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -8216,6 +9108,12 @@
           </r>
         </is>
       </c>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
+      <c r="U1"/>
+      <c r="V1"/>
+      <c r="W1"/>
     </row>
     <row r="2" spans="1:23" customHeight="1" ht="60" s="245" customFormat="1">
       <c r="A2" s="282" t="inlineStr">
@@ -8241,6 +9139,12 @@
       <c r="O2" s="250"/>
       <c r="P2" s="250"/>
       <c r="Q2" s="251"/>
+      <c r="R2" s="245"/>
+      <c r="S2" s="245"/>
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
     </row>
     <row r="3" spans="1:23" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A3" s="1"/>
@@ -8290,6 +9194,12 @@
       </c>
       <c r="P3" s="252"/>
       <c r="Q3" s="253"/>
+      <c r="R3" s="245"/>
+      <c r="S3" s="245"/>
+      <c r="T3" s="245"/>
+      <c r="U3" s="245"/>
+      <c r="V3" s="245"/>
+      <c r="W3" s="245"/>
     </row>
     <row r="4" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A4" s="172" t="inlineStr">
@@ -8336,6 +9246,12 @@
         <v>0</v>
       </c>
       <c r="Q4" s="255"/>
+      <c r="R4" s="245"/>
+      <c r="S4" s="245"/>
+      <c r="T4" s="245"/>
+      <c r="U4" s="245"/>
+      <c r="V4" s="245"/>
+      <c r="W4" s="245"/>
     </row>
     <row r="5" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A5" s="172" t="inlineStr">
@@ -8376,6 +9292,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="255"/>
+      <c r="R5" s="245"/>
       <c r="S5" s="245" t="inlineStr">
         <is>
           <r>
@@ -8383,6 +9300,10 @@
           </r>
         </is>
       </c>
+      <c r="T5" s="245"/>
+      <c r="U5" s="245"/>
+      <c r="V5" s="245"/>
+      <c r="W5" s="245"/>
     </row>
     <row r="6" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A6" s="172" t="inlineStr">
@@ -8420,6 +9341,7 @@
       <c r="O6" s="254"/>
       <c r="P6" s="254"/>
       <c r="Q6" s="255"/>
+      <c r="R6" s="245"/>
       <c r="S6" s="283" t="inlineStr">
         <is>
           <r>
@@ -8427,6 +9349,10 @@
           </r>
         </is>
       </c>
+      <c r="T6" s="245"/>
+      <c r="U6" s="245"/>
+      <c r="V6" s="245"/>
+      <c r="W6" s="245"/>
     </row>
     <row r="7" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A7" s="172" t="inlineStr">
@@ -8454,6 +9380,12 @@
       <c r="O7" s="254"/>
       <c r="P7" s="254"/>
       <c r="Q7" s="255"/>
+      <c r="R7" s="245"/>
+      <c r="S7" s="245"/>
+      <c r="T7" s="245"/>
+      <c r="U7" s="245"/>
+      <c r="V7" s="245"/>
+      <c r="W7" s="245"/>
     </row>
     <row r="8" spans="1:23" customHeight="1" ht="30" s="245" customFormat="1">
       <c r="A8" s="258" t="inlineStr">
@@ -8506,6 +9438,11 @@
           </r>
         </is>
       </c>
+      <c r="S8" s="245"/>
+      <c r="T8" s="245"/>
+      <c r="U8" s="245"/>
+      <c r="V8" s="245"/>
+      <c r="W8" s="245"/>
     </row>
     <row r="9" spans="1:23" customHeight="1" ht="6.75" s="245" customFormat="1">
       <c r="A9" s="1"/>
@@ -8525,6 +9462,12 @@
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="3"/>
+      <c r="R9" s="245"/>
+      <c r="S9" s="245"/>
+      <c r="T9" s="245"/>
+      <c r="U9" s="245"/>
+      <c r="V9" s="245"/>
+      <c r="W9" s="245"/>
     </row>
     <row r="10" spans="1:23" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A10" s="284" t="inlineStr">
@@ -8534,7 +9477,28 @@
           </r>
         </is>
       </c>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="245"/>
+      <c r="G10" s="245"/>
+      <c r="H10" s="245"/>
+      <c r="I10" s="245"/>
+      <c r="J10" s="245"/>
+      <c r="K10" s="245"/>
+      <c r="L10" s="245"/>
+      <c r="M10" s="245"/>
+      <c r="N10" s="245"/>
+      <c r="O10" s="245"/>
+      <c r="P10" s="245"/>
       <c r="Q10" s="262"/>
+      <c r="R10" s="245"/>
+      <c r="S10" s="245"/>
+      <c r="T10" s="245"/>
+      <c r="U10" s="245"/>
+      <c r="V10" s="245"/>
+      <c r="W10" s="245"/>
     </row>
     <row r="11" spans="1:23" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A11" s="1"/>
@@ -8545,7 +9509,27 @@
           </r>
         </is>
       </c>
+      <c r="C11" s="245"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
+      <c r="I11" s="245"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
+      <c r="M11" s="245"/>
+      <c r="N11" s="245"/>
+      <c r="O11" s="245"/>
+      <c r="P11" s="245"/>
       <c r="Q11" s="262"/>
+      <c r="R11" s="245"/>
+      <c r="S11" s="245"/>
+      <c r="T11" s="245"/>
+      <c r="U11" s="245"/>
+      <c r="V11" s="245"/>
+      <c r="W11" s="245"/>
     </row>
     <row r="12" spans="1:23" customHeight="1" ht="20.25" s="245" customFormat="1">
       <c r="A12" s="1"/>
@@ -8571,6 +9555,12 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="3"/>
+      <c r="R12" s="245"/>
+      <c r="S12" s="245"/>
+      <c r="T12" s="245"/>
+      <c r="U12" s="245"/>
+      <c r="V12" s="245"/>
+      <c r="W12" s="245"/>
     </row>
     <row r="13" spans="1:23" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A13" s="4" t="inlineStr">
@@ -8587,6 +9577,13 @@
           </r>
         </is>
       </c>
+      <c r="C13" s="245"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
+      <c r="I13" s="245"/>
       <c r="J13" s="245" t="inlineStr">
         <is>
           <r>
@@ -8594,29 +9591,73 @@
           </r>
         </is>
       </c>
+      <c r="K13" s="245"/>
       <c r="L13" s="168" t="str">
         <f>구매리스트!I3</f>
         <v>0</v>
       </c>
+      <c r="M13" s="245"/>
+      <c r="N13" s="245"/>
       <c r="O13" s="245"/>
       <c r="P13" s="263"/>
       <c r="Q13" s="5"/>
+      <c r="R13" s="245"/>
       <c r="S13" s="72"/>
+      <c r="T13" s="245"/>
+      <c r="U13" s="245"/>
+      <c r="V13" s="245"/>
+      <c r="W13" s="245"/>
     </row>
     <row r="14" spans="1:23" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A14" s="4"/>
+      <c r="B14" s="245"/>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="245"/>
+      <c r="G14" s="245"/>
+      <c r="H14" s="245"/>
+      <c r="I14" s="245"/>
+      <c r="J14" s="245"/>
+      <c r="K14" s="245"/>
+      <c r="L14" s="245"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="5"/>
+      <c r="R14" s="245"/>
+      <c r="S14" s="245"/>
+      <c r="T14" s="245"/>
+      <c r="U14" s="245"/>
+      <c r="V14" s="245"/>
+      <c r="W14" s="245"/>
     </row>
     <row r="15" spans="1:23" customHeight="1" ht="39" s="245" customFormat="1">
       <c r="A15" s="4"/>
+      <c r="B15" s="245"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="245"/>
+      <c r="H15" s="245"/>
+      <c r="I15" s="245"/>
       <c r="J15" s="393" t="s">
         <v>190</v>
       </c>
+      <c r="K15" s="245"/>
+      <c r="L15" s="245"/>
+      <c r="M15" s="245"/>
+      <c r="N15" s="245"/>
+      <c r="O15" s="245"/>
+      <c r="P15" s="245"/>
       <c r="Q15" s="262"/>
+      <c r="R15" s="245"/>
+      <c r="S15" s="245"/>
+      <c r="T15" s="245"/>
+      <c r="U15" s="245"/>
+      <c r="V15" s="245"/>
       <c r="W15" s="245" t="inlineStr">
         <is>
           <r>
@@ -8643,6 +9684,12 @@
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="9"/>
+      <c r="R16" s="245"/>
+      <c r="S16" s="245"/>
+      <c r="T16" s="245"/>
+      <c r="U16" s="245"/>
+      <c r="V16" s="245"/>
+      <c r="W16" s="245"/>
     </row>
     <row r="17" spans="1:23" customHeight="1" ht="8.25" s="245" customFormat="1">
       <c r="A17" s="4"/>
@@ -8653,13 +9700,27 @@
           </r>
         </is>
       </c>
+      <c r="C17" s="245"/>
+      <c r="D17" s="245"/>
+      <c r="E17" s="245"/>
+      <c r="F17" s="245"/>
+      <c r="G17" s="245"/>
+      <c r="H17" s="245"/>
       <c r="I17" s="264"/>
       <c r="J17" s="264"/>
       <c r="K17" s="264"/>
       <c r="L17" s="264"/>
       <c r="M17" s="264"/>
       <c r="N17" s="264"/>
+      <c r="O17" s="245"/>
+      <c r="P17" s="245"/>
       <c r="Q17" s="5"/>
+      <c r="R17" s="245"/>
+      <c r="S17" s="245"/>
+      <c r="T17" s="245"/>
+      <c r="U17" s="245"/>
+      <c r="V17" s="245"/>
+      <c r="W17" s="245"/>
     </row>
     <row r="18" spans="1:23" customHeight="1" ht="21.75" s="245" customFormat="1">
       <c r="A18" s="265" t="inlineStr">
@@ -8678,6 +9739,7 @@
       <c r="H18" s="254"/>
       <c r="I18" s="254"/>
       <c r="J18" s="255"/>
+      <c r="K18" s="245"/>
       <c r="L18" s="266" t="inlineStr">
         <is>
           <r>
@@ -8690,6 +9752,12 @@
       <c r="O18" s="254"/>
       <c r="P18" s="254"/>
       <c r="Q18" s="255"/>
+      <c r="R18" s="245"/>
+      <c r="S18" s="245"/>
+      <c r="T18" s="245"/>
+      <c r="U18" s="245"/>
+      <c r="V18" s="245"/>
+      <c r="W18" s="245"/>
     </row>
     <row r="19" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A19" s="60" t="inlineStr">
@@ -8717,6 +9785,7 @@
       <c r="H19" s="250"/>
       <c r="I19" s="250"/>
       <c r="J19" s="251"/>
+      <c r="K19" s="245"/>
       <c r="L19" s="285" t="inlineStr">
         <is>
           <r>
@@ -8763,6 +9832,12 @@
           </r>
         </is>
       </c>
+      <c r="R19" s="245"/>
+      <c r="S19" s="245"/>
+      <c r="T19" s="245"/>
+      <c r="U19" s="245"/>
+      <c r="V19" s="245"/>
+      <c r="W19" s="245"/>
     </row>
     <row r="20" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A20" s="58" t="inlineStr">
@@ -8787,12 +9862,19 @@
       <c r="H20" s="252"/>
       <c r="I20" s="252"/>
       <c r="J20" s="253"/>
+      <c r="K20" s="245"/>
       <c r="L20" s="290"/>
       <c r="M20" s="290"/>
       <c r="N20" s="290"/>
       <c r="O20" s="290"/>
       <c r="P20" s="290"/>
       <c r="Q20" s="290"/>
+      <c r="R20" s="245"/>
+      <c r="S20" s="245"/>
+      <c r="T20" s="245"/>
+      <c r="U20" s="245"/>
+      <c r="V20" s="245"/>
+      <c r="W20" s="245"/>
     </row>
     <row r="21" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A21" s="62" t="inlineStr">
@@ -8847,6 +9929,7 @@
           </r>
         </is>
       </c>
+      <c r="K21" s="245"/>
       <c r="L21" s="121" t="str">
         <f>구매리스트!I10</f>
         <v>0</v>
@@ -8869,6 +9952,11 @@
           </r>
         </is>
       </c>
+      <c r="S21" s="245"/>
+      <c r="T21" s="245"/>
+      <c r="U21" s="245"/>
+      <c r="V21" s="245"/>
+      <c r="W21" s="245"/>
     </row>
     <row r="22" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A22" s="63" t="inlineStr">
@@ -8923,12 +10011,14 @@
           </r>
         </is>
       </c>
+      <c r="K22" s="245"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
       <c r="N22" s="14"/>
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
+      <c r="R22" s="245"/>
       <c r="S22" s="245" t="inlineStr">
         <is>
           <r>
@@ -8936,6 +10026,10 @@
           </r>
         </is>
       </c>
+      <c r="T22" s="245"/>
+      <c r="U22" s="245"/>
+      <c r="V22" s="245"/>
+      <c r="W22" s="245"/>
     </row>
     <row r="23" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A23" s="63" t="inlineStr">
@@ -8990,12 +10084,19 @@
           </r>
         </is>
       </c>
+      <c r="K23" s="245"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
       <c r="N23" s="14"/>
       <c r="O23" s="14"/>
       <c r="P23" s="14"/>
       <c r="Q23" s="14"/>
+      <c r="R23" s="245"/>
+      <c r="S23" s="245"/>
+      <c r="T23" s="245"/>
+      <c r="U23" s="245"/>
+      <c r="V23" s="245"/>
+      <c r="W23" s="245"/>
     </row>
     <row r="24" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A24" s="268" t="inlineStr">
@@ -9029,12 +10130,14 @@
         </is>
       </c>
       <c r="J24" s="251"/>
+      <c r="K24" s="245"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
+      <c r="R24" s="245"/>
       <c r="S24" s="245" t="inlineStr">
         <is>
           <r>
@@ -9042,6 +10145,10 @@
           </r>
         </is>
       </c>
+      <c r="T24" s="245"/>
+      <c r="U24" s="245"/>
+      <c r="V24" s="245"/>
+      <c r="W24" s="245"/>
     </row>
     <row r="25" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A25" s="271"/>
@@ -9055,13 +10162,25 @@
       </c>
       <c r="C25" s="262"/>
       <c r="D25" s="271"/>
+      <c r="E25" s="245"/>
+      <c r="F25" s="245"/>
+      <c r="G25" s="245"/>
+      <c r="H25" s="245"/>
+      <c r="I25" s="245"/>
       <c r="J25" s="262"/>
+      <c r="K25" s="245"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
+      <c r="R25" s="245"/>
+      <c r="S25" s="245"/>
+      <c r="T25" s="245"/>
+      <c r="U25" s="245"/>
+      <c r="V25" s="245"/>
+      <c r="W25" s="245"/>
     </row>
     <row r="26" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A26" s="272"/>
@@ -9074,12 +10193,14 @@
       <c r="H26" s="252"/>
       <c r="I26" s="252"/>
       <c r="J26" s="253"/>
+      <c r="K26" s="245"/>
       <c r="L26" s="68"/>
       <c r="M26" s="68"/>
       <c r="N26" s="68"/>
       <c r="O26" s="68"/>
       <c r="P26" s="68"/>
       <c r="Q26" s="68"/>
+      <c r="R26" s="245"/>
       <c r="S26" s="245" t="inlineStr">
         <is>
           <r>
@@ -9087,6 +10208,10 @@
           </r>
         </is>
       </c>
+      <c r="T26" s="245"/>
+      <c r="U26" s="245"/>
+      <c r="V26" s="245"/>
+      <c r="W26" s="245"/>
     </row>
     <row r="27" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A27" s="63" t="inlineStr">
@@ -9120,12 +10245,19 @@
       </c>
       <c r="I27" s="254"/>
       <c r="J27" s="255"/>
+      <c r="K27" s="245"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
       <c r="N27" s="14"/>
       <c r="O27" s="14"/>
       <c r="P27" s="14"/>
       <c r="Q27" s="14"/>
+      <c r="R27" s="245"/>
+      <c r="S27" s="245"/>
+      <c r="T27" s="245"/>
+      <c r="U27" s="245"/>
+      <c r="V27" s="245"/>
+      <c r="W27" s="245"/>
     </row>
     <row r="28" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A28" s="64" t="inlineStr">
@@ -9160,12 +10292,19 @@
         </is>
       </c>
       <c r="J28" s="251"/>
+      <c r="K28" s="245"/>
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
       <c r="N28" s="14"/>
       <c r="O28" s="14"/>
       <c r="P28" s="14"/>
       <c r="Q28" s="14"/>
+      <c r="R28" s="245"/>
+      <c r="S28" s="245"/>
+      <c r="T28" s="245"/>
+      <c r="U28" s="245"/>
+      <c r="V28" s="245"/>
+      <c r="W28" s="245"/>
     </row>
     <row r="29" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A29" s="292" t="inlineStr">
@@ -9175,15 +10314,28 @@
           </r>
         </is>
       </c>
+      <c r="B29" s="245"/>
       <c r="C29" s="262"/>
       <c r="D29" s="271"/>
+      <c r="E29" s="245"/>
+      <c r="F29" s="245"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
       <c r="J29" s="262"/>
+      <c r="K29" s="245"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
       <c r="N29" s="14"/>
       <c r="O29" s="14"/>
       <c r="P29" s="14"/>
       <c r="Q29" s="14"/>
+      <c r="R29" s="245"/>
+      <c r="S29" s="245"/>
+      <c r="T29" s="245"/>
+      <c r="U29" s="245"/>
+      <c r="V29" s="245"/>
+      <c r="W29" s="245"/>
     </row>
     <row r="30" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A30" s="293" t="inlineStr">
@@ -9202,12 +10354,19 @@
       <c r="H30" s="252"/>
       <c r="I30" s="252"/>
       <c r="J30" s="253"/>
+      <c r="K30" s="245"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
+      <c r="R30" s="245"/>
+      <c r="S30" s="245"/>
+      <c r="T30" s="245"/>
+      <c r="U30" s="245"/>
+      <c r="V30" s="245"/>
+      <c r="W30" s="245"/>
     </row>
     <row r="31" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A31" s="65" t="inlineStr">
@@ -9245,12 +10404,19 @@
       </c>
       <c r="I31" s="254"/>
       <c r="J31" s="255"/>
+      <c r="K31" s="245"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
       <c r="O31" s="14"/>
       <c r="P31" s="14"/>
       <c r="Q31" s="14"/>
+      <c r="R31" s="245"/>
+      <c r="S31" s="245"/>
+      <c r="T31" s="245"/>
+      <c r="U31" s="245"/>
+      <c r="V31" s="245"/>
+      <c r="W31" s="245"/>
     </row>
     <row r="32" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A32" s="66" t="inlineStr">
@@ -9300,12 +10466,19 @@
         </is>
       </c>
       <c r="J32" s="255"/>
+      <c r="K32" s="245"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
       <c r="O32" s="14"/>
       <c r="P32" s="14"/>
       <c r="Q32" s="14"/>
+      <c r="R32" s="245"/>
+      <c r="S32" s="245"/>
+      <c r="T32" s="245"/>
+      <c r="U32" s="245"/>
+      <c r="V32" s="245"/>
+      <c r="W32" s="245"/>
     </row>
     <row r="33" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A33" s="66" t="inlineStr">
@@ -9349,12 +10522,19 @@
         </is>
       </c>
       <c r="J33" s="255"/>
+      <c r="K33" s="245"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
       <c r="O33" s="14"/>
       <c r="P33" s="14"/>
       <c r="Q33" s="14"/>
+      <c r="R33" s="245"/>
+      <c r="S33" s="245"/>
+      <c r="T33" s="245"/>
+      <c r="U33" s="245"/>
+      <c r="V33" s="245"/>
+      <c r="W33" s="245"/>
     </row>
     <row r="34" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A34" s="277" t="inlineStr">
@@ -9373,32 +10553,69 @@
       <c r="H34" s="250"/>
       <c r="I34" s="250"/>
       <c r="J34" s="251"/>
+      <c r="K34" s="245"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
       <c r="O34" s="14"/>
       <c r="P34" s="14"/>
       <c r="Q34" s="14"/>
+      <c r="R34" s="245"/>
+      <c r="S34" s="245"/>
+      <c r="T34" s="245"/>
+      <c r="U34" s="245"/>
+      <c r="V34" s="245"/>
+      <c r="W34" s="245"/>
     </row>
     <row r="35" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A35" s="271"/>
+      <c r="B35" s="245"/>
+      <c r="C35" s="245"/>
+      <c r="D35" s="245"/>
+      <c r="E35" s="245"/>
+      <c r="F35" s="245"/>
+      <c r="G35" s="245"/>
+      <c r="H35" s="245"/>
+      <c r="I35" s="245"/>
       <c r="J35" s="262"/>
+      <c r="K35" s="245"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
       <c r="O35" s="14"/>
       <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
+      <c r="R35" s="245"/>
+      <c r="S35" s="245"/>
+      <c r="T35" s="245"/>
+      <c r="U35" s="245"/>
+      <c r="V35" s="245"/>
+      <c r="W35" s="245"/>
     </row>
     <row r="36" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A36" s="271"/>
+      <c r="B36" s="245"/>
+      <c r="C36" s="245"/>
+      <c r="D36" s="245"/>
+      <c r="E36" s="245"/>
+      <c r="F36" s="245"/>
+      <c r="G36" s="245"/>
+      <c r="H36" s="245"/>
+      <c r="I36" s="245"/>
       <c r="J36" s="262"/>
+      <c r="K36" s="245"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
       <c r="O36" s="14"/>
       <c r="P36" s="14"/>
       <c r="Q36" s="14"/>
+      <c r="R36" s="245"/>
+      <c r="S36" s="245"/>
+      <c r="T36" s="245"/>
+      <c r="U36" s="245"/>
+      <c r="V36" s="245"/>
+      <c r="W36" s="245"/>
     </row>
     <row r="37" spans="1:23" customHeight="1" ht="20.45" s="245" customFormat="1">
       <c r="A37" s="272"/>
@@ -9411,12 +10628,19 @@
       <c r="H37" s="252"/>
       <c r="I37" s="252"/>
       <c r="J37" s="253"/>
+      <c r="K37" s="245"/>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
       <c r="O37" s="15"/>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
+      <c r="R37" s="245"/>
+      <c r="S37" s="245"/>
+      <c r="T37" s="245"/>
+      <c r="U37" s="245"/>
+      <c r="V37" s="245"/>
+      <c r="W37" s="245"/>
     </row>
     <row r="38" spans="1:23" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A38" s="172" t="inlineStr">
@@ -9435,6 +10659,7 @@
       <c r="H38" s="254"/>
       <c r="I38" s="254"/>
       <c r="J38" s="255"/>
+      <c r="K38" s="245"/>
       <c r="L38" s="296" t="inlineStr">
         <is>
           <r>
@@ -9447,6 +10672,12 @@
       <c r="O38" s="250"/>
       <c r="P38" s="250"/>
       <c r="Q38" s="251"/>
+      <c r="R38" s="245"/>
+      <c r="S38" s="245"/>
+      <c r="T38" s="245"/>
+      <c r="U38" s="245"/>
+      <c r="V38" s="245"/>
+      <c r="W38" s="245"/>
     </row>
     <row r="39" spans="1:23" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A39" s="279" t="inlineStr">
@@ -9478,6 +10709,7 @@
       </c>
       <c r="I39" s="254"/>
       <c r="J39" s="255"/>
+      <c r="K39" s="245"/>
       <c r="L39" s="299" t="inlineStr">
         <is>
           <r>
@@ -9490,6 +10722,12 @@
       <c r="O39" s="250"/>
       <c r="P39" s="250"/>
       <c r="Q39" s="251"/>
+      <c r="R39" s="245"/>
+      <c r="S39" s="245"/>
+      <c r="T39" s="245"/>
+      <c r="U39" s="245"/>
+      <c r="V39" s="245"/>
+      <c r="W39" s="245"/>
     </row>
     <row r="40" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A40" s="136" t="inlineStr">
@@ -9526,8 +10764,19 @@
       </c>
       <c r="I40" s="254"/>
       <c r="J40" s="255"/>
+      <c r="K40" s="245"/>
       <c r="L40" s="4"/>
+      <c r="M40" s="245"/>
+      <c r="N40" s="245"/>
+      <c r="O40" s="245"/>
+      <c r="P40" s="245"/>
       <c r="Q40" s="5"/>
+      <c r="R40" s="245"/>
+      <c r="S40" s="245"/>
+      <c r="T40" s="245"/>
+      <c r="U40" s="245"/>
+      <c r="V40" s="245"/>
+      <c r="W40" s="245"/>
     </row>
     <row r="41" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A41" s="136" t="inlineStr">
@@ -9564,7 +10813,10 @@
       </c>
       <c r="I41" s="254"/>
       <c r="J41" s="255"/>
+      <c r="K41" s="245"/>
       <c r="L41" s="4"/>
+      <c r="M41" s="245"/>
+      <c r="N41" s="245"/>
       <c r="O41" s="245" t="inlineStr">
         <is>
           <r>
@@ -9572,7 +10824,14 @@
           </r>
         </is>
       </c>
+      <c r="P41" s="245"/>
       <c r="Q41" s="5"/>
+      <c r="R41" s="245"/>
+      <c r="S41" s="245"/>
+      <c r="T41" s="245"/>
+      <c r="U41" s="245"/>
+      <c r="V41" s="245"/>
+      <c r="W41" s="245"/>
     </row>
     <row r="42" spans="1:23" customHeight="1" ht="33" s="245" customFormat="1">
       <c r="A42" s="297" t="inlineStr">
@@ -9591,8 +10850,19 @@
       <c r="H42" s="254"/>
       <c r="I42" s="254"/>
       <c r="J42" s="255"/>
+      <c r="K42" s="245"/>
       <c r="L42" s="4"/>
+      <c r="M42" s="245"/>
+      <c r="N42" s="245"/>
+      <c r="O42" s="245"/>
+      <c r="P42" s="245"/>
       <c r="Q42" s="5"/>
+      <c r="R42" s="245"/>
+      <c r="S42" s="245"/>
+      <c r="T42" s="245"/>
+      <c r="U42" s="245"/>
+      <c r="V42" s="245"/>
+      <c r="W42" s="245"/>
     </row>
     <row r="43" spans="1:23" customHeight="1" ht="22.5" s="245" customFormat="1">
       <c r="A43" s="300" t="inlineStr">
@@ -9617,8 +10887,19 @@
       </c>
       <c r="I43" s="254"/>
       <c r="J43" s="255"/>
+      <c r="K43" s="245"/>
       <c r="L43" s="4"/>
+      <c r="M43" s="245"/>
+      <c r="N43" s="245"/>
+      <c r="O43" s="245"/>
+      <c r="P43" s="245"/>
       <c r="Q43" s="5"/>
+      <c r="R43" s="245"/>
+      <c r="S43" s="245"/>
+      <c r="T43" s="245"/>
+      <c r="U43" s="245"/>
+      <c r="V43" s="245"/>
+      <c r="W43" s="245"/>
     </row>
     <row r="44" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A44" s="136" t="inlineStr">
@@ -9643,8 +10924,19 @@
       </c>
       <c r="I44" s="254"/>
       <c r="J44" s="255"/>
+      <c r="K44" s="245"/>
       <c r="L44" s="4"/>
+      <c r="M44" s="245"/>
+      <c r="N44" s="245"/>
+      <c r="O44" s="245"/>
+      <c r="P44" s="245"/>
       <c r="Q44" s="5"/>
+      <c r="R44" s="245"/>
+      <c r="S44" s="245"/>
+      <c r="T44" s="245"/>
+      <c r="U44" s="245"/>
+      <c r="V44" s="245"/>
+      <c r="W44" s="245"/>
     </row>
     <row r="45" spans="1:23" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A45" s="136" t="inlineStr">
@@ -9676,9 +10968,45 @@
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="9"/>
-    </row>
-    <row r="46" spans="1:23" customHeight="1" ht="6" s="245" customFormat="1"/>
+      <c r="R45" s="245"/>
+      <c r="S45" s="245"/>
+      <c r="T45" s="245"/>
+      <c r="U45" s="245"/>
+      <c r="V45" s="245"/>
+      <c r="W45" s="245"/>
+    </row>
+    <row r="46" spans="1:23" customHeight="1" ht="6" s="245" customFormat="1">
+      <c r="A46" s="245"/>
+      <c r="B46" s="245"/>
+      <c r="C46" s="245"/>
+      <c r="D46" s="245"/>
+      <c r="E46" s="245"/>
+      <c r="F46" s="245"/>
+      <c r="G46" s="245"/>
+      <c r="H46" s="245"/>
+      <c r="I46" s="245"/>
+      <c r="J46" s="245"/>
+      <c r="K46" s="245"/>
+      <c r="L46" s="245"/>
+      <c r="M46" s="245"/>
+      <c r="N46" s="245"/>
+      <c r="O46" s="245"/>
+      <c r="P46" s="245"/>
+      <c r="Q46" s="245"/>
+      <c r="R46" s="245"/>
+      <c r="S46" s="245"/>
+      <c r="T46" s="245"/>
+      <c r="U46" s="245"/>
+      <c r="V46" s="245"/>
+      <c r="W46" s="245"/>
+    </row>
     <row r="47" spans="1:23" customHeight="1" ht="23.25" s="245" customFormat="1">
+      <c r="A47" s="245"/>
+      <c r="B47" s="245"/>
+      <c r="C47" s="245"/>
+      <c r="D47" s="245"/>
+      <c r="E47" s="245"/>
+      <c r="F47" s="245"/>
       <c r="G47" s="162" t="inlineStr">
         <is>
           <r>
@@ -9686,6 +11014,12 @@
           </r>
         </is>
       </c>
+      <c r="H47" s="245"/>
+      <c r="I47" s="245"/>
+      <c r="J47" s="245"/>
+      <c r="K47" s="245"/>
+      <c r="L47" s="245"/>
+      <c r="M47" s="245"/>
       <c r="N47" s="163" t="inlineStr">
         <is>
           <r>
@@ -9693,6 +11027,15 @@
           </r>
         </is>
       </c>
+      <c r="O47" s="245"/>
+      <c r="P47" s="245"/>
+      <c r="Q47" s="245"/>
+      <c r="R47" s="245"/>
+      <c r="S47" s="245"/>
+      <c r="T47" s="245"/>
+      <c r="U47" s="245"/>
+      <c r="V47" s="245"/>
+      <c r="W47" s="245"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -9841,6 +11184,20 @@
           </r>
         </is>
       </c>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="245"/>
+      <c r="F1" s="245"/>
+      <c r="G1" s="245"/>
+      <c r="H1" s="245"/>
+      <c r="I1" s="245"/>
+      <c r="J1" s="245"/>
+      <c r="K1" s="245"/>
+      <c r="L1" s="245"/>
+      <c r="M1" s="245"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="245"/>
     </row>
     <row r="2" spans="1:15" customHeight="1" ht="17.25" s="245" customFormat="1">
       <c r="A2" s="200" t="inlineStr">
@@ -9850,6 +11207,20 @@
           </r>
         </is>
       </c>
+      <c r="B2" s="245"/>
+      <c r="C2" s="245"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="245"/>
+      <c r="H2" s="245"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
+      <c r="M2" s="245"/>
+      <c r="N2" s="245"/>
+      <c r="O2" s="245"/>
     </row>
     <row r="3" spans="1:15" customHeight="1" ht="17.25" s="245" customFormat="1">
       <c r="A3" s="200" t="inlineStr">
@@ -9859,6 +11230,20 @@
           </r>
         </is>
       </c>
+      <c r="B3" s="245"/>
+      <c r="C3" s="245"/>
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="245"/>
+      <c r="H3" s="245"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="M3" s="245"/>
+      <c r="N3" s="245"/>
+      <c r="O3" s="245"/>
     </row>
     <row r="4" spans="1:15" customHeight="1" ht="38.25" s="245" customFormat="1">
       <c r="A4" s="196" t="inlineStr">
@@ -9868,6 +11253,20 @@
           </r>
         </is>
       </c>
+      <c r="B4" s="245"/>
+      <c r="C4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
+      <c r="M4" s="245"/>
+      <c r="N4" s="245"/>
+      <c r="O4" s="245"/>
     </row>
     <row r="5" spans="1:15" customHeight="1" ht="27.75" s="245" customFormat="1">
       <c r="A5" s="203" t="inlineStr">
@@ -9877,6 +11276,20 @@
           </r>
         </is>
       </c>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="M5" s="245"/>
+      <c r="N5" s="245"/>
+      <c r="O5" s="245"/>
     </row>
     <row r="6" spans="1:15" customHeight="1" ht="24.95" s="245" customFormat="1">
       <c r="A6" s="92" t="inlineStr">
@@ -9993,6 +11406,7 @@
       <c r="O8" s="81"/>
     </row>
     <row r="9" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A9" s="245"/>
       <c r="B9" s="304"/>
       <c r="C9" s="180" t="inlineStr">
         <is>
@@ -10015,15 +11429,19 @@
           </r>
         </is>
       </c>
+      <c r="I9" s="245"/>
       <c r="J9" s="304"/>
       <c r="K9" s="202" t="str">
         <f>구매리스트!D7</f>
         <v>0</v>
       </c>
+      <c r="L9" s="245"/>
+      <c r="M9" s="245"/>
       <c r="N9" s="82"/>
       <c r="O9" s="83"/>
     </row>
     <row r="10" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A10" s="245"/>
       <c r="B10" s="304"/>
       <c r="C10" s="201" t="inlineStr">
         <is>
@@ -10058,6 +11476,7 @@
       <c r="O10" s="308"/>
     </row>
     <row r="11" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A11" s="245"/>
       <c r="B11" s="304"/>
       <c r="C11" s="199" t="inlineStr">
         <is>
@@ -10086,6 +11505,7 @@
       <c r="O11" s="312"/>
     </row>
     <row r="12" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A12" s="245"/>
       <c r="B12" s="304"/>
       <c r="C12" s="180" t="inlineStr">
         <is>
@@ -10099,6 +11519,7 @@
         <f>구매리스트!I4</f>
         <v>0</v>
       </c>
+      <c r="F12" s="245"/>
       <c r="G12" s="304"/>
       <c r="H12" s="180" t="inlineStr">
         <is>
@@ -10107,13 +11528,19 @@
           </r>
         </is>
       </c>
+      <c r="I12" s="245"/>
       <c r="J12" s="304"/>
       <c r="K12" s="183" t="str">
         <f>구매리스트!D6</f>
         <v>0</v>
       </c>
+      <c r="L12" s="245"/>
+      <c r="M12" s="245"/>
+      <c r="N12" s="245"/>
+      <c r="O12" s="245"/>
     </row>
     <row r="13" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A13" s="245"/>
       <c r="B13" s="304"/>
       <c r="C13" s="180" t="inlineStr">
         <is>
@@ -10124,6 +11551,7 @@
       </c>
       <c r="D13" s="304"/>
       <c r="E13" s="305"/>
+      <c r="F13" s="245"/>
       <c r="G13" s="304"/>
       <c r="H13" s="180" t="inlineStr">
         <is>
@@ -10132,10 +11560,16 @@
           </r>
         </is>
       </c>
+      <c r="I13" s="245"/>
       <c r="J13" s="304"/>
       <c r="K13" s="305"/>
+      <c r="L13" s="245"/>
+      <c r="M13" s="245"/>
+      <c r="N13" s="245"/>
+      <c r="O13" s="245"/>
     </row>
     <row r="14" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A14" s="245"/>
       <c r="B14" s="304"/>
       <c r="C14" s="178" t="inlineStr">
         <is>
@@ -10171,6 +11605,7 @@
       <c r="O14" s="315"/>
     </row>
     <row r="15" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A15" s="245"/>
       <c r="B15" s="304"/>
       <c r="C15" s="180" t="inlineStr">
         <is>
@@ -10181,12 +11616,19 @@
       </c>
       <c r="D15" s="304"/>
       <c r="E15" s="305"/>
+      <c r="F15" s="245"/>
       <c r="G15" s="304"/>
       <c r="H15" s="305"/>
+      <c r="I15" s="245"/>
       <c r="J15" s="304"/>
       <c r="K15" s="305"/>
+      <c r="L15" s="245"/>
+      <c r="M15" s="245"/>
+      <c r="N15" s="245"/>
+      <c r="O15" s="245"/>
     </row>
     <row r="16" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A16" s="245"/>
       <c r="B16" s="304"/>
       <c r="C16" s="179" t="inlineStr">
         <is>
@@ -10209,6 +11651,7 @@
       <c r="O16" s="319"/>
     </row>
     <row r="17" spans="1:15" customHeight="1" ht="21.95" s="245" customFormat="1">
+      <c r="A17" s="245"/>
       <c r="B17" s="304"/>
       <c r="C17" s="180" t="inlineStr">
         <is>
@@ -10222,6 +11665,7 @@
         <f>구매리스트!B6</f>
         <v>0</v>
       </c>
+      <c r="F17" s="245"/>
       <c r="G17" s="304"/>
       <c r="H17" s="180" t="inlineStr">
         <is>
@@ -10230,6 +11674,7 @@
           </r>
         </is>
       </c>
+      <c r="I17" s="245"/>
       <c r="J17" s="304"/>
       <c r="K17" s="209" t="inlineStr">
         <is>
@@ -10238,8 +11683,13 @@
           </r>
         </is>
       </c>
+      <c r="L17" s="245"/>
+      <c r="M17" s="245"/>
+      <c r="N17" s="245"/>
+      <c r="O17" s="245"/>
     </row>
     <row r="18" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
+      <c r="A18" s="245"/>
       <c r="B18" s="304"/>
       <c r="C18" s="180" t="inlineStr">
         <is>
@@ -10250,6 +11700,7 @@
       </c>
       <c r="D18" s="304"/>
       <c r="E18" s="305"/>
+      <c r="F18" s="245"/>
       <c r="G18" s="304"/>
       <c r="H18" s="180" t="inlineStr">
         <is>
@@ -10258,8 +11709,13 @@
           </r>
         </is>
       </c>
+      <c r="I18" s="245"/>
       <c r="J18" s="304"/>
       <c r="K18" s="305"/>
+      <c r="L18" s="245"/>
+      <c r="M18" s="245"/>
+      <c r="N18" s="245"/>
+      <c r="O18" s="245"/>
     </row>
     <row r="19" spans="1:15" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A19" s="252"/>
@@ -10480,6 +11936,8 @@
           </r>
         </is>
       </c>
+      <c r="B26" s="245"/>
+      <c r="C26" s="245"/>
       <c r="D26" s="304"/>
       <c r="E26" s="216" t="inlineStr">
         <is>
@@ -10488,6 +11946,7 @@
           </r>
         </is>
       </c>
+      <c r="F26" s="245"/>
       <c r="G26" s="304"/>
       <c r="H26" s="180" t="inlineStr">
         <is>
@@ -10496,6 +11955,7 @@
           </r>
         </is>
       </c>
+      <c r="I26" s="245"/>
       <c r="J26" s="304"/>
       <c r="K26" s="94" t="inlineStr">
         <is>
@@ -10597,6 +12057,20 @@
           </r>
         </is>
       </c>
+      <c r="B29" s="245"/>
+      <c r="C29" s="245"/>
+      <c r="D29" s="245"/>
+      <c r="E29" s="245"/>
+      <c r="F29" s="245"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
+      <c r="J29" s="245"/>
+      <c r="K29" s="245"/>
+      <c r="L29" s="245"/>
+      <c r="M29" s="245"/>
+      <c r="N29" s="245"/>
+      <c r="O29" s="245"/>
     </row>
     <row r="30" spans="1:15" customHeight="1" ht="32.25" s="245" customFormat="1">
       <c r="A30" s="217" t="inlineStr">
@@ -10606,6 +12080,20 @@
           </r>
         </is>
       </c>
+      <c r="B30" s="245"/>
+      <c r="C30" s="245"/>
+      <c r="D30" s="245"/>
+      <c r="E30" s="245"/>
+      <c r="F30" s="245"/>
+      <c r="G30" s="245"/>
+      <c r="H30" s="245"/>
+      <c r="I30" s="245"/>
+      <c r="J30" s="245"/>
+      <c r="K30" s="245"/>
+      <c r="L30" s="245"/>
+      <c r="M30" s="245"/>
+      <c r="N30" s="245"/>
+      <c r="O30" s="245"/>
     </row>
     <row r="31" spans="1:15" customHeight="1" ht="32.25" s="245" customFormat="1">
       <c r="A31" s="217" t="inlineStr">
@@ -10615,6 +12103,20 @@
           </r>
         </is>
       </c>
+      <c r="B31" s="245"/>
+      <c r="C31" s="245"/>
+      <c r="D31" s="245"/>
+      <c r="E31" s="245"/>
+      <c r="F31" s="245"/>
+      <c r="G31" s="245"/>
+      <c r="H31" s="245"/>
+      <c r="I31" s="245"/>
+      <c r="J31" s="245"/>
+      <c r="K31" s="245"/>
+      <c r="L31" s="245"/>
+      <c r="M31" s="245"/>
+      <c r="N31" s="245"/>
+      <c r="O31" s="245"/>
     </row>
     <row r="32" spans="1:15" customHeight="1" ht="9.75" s="245" customFormat="1">
       <c r="A32" s="77"/>
@@ -10659,10 +12161,16 @@
           </r>
         </is>
       </c>
+      <c r="H33" s="245"/>
+      <c r="I33" s="245"/>
+      <c r="J33" s="245"/>
       <c r="K33" s="218" t="str">
         <f>E24</f>
         <v>0</v>
       </c>
+      <c r="L33" s="245"/>
+      <c r="M33" s="245"/>
+      <c r="N33" s="245"/>
       <c r="O33" s="77"/>
     </row>
     <row r="34" spans="1:15" customHeight="1" ht="85.5" s="245" customFormat="1">
@@ -10692,6 +12200,18 @@
           </r>
         </is>
       </c>
+      <c r="B35" s="245"/>
+      <c r="C35" s="245"/>
+      <c r="D35" s="245"/>
+      <c r="E35" s="245"/>
+      <c r="F35" s="245"/>
+      <c r="G35" s="245"/>
+      <c r="H35" s="245"/>
+      <c r="I35" s="245"/>
+      <c r="J35" s="245"/>
+      <c r="K35" s="245"/>
+      <c r="L35" s="245"/>
+      <c r="M35" s="245"/>
       <c r="N35" s="77"/>
       <c r="O35" s="77"/>
     </row>
@@ -10703,6 +12223,18 @@
           </r>
         </is>
       </c>
+      <c r="B36" s="245"/>
+      <c r="C36" s="245"/>
+      <c r="D36" s="245"/>
+      <c r="E36" s="245"/>
+      <c r="F36" s="245"/>
+      <c r="G36" s="245"/>
+      <c r="H36" s="245"/>
+      <c r="I36" s="245"/>
+      <c r="J36" s="245"/>
+      <c r="K36" s="245"/>
+      <c r="L36" s="245"/>
+      <c r="M36" s="245"/>
       <c r="N36" s="78"/>
       <c r="O36" s="77"/>
     </row>
@@ -10714,6 +12246,18 @@
           </r>
         </is>
       </c>
+      <c r="B37" s="245"/>
+      <c r="C37" s="245"/>
+      <c r="D37" s="245"/>
+      <c r="E37" s="245"/>
+      <c r="F37" s="245"/>
+      <c r="G37" s="245"/>
+      <c r="H37" s="245"/>
+      <c r="I37" s="245"/>
+      <c r="J37" s="245"/>
+      <c r="K37" s="245"/>
+      <c r="L37" s="245"/>
+      <c r="M37" s="245"/>
       <c r="N37" s="86"/>
       <c r="O37" s="87"/>
     </row>
@@ -10771,6 +12315,20 @@
           </r>
         </is>
       </c>
+      <c r="B40" s="245"/>
+      <c r="C40" s="245"/>
+      <c r="D40" s="245"/>
+      <c r="E40" s="245"/>
+      <c r="F40" s="245"/>
+      <c r="G40" s="245"/>
+      <c r="H40" s="245"/>
+      <c r="I40" s="245"/>
+      <c r="J40" s="245"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="245"/>
+      <c r="M40" s="245"/>
+      <c r="N40" s="245"/>
+      <c r="O40" s="245"/>
     </row>
     <row r="41" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A41" s="191" t="inlineStr">
@@ -10780,6 +12338,20 @@
           </r>
         </is>
       </c>
+      <c r="B41" s="245"/>
+      <c r="C41" s="245"/>
+      <c r="D41" s="245"/>
+      <c r="E41" s="245"/>
+      <c r="F41" s="245"/>
+      <c r="G41" s="245"/>
+      <c r="H41" s="245"/>
+      <c r="I41" s="245"/>
+      <c r="J41" s="245"/>
+      <c r="K41" s="245"/>
+      <c r="L41" s="245"/>
+      <c r="M41" s="245"/>
+      <c r="N41" s="245"/>
+      <c r="O41" s="245"/>
     </row>
     <row r="42" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A42" s="191" t="inlineStr">
@@ -10789,6 +12361,20 @@
           </r>
         </is>
       </c>
+      <c r="B42" s="245"/>
+      <c r="C42" s="245"/>
+      <c r="D42" s="245"/>
+      <c r="E42" s="245"/>
+      <c r="F42" s="245"/>
+      <c r="G42" s="245"/>
+      <c r="H42" s="245"/>
+      <c r="I42" s="245"/>
+      <c r="J42" s="245"/>
+      <c r="K42" s="245"/>
+      <c r="L42" s="245"/>
+      <c r="M42" s="245"/>
+      <c r="N42" s="245"/>
+      <c r="O42" s="245"/>
     </row>
     <row r="43" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
       <c r="A43" s="221" t="inlineStr">
@@ -10866,6 +12452,9 @@
       <c r="I45" s="76"/>
       <c r="J45" s="76"/>
       <c r="K45" s="333"/>
+      <c r="L45" s="245"/>
+      <c r="M45" s="245"/>
+      <c r="N45" s="245"/>
       <c r="O45" s="334"/>
     </row>
     <row r="46" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
@@ -10876,7 +12465,19 @@
           </r>
         </is>
       </c>
+      <c r="B46" s="245"/>
+      <c r="C46" s="245"/>
+      <c r="D46" s="245"/>
+      <c r="E46" s="245"/>
+      <c r="F46" s="245"/>
+      <c r="G46" s="245"/>
+      <c r="H46" s="245"/>
+      <c r="I46" s="245"/>
+      <c r="J46" s="245"/>
       <c r="K46" s="333"/>
+      <c r="L46" s="245"/>
+      <c r="M46" s="245"/>
+      <c r="N46" s="245"/>
       <c r="O46" s="334"/>
     </row>
     <row r="47" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
@@ -10887,7 +12488,19 @@
           </r>
         </is>
       </c>
+      <c r="B47" s="245"/>
+      <c r="C47" s="245"/>
+      <c r="D47" s="245"/>
+      <c r="E47" s="245"/>
+      <c r="F47" s="245"/>
+      <c r="G47" s="245"/>
+      <c r="H47" s="245"/>
+      <c r="I47" s="245"/>
+      <c r="J47" s="245"/>
       <c r="K47" s="333"/>
+      <c r="L47" s="245"/>
+      <c r="M47" s="245"/>
+      <c r="N47" s="245"/>
       <c r="O47" s="334"/>
     </row>
     <row r="48" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
@@ -10898,7 +12511,19 @@
           </r>
         </is>
       </c>
+      <c r="B48" s="245"/>
+      <c r="C48" s="245"/>
+      <c r="D48" s="245"/>
+      <c r="E48" s="245"/>
+      <c r="F48" s="245"/>
+      <c r="G48" s="245"/>
+      <c r="H48" s="245"/>
+      <c r="I48" s="245"/>
+      <c r="J48" s="245"/>
       <c r="K48" s="333"/>
+      <c r="L48" s="245"/>
+      <c r="M48" s="245"/>
+      <c r="N48" s="245"/>
       <c r="O48" s="334"/>
     </row>
     <row r="49" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
@@ -10910,7 +12535,18 @@
         </is>
       </c>
       <c r="B49" s="245"/>
+      <c r="C49" s="245"/>
+      <c r="D49" s="245"/>
+      <c r="E49" s="245"/>
+      <c r="F49" s="245"/>
+      <c r="G49" s="245"/>
+      <c r="H49" s="245"/>
+      <c r="I49" s="245"/>
+      <c r="J49" s="245"/>
       <c r="K49" s="333"/>
+      <c r="L49" s="245"/>
+      <c r="M49" s="245"/>
+      <c r="N49" s="245"/>
       <c r="O49" s="334"/>
     </row>
     <row r="50" spans="1:15" customHeight="1" ht="19.5" s="245" customFormat="1">
@@ -11054,9 +12690,37 @@
           </r>
         </is>
       </c>
+      <c r="B55" s="89"/>
+      <c r="C55" s="89"/>
+      <c r="D55" s="89"/>
+      <c r="E55" s="89"/>
+      <c r="F55" s="89"/>
+      <c r="G55" s="89"/>
+      <c r="H55" s="89"/>
+      <c r="I55" s="89"/>
+      <c r="J55" s="89"/>
+      <c r="K55" s="89"/>
+      <c r="L55" s="89"/>
+      <c r="M55" s="89"/>
+      <c r="N55" s="89"/>
+      <c r="O55" s="89"/>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="245"/>
+      <c r="B56" s="245"/>
+      <c r="C56" s="245"/>
+      <c r="D56" s="245"/>
+      <c r="E56" s="245"/>
+      <c r="F56" s="245"/>
+      <c r="G56" s="245"/>
+      <c r="H56" s="245"/>
+      <c r="I56" s="245"/>
+      <c r="J56" s="245"/>
+      <c r="K56" s="245"/>
+      <c r="L56" s="245"/>
+      <c r="M56" s="245"/>
+      <c r="N56" s="245"/>
+      <c r="O56" s="245"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -11206,6 +12870,7 @@
       <c r="G1" s="254"/>
       <c r="H1" s="254"/>
       <c r="I1" s="255"/>
+      <c r="J1" s="245"/>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A2" s="342" t="inlineStr">
@@ -11238,6 +12903,7 @@
         </is>
       </c>
       <c r="I2" s="251"/>
+      <c r="J2" s="245"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A3" s="344" t="inlineStr">
@@ -11251,6 +12917,8 @@
           </r>
         </is>
       </c>
+      <c r="B3" s="245"/>
+      <c r="C3" s="245"/>
       <c r="D3" s="262"/>
       <c r="E3" s="228" t="inlineStr">
         <is>
@@ -11259,15 +12927,19 @@
           </r>
         </is>
       </c>
+      <c r="F3" s="245"/>
       <c r="G3" s="129" t="str">
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
       <c r="H3" s="272"/>
       <c r="I3" s="253"/>
+      <c r="J3" s="245"/>
     </row>
     <row r="4" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A4" s="271"/>
+      <c r="B4" s="245"/>
+      <c r="C4" s="245"/>
       <c r="D4" s="262"/>
       <c r="E4" s="345" t="inlineStr">
         <is>
@@ -11276,16 +12948,28 @@
           </r>
         </is>
       </c>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
       <c r="I4" s="262"/>
+      <c r="J4" s="245"/>
     </row>
     <row r="5" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A5" s="271"/>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
       <c r="D5" s="262"/>
       <c r="E5" s="271"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
       <c r="I5" s="262"/>
+      <c r="J5" s="245"/>
     </row>
     <row r="6" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A6" s="271"/>
+      <c r="B6" s="245"/>
+      <c r="C6" s="245"/>
       <c r="D6" s="262"/>
       <c r="E6" s="346" t="inlineStr">
         <is>
@@ -11294,7 +12978,11 @@
           </r>
         </is>
       </c>
+      <c r="F6" s="245"/>
+      <c r="G6" s="245"/>
+      <c r="H6" s="245"/>
       <c r="I6" s="262"/>
+      <c r="J6" s="245"/>
     </row>
     <row r="7" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A7" s="272"/>
@@ -11308,7 +12996,11 @@
           </r>
         </is>
       </c>
+      <c r="F7" s="245"/>
+      <c r="G7" s="245"/>
+      <c r="H7" s="245"/>
       <c r="I7" s="262"/>
+      <c r="J7" s="245"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A8" s="342" t="inlineStr">
@@ -11332,12 +13024,15 @@
       <c r="G8" s="252"/>
       <c r="H8" s="252"/>
       <c r="I8" s="253"/>
+      <c r="J8" s="245"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="245" customFormat="1">
       <c r="A9" s="348" t="str">
         <f>구매리스트!B14</f>
         <v>0</v>
       </c>
+      <c r="B9" s="245"/>
+      <c r="C9" s="245"/>
       <c r="D9" s="262"/>
       <c r="E9" s="234" t="inlineStr">
         <is>
@@ -11360,6 +13055,8 @@
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A10" s="271"/>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
       <c r="D10" s="262"/>
       <c r="E10" s="225" t="inlineStr">
         <is>
@@ -11372,6 +13069,7 @@
       <c r="G10" s="250"/>
       <c r="H10" s="250"/>
       <c r="I10" s="251"/>
+      <c r="J10" s="245"/>
     </row>
     <row r="11" spans="1:10" customHeight="1" ht="35.25" s="245" customFormat="1">
       <c r="A11" s="272"/>
@@ -11382,10 +13080,14 @@
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
       <c r="I11" s="53" t="str">
         <f>TODAY()</f>
         <v>0</v>
       </c>
+      <c r="J11" s="245"/>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A12" s="342" t="inlineStr">
@@ -11409,6 +13111,7 @@
       <c r="G12" s="250"/>
       <c r="H12" s="250"/>
       <c r="I12" s="251"/>
+      <c r="J12" s="245"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A13" s="349" t="inlineStr">
@@ -11418,6 +13121,8 @@
           </r>
         </is>
       </c>
+      <c r="B13" s="245"/>
+      <c r="C13" s="245"/>
       <c r="D13" s="262"/>
       <c r="E13" s="229" t="inlineStr">
         <is>
@@ -11426,7 +13131,11 @@
           </r>
         </is>
       </c>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
       <c r="I13" s="262"/>
+      <c r="J13" s="245"/>
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="9.75" s="245" customFormat="1">
       <c r="A14" s="272"/>
@@ -11438,6 +13147,7 @@
       <c r="G14" s="252"/>
       <c r="H14" s="252"/>
       <c r="I14" s="253"/>
+      <c r="J14" s="245"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
       <c r="A15" s="342" t="inlineStr">
@@ -11467,6 +13177,7 @@
       <c r="G15" s="250"/>
       <c r="H15" s="250"/>
       <c r="I15" s="251"/>
+      <c r="J15" s="245"/>
     </row>
     <row r="16" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A16" s="231" t="str">
@@ -11486,7 +13197,11 @@
           </r>
         </is>
       </c>
+      <c r="F16" s="245"/>
+      <c r="G16" s="245"/>
+      <c r="H16" s="245"/>
       <c r="I16" s="262"/>
+      <c r="J16" s="245"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
       <c r="A17" s="342" t="inlineStr">
@@ -11513,6 +13228,7 @@
       <c r="G17" s="250"/>
       <c r="H17" s="250"/>
       <c r="I17" s="251"/>
+      <c r="J17" s="245"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A18" s="350" t="str">
@@ -11530,6 +13246,7 @@
       <c r="G18" s="252"/>
       <c r="H18" s="252"/>
       <c r="I18" s="253"/>
+      <c r="J18" s="245"/>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A19" s="22" t="inlineStr">
@@ -11577,6 +13294,7 @@
           </r>
         </is>
       </c>
+      <c r="J19" s="245"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="10.5" s="245" customFormat="1">
       <c r="A20" s="30"/>
@@ -11588,6 +13306,7 @@
       <c r="G20" s="31"/>
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
+      <c r="J20" s="245"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A21" s="36" t="inlineStr">
@@ -12033,7 +13752,9 @@
           </r>
         </is>
       </c>
+      <c r="F33" s="245"/>
       <c r="G33" s="245"/>
+      <c r="H33" s="245"/>
       <c r="I33" s="29"/>
       <c r="J33" s="18"/>
     </row>
@@ -12055,7 +13776,11 @@
           </r>
         </is>
       </c>
+      <c r="F34" s="245"/>
+      <c r="G34" s="245"/>
+      <c r="H34" s="245"/>
       <c r="I34" s="32"/>
+      <c r="J34"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="30" t="inlineStr">
@@ -12073,6 +13798,7 @@
       <c r="G35" s="31"/>
       <c r="H35" s="31"/>
       <c r="I35" s="32"/>
+      <c r="J35"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="30"/>
@@ -12084,6 +13810,7 @@
       <c r="G36" s="31"/>
       <c r="H36" s="31"/>
       <c r="I36" s="32"/>
+      <c r="J36"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="30"/>
@@ -12095,6 +13822,7 @@
       <c r="G37" s="31"/>
       <c r="H37" s="31"/>
       <c r="I37" s="32"/>
+      <c r="J37"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="30"/>
@@ -12106,6 +13834,7 @@
       <c r="G38" s="31"/>
       <c r="H38" s="31"/>
       <c r="I38" s="32"/>
+      <c r="J38"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="30"/>
@@ -12117,6 +13846,7 @@
       <c r="G39" s="31"/>
       <c r="H39" s="31"/>
       <c r="I39" s="32"/>
+      <c r="J39"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="33"/>
@@ -12128,6 +13858,7 @@
       <c r="G40" s="34"/>
       <c r="H40" s="34"/>
       <c r="I40" s="35"/>
+      <c r="J40"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -12232,6 +13963,7 @@
       <c r="G1" s="254"/>
       <c r="H1" s="254"/>
       <c r="I1" s="255"/>
+      <c r="J1" s="245"/>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A2" s="342" t="inlineStr">
@@ -12264,11 +13996,14 @@
         </is>
       </c>
       <c r="I2" s="251"/>
+      <c r="J2" s="245"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A3" s="344" t="s">
         <v>347</v>
       </c>
+      <c r="B3" s="245"/>
+      <c r="C3" s="245"/>
       <c r="D3" s="262"/>
       <c r="E3" s="228" t="inlineStr">
         <is>
@@ -12277,15 +14012,19 @@
           </r>
         </is>
       </c>
+      <c r="F3" s="245"/>
       <c r="G3" s="129" t="str">
         <f>차량인보이스!G3</f>
         <v>0</v>
       </c>
       <c r="H3" s="272"/>
       <c r="I3" s="253"/>
+      <c r="J3" s="245"/>
     </row>
     <row r="4" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A4" s="271"/>
+      <c r="B4" s="245"/>
+      <c r="C4" s="245"/>
       <c r="D4" s="262"/>
       <c r="E4" s="345" t="inlineStr">
         <is>
@@ -12294,16 +14033,28 @@
           </r>
         </is>
       </c>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
       <c r="I4" s="262"/>
+      <c r="J4" s="245"/>
     </row>
     <row r="5" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A5" s="271"/>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
       <c r="D5" s="262"/>
       <c r="E5" s="271"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
       <c r="I5" s="262"/>
+      <c r="J5" s="245"/>
     </row>
     <row r="6" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A6" s="271"/>
+      <c r="B6" s="245"/>
+      <c r="C6" s="245"/>
       <c r="D6" s="262"/>
       <c r="E6" s="346" t="inlineStr">
         <is>
@@ -12312,7 +14063,11 @@
           </r>
         </is>
       </c>
+      <c r="F6" s="245"/>
+      <c r="G6" s="245"/>
+      <c r="H6" s="245"/>
       <c r="I6" s="262"/>
+      <c r="J6" s="245"/>
     </row>
     <row r="7" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A7" s="272"/>
@@ -12326,7 +14081,11 @@
           </r>
         </is>
       </c>
+      <c r="F7" s="245"/>
+      <c r="G7" s="245"/>
+      <c r="H7" s="245"/>
       <c r="I7" s="262"/>
+      <c r="J7" s="245"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A8" s="342" t="inlineStr">
@@ -12350,12 +14109,15 @@
       <c r="G8" s="252"/>
       <c r="H8" s="252"/>
       <c r="I8" s="253"/>
+      <c r="J8" s="245"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="245" customFormat="1">
       <c r="A9" s="371" t="str">
         <f>차량인보이스!A9</f>
         <v>0</v>
       </c>
+      <c r="B9" s="245"/>
+      <c r="C9" s="245"/>
       <c r="D9" s="262"/>
       <c r="E9" s="234" t="inlineStr">
         <is>
@@ -12378,6 +14140,8 @@
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A10" s="271"/>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
       <c r="D10" s="262"/>
       <c r="E10" s="225" t="inlineStr">
         <is>
@@ -12390,6 +14154,7 @@
       <c r="G10" s="250"/>
       <c r="H10" s="250"/>
       <c r="I10" s="251"/>
+      <c r="J10" s="245"/>
     </row>
     <row r="11" spans="1:10" customHeight="1" ht="35.25" s="245" customFormat="1">
       <c r="A11" s="272"/>
@@ -12400,10 +14165,14 @@
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
       <c r="I11" s="53" t="str">
         <f>TODAY()</f>
         <v>0</v>
       </c>
+      <c r="J11" s="245"/>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A12" s="342" t="inlineStr">
@@ -12427,6 +14196,7 @@
       <c r="G12" s="250"/>
       <c r="H12" s="250"/>
       <c r="I12" s="251"/>
+      <c r="J12" s="245"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A13" s="349" t="inlineStr">
@@ -12436,6 +14206,8 @@
           </r>
         </is>
       </c>
+      <c r="B13" s="245"/>
+      <c r="C13" s="245"/>
       <c r="D13" s="262"/>
       <c r="E13" s="229" t="inlineStr">
         <is>
@@ -12444,7 +14216,11 @@
           </r>
         </is>
       </c>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
       <c r="I13" s="262"/>
+      <c r="J13" s="245"/>
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="9.75" s="245" customFormat="1">
       <c r="A14" s="272"/>
@@ -12456,6 +14232,7 @@
       <c r="G14" s="252"/>
       <c r="H14" s="252"/>
       <c r="I14" s="253"/>
+      <c r="J14" s="245"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
       <c r="A15" s="342" t="inlineStr">
@@ -12485,6 +14262,7 @@
       <c r="G15" s="250"/>
       <c r="H15" s="250"/>
       <c r="I15" s="251"/>
+      <c r="J15" s="245"/>
     </row>
     <row r="16" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A16" s="231" t="str">
@@ -12504,7 +14282,11 @@
           </r>
         </is>
       </c>
+      <c r="F16" s="245"/>
+      <c r="G16" s="245"/>
+      <c r="H16" s="245"/>
       <c r="I16" s="262"/>
+      <c r="J16" s="245"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="16.5" s="245" customFormat="1">
       <c r="A17" s="342" t="inlineStr">
@@ -12531,6 +14313,7 @@
       <c r="G17" s="250"/>
       <c r="H17" s="250"/>
       <c r="I17" s="251"/>
+      <c r="J17" s="245"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="24" s="245" customFormat="1">
       <c r="A18" s="350" t="str">
@@ -12548,6 +14331,7 @@
       <c r="G18" s="252"/>
       <c r="H18" s="252"/>
       <c r="I18" s="253"/>
+      <c r="J18" s="245"/>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A19" s="22" t="inlineStr">
@@ -12595,6 +14379,7 @@
           </r>
         </is>
       </c>
+      <c r="J19" s="245"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="10.5" s="245" customFormat="1">
       <c r="A20" s="30"/>
@@ -12606,6 +14391,7 @@
       <c r="G20" s="31"/>
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
+      <c r="J20" s="245"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="27" s="245" customFormat="1">
       <c r="A21" s="36" t="inlineStr">
@@ -13074,7 +14860,9 @@
           </r>
         </is>
       </c>
+      <c r="F33" s="245"/>
       <c r="G33" s="245"/>
+      <c r="H33" s="245"/>
       <c r="I33" s="29"/>
       <c r="J33" s="18"/>
     </row>
@@ -13096,7 +14884,11 @@
           </r>
         </is>
       </c>
+      <c r="F34" s="245"/>
+      <c r="G34" s="245"/>
+      <c r="H34" s="245"/>
       <c r="I34" s="32"/>
+      <c r="J34"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="30" t="inlineStr">
@@ -13114,6 +14906,7 @@
       <c r="G35" s="31"/>
       <c r="H35" s="31"/>
       <c r="I35" s="32"/>
+      <c r="J35"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="30"/>
@@ -13125,6 +14918,7 @@
       <c r="G36" s="31"/>
       <c r="H36" s="31"/>
       <c r="I36" s="32"/>
+      <c r="J36"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="30"/>
@@ -13136,6 +14930,7 @@
       <c r="G37" s="31"/>
       <c r="H37" s="31"/>
       <c r="I37" s="32"/>
+      <c r="J37"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="30"/>
@@ -13147,6 +14942,7 @@
       <c r="G38" s="31"/>
       <c r="H38" s="31"/>
       <c r="I38" s="32"/>
+      <c r="J38"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="30"/>
@@ -13158,6 +14954,7 @@
       <c r="G39" s="31"/>
       <c r="H39" s="31"/>
       <c r="I39" s="32"/>
+      <c r="J39"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="33"/>
@@ -13169,6 +14966,7 @@
       <c r="G40" s="34"/>
       <c r="H40" s="34"/>
       <c r="I40" s="35"/>
+      <c r="J40"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -13256,23 +15054,34 @@
   <sheetData>
     <row r="1" spans="1:7" customHeight="1" ht="84" s="245" customFormat="1">
       <c r="A1" s="242"/>
+      <c r="B1" s="245"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
       <c r="E1" s="241" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">PROFORM INVOICE</t>
-          </r>
-        </is>
-      </c>
+            <t xml:space="preserve">PROFORMA INVOICE</t>
+          </r>
+        </is>
+      </c>
+      <c r="F1" s="245"/>
+      <c r="G1" s="245"/>
     </row>
     <row r="2" spans="1:7" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A2" s="243" t="s">
         <v>351</v>
       </c>
+      <c r="B2" s="245"/>
+      <c r="C2" s="245"/>
       <c r="D2" s="243"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="245"/>
     </row>
     <row r="3" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
+      <c r="A3" s="245"/>
+      <c r="B3" s="245"/>
+      <c r="C3" s="245"/>
       <c r="D3" s="243"/>
       <c r="E3" s="44" t="inlineStr">
         <is>
@@ -13308,6 +15117,8 @@
     <row r="5" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A5" s="238"/>
       <c r="B5" s="238"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
       <c r="E5" s="44" t="inlineStr">
         <is>
           <r>
@@ -13324,6 +15135,8 @@
     <row r="6" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A6" s="238"/>
       <c r="B6" s="238"/>
+      <c r="C6" s="245"/>
+      <c r="D6" s="245"/>
       <c r="E6" s="44" t="inlineStr">
         <is>
           <r>
@@ -13336,10 +15149,13 @@
     </row>
     <row r="7" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A7" s="238"/>
+      <c r="B7" s="245"/>
+      <c r="C7" s="245"/>
+      <c r="D7" s="245"/>
       <c r="E7" s="44" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Adress</t>
+            <t xml:space="preserve">Address</t>
           </r>
         </is>
       </c>
@@ -13348,6 +15164,9 @@
     </row>
     <row r="8" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A8" s="238"/>
+      <c r="B8" s="245"/>
+      <c r="C8" s="245"/>
+      <c r="D8" s="245"/>
       <c r="E8" s="44" t="inlineStr">
         <is>
           <r>
@@ -13361,6 +15180,8 @@
     <row r="9" spans="1:7" customHeight="1" ht="24.75" s="245" customFormat="1">
       <c r="A9" s="238"/>
       <c r="B9" s="238"/>
+      <c r="C9" s="245"/>
+      <c r="D9" s="245"/>
       <c r="E9" s="44" t="inlineStr">
         <is>
           <r>
@@ -13373,6 +15194,9 @@
     </row>
     <row r="10" spans="1:7" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A10" s="238"/>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
+      <c r="D10" s="245"/>
       <c r="E10" s="44"/>
       <c r="F10" s="46"/>
       <c r="G10" s="45"/>
@@ -13380,6 +15204,8 @@
     <row r="11" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A11" s="237"/>
       <c r="B11" s="237"/>
+      <c r="C11" s="245"/>
+      <c r="D11" s="245"/>
       <c r="E11" s="44" t="inlineStr">
         <is>
           <r>
@@ -13395,6 +15221,9 @@
     </row>
     <row r="12" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A12" s="237"/>
+      <c r="B12" s="245"/>
+      <c r="C12" s="245"/>
+      <c r="D12" s="245"/>
       <c r="E12" s="44" t="inlineStr">
         <is>
           <r>
@@ -13410,6 +15239,7 @@
     </row>
     <row r="13" spans="1:7" customHeight="1" ht="23.25" s="245" customFormat="1">
       <c r="A13" s="244"/>
+      <c r="B13" s="245"/>
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="44" t="inlineStr">
@@ -13427,9 +15257,12 @@
     </row>
     <row r="14" spans="1:7" customHeight="1" ht="17.25" s="245" customFormat="1">
       <c r="A14" s="244"/>
+      <c r="B14" s="245"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
       <c r="E14" s="380"/>
+      <c r="F14" s="245"/>
+      <c r="G14" s="245"/>
     </row>
     <row r="15" spans="1:7" customHeight="1" ht="26.25" s="245" customFormat="1">
       <c r="A15" s="381" t="inlineStr">
@@ -13479,7 +15312,7 @@
       <c r="A17" s="239" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Swift Cose</t>
+            <t xml:space="preserve">Swift Code</t>
           </r>
         </is>
       </c>
@@ -13495,7 +15328,7 @@
       <c r="E17" s="239" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Bank Adress</t>
+            <t xml:space="preserve">Bank Address</t>
           </r>
         </is>
       </c>
@@ -13524,7 +15357,7 @@
       <c r="E18" s="239" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Beneficiary Adress</t>
+            <t xml:space="preserve">Beneficiary Address</t>
           </r>
         </is>
       </c>
@@ -13538,9 +15371,13 @@
       <c r="G18" s="383"/>
     </row>
     <row r="19" spans="1:7">
+      <c r="A19" s="245"/>
+      <c r="B19" s="245"/>
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
       <c r="E19" s="380"/>
+      <c r="F19" s="245"/>
+      <c r="G19" s="245"/>
     </row>
     <row r="20" spans="1:7" customHeight="1" ht="25.5" s="245" customFormat="1">
       <c r="A20" s="42" t="inlineStr">

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="3" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
+    <workbookView activeTab="4" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="구매리스트" sheetId="1" r:id="rId4"/>
@@ -3495,7 +3495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="401">
+  <cellXfs count="403">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4698,6 +4698,12 @@
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="13" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="11" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="11" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12855,7 +12861,7 @@
     <col min="4" max="4" width="23.625" customWidth="true" style="244"/>
     <col min="5" max="5" width="7.75" customWidth="true" style="244"/>
     <col min="6" max="6" width="2.125" customWidth="true" style="244"/>
-    <col min="7" max="7" width="12.25" customWidth="true" style="244"/>
+    <col min="7" max="7" width="19.5" customWidth="true" style="244"/>
     <col min="8" max="8" width="13.75" customWidth="true" style="244"/>
     <col min="9" max="9" width="13.25" customWidth="true" style="244"/>
   </cols>
@@ -12897,7 +12903,7 @@
         </is>
       </c>
       <c r="F2" s="249"/>
-      <c r="G2" s="128" t="str">
+      <c r="G2" s="401" t="str">
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
@@ -12934,7 +12940,7 @@
         </is>
       </c>
       <c r="F3" s="244"/>
-      <c r="G3" s="129" t="str">
+      <c r="G3" s="402" t="str">
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -5816,10 +5816,7 @@
           </r>
         </is>
       </c>
-      <c r="I6" s="115" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G6,"승용 소형","Small Passenger"),"승용 중형","Medium Passenger"),"승용 대형","HEAVY Passenger"),"중형 승합","Medium Ven"),"대형 승합","Large Ven"),"중형 화물","Medium Cargo")</f>
-        <v>0</v>
-      </c>
+      <c r="I6" s="115"/>
       <c r="J6" s="242"/>
       <c r="K6" s="242"/>
       <c r="L6" s="242"/>

--- a/resources/templates/heyman/clearance_set.xlsx
+++ b/resources/templates/heyman/clearance_set.xlsx
@@ -6154,10 +6154,7 @@
         </is>
       </c>
       <c r="H13" s="243"/>
-      <c r="I13" s="113" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G13,"휘발유","GASOLINE"),"경유","DIESEL"),"LPG","LPG"),"하이브리드","HYBRID")</f>
-        <v>0</v>
-      </c>
+      <c r="I13" s="113"/>
       <c r="J13" s="242"/>
       <c r="K13" s="242"/>
       <c r="L13" s="242"/>
